--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -10,20 +10,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Use Cases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Stack" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Edits" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="To-Do" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activity Diagrams" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Stack" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Edits" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="To-Do" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$K$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Use Cases'!$A$1:$F$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contradictions'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Tech Stack'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Paper Edits'!$A$1:$B$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'To-Do'!$A$1:$I$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Figures'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Activity Diagrams'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Contradictions'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tech Stack'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Paper Edits'!$A$1:$B$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'To-Do'!$A$1:$I$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Figures'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -555,7 +557,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reviewed: full manuscript text incl. 4 interview transcripts; Figures 2.2-2.6. Pending: Figures 2.7-2.15 images (activity diagram text already reviewed).</t>
+          <t>Reviewed: full manuscript text incl. 4 interview transcripts; Figures 2.2-2.11. Pending: Figures 2.12-2.15 images (their text is already reviewed).</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3106,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>In-platform bell works; no email notifications are sent (EmailJS is only used for OTP).</t>
+          <t>In-platform bell works; no email notifications are sent (EmailJS is only used for OTP). No notification at all when an order is placed (Fig 2.10 'Send Order Submission Notification').</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -3129,7 +3131,7 @@
       </c>
       <c r="K40" s="11" t="inlineStr">
         <is>
-          <t>p.51</t>
+          <t>p.51; Fig 2.10</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6355,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Approve-and-credit matches Activity 2.11 and Interview 4; fix the bug and reword REQ098.</t>
+          <t>The paper says hold everywhere (REQ095, REQ098, Fig 2.6 text, Fig 2.11 text and diagram); approve-and-credit is what the client agreed to in the Interview 4 walkthrough. Fix the bug and reword the paper (C2).</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -9431,7 +9433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11182,7 +11184,7 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>(no bubble) Wholesale Exchange / Free-of-Cost</t>
+          <t>(no bubble) Free-of-Cost Distribution</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -11197,17 +11199,385 @@
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>REQ090-091</t>
+          <t>REQ091</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>Paper: has Activity 2.15 but no use case in Fig 2.2 or 2.6.</t>
+          <t>Paper: no use case in any figure (wholesale exchange is in Fig 2.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Manage Live Chat</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>Technical Staff (+BM)</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>REQ108-110</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>Connected here, but not in Fig 2.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Manage Product Catalog</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Technical Staff (+BM)</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>REQ068-070</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>Dosage notes missing; category rename uses native prompt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>Manage Supplier Accounts</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>Technical Staff (+BM)</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>REQ069</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Manage Wholesale Accounts</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>Technical Staff (+BM)</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>REQ085-086</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>No document expiry tracking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>&lt;&lt;extend&gt;&gt; Process Wholesale Exchange Request</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>Technical Staff (+BM)</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>REQ090</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>&lt;&lt;include&gt;&gt; Adjust Inventory for Exchange</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>Technical Staff (+BM)</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>REQ090</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>Manage Online Customer Accounts</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>Technical Staff (+BM)</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>REQ116-117</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>No order history list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>View Audit Log</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>Technical Staff (+BM)</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>REQ123-124</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>Update Product Price</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>Branch Manager</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>REQ071-072</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>Non-BM staff can set prices on new/imported products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>&lt;&lt;include&gt;&gt; Record Price Change in Audit Log</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Branch Manager</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>REQ073</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>No reason captured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Create Staff Account &lt;&lt;include&gt;&gt; Assign Staff Role</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>Branch Manager</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>REQ118-119</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>Shared validators not applied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Manage Staff Accounts</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Branch Manager</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>REQ118</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>Editing an Administrator silently changes it to Branch Manager.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F59"/>
+  <autoFilter ref="A1:F71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11218,7 +11588,977 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Step / flow</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Paper shows</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>System does</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Validate credentials -&gt; role redirect</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Valid login: customer to Home, staff to Dashboard</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Same (js/auth.js:94)</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Failed attempts</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Increment count; at 5, lock 2 minutes; back to Login page</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Same (js/auth.js:57)</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Device recognition + OTP</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Check if device is recognized; if not, send and validate OTP</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>REQ005/REQ044.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Wrong OTP</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Diagram: 'No' from Validate OTP joins the failed-attempt counter (counts toward lockout). Text p.77: user is prompted to request a new OTP.</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Diagram and text disagree (C13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Steps the system has that the diagram lacks</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Not shown</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>reCAPTCHA check, rejecting attempts while locked, blocking deactivated accounts, sending unverified customers to email verification</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Add to diagram; all are in requirements (REQ003, REQ004, REQ117, REQ002).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Validate fields -&gt; duplicate email -&gt; Terms -&gt; send code</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Fields validated, then duplicate check, then Terms shown and accepted, then code sent</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Terms modal opens when the checkbox is ticked (before submit); duplicate email is caught by Firebase at account creation; code sent after</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Same outcome, different order (C14).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Wrong / expired code</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Loop back to Enter Code (diagram); text p.79 adds 'request a new code'</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Retry or Resend link (js/verify-email.js)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Add Resend to diagram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>After verification</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Go to Login</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Goes straight to the shop, already signed in</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>C10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Account activation</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Account activated only after the code is verified</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Login account is created first with emailVerified:false; unverified customers are redirected to verification on login</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Functionally equivalent; note the REQ002 bypass issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Catalog -&gt; cart -&gt; checkout</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Browse, add to cart, updated cart summary, checkout</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Same, plus choosing which cart items to check out</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Cart selection is an addition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Default address</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>If saved, pre-fill; else enter</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Same (js/checkout.js)</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>RX check position</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Diagram: RX is checked after the address and after uploading payment proof, so RX customers are still asked for a delivery address. Text p.81: RX check comes before payment and delivery is not allowed.</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>RX detected when checkout opens; address section hidden; pick-up only</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Diagram contradicts REQ023 and its own text (C15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Prescription photo upload</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Not shown in the diagram (text p.81 and REQ021 require it)</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Required on the payment page for RX orders</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>C15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Order status after submission</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Recorded as Pending Payment Verification (RX included)</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Same ('placed' = Order Pending Verification)</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Diagram supports the system; REQ024 says 'Pending Prescription Verification' (C3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Order submission notification</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>System sends a notification to the customer</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Only an on-screen confirmation with the order number; no notification</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Small: add an order-placed entry to the customer bell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Steps the system has that the diagram lacks</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Not shown</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Login required to check out, delivery schedule, store credit discount, live stock re-check before submitting</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>Optional: add to diagram (delivery schedule is in Modules p.39).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Valid payment</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Confirm -&gt; notify customer -&gt; FEFO stock deduction -&gt; receipt</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Stock is deducted first; if stock ran out the order goes on an Out of Stock hold instead</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Diagram has no out-of-stock path (C19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>RX pre-order after confirmation</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Diagram: admin copies delivery details, books courier and provides a tracking link before the system checks for RX</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>RX orders skip courier booking and go straight to Ready for Pick-up</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>RX orders can't be delivered (REQ080) (C17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Prescription review</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Not shown (payment screenshot only)</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Not built (payment approval only)</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>REQ077-079 require it (C3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Admin provides tracking link; system marks Dispatched</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Admin pastes the link and marks Dispatched in one step; customer can't see the link</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>REQ034.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Invalid payment</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>On Hold -&gt; record reason -&gt; notify customer -&gt; re-upload -&gt; back to admin review</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Same (js/admin-online-orders.js:561; js/order-details.js)</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Resolution without re-upload</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Diagram: if the customer 'performed resolution action', the system confirms the order with no admin review</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Every resolution returns to staff (resubmission or Release Hold)</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Diagram contradicts REQ101 (C18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Overpayment</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Treated as an invalid payment (hold)</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Approved immediately; excess added to store credit</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>C2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Expired hold</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Admin marks the order Unresolved</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Closed automatically after 7 days, with verified payment kept as credit</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>REQ100 says automatic; move step to System lane and add credit retention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Steps the system has that the diagram lacks</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Not shown</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Fully credit-covered orders (no screenshot), Release Hold by staff</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Optional to add.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G26"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11295,7 +12635,7 @@
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>REQ095 and REQ098 ('On Hold - Overpayment') vs Activity 2.11 and Payment Verification Module (excess recorded as unapplied value) vs Interview 4 (excess goes to customer's account for next order)</t>
+          <t>REQ095, REQ098, Fig 2.6 text and Fig 2.11 text + diagram all treat overpayment as a hold (excess recorded as unapplied value) vs Interview 4 walkthrough (enter the excess; it goes to the customer's account for the next order; client agreed)</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
@@ -11305,7 +12645,7 @@
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Change paper: rewrite REQ098 to approve-and-credit; drop overpayment from the hold types.</t>
+          <t>Change paper: rewrite REQ098 and Fig 2.6/2.11 to approve-and-credit; drop overpayment from the hold types.</t>
         </is>
       </c>
     </row>
@@ -11322,17 +12662,17 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>REQ024, REQ077-079, Modules p.43, Conceptual Framework (dedicated RX queue, approve/reject with reason) vs Activity 2.11 (RX pre-orders 'confirmed in the same manner', verification in person)</t>
+          <t>REQ024, REQ077-079, Modules p.43, Conceptual Framework, Fig 2.10 text (dedicated RX queue, 'Pending Prescription Verification', approve/reject with reason) vs Fig 2.10 diagram (RX recorded as Pending Payment Verification) and Fig 2.11 text + diagram (RX confirmed like any order, verification in person)</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Same as Activity 2.11 (payment approval only).</t>
+          <t>Same as Fig 2.10/2.11 diagrams (payment approval only).</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Change system to match REQ077-079; fix Activity 2.11 text.</t>
+          <t>Change system to match REQ077-079; then fix Fig 2.10 and 2.11.</t>
         </is>
       </c>
     </row>
@@ -11511,7 +12851,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Activity 2.9 (after verification, redirect to login page)</t>
+          <t>Fig 2.9 text + diagram (after verification, go to Login)</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -11538,7 +12878,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 has no Create Purchase Order, Batch Upload, Verify Prescription, Payment Verification, Delivery, Customer Accounts, Suppliers, Notifications, Wholesale Exchange; 'Manage Live Chat' has no actor</t>
+          <t>Fig 2.2 has no Create Purchase Order, Batch Upload, Verify Prescription, Payment Verification, Delivery, Customer Accounts, Suppliers, Notifications, Wholesale Exchange (all appear in Figs 2.5-2.7); 'Manage Live Chat' has no actor in 2.2 but is linked to Technical Staff in 2.7</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -11548,7 +12888,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Change paper: add the missing bubbles or say Fig 2.2 is a summary.</t>
+          <t>Change paper: add the missing bubbles to 2.2 or say it's a summary; connect Manage Live Chat.</t>
         </is>
       </c>
     </row>
@@ -11579,13 +12919,202 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Wrong OTP at login</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.8 diagram (wrong OTP feeds the failed-attempt counter) vs Fig 2.8 text p.77 (prompted to request a new OTP)</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>No OTP yet.</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Pick one when building REQ005/044; update the other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Registration order</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.9 (validate, duplicate check, then Terms) vs system (Terms when ticking the checkbox, duplicate check at account creation)</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>See left.</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Change paper: Terms before submit; duplicate check after.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>RX in the purchasing flow</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.10 diagram (RX checked after address and payment upload; no prescription upload) vs Fig 2.10 text p.81 and REQ021/023 (RX decided first, pick-up only, prescription photo required)</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Matches the text, not the diagram.</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Change paper: redraw the RX branch in Fig 2.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Order submission notification</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.10 (system notifies customer on submission) vs REQ039 (order confirmations)</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>No notification on submission.</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Change system (small).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>RX pre-orders and couriers</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.11 diagram (courier booked and tracking link sent before the RX check) vs REQ023/080 (never delivered)</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>RX skips courier booking.</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Change paper: branch RX before the courier steps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Resolving a hold</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.11 diagram (customer resolution without re-upload confirms the order automatically) vs REQ101 (admin approval confirms)</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Every resolution goes back to staff.</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Change paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>C19</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Stock check at confirmation</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.11 (notify confirmed, then FEFO deduction; no shortage path) vs REQ050</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Deducts first; shortage puts the order on an Out of Stock hold.</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Change paper: add the out-of-stock hold branch.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11919,13 +13448,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12091,76 +13620,112 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 text p.79</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>After verification the customer goes to the shop, already signed in (C10).</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 text p.83</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Prescription pre-orders need prescription approval/rejection before confirmation (C3) - after it is built.</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
+          <t>Fig 2.11 diagram + text p.82-83</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Modules FEFO p.41</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Add the 2-month Bad Order step (C7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background p.35-37; Budget p.99</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t>Decision-dependent</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B18"/>
+  <autoFilter ref="A1:B21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14013,54 +15578,95 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>REQ039, Fig 2.10, C16</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr"/>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
           <t>Apply all paper edits (see Paper Edits sheet)</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>Paper Edits sheet</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>Paper</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Change paper</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>Do after system decisions are final.</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="I45" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I44"/>
-  <conditionalFormatting sqref="I2:I44">
+  <autoFilter ref="A1:I45"/>
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14068,7 +15674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14228,10 +15834,14 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr"/>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -14246,12 +15856,12 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Text reviewed (p.76-77)</t>
+          <t>Reviewed</t>
         </is>
       </c>
     </row>
@@ -14268,12 +15878,12 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Text reviewed (p.78-79)</t>
+          <t>Reviewed</t>
         </is>
       </c>
     </row>
@@ -14290,12 +15900,12 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Text reviewed (p.80-81)</t>
+          <t>Reviewed</t>
         </is>
       </c>
     </row>
@@ -14312,12 +15922,12 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Text reviewed (p.82-83)</t>
+          <t>Reviewed</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -8,24 +8,26 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Use Cases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activity Diagrams" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Stack" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Edits" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="To-Do" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="To-Do" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Use Cases" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activity Diagrams" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Stack" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Edits" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manuscript Pass" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$K$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Activity Diagrams'!$A$1:$G$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Contradictions'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tech Stack'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Paper Edits'!$A$1:$B$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'To-Do'!$A$1:$I$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Figures'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$J$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Contradictions'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Tech Stack'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Paper Edits'!$A$1:$B$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Manuscript Pass'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Figures'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,7 +559,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reviewed: full manuscript text incl. 4 interview transcripts; Figures 2.2-2.11. Pending: Figures 2.12-2.15 images (their text is already reviewed).</t>
+          <t>Reviewed: full manuscript text incl. 4 interview transcripts; Figures 2.2-2.15 (diagrams + text), second full pass of every section incl. tech stack, Gantt, budget, references. Not compared: wireframes 2.16-2.21. The To-Do sheet is the master list.</t>
         </is>
       </c>
     </row>
@@ -751,13 +753,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>None</t>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Open to-do items</t>
         </is>
       </c>
       <c r="B20">
-        <f>COUNTIF(Requirements!G:G,"None")</f>
+        <f>COUNTIF('To-Do'!J:J,"Open")</f>
         <v/>
       </c>
     </row>
@@ -893,7 +895,4988 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Overall Use Case Diagram</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Use Case: Platform Access and Account Management</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Use Case: Customer Ordering and Purchase</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Use Case: Inventory Management</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Use Case: Order Processing and Sales Operations</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Use Case: Administrative Controls</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Activity: Login Process</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Activity: Account Registration</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Activity: Customer Purchasing</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Activity: Payment Verification and Order Processing</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Activity: Inventory Management</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Activity: Wholesale Order Processing</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Activity: Walk-in Order Processing (POS)</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Activity: Wholesale Exchange Processing</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>2.16-2.21</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Wireframes</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Not requested</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Optional - send if you want UI compared to wireframes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J105"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Where / refs</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>Defense risk</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Client items (-)</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Get from the client: the QR Ph image, the sample report format, and the sales invoice format (promised in Interviews 2-4); confirm decisions with them.</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr"/>
+      <c r="I2" s="11" t="inlineStr"/>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>REQ035-038, REQ108-110, REQNF008, REQNF012</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Live chat (guest/customer widget, staff console, resolve threads; AI replies)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr"/>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Comparative Analysis (p.18)</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>The proposed system gets a tick for 'AI-powered live chat'; keep only if chat is built.</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr"/>
+      <c r="I4" s="11" t="inlineStr"/>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>REQ066, Title, Obj. 2</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Near-expiry stock removed from sale by date on every sale/catalog load, not only when Inventory is opened</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Title feature.</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>REQ058, REQ111-115, REQNF020, Obj. 3</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Build the Reports module: daily sales (per customer, items with batch + expiry), monthly inventory + purchases (batch, expiry, date received, receipt no., supplier), pull-out, discrepancy; date range; PDF + Excel. Wire the 5 blank Export buttons to it.</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Client's one remaining ask (Interview 4). Get the sample report format the client said they'd send.</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>REQ024-025, REQ077-081, C3</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Prescription verification: approve/reject with mandatory reason, 'Ready for pick-up' notification, record who verified, RX filter in the queue</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr"/>
+      <c r="I7" s="11" t="inlineStr"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>REQ034, REQ104-105</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Show the Lalamove tracking link to the customer on their order page</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr"/>
+      <c r="I8" s="11" t="inlineStr"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>REQ028</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Add the client's real QR PH image (assets/payment-qr.png)</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Need the image from the client.</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>REQ010-011</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Wire product search (header box) + add price-range and stock-status filters</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr"/>
+      <c r="I10" s="11" t="inlineStr"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Client's #1 pain point (Interview 4).</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>REQ098, REQ102, C2</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Objectives / evaluation (p.5-6, 21-24)</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr"/>
+      <c r="I14" s="11" t="inlineStr"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>REQ121</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Orders access was added on purpose on 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>REQNF005</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Live updates without refresh on verification queue + customer order page</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr"/>
+      <c r="I16" s="11" t="inlineStr"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>REQNF010, REQNF013</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr"/>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Limitations (p.7)</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr"/>
+      <c r="I18" s="11" t="inlineStr"/>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Limitations (p.7)</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background (p.35, 37)</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>REQ002</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr"/>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Unrecognized-device OTP for customers and staff</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>REQ086, REQ089, REQ091, REQ092</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale: purchase history per account, wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr"/>
+      <c r="I24" s="11" t="inlineStr"/>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>REQ090, REQ114, Fig 2.15</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>REQ067, C7</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr"/>
+      <c r="I26" s="11" t="inlineStr"/>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr"/>
+      <c r="I27" s="11" t="inlineStr"/>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>REQ084</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>POS: RX Verified checkbox + optional notes</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr"/>
+      <c r="I28" s="11" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>REQ061, C5</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr"/>
+      <c r="I29" s="11" t="inlineStr"/>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>REQNF025, REQNF029</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr"/>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>REQ039, REQ042</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>EmailJS free tier: 200/month.</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr"/>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>REQ122</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr"/>
+      <c r="I32" s="11" t="inlineStr"/>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>REQ014</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Save cart to the customer's account</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr"/>
+      <c r="I33" s="11" t="inlineStr"/>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>REQNF003, REQNF007</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Phone/tablet and cross-browser test pass</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>Not verified</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr"/>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Project Context (p.1)</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr"/>
+      <c r="I35" s="11" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Theoretical Framework (p.24)</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr"/>
+      <c r="I36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Conceptual Framework (Output) (p.27)</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr"/>
+      <c r="I37" s="11" t="inlineStr"/>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Modules: Staff roles (p.45-46)</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr"/>
+      <c r="I38" s="11" t="inlineStr"/>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>REQ007 / Technical Background p.35-36</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>REQ008 p.47; Modules p.38</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Home shows featured products and categories (drop 'announcements, promotions') unless you want a banner built.</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr"/>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>REQ031 p.50</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr"/>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>REQ073 p.55</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr"/>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr"/>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr"/>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr"/>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>REQ121 p.61</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr"/>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.2 text p.67</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr"/>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.2 diagram</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr"/>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.5 text p.72</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr"/>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.2 / 2.7 diagrams</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr"/>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.8 diagram + text p.76-77</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr"/>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.9 diagram + text p.78-79</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr"/>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.10 diagram</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr"/>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>Fig 2.11 diagram + text p.82-83</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr"/>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>Title page / cover (i)</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr"/>
+      <c r="I56" s="11" t="inlineStr"/>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>Whole paper (-)</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr"/>
+      <c r="I57" s="11" t="inlineStr"/>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>Comparative Analysis (p.18)</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr"/>
+      <c r="I58" s="11" t="inlineStr"/>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>Conceptual Framework (Input) (p.25)</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="inlineStr"/>
+      <c r="I59" s="11" t="inlineStr"/>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>Methodology: sprint plan (p.30-35)</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr"/>
+      <c r="I60" s="11" t="inlineStr"/>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities (p.96-98)</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr"/>
+      <c r="I61" s="11" t="inlineStr"/>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities (p.96-98)</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr"/>
+      <c r="I62" s="11" t="inlineStr"/>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>REQ088</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Hide costing/wholesale prices from public reads</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr"/>
+      <c r="I63" s="11" t="inlineStr"/>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background (p.35)</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr"/>
+      <c r="I64" s="11" t="inlineStr"/>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>REQ013, REQ068</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Dosage/usage notes field on products</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr"/>
+      <c r="I65" s="11" t="inlineStr"/>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>REQ049</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>Supplier column in the inventory batch table</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr"/>
+      <c r="I66" s="11" t="inlineStr"/>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>REQ103, REQ107</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="inlineStr"/>
+      <c r="I67" s="11" t="inlineStr"/>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>REQ116</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>Customer Accounts: list of the customer's orders</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr"/>
+      <c r="I68" s="11" t="inlineStr"/>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>REQ118</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr"/>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>REQ070</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>Category rename: replace native prompt() with app dialog</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr"/>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>REQ033, REQ093</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr"/>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>REQ099</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>'Payment not received' as its own hold type</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr"/>
+      <c r="I72" s="11" t="inlineStr"/>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>REQ026</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Checkout pick-up notice mentions bringing the original prescription</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr"/>
+      <c r="I73" s="11" t="inlineStr"/>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>REQ009</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>Show quantity in stock on catalog cards</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr"/>
+      <c r="I74" s="11" t="inlineStr"/>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>REQ040</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>Profile picture in Account Settings</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr"/>
+      <c r="I75" s="11" t="inlineStr"/>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>REQNF028</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr"/>
+      <c r="I76" s="11" t="inlineStr"/>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>REQ047</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr"/>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>REQNF017</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>README with setup steps; fix the error message that points to it</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr"/>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>REQ001</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Normalize phone number at registration</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr"/>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>REQ039, Fig 2.10, C16</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H80" s="11" t="inlineStr"/>
+      <c r="I80" s="11" t="inlineStr"/>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>System roles (-)</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr"/>
+      <c r="I81" s="11" t="inlineStr"/>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>Whole paper + system (-)</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H82" s="11" t="inlineStr"/>
+      <c r="I82" s="11" t="inlineStr"/>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>Modules FEFO p.41</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>Add the 2-month Bad Order step (C7).</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr"/>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background p.35-37; Budget p.99</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr"/>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Decision-dependent</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr"/>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>Whole paper (-)</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H86" s="11" t="inlineStr"/>
+      <c r="I86" s="11" t="inlineStr"/>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Scope (p.6)</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr"/>
+      <c r="I87" s="11" t="inlineStr"/>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>Theoretical Framework (p.22-23)</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G88" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H88" s="11" t="inlineStr"/>
+      <c r="I88" s="11" t="inlineStr"/>
+      <c r="J88" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>Methodology: sprint plan (p.32)</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr"/>
+      <c r="I89" s="11" t="inlineStr"/>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background (p.35)</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H90" s="11" t="inlineStr"/>
+      <c r="I90" s="11" t="inlineStr"/>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background (p.35-36)</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr"/>
+      <c r="I91" s="11" t="inlineStr"/>
+      <c r="J91" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background (p.35-36)</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G92" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H92" s="11" t="inlineStr"/>
+      <c r="I92" s="11" t="inlineStr"/>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background (p.35, 37)</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="inlineStr"/>
+      <c r="I93" s="11" t="inlineStr"/>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background: Software (p.36-38)</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G94" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H94" s="11" t="inlineStr"/>
+      <c r="I94" s="11" t="inlineStr"/>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="11" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background: Software (p.38)</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr"/>
+      <c r="I95" s="11" t="inlineStr"/>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>Modules: Price Management (p.42)</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H96" s="11" t="inlineStr"/>
+      <c r="I96" s="11" t="inlineStr"/>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr"/>
+      <c r="I97" s="11" t="inlineStr"/>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities (p.97-98)</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr"/>
+      <c r="I98" s="11" t="inlineStr"/>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr"/>
+      <c r="I99" s="11" t="inlineStr"/>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr"/>
+      <c r="I100" s="11" t="inlineStr"/>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>References (p.100)</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr"/>
+      <c r="I101" s="11" t="inlineStr"/>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>References (p.10 / refs)</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr"/>
+      <c r="I102" s="11" t="inlineStr"/>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>References (p.17 / refs)</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr"/>
+      <c r="I103" s="11" t="inlineStr"/>
+      <c r="J103" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>Appendices (p.124)</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr"/>
+      <c r="I104" s="11" t="inlineStr"/>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr"/>
+      <c r="I105" s="11" t="inlineStr"/>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J105"/>
+  <conditionalFormatting sqref="J2:J105">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Open,In progress,Done,Dropped"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4561,40 +9544,44 @@
           <t>Flag batches within 6 months; remove from sellable; wholesale free-of-cost only</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>Matches</t>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>js/products-data.js:384</t>
+          <t>js/products-data.js:384; js/admin-inventory.js (only caller)</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>Flags wholesale_only. Free-of-cost distribution itself is not a recorded transaction type (see REQ091).</t>
+          <t>The flag only runs when someone opens the Inventory page. Until then, near-expiry batches stay sellable online and at the POS. Free-of-cost distribution is not a recorded transaction type (see REQ091).</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H67" s="11" t="inlineStr"/>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>This is the title feature ('Real-Time Expiry Monitoring') and Objective 2; exclude near-expiry batches from sellable stock by date everywhere, not only on that page.</t>
+        </is>
+      </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr">
         <is>
-          <t>p.54</t>
+          <t>p.54; Title; Obj. 2</t>
         </is>
       </c>
     </row>
@@ -6019,7 +11006,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>Walk-in and online receipts exist; no wholesale sales invoice.</t>
+          <t>Walk-in and online receipts exist; no wholesale sales invoice. Receipts show no batch numbers or expiry dates, which the Project Context (p.1) names as the old POS's main gap.</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -6044,7 +11031,7 @@
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>p.58</t>
+          <t>p.58; p.1</t>
         </is>
       </c>
     </row>
@@ -7685,7 +12672,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Logs price changes, write-offs, reconciliation, wholesale orders, account changes. Voids and exchanges don't exist yet. Before/after values are free text, reasons mostly missing, IP shown as '-'.</t>
+          <t>Logs price changes, write-offs, reconciliation, wholesale orders, account changes. Stock receiving is not logged (Fig 2.12 shows it). Voids and exchanges don't exist yet. Before/after values are free text, reasons mostly missing, IP shown as '-'.</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
@@ -9427,7 +14414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11582,13 +16569,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12546,13 +17533,745 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Write-off</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Select product + qty, reason -&gt; deduct -&gt; audit log -&gt; low-stock check/alert</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Same (js/admin-inventory.js:994)</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Stock receiving with a PO</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Link PO -&gt; enter details -&gt; match? add stock -&gt; audit log -&gt; low-stock check</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Same, except receiving is not written to the audit log</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>REQ122.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Stock receiving: PO mismatch</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Diagram box repeats 'Verify if received quantities match PO quantities' -&gt; partial stock added -&gt; end</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Partial stock added, PO marked Discrepancy, acknowledgment required to close</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Copy-paste error in the diagram; should be 'Generate Discrepancy Report / Mark PO as Discrepancy', plus the acknowledgment step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Stock receiving without a PO / batch upload</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Not shown (text p.85 describes both)</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Both exist (manual Receive Stock, Excel/CSV upload)</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>Deviates</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Add the no-PO branch and batch upload to the diagram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>6-month flag</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Flag for pull-out -&gt; expiration alert -&gt; admin chooses Write Off or Reserve for Free-of-Cost</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Flagged automatically as Wholesale Only (only when Inventory opens) + alert; no pull-out action choice</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>REQ066 timing fix; 'Reserve for free-of-cost' could just be the Wholesale Only flag + REQ091.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>2-month Bad Order</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Flag Bad Order -&gt; alert -&gt; 'Apply FEFO-Based Stock Deduction'</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>Build REQ067; diagram should say 'Write off / deduct the batch', not FEFO deduction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Expiry decision order</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Diagram tests '&lt;6 months' before '&lt;2 months' (every &lt;2-month batch also matches &lt;6)</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Test &lt;2 months first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Find or create buyer account</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Search -&gt; if new, enter details, upload documents, save</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Accounts searchable; create with LTO/permit upload (js/admin-wholesale-accounts.js:270)</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Check documents are current</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Text p.87: verify documents, upload renewals if expired. Diagram: 'View Buyer Documents' only</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Documents viewable; no expiry tracking</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>REQ086 expiry dates; add the validity check to the diagram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Purchase history</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>View purchase history</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>REQ089.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Near-expiry items</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Enable free-of-cost pricing option for near-expiry items</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Near-expiry stock is used first automatically; price can be typed as 0 but there is no free-of-cost option</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>REQ091.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Confirm -&gt; FEFO -&gt; sales invoice</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Confirm, FEFO deduction, generate sales invoice</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Confirm + FEFO deduction + audit entry; no sales invoice</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>REQ092.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Select products, confirm, FEFO</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Select products + qty -&gt; confirm -&gt; FEFO deduction</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Same, plus a review screen with Edit/Confirm, payment method and change</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Optionally add the review step and payment method to the diagram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>RX item</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Physically verify prescription -&gt; 'Mark RX as Verified' (drawn in the System lane)</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>No RX check in POS</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>Build REQ084. In the diagram, marking verified is a staff action, so it belongs in the staff lane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Print receipt</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>System prints receipt</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Receipt shown on screen only</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>Thermal print layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Void</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Not shown (text p.89 and Fig 2.6 include it)</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>Build REQ083; add the void branch to the diagram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Select buyer -&gt; order -&gt; returned item -&gt; replacement -&gt; reason</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>As listed</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>Change system</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>REQ090.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Inventory adjustment</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Diagram: FEFO deduction of the replacement only. Text p.91: returned item also added back to stock</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Add 'Return item to stock' to the diagram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Audit log + document</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Diagram: 'Generate Sales Invoice'. Text p.91: audit log entry + 'wholesale exchange document'</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>System + paper</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>Add the audit step and use one document name; REQ114 reports on these.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Lane placement</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>'Display Buyer Account and Order History' drawn in the Admin lane</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>Move to the System lane.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G26"/>
+  <autoFilter ref="A1:G46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13114,13 +18833,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13399,56 +19118,218 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>CAPTCHA</t>
+          <t>Database wording</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Google reCAPTCHA</t>
+          <t>'Real-time database' (p.35-36)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Cloud Firestore (one-time reads, not live listeners)</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr"/>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Name the product correctly; see REQNF005 on live updates.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
+          <t>Icons / fonts</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Bootstrap Icons, Google Fonts (Roboto)</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Add to Software list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Version control / CI</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Netlify continuous integration with the repo</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>GitHub repo (phobiaax/Amson, branch webapp); no CI/deploy</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Add Git/GitHub; CI depends on hosting decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Local serving</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Node.js http-server via start-server.bat</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Mention for the demo setup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Mockup tool</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Canva (p.38) vs 'Creation of Figma' (Gantt p.97)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Use one name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Dashboard analytics</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Chart.js for sales and inventory movement</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Sales charts only; inventory as count tiles</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Change paper</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Reword or add an inventory chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>CAPTCHA</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Google reCAPTCHA</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
           <t>Auth / database</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Firebase Auth + Firestore</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Same</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr"/>
+      <c r="E18" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13719,2330 +19600,1561 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>Refs</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>Recommendation</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>Effort</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>Defense risk</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Build the Reports module: daily sales (per customer, items with batch + expiry), monthly inventory + purchases (batch, expiry, date received, receipt no., supplier), pull-out, discrepancy; date range; PDF + Excel. Wire the 5 blank Export buttons to it.</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>REQ058, REQ111-115, REQNF020, Obj. 3</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>Client's one remaining ask (Interview 4). Get the sample report format the client said they'd send.</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>System + paper</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>Client's #1 pain point (Interview 4).</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Live chat (guest/customer widget, staff console, resolve threads; AI replies)</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>REQ035-038, REQ108-110, REQNF008, REQNF012</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Decision needed</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Prescription verification: approve/reject with mandatory reason, 'Ready for pick-up' notification, record who verified, RX filter in the queue</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>REQ024-025, REQ077-081, C3</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Show the Lalamove tracking link to the customer on their order page</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>REQ034, REQ104-105</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr"/>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Add the client's real QR PH image (assets/payment-qr.png)</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>REQ028</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>Need the image from the client.</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Wire product search (header box) + add price-range and stock-status filters</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>REQ010-011</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>REQ098, REQ102, C2</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>System + paper</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>System + paper</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr"/>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>REQ002</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Unrecognized-device OTP for customers and staff</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Wholesale: purchase history per account, wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>REQ086, REQ089, REQ091, REQ092</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr"/>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>REQ090, REQ114, Fig 2.15</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>REQ067, C7</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr"/>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>POS: RX Verified checkbox + optional notes</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>REQ084</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr"/>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>REQ061, C5</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>REQ121</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Deviates</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Decision needed</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>Orders access was added on purpose on 2026-10-01.</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>REQNF025, REQNF029</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Polish</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>REQ039, REQ042</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>EmailJS free tier: 200/month.</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Live updates without refresh on verification queue + customer order page</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>REQNF005</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Deviates</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Decision needed</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>REQ122</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr"/>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Save cart to the customer's account</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>REQ014</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Deviates</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr"/>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>REQNF010, REQNF013</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>Decision needed</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr"/>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Dosage/usage notes field on products</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>REQ013, REQ068</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr"/>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Supplier column in the inventory batch table</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>REQ049</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr"/>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>REQ103, REQ107</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr"/>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Customer Accounts: list of the customer's orders</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>REQ116</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr"/>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>REQ118</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Category rename: replace native prompt() with app dialog</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>REQ070</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Polish</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>REQ033, REQ093</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>'Payment not received' as its own hold type</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>REQ099</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H34" s="11" t="inlineStr"/>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>Checkout pick-up notice mentions bringing the original prescription</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>REQ026</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr"/>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>Show quantity in stock on catalog cards</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>REQ009</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="inlineStr"/>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Profile picture in Account Settings</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>REQ040</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="inlineStr"/>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>REQNF028</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="inlineStr"/>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>REQ047</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>README with setup steps; fix the error message that points to it</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>REQNF017</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>Normalize phone number at registration</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>REQ001</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>Hide costing/wholesale prices from public reads</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>REQ088</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E42" s="11" t="inlineStr">
-        <is>
-          <t>Decision needed</t>
-        </is>
-      </c>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H42" s="11" t="inlineStr"/>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>Phone/tablet and cross-browser test pass</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>REQNF003, REQNF007</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H43" s="11" t="inlineStr"/>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>REQ039, Fig 2.10, C16</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="inlineStr"/>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>Apply all paper edits (see Paper Edits sheet)</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>Paper Edits sheet</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>Change paper</t>
-        </is>
-      </c>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>Do after system decisions are final.</t>
-        </is>
-      </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I45"/>
-  <conditionalFormatting sqref="I2:I45">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"Done"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="I2:I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Open,In progress,Done,Dropped"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Defense risk</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Effort</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>Title page / cover</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Overall Use Case Diagram</t>
+          <t>i</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Reviewed</t>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Use Case: Platform Access and Account Management</t>
+          <t>i</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>'Integrated Real-Time Expiry Monitoring': near-expiry stock is only flagged when the Inventory page opens (REQ066). Fix the system so the title holds (To-Do: REQ066 item).</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Reviewed</t>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>Whole paper</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Use Case: Customer Ordering and Purchase</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Reviewed</t>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>Whole paper</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Use Case: Inventory Management</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Reviewed</t>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>Whole paper + system</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Use Case: Order Processing and Sales Operations</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Reviewed</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>Project Context</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Use Case: Administrative Controls</t>
+          <t>p.1</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Reviewed</t>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>Project Context / Purpose</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Activity: Login Process</t>
+          <t>p.2-4</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>AI chat 'addresses inquiries at any hour': depends on the live chat decision.</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Reviewed</t>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>Purpose and Description</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Activity: Account Registration</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>'Each completed transaction ... made available for printing and reporting': needs receipt printing and the Reports module.</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Reviewed</t>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>Objectives</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Activity: Customer Purchasing</t>
+          <t>p.5</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Obj. 1 promises AI chat support (live chat decision). Obj. 2 promises auto-removal of near-expiry stock (REQ066 fix). Obj. 3 promises exportable daily/monthly reports with batch + expiry (Reports module).</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Reviewed</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Objectives / evaluation</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Activity: Payment Verification and Order Processing</t>
+          <t>p.5-6, 21-24</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Reviewed</t>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Activity: Inventory Management</t>
+          <t>p.6</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Text reviewed (p.84-85)</t>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Activity: Wholesale Order Processing</t>
+          <t>p.7</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>'Automated daily sales and inventory reports are generated': depends on the Reports module.</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Text reviewed (p.86-87)</t>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Activity: Walk-in Order Processing (POS)</t>
+          <t>p.7</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>AI live chat bullet: live chat decision.</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Text reviewed (p.88-89)</t>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>Limitations</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Activity: Wholesale Exchange Processing</t>
+          <t>p.7</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Text reviewed (p.90-91)</t>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>2.16-2.21</t>
+          <t>Limitations</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Wireframes</t>
+          <t>p.7</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Not requested</t>
+          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Optional - send if you want UI compared to wireframes</t>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Comparative Analysis</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>p.18</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Comparative Analysis</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>p.18</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>The proposed system gets a tick for 'AI-powered live chat'; keep only if chat is built.</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Theoretical Framework</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>p.22-23</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Theoretical Framework</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>p.24</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Conceptual Framework (Input)</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>p.25</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Conceptual Framework (Output)</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>p.27</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Methodology: sprint plan</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>p.32</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Methodology: sprint plan</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>p.30-35</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Methodology: Deployment</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>p.30</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>'Deployed in a controlled environment using actual client data': not done yet. Decide hosting, then either do it or reword.</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>p.35</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>p.35-36</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>p.35-36</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>p.35, 37</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>p.35, 37</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background: Software</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>p.36-38</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background: Software</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>p.38</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>p.35</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Modules: Staff roles</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>p.45-46</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Modules: Price Management</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>p.42</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>System roles</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Wireframes (Figs 2.16-2.21)</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>p.92-95</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>p.96-98</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>p.96-98</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>p.97-98</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>p.99</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>p.99</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>p.100</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>p.10 / refs</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>p.17 / refs</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Appendices</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>p.124</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>p.iv-vi</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Client items</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Get from the client: the QR Ph image, the sample report format, and the sales invoice format (promised in Interviews 2-4); confirm decisions with them.</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D16"/>
+  <autoFilter ref="A1:F48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -15,19 +15,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Stack" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Edits" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manuscript Pass" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Asks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manuscript Pass" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$J$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$J$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Contradictions'!$A$1:$E$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Tech Stack'!$A$1:$E$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Paper Edits'!$A$1:$B$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Manuscript Pass'!$A$1:$F$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Figures'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Paper Edits'!$A$1:$B$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Interview Asks'!$A$1:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Manuscript Pass'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Figures'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -901,6 +903,1565 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Defense risk</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Title page / cover</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>'Integrated Real-Time Expiry Monitoring': near-expiry stock is only flagged when the Inventory page opens (REQ066). Fix the system so the title holds (To-Do: REQ066 item).</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Whole paper</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Whole paper</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Whole paper + system</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Project Context</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>p.1</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Project Context / Purpose</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>p.2-4</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>AI chat 'addresses inquiries at any hour': depends on the live chat decision.</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Purpose and Description</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>'Each completed transaction ... made available for printing and reporting': needs receipt printing and the Reports module.</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>p.5</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Obj. 1 promises AI chat support (live chat decision). Obj. 2 promises auto-removal of near-expiry stock (REQ066 fix). Obj. 3 promises exportable daily/monthly reports with batch + expiry (Reports module).</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Objectives / evaluation</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>p.5-6, 21-24</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>p.6</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>p.7</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>'Automated daily sales and inventory reports are generated': depends on the Reports module.</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>p.7</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>AI live chat bullet: live chat decision.</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Limitations</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>p.7</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Limitations</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>p.7</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Comparative Analysis</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>p.18</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Comparative Analysis</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>p.18</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>The proposed system gets a tick for 'AI-powered live chat'; keep only if chat is built.</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Theoretical Framework</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>p.22-23</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Theoretical Framework</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>p.24</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Conceptual Framework (Input)</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>p.25</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Conceptual Framework (Output)</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>p.27</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Methodology: sprint plan</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>p.32</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Methodology: sprint plan</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>p.30-35</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Methodology: Deployment</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>p.30</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>'Deployed in a controlled environment using actual client data': not done yet. Decide hosting, then either do it or reword.</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>p.35</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>p.35-36</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>p.35-36</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>p.35, 37</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>p.35, 37</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background: Software</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>p.36-38</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background: Software</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>p.38</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>p.35</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Modules: Staff roles</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>p.45-46</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Modules: Price Management</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>p.42</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>System roles</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Wireframes (Figs 2.16-2.21)</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>p.92-95</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>p.96-98</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>p.96-98</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>p.97-98</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>p.99</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>p.99</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>p.100</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>p.10 / refs</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>p.17 / refs</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Appendices</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>p.124</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>p.iv-vi</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Client items</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Get from the client: the QR Ph image, the sample report format, and the sales invoice format (promised in Interviews 2-4); confirm decisions with them.</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F48"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1274,7 +2835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1553,7 +3114,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Client's one remaining ask (Interview 4). Get the sample report format the client said they'd send.</t>
+          <t>Client's one remaining ask (Interview 4). Match the client's sample format; Excel output must paste cleanly into the main office's own sheets (Interviews 1, 2, 4); daily sales should total by payment method to match the daily cash remittance (Interview 2).</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr"/>
@@ -1741,27 +3302,27 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
+          <t>Purpose p.3; Interviews 1-2</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
+          <t>Stop calling system documents 'Official Receipt': relabel the online PDF (js/orders.js:263) and add 'This is not an official receipt' to all system receipts/invoices</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1771,7 +3332,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Client's #1 pain point (Interview 4).</t>
+          <t>Client is not BIR-connected by choice and issues BIR/VAT receipts manually on request.</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr"/>
@@ -1787,22 +3348,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>REQ098, REQ102, C2</t>
+          <t>Modules p.43; Fig 2.14; Interview 4</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
+          <t>Sequential receipt numbers for walk-in sales (receipt currently shows '-')</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -1817,7 +3378,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>Needed to void by original receipt number.</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr"/>
@@ -1833,17 +3394,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
+          <t>REQ006, REQNF025, Limitations p.7; Interviews 1-3</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
+          <t>Rewrite Terms &amp; Privacy to the client's actual policies: no refunds (exchange only), no cancellation after payment, 7-day hold then closure with credit kept, delivery fee and failed-delivery fees paid by the customer to the rider, RX pick-up only with original prescription, QR Ph only, Data Privacy Act 2012. Remove 'refunds case-by-case' and 'request deletion' (system only deactivates). Replace placeholder support@amson.ph with a real contact.</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -1861,7 +3422,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Panel may read the Terms during the demo.</t>
+        </is>
+      </c>
       <c r="I13" s="11" t="inlineStr"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
@@ -1875,27 +3440,27 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Objectives / evaluation (p.5-6, 21-24)</t>
+          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
+          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -1903,7 +3468,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
+        </is>
+      </c>
       <c r="I14" s="11" t="inlineStr"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
@@ -1917,22 +3486,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>REQ121</t>
+          <t>REQ098, REQ102, C2</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
+          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1942,12 +3511,12 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Orders access was added on purpose on 2026-10-01.</t>
+          <t>From the first review.</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr"/>
@@ -1963,32 +3532,32 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>REQNF005</t>
+          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Live updates without refresh on verification queue + customer order page</t>
+          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr"/>
@@ -2005,32 +3574,32 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>REQNF010, REQNF013</t>
+          <t>Objectives / evaluation (p.5-6, 21-24)</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
+          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr"/>
@@ -2052,17 +3621,17 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>REQ121</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
+          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -2075,7 +3644,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Orders access was added on purpose on 2026-10-01.</t>
+        </is>
+      </c>
       <c r="I18" s="11" t="inlineStr"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -2094,22 +3667,22 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>REQNF005</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
+          <t>Live updates without refresh on verification queue + customer order page</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2136,17 +3709,17 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>REQNF010, REQNF013</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -2173,22 +3746,22 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
+          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2201,11 +3774,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H21" s="11" t="inlineStr"/>
       <c r="I21" s="11" t="inlineStr"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
@@ -2219,22 +3788,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>REQ002</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
+          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -2247,11 +3816,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H22" s="11" t="inlineStr"/>
       <c r="I22" s="11" t="inlineStr"/>
       <c r="J22" s="11" t="inlineStr">
         <is>
@@ -2265,27 +3830,27 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Unrecognized-device OTP for customers and staff</t>
+          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2312,22 +3877,22 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>REQ086, REQ089, REQ091, REQ092</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Wholesale: purchase history per account, wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
+          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -2335,7 +3900,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr"/>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I24" s="11" t="inlineStr"/>
       <c r="J24" s="11" t="inlineStr">
         <is>
@@ -2354,22 +3923,22 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>REQ090, REQ114, Fig 2.15</t>
+          <t>REQ002</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
+          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -2377,7 +3946,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I25" s="11" t="inlineStr"/>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -2396,12 +3969,12 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>REQ067, C7</t>
+          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
+          <t>Unrecognized-device OTP for customers and staff</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -2438,22 +4011,22 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
+          <t>REQ086, REQ089, REQ091, REQ092</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
+          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2461,7 +4034,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
+        </is>
+      </c>
       <c r="I27" s="11" t="inlineStr"/>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -2480,12 +4057,12 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>REQ084</t>
+          <t>REQ090, REQ114, Fig 2.15</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>POS: RX Verified checkbox + optional notes</t>
+          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -2495,7 +4072,7 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -2522,22 +4099,22 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>REQ061, C5</t>
+          <t>REQ067, C7</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
+          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2564,17 +4141,17 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>REQNF025, REQNF029</t>
+          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
+          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -2587,11 +4164,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H30" s="11" t="inlineStr"/>
       <c r="I30" s="11" t="inlineStr"/>
       <c r="J30" s="11" t="inlineStr">
         <is>
@@ -2610,22 +4183,22 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>REQ039, REQ042</t>
+          <t>REQ084</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
+          <t>POS: RX Verified checkbox + optional notes</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2633,11 +4206,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>EmailJS free tier: 200/month.</t>
-        </is>
-      </c>
+      <c r="H31" s="11" t="inlineStr"/>
       <c r="I31" s="11" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
@@ -2656,12 +4225,12 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>REQ122</t>
+          <t>REQ061, C5</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
+          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -2671,7 +4240,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -2698,17 +4267,17 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>REQ014</t>
+          <t>REQNF025, REQNF029</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Save cart to the customer's account</t>
+          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -2721,7 +4290,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I33" s="11" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
@@ -2740,22 +4313,22 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>REQNF003, REQNF007</t>
+          <t>REQ039, REQ042</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Phone/tablet and cross-browser test pass</t>
+          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -2763,7 +4336,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>EmailJS free tier: 200/month.</t>
+        </is>
+      </c>
       <c r="I34" s="11" t="inlineStr"/>
       <c r="J34" s="11" t="inlineStr">
         <is>
@@ -2782,22 +4359,22 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Project Context (p.1)</t>
+          <t>REQ122</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -2824,17 +4401,17 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.24)</t>
+          <t>REQ014</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Save cart to the customer's account</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -2866,17 +4443,17 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output) (p.27)</t>
+          <t>REQNF003, REQNF007</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>Phone/tablet and cross-browser test pass</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Not verified</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -2903,22 +4480,22 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles (p.45-46)</t>
+          <t>Interviews 2, 4</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -2931,7 +4508,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Required column in the monthly purchases report.</t>
+        </is>
+      </c>
       <c r="I38" s="11" t="inlineStr"/>
       <c r="J38" s="11" t="inlineStr">
         <is>
@@ -2945,22 +4526,22 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>REQ007 / Technical Background p.35-36</t>
+          <t>Interview 4 walkthrough</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+          <t>Supplier history: everything received from each supplier</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -2975,7 +4556,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Shown to the client during the prototype walkthrough.</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr"/>
@@ -2991,27 +4572,27 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>REQ008 p.47; Modules p.38</t>
+          <t>Methodology p.30; Interview 4</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Home shows featured products and categories (drop 'announcements, promotions') unless you want a banner built.</t>
+          <t>User manual + hands-on training + handover to the branch</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -3021,7 +4602,7 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr"/>
@@ -3037,22 +4618,22 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>REQ031 p.50</t>
+          <t>Project Context (p.1)</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3065,11 +4646,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H41" s="11" t="inlineStr"/>
       <c r="I41" s="11" t="inlineStr"/>
       <c r="J41" s="11" t="inlineStr">
         <is>
@@ -3083,22 +4660,22 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>REQ073 p.55</t>
+          <t>Theoretical Framework (p.24)</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -3111,11 +4688,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H42" s="11" t="inlineStr"/>
       <c r="I42" s="11" t="inlineStr"/>
       <c r="J42" s="11" t="inlineStr">
         <is>
@@ -3129,22 +4702,22 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+          <t>Conceptual Framework (Output) (p.27)</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3157,11 +4730,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H43" s="11" t="inlineStr"/>
       <c r="I43" s="11" t="inlineStr"/>
       <c r="J43" s="11" t="inlineStr">
         <is>
@@ -3175,22 +4744,22 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087 p.57; Modules p.44</t>
+          <t>Modules: Staff roles (p.45-46)</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Default wholesale price per product, adjustable per order (C9).</t>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -3203,11 +4772,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H44" s="11" t="inlineStr"/>
       <c r="I44" s="11" t="inlineStr"/>
       <c r="J44" s="11" t="inlineStr">
         <is>
@@ -3226,12 +4791,12 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+          <t>REQ007 / Technical Background p.35-36</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
@@ -3272,12 +4837,12 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -3318,12 +4883,12 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>REQ121 p.61</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
@@ -3364,12 +4929,12 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 text p.67</t>
+          <t>REQ073 p.55</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -3410,12 +4975,12 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 diagram</t>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -3456,12 +5021,12 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.5 text p.72</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -3502,12 +5067,12 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 / 2.7 diagrams</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
@@ -3548,12 +5113,12 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.8 diagram + text p.76-77</t>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -3594,12 +5159,12 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 diagram + text p.78-79</t>
+          <t>REQ121 p.61</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
@@ -3640,12 +5205,12 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.10 diagram</t>
+          <t>Fig 2.2 text p.67</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -3686,12 +5251,12 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 diagram + text p.82-83</t>
+          <t>Fig 2.2 diagram</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
@@ -3732,17 +5297,17 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover (i)</t>
+          <t>Fig 2.5 text p.72</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -3755,7 +5320,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H56" s="11" t="inlineStr"/>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I56" s="11" t="inlineStr"/>
       <c r="J56" s="11" t="inlineStr">
         <is>
@@ -3774,22 +5343,22 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -3797,7 +5366,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H57" s="11" t="inlineStr"/>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I57" s="11" t="inlineStr"/>
       <c r="J57" s="11" t="inlineStr">
         <is>
@@ -3816,17 +5389,17 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
@@ -3839,7 +5412,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H58" s="11" t="inlineStr"/>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I58" s="11" t="inlineStr"/>
       <c r="J58" s="11" t="inlineStr">
         <is>
@@ -3858,17 +5435,17 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input) (p.25)</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -3881,7 +5458,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H59" s="11" t="inlineStr"/>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I59" s="11" t="inlineStr"/>
       <c r="J59" s="11" t="inlineStr">
         <is>
@@ -3900,17 +5481,17 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.30-35)</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
@@ -3923,7 +5504,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H60" s="11" t="inlineStr"/>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I60" s="11" t="inlineStr"/>
       <c r="J60" s="11" t="inlineStr">
         <is>
@@ -3942,17 +5527,17 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Fig 2.11 diagram + text p.82-83</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -3965,7 +5550,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H61" s="11" t="inlineStr"/>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I61" s="11" t="inlineStr"/>
       <c r="J61" s="11" t="inlineStr">
         <is>
@@ -3984,12 +5573,12 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Title page / cover (i)</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -4021,22 +5610,22 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>REQ088</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Hide costing/wholesale prices from public reads</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -4046,7 +5635,7 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr"/>
@@ -4063,17 +5652,17 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -4088,7 +5677,7 @@
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr"/>
@@ -4105,22 +5694,22 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>REQ013, REQ068</t>
+          <t>Conceptual Framework (Input) (p.25)</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Dosage/usage notes field on products</t>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -4130,7 +5719,7 @@
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr"/>
@@ -4147,22 +5736,22 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>REQ049</t>
+          <t>Methodology: sprint plan (p.30-35)</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Supplier column in the inventory batch table</t>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
@@ -4172,7 +5761,7 @@
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr"/>
@@ -4189,22 +5778,22 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>REQ103, REQ107</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -4214,7 +5803,7 @@
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr"/>
@@ -4231,22 +5820,22 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>REQ116</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Customer Accounts: list of the customer's orders</t>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
@@ -4256,7 +5845,7 @@
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr"/>
@@ -4273,27 +5862,27 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>REQ088</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
+          <t>Hide costing/wholesale prices from public reads</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -4301,11 +5890,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H69" s="11" t="inlineStr"/>
       <c r="I69" s="11" t="inlineStr"/>
       <c r="J69" s="11" t="inlineStr">
         <is>
@@ -4319,27 +5904,27 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>REQ070</t>
+          <t>Interview 1</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Category rename: replace native prompt() with app dialog</t>
+          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -4349,7 +5934,7 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>Client's current POS practice; not in the paper.</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr"/>
@@ -4365,22 +5950,22 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>REQ033, REQ093</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -4393,11 +5978,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H71" s="11" t="inlineStr"/>
       <c r="I71" s="11" t="inlineStr"/>
       <c r="J71" s="11" t="inlineStr">
         <is>
@@ -4416,17 +5997,17 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>REQ099</t>
+          <t>REQ013, REQ068</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>'Payment not received' as its own hold type</t>
+          <t>Dosage/usage notes field on products</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
@@ -4458,12 +6039,12 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>REQ026</t>
+          <t>REQ049</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Checkout pick-up notice mentions bringing the original prescription</t>
+          <t>Supplier column in the inventory batch table</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
@@ -4500,12 +6081,12 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>REQ009</t>
+          <t>REQ103, REQ107</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Show quantity in stock on catalog cards</t>
+          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -4523,7 +6104,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H74" s="11" t="inlineStr"/>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
+        </is>
+      </c>
       <c r="I74" s="11" t="inlineStr"/>
       <c r="J74" s="11" t="inlineStr">
         <is>
@@ -4542,17 +6127,17 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>REQ040</t>
+          <t>REQ116</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Profile picture in Account Settings</t>
+          <t>Customer Accounts: list of the customer's orders</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -4584,17 +6169,17 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>REQNF028</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
+          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -4607,7 +6192,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H76" s="11" t="inlineStr"/>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I76" s="11" t="inlineStr"/>
       <c r="J76" s="11" t="inlineStr">
         <is>
@@ -4626,17 +6215,17 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>REQ047</t>
+          <t>REQ070</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
+          <t>Category rename: replace native prompt() with app dialog</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4672,17 +6261,17 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>REQNF017</t>
+          <t>REQ033, REQ093</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>README with setup steps; fix the error message that points to it</t>
+          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -4718,17 +6307,17 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>REQ001</t>
+          <t>REQ099</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Normalize phone number at registration</t>
+          <t>'Payment not received' as its own hold type</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -4741,11 +6330,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H79" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H79" s="11" t="inlineStr"/>
       <c r="I79" s="11" t="inlineStr"/>
       <c r="J79" s="11" t="inlineStr">
         <is>
@@ -4764,17 +6349,17 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>REQ039, Fig 2.10, C16</t>
+          <t>REQ026</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+          <t>Checkout pick-up notice mentions bringing the original prescription</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
@@ -4806,17 +6391,17 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>System roles (-)</t>
+          <t>REQ009</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+          <t>Show quantity in stock on catalog cards</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -4843,22 +6428,22 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Whole paper + system (-)</t>
+          <t>REQ040</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+          <t>Profile picture in Account Settings</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
@@ -4885,22 +6470,22 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>REQNF028</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -4913,11 +6498,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H83" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H83" s="11" t="inlineStr"/>
       <c r="I83" s="11" t="inlineStr"/>
       <c r="J83" s="11" t="inlineStr">
         <is>
@@ -4931,22 +6512,22 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>REQ047</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -4961,7 +6542,7 @@
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>From the first review.</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr"/>
@@ -4977,22 +6558,22 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Decision-dependent</t>
+          <t>REQNF017</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+          <t>README with setup steps; fix the error message that points to it</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -5007,7 +6588,7 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>From the first review.</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr"/>
@@ -5023,22 +6604,22 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>REQ001</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>Normalize phone number at registration</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -5051,7 +6632,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H86" s="11" t="inlineStr"/>
+      <c r="H86" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I86" s="11" t="inlineStr"/>
       <c r="J86" s="11" t="inlineStr">
         <is>
@@ -5065,22 +6650,22 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Scope (p.6)</t>
+          <t>REQ008; Interview 1</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>Store announcement banner (e.g. closure days)</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -5107,22 +6692,22 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.22-23)</t>
+          <t>REQ039, Fig 2.10, C16</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
@@ -5149,17 +6734,17 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.32)</t>
+          <t>System roles (-)</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
@@ -5191,17 +6776,17 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Whole paper + system (-)</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -5238,17 +6823,17 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Modules FEFO p.41</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Add the 2-month Bad Order step (C7).</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -5261,7 +6846,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H91" s="11" t="inlineStr"/>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I91" s="11" t="inlineStr"/>
       <c r="J91" s="11" t="inlineStr">
         <is>
@@ -5280,17 +6869,17 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Technical Background p.35-37; Budget p.99</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
@@ -5303,7 +6892,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H92" s="11" t="inlineStr"/>
+      <c r="H92" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I92" s="11" t="inlineStr"/>
       <c r="J92" s="11" t="inlineStr">
         <is>
@@ -5322,17 +6915,17 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Scope and Limitations p.7</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -5345,7 +6938,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H93" s="11" t="inlineStr"/>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I93" s="11" t="inlineStr"/>
       <c r="J93" s="11" t="inlineStr">
         <is>
@@ -5364,17 +6961,17 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.36-38)</t>
+          <t>Decision-dependent</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -5387,7 +6984,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H94" s="11" t="inlineStr"/>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I94" s="11" t="inlineStr"/>
       <c r="J94" s="11" t="inlineStr">
         <is>
@@ -5406,12 +7007,12 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.38)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
@@ -5448,12 +7049,12 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Modules: Price Management (p.42)</t>
+          <t>Scope (p.6)</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -5490,12 +7091,12 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+          <t>Theoretical Framework (p.22-23)</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
@@ -5532,12 +7133,12 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.97-98)</t>
+          <t>Methodology: sprint plan (p.32)</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -5574,12 +7175,12 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
@@ -5616,12 +7217,12 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -5658,12 +7259,12 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>References (p.100)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
@@ -5700,12 +7301,12 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>References (p.10 / refs)</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -5742,12 +7343,12 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>References (p.17 / refs)</t>
+          <t>Technical Background: Software (p.36-38)</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
@@ -5784,12 +7385,12 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Appendices (p.124)</t>
+          <t>Technical Background: Software (p.38)</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
@@ -5826,12 +7427,12 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+          <t>Modules: Price Management (p.42)</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Regenerate page numbers after all edits.</t>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
@@ -5857,18 +7458,396 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr"/>
+      <c r="I106" s="11" t="inlineStr"/>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities (p.97-98)</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr"/>
+      <c r="I107" s="11" t="inlineStr"/>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr"/>
+      <c r="I108" s="11" t="inlineStr"/>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr"/>
+      <c r="I109" s="11" t="inlineStr"/>
+      <c r="J109" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>References (p.100)</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H110" s="11" t="inlineStr"/>
+      <c r="I110" s="11" t="inlineStr"/>
+      <c r="J110" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>References (p.10 / refs)</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr"/>
+      <c r="I111" s="11" t="inlineStr"/>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>References (p.17 / refs)</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr"/>
+      <c r="I112" s="11" t="inlineStr"/>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>Appendices (p.124)</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr"/>
+      <c r="I113" s="11" t="inlineStr"/>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr"/>
+      <c r="I114" s="11" t="inlineStr"/>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J105"/>
-  <conditionalFormatting sqref="J2:J105">
+  <autoFilter ref="A1:J114"/>
+  <conditionalFormatting sqref="J2:J114">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6375,12 +8354,12 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Change paper</t>
+          <t>Change system</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>No client ask for promotions in any interview; reword to featured products/categories.</t>
+          <t>The client announces store closures (e.g. long weekends) to buyers today (Interview 1); a simple staff-editable announcement banner covers it. Promotions can be dropped from the paper.</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -6395,7 +8374,7 @@
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.47; Interview 1</t>
         </is>
       </c>
     </row>
@@ -19335,7 +21314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -19374,7 +21353,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Home shows featured products and categories (drop 'announcements, promotions') unless you want a banner built.</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
     </row>
@@ -19585,17 +21564,29 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
+          <t>Scope and Limitations p.7</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
           <t>Decision-dependent</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B21"/>
+  <autoFilter ref="A1:B22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19606,1555 +21597,765 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>What the client asked</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Where it's covered</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>Defense risk</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>Effort</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>Price lock: one person changes prices, can lower then restore, changes monitored</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>To-Do: price lock item; REQ071-073</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>1, 4</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>Void / cancel with lock, reason, receipt number, stock restore, exchange</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>'Integrated Real-Time Expiry Monitoring': near-expiry stock is only flagged when the Inventory page opens (REQ066). Fix the system so the title holds (To-Do: REQ066 item).</t>
+          <t>To-Do: walk-in void; receipt numbers</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Covered (rules added from Interview 4)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Whole paper</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Reports with batch + expiry, summarized, copy-paste into office Excel</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>To-Do: Reports module</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Whole paper</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>'Keep' a punched walk-in order until the customer confirms</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>To-Do: park/hold sale</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Added now (Decision)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Whole paper + system</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Small thermal receipt printer</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+          <t>To-Do: receipt printing</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Project Context</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>p.1</t>
+          <t>Usable on the manager's phone</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>REQNF003 test pass</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Project Context / Purpose</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>p.2-4</t>
+          <t>Not connected to BIR or government; confidential</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>AI chat 'addresses inquiries at any hour': depends on the live chat decision.</t>
+          <t>To-Do: 'not an official receipt' relabel; Limitations edit</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Added now</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Purpose and Description</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>p.3</t>
+          <t>Announce closure days to buyers</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>'Each completed transaction ... made available for printing and reporting': needs receipt printing and the Reports module.</t>
+          <t>To-Do: announcement banner (REQ008)</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Added now</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Objectives</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>p.5</t>
+          <t>Free goods: near-expiry RX only to doctors, vitamins to all</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Obj. 1 promises AI chat support (live chat decision). Obj. 2 promises auto-removal of near-expiry stock (REQ066 fix). Obj. 3 promises exportable daily/monthly reports with batch + expiry (Reports module).</t>
+          <t>To-Do: wholesale free-of-cost (note)</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Added now (note)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Objectives / evaluation</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>p.5-6, 21-24</t>
+          <t>Multi-branch / Manila branch use</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
+          <t>Limitations p.7 (single branch)</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>Out of scope</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>Sales Staff = POS only</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>REQ121 decision</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>p.7</t>
+          <t>Wholesale not online; retail price only online</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>'Automated daily sales and inventory reports are generated': depends on the Reports module.</t>
+          <t>REQ088 (wholesale price visibility)</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>p.7</t>
+          <t>Wholesale documents: LTO + business permit, latest copies</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>AI live chat bullet: live chat decision.</t>
+          <t>REQ086 expiry tracking</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Limitations</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>p.7</t>
+          <t>POS receipt printed; BIR receipt with VAT only on request</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
+          <t>'Not an official receipt' item; Limitations edit</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Added now</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Limitations</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>p.7</t>
+          <t>Send the sales invoice format</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
+          <t>Client item</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>p.18</t>
+          <t>Price change needs reason and date (option or free note, e.g. 'approved by boss')</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>Price lock item</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>p.18</t>
+          <t>Customer file per wholesale buyer; reorder past purchases</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>The proposed system gets a tick for 'AI-powered live chat'; keep only if chat is built.</t>
+          <t>Wholesale history item (reorder added)</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Added now (reorder)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>p.22-23</t>
+          <t>Daily sales (per customer, items, batch, expiry); monthly purchases (batch, expiry, purchase date, receipt no., supplier); monthly inventory; pull-out; returns</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>Reports module; supplier DR number field</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Added now (DR number)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>p.24</t>
+          <t>Wholesale returns as item exchange, no money back</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Wholesale exchange item</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>p.25</t>
+          <t>Free-of-cost for wholesale only</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>Wholesale free-of-cost item</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output)</t>
+          <t>2, 3</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>p.27</t>
+          <t>Lalamove only; payment first, no COD; customer pays rider</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>REQ020; Terms rewrite</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan</t>
+          <t>2, 3</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>p.32</t>
+          <t>Rider details recorded</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>Delivery notes item (note)</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Added now (note)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>p.30-35</t>
+          <t>Daily cash remitted to main office</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>Reports module (totals by payment method)</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Added now (note)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Methodology: Deployment</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>p.30</t>
+          <t>Live chat on the website</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>'Deployed in a controlled environment using actual client data': not done yet. Decide hosting, then either do it or reword.</t>
+          <t>Live chat decision</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Technical Background</t>
+          <t>3, 4</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>p.35</t>
+          <t>No third-party payment; QR Ph direct, verified on the spot</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>REQ028 QR image</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Technical Background</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>p.35-36</t>
+          <t>Wrong item delivered: exchange, no refund; no cancellation after payment; failed-delivery fees on customer</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Terms rewrite</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Added now</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Technical Background</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>p.35-36</t>
+          <t>Report export must look like the client's sample</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>Client item; Reports module</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Technical Background</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>p.35, 37</t>
+          <t>Export the dashboard</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>Reports module (Dashboard Export button)</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Technical Background</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>p.35, 37</t>
+          <t>See history of what came from each supplier</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+          <t>Supplier history item</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Added now</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>p.36-38</t>
+          <t>See wholesale permit expiry</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>REQ086</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>p.38</t>
+          <t>Audit log shows who added stock/products</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>REQ122 completeness</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Covered</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>Technical Background</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>p.35</t>
+          <t>Void restricted: a second person must see it</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+          <t>Walk-in void item (note)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Added now (note)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>p.45-46</t>
+          <t>Hands-on before go-live</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>User manual + training item</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Modules: Price Management</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>p.42</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>System roles</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Wireframes (Figs 2.16-2.21)</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>p.92-95</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Calendar of Activities</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>p.96-98</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Calendar of Activities</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>p.96-98</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Calendar of Activities</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>p.97-98</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>Budgetary Estimate</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>p.99</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>Budgetary Estimate</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>p.99</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E42" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>References</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>p.100</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>References</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>p.10 / refs</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>References</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>p.17 / refs</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>Appendices</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>p.124</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>Table of Contents / List of Figures</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>p.iv-vi</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>Regenerate page numbers after all edits.</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F47" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>Client items</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>Get from the client: the QR Ph image, the sample report format, and the sales invoice format (promised in Interviews 2-4); confirm decisions with them.</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>Added now</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F48"/>
+  <autoFilter ref="A1:D34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -15,21 +15,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Stack" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Edits" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Asks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manuscript Pass" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Formats" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Asks" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manuscript Pass" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$J$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$J$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Contradictions'!$A$1:$E$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Tech Stack'!$A$1:$E$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Paper Edits'!$A$1:$B$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Interview Asks'!$A$1:$D$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Manuscript Pass'!$A$1:$F$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Figures'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Paper Edits'!$A$1:$B$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report Formats'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Interview Asks'!$A$1:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Manuscript Pass'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Figures'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -903,6 +905,775 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>What the client asked</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Where it's covered</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Price lock: one person changes prices, can lower then restore, changes monitored</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>To-Do: price lock item; REQ071-073</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>1, 4</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Void / cancel with lock, reason, receipt number, stock restore, exchange</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>To-Do: walk-in void; receipt numbers</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Covered (rules added from Interview 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Reports with batch + expiry, summarized, copy-paste into office Excel</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>To-Do: Reports module</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>'Keep' a punched walk-in order until the customer confirms</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>To-Do: park/hold sale</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Added now (Decision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Small thermal receipt printer</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>To-Do: receipt printing</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Usable on the manager's phone</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>REQNF003 test pass</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Not connected to BIR or government; confidential</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>To-Do: 'not an official receipt' relabel; Limitations edit</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Added now</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Announce closure days to buyers</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>To-Do: announcement banner (REQ008)</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Added now</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Free goods: near-expiry RX only to doctors, vitamins to all</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>To-Do: wholesale free-of-cost (note)</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Added now (note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Multi-branch / Manila branch use</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Limitations p.7 (single branch)</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Out of scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Sales Staff = POS only</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>REQ121 decision</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale not online; retail price only online</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>REQ088 (wholesale price visibility)</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale documents: LTO + business permit, latest copies</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>REQ086 expiry tracking</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>POS receipt printed; BIR receipt with VAT only on request</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>'Not an official receipt' item; Limitations edit</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Added now</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Send the sales invoice format</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Client item</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Price change needs reason and date (option or free note, e.g. 'approved by boss')</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Price lock item</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Customer file per wholesale buyer; reorder past purchases</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale history item (reorder added)</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Added now (reorder)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Daily sales (per customer, items, batch, expiry); monthly purchases (batch, expiry, purchase date, receipt no., supplier); monthly inventory; pull-out; returns</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Reports module; supplier DR number field</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Added now (DR number)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale returns as item exchange, no money back</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale exchange item</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Free-of-cost for wholesale only</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale free-of-cost item</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>2, 3</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Lalamove only; payment first, no COD; customer pays rider</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>REQ020; Terms rewrite</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>2, 3</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Rider details recorded</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Delivery notes item (note)</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Added now (note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Daily cash remitted to main office</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Reports module (totals by payment method)</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Added now (note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Live chat on the website</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Live chat decision</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>3, 4</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>No third-party payment; QR Ph direct, verified on the spot</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>REQ028 QR image</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Wrong item delivered: exchange, no refund; no cancellation after payment; failed-delivery fees on customer</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Terms rewrite</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Added now</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Report export must look like the client's sample</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Client item; Reports module</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Export the dashboard</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Reports module (Dashboard Export button)</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>See history of what came from each supplier</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Supplier history item</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Added now</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>See wholesale permit expiry</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>REQ086</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Audit log shows who added stock/products</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>REQ122 completeness</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Void restricted: a second person must see it</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Walk-in void item (note)</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Added now (note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Hands-on before go-live</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>User manual + training item</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Added now</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D34"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2431,7 +3202,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Get from the client: the QR Ph image, the sample report format, and the sales invoice format (promised in Interviews 2-4); confirm decisions with them.</t>
+          <t>Get from the client: the QR Ph image and the sales invoice format (sample reports received). Ask them: are all sales VAT-exempt (sample shows VATable 0.00), is pay-in/pay-out used, who tracks credit collections, which categories to use, may we load the real catalog for the demo?</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -2456,7 +3227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2835,7 +3606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2918,7 +3689,7 @@
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Get from the client: the QR Ph image, the sample report format, and the sales invoice format (promised in Interviews 2-4); confirm decisions with them.</t>
+          <t>Get from the client: the QR Ph image and the sales invoice format (sample reports received). Ask them: are all sales VAT-exempt (sample shows VATable 0.00), is pay-in/pay-out used, who tracks credit collections, which categories to use, may we load the real catalog for the demo?</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
@@ -3114,7 +3885,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Client's one remaining ask (Interview 4). Match the client's sample format; Excel output must paste cleanly into the main office's own sheets (Interviews 1, 2, 4); daily sales should total by payment method to match the daily cash remittance (Interview 2).</t>
+          <t>Client's one remaining ask (Interview 4). Build to the 4 client samples (see Report Formats sheet); Excel output must paste cleanly into the main office's own sheets (Interviews 1, 2, 4); daily sales should total by payment method to match the daily cash remittance (Interview 2).</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr"/>
@@ -3353,17 +4124,17 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Modules p.43; Fig 2.14; Interview 4</t>
+          <t>REQ006, REQNF025, Limitations p.7; Interviews 1-3</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Sequential receipt numbers for walk-in sales (receipt currently shows '-')</t>
+          <t>Rewrite Terms &amp; Privacy to the client's actual policies: no refunds (exchange only), no cancellation after payment, 7-day hold then closure with credit kept, delivery fee and failed-delivery fees paid by the customer to the rider, RX pick-up only with original prescription, QR Ph only, Data Privacy Act 2012. Remove 'refunds case-by-case' and 'request deletion' (system only deactivates). Replace placeholder support@amson.ph with a real contact.</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -3378,7 +4149,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Needed to void by original receipt number.</t>
+          <t>Panel may read the Terms during the demo.</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr"/>
@@ -3399,22 +4170,22 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>REQ006, REQNF025, Limitations p.7; Interviews 1-3</t>
+          <t>Report Formats sheet; REQ111; Interviews 2, 4</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Rewrite Terms &amp; Privacy to the client's actual policies: no refunds (exchange only), no cancellation after payment, 7-day hold then closure with credit kept, delivery fee and failed-delivery fees paid by the customer to the rider, RX pick-up only with original prescription, QR Ph only, Data Privacy Act 2012. Remove 'refunds case-by-case' and 'request deletion' (system only deactivates). Replace placeholder support@amson.ph with a real contact.</t>
+          <t>Record which batch (batch no. + expiry) each sold item came from, on every POS, online and wholesale sale</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -3424,7 +4195,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Panel may read the Terms during the demo.</t>
+          <t>Every client report lists batch + expiry per sold line; today FEFO deducts the right batch but the sale doesn't remember which. Blocks the Reports module.</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr"/>
@@ -3440,17 +4211,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
+          <t>Report Formats sheet (SI# 00008247...); Modules p.43</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
+          <t>One sequential Sales Invoice (SI#) number across walk-in, online and wholesale sales</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -3460,7 +4231,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -3470,7 +4241,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
+          <t>Replaces the separate 'receipt numbers' item; voids reference it.</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr"/>
@@ -3486,22 +4257,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>REQ098, REQ102, C2</t>
+          <t>Report Formats sheet (Payment Method section, Terms of Payment)</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
+          <t>Payment method + terms on every sale: Cash, G-Cash/QR Ph, Bank Transfer, Terminal (card), Credit (pay later); add to wholesale orders, which record none today</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -3516,7 +4287,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>Credit was ₱57,534 of ₱81,181 on the sample day.</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr"/>
@@ -3537,22 +4308,22 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
+          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
+          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -3560,7 +4331,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
+        </is>
+      </c>
       <c r="I16" s="11" t="inlineStr"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
@@ -3574,27 +4349,27 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Objectives / evaluation (p.5-6, 21-24)</t>
+          <t>REQ098, REQ102, C2</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
+          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -3602,7 +4377,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I17" s="11" t="inlineStr"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
@@ -3616,22 +4395,22 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>REQ121</t>
+          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
+          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -3641,14 +4420,10 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Orders access was added on purpose on 2026-10-01.</t>
-        </is>
-      </c>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr"/>
       <c r="I18" s="11" t="inlineStr"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -3662,32 +4437,32 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>REQNF005</t>
+          <t>Objectives / evaluation (p.5-6, 21-24)</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Live updates without refresh on verification queue + customer order page</t>
+          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr"/>
@@ -3709,17 +4484,17 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>REQNF010, REQNF013</t>
+          <t>REQ121</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
+          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -3732,7 +4507,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Orders access was added on purpose on 2026-10-01.</t>
+        </is>
+      </c>
       <c r="I20" s="11" t="inlineStr"/>
       <c r="J20" s="11" t="inlineStr">
         <is>
@@ -3751,22 +4530,22 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>REQNF005</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
+          <t>Live updates without refresh on verification queue + customer order page</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -3793,17 +4572,17 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>REQNF010, REQNF013</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
+          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -3835,22 +4614,22 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Report Formats sheet (Discount/Deductions columns); Interview 2</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+          <t>Discount / deduction per sale or line, with reason and audit entry</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -3858,7 +4637,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr"/>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Not in the paper; client gives boss-approved discounts today.</t>
+        </is>
+      </c>
       <c r="I23" s="11" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -3872,27 +4655,27 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Methodology p.30 ('actual client data'); Report Formats sheet</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
+          <t>Load the client's real March-end catalog (prices, batches, expiry) from their workbook via the existing upload templates</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -3902,7 +4685,7 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr"/>
@@ -3918,22 +4701,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>REQ002</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
+          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -3946,11 +4729,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H25" s="11" t="inlineStr"/>
       <c r="I25" s="11" t="inlineStr"/>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -3964,27 +4743,27 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Unrecognized-device OTP for customers and staff</t>
+          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -4006,27 +4785,27 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>REQ086, REQ089, REQ091, REQ092</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
+          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -4034,11 +4813,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
-        </is>
-      </c>
+      <c r="H27" s="11" t="inlineStr"/>
       <c r="I27" s="11" t="inlineStr"/>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -4057,22 +4832,22 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>REQ090, REQ114, Fig 2.15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
+          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -4080,7 +4855,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I28" s="11" t="inlineStr"/>
       <c r="J28" s="11" t="inlineStr">
         <is>
@@ -4099,22 +4878,22 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>REQ067, C7</t>
+          <t>REQ002</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
+          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -4122,7 +4901,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I29" s="11" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
@@ -4141,12 +4924,12 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
+          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
+          <t>Unrecognized-device OTP for customers and staff</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -4156,7 +4939,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -4183,22 +4966,22 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>REQ084</t>
+          <t>REQ086, REQ089, REQ091, REQ092</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>POS: RX Verified checkbox + optional notes</t>
+          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -4206,7 +4989,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
+        </is>
+      </c>
       <c r="I31" s="11" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
@@ -4225,22 +5012,22 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>REQ061, C5</t>
+          <t>REQ090, REQ114, Fig 2.15</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
+          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -4267,22 +5054,22 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>REQNF025, REQNF029</t>
+          <t>REQ067, C7</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
+          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -4290,11 +5077,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H33" s="11" t="inlineStr"/>
       <c r="I33" s="11" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
@@ -4313,22 +5096,22 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>REQ039, REQ042</t>
+          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
+          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -4336,11 +5119,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
-        <is>
-          <t>EmailJS free tier: 200/month.</t>
-        </is>
-      </c>
+      <c r="H34" s="11" t="inlineStr"/>
       <c r="I34" s="11" t="inlineStr"/>
       <c r="J34" s="11" t="inlineStr">
         <is>
@@ -4359,22 +5138,22 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>REQ122</t>
+          <t>REQ084</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
+          <t>POS: RX Verified checkbox + optional notes</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -4401,17 +5180,17 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>REQ014</t>
+          <t>REQ061, C5</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Save cart to the customer's account</t>
+          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -4443,17 +5222,17 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>REQNF003, REQNF007</t>
+          <t>REQNF025, REQNF029</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Phone/tablet and cross-browser test pass</t>
+          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -4466,7 +5245,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I37" s="11" t="inlineStr"/>
       <c r="J37" s="11" t="inlineStr">
         <is>
@@ -4485,22 +5268,22 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Interviews 2, 4</t>
+          <t>REQ039, REQ042</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
+          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -4510,7 +5293,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Required column in the monthly purchases report.</t>
+          <t>EmailJS free tier: 200/month.</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr"/>
@@ -4531,22 +5314,22 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Interview 4 walkthrough</t>
+          <t>REQ122</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Supplier history: everything received from each supplier</t>
+          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -4554,11 +5337,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>Shown to the client during the prototype walkthrough.</t>
-        </is>
-      </c>
+      <c r="H39" s="11" t="inlineStr"/>
       <c r="I39" s="11" t="inlineStr"/>
       <c r="J39" s="11" t="inlineStr">
         <is>
@@ -4577,22 +5356,22 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Methodology p.30; Interview 4</t>
+          <t>REQ014</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>User manual + hands-on training + handover to the branch</t>
+          <t>Save cart to the customer's account</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -4600,11 +5379,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
-        </is>
-      </c>
+      <c r="H40" s="11" t="inlineStr"/>
       <c r="I40" s="11" t="inlineStr"/>
       <c r="J40" s="11" t="inlineStr">
         <is>
@@ -4623,17 +5398,17 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Project Context (p.1)</t>
+          <t>REQNF003, REQNF007</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>Phone/tablet and cross-browser test pass</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Not verified</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -4665,17 +5440,17 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.24)</t>
+          <t>Interviews 2, 4</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -4688,7 +5463,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Required column in the monthly purchases report.</t>
+        </is>
+      </c>
       <c r="I42" s="11" t="inlineStr"/>
       <c r="J42" s="11" t="inlineStr">
         <is>
@@ -4707,17 +5486,17 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output) (p.27)</t>
+          <t>Interview 4 walkthrough</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>Supplier history: everything received from each supplier</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -4730,7 +5509,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Shown to the client during the prototype walkthrough.</t>
+        </is>
+      </c>
       <c r="I43" s="11" t="inlineStr"/>
       <c r="J43" s="11" t="inlineStr">
         <is>
@@ -4744,27 +5527,27 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles (p.45-46)</t>
+          <t>Methodology p.30; Interview 4</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>User manual + hands-on training + handover to the branch</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
@@ -4772,7 +5555,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
+        </is>
+      </c>
       <c r="I44" s="11" t="inlineStr"/>
       <c r="J44" s="11" t="inlineStr">
         <is>
@@ -4786,22 +5573,22 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>REQ007 / Technical Background p.35-36</t>
+          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -4816,7 +5603,7 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Customer File groups every sale by customer name.</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr"/>
@@ -4832,22 +5619,22 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>REQ008 p.47; Modules p.38</t>
+          <t>Report Formats sheet (Supplier sheets)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
+          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -4862,7 +5649,7 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr"/>
@@ -4878,22 +5665,22 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>REQ031 p.50</t>
+          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies, Grocery</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4908,7 +5695,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr"/>
@@ -4924,22 +5711,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>REQ073 p.55</t>
+          <t>Project Context (p.1)</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -4952,11 +5739,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H48" s="11" t="inlineStr"/>
       <c r="I48" s="11" t="inlineStr"/>
       <c r="J48" s="11" t="inlineStr">
         <is>
@@ -4970,22 +5753,22 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+          <t>Theoretical Framework (p.24)</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4998,11 +5781,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H49" s="11" t="inlineStr"/>
       <c r="I49" s="11" t="inlineStr"/>
       <c r="J49" s="11" t="inlineStr">
         <is>
@@ -5016,22 +5795,22 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087 p.57; Modules p.44</t>
+          <t>Conceptual Framework (Output) (p.27)</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Default wholesale price per product, adjustable per order (C9).</t>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -5044,11 +5823,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H50" s="11" t="inlineStr"/>
       <c r="I50" s="11" t="inlineStr"/>
       <c r="J50" s="11" t="inlineStr">
         <is>
@@ -5062,22 +5837,22 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+          <t>Modules: Staff roles (p.45-46)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -5090,11 +5865,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H51" s="11" t="inlineStr"/>
       <c r="I51" s="11" t="inlineStr"/>
       <c r="J51" s="11" t="inlineStr">
         <is>
@@ -5113,12 +5884,12 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+          <t>REQ007 / Technical Background p.35-36</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -5159,12 +5930,12 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>REQ121 p.61</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
@@ -5205,12 +5976,12 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 text p.67</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -5251,12 +6022,12 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 diagram</t>
+          <t>REQ073 p.55</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
@@ -5297,12 +6068,12 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.5 text p.72</t>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -5343,12 +6114,12 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 / 2.7 diagrams</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
@@ -5389,12 +6160,12 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.8 diagram + text p.76-77</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -5435,12 +6206,12 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 diagram + text p.78-79</t>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
@@ -5481,12 +6252,12 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.10 diagram</t>
+          <t>REQ121 p.61</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -5527,12 +6298,12 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 diagram + text p.82-83</t>
+          <t>Fig 2.2 text p.67</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
@@ -5573,17 +6344,17 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover (i)</t>
+          <t>Fig 2.2 diagram</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -5596,7 +6367,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H62" s="11" t="inlineStr"/>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I62" s="11" t="inlineStr"/>
       <c r="J62" s="11" t="inlineStr">
         <is>
@@ -5615,22 +6390,22 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Fig 2.5 text p.72</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5638,7 +6413,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H63" s="11" t="inlineStr"/>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I63" s="11" t="inlineStr"/>
       <c r="J63" s="11" t="inlineStr">
         <is>
@@ -5657,17 +6436,17 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
@@ -5680,7 +6459,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H64" s="11" t="inlineStr"/>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I64" s="11" t="inlineStr"/>
       <c r="J64" s="11" t="inlineStr">
         <is>
@@ -5699,17 +6482,17 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input) (p.25)</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5722,7 +6505,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H65" s="11" t="inlineStr"/>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I65" s="11" t="inlineStr"/>
       <c r="J65" s="11" t="inlineStr">
         <is>
@@ -5741,17 +6528,17 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.30-35)</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
@@ -5764,7 +6551,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H66" s="11" t="inlineStr"/>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I66" s="11" t="inlineStr"/>
       <c r="J66" s="11" t="inlineStr">
         <is>
@@ -5783,17 +6574,17 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5806,7 +6597,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H67" s="11" t="inlineStr"/>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I67" s="11" t="inlineStr"/>
       <c r="J67" s="11" t="inlineStr">
         <is>
@@ -5825,17 +6620,17 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Fig 2.11 diagram + text p.82-83</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
@@ -5848,7 +6643,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H68" s="11" t="inlineStr"/>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I68" s="11" t="inlineStr"/>
       <c r="J68" s="11" t="inlineStr">
         <is>
@@ -5862,32 +6661,32 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>REQ088</t>
+          <t>Title page / cover (i)</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Hide costing/wholesale prices from public reads</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr"/>
@@ -5904,22 +6703,22 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Interview 1</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
@@ -5929,14 +6728,10 @@
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H70" s="11" t="inlineStr">
-        <is>
-          <t>Client's current POS practice; not in the paper.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr"/>
       <c r="I70" s="11" t="inlineStr"/>
       <c r="J70" s="11" t="inlineStr">
         <is>
@@ -5950,17 +6745,17 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
@@ -5975,7 +6770,7 @@
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr"/>
@@ -5992,22 +6787,22 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>REQ013, REQ068</t>
+          <t>Conceptual Framework (Input) (p.25)</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Dosage/usage notes field on products</t>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
@@ -6017,7 +6812,7 @@
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr"/>
@@ -6034,22 +6829,22 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>REQ049</t>
+          <t>Methodology: sprint plan (p.30-35)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Supplier column in the inventory batch table</t>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -6059,7 +6854,7 @@
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr"/>
@@ -6076,22 +6871,22 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>REQ103, REQ107</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -6101,14 +6896,10 @@
       </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H74" s="11" t="inlineStr">
-        <is>
-          <t>Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr"/>
       <c r="I74" s="11" t="inlineStr"/>
       <c r="J74" s="11" t="inlineStr">
         <is>
@@ -6122,22 +6913,22 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>REQ116</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Customer Accounts: list of the customer's orders</t>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6147,7 +6938,7 @@
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr"/>
@@ -6164,27 +6955,27 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>REQ088</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
+          <t>Hide costing/wholesale prices from public reads</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr">
@@ -6192,11 +6983,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H76" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H76" s="11" t="inlineStr"/>
       <c r="I76" s="11" t="inlineStr"/>
       <c r="J76" s="11" t="inlineStr">
         <is>
@@ -6210,27 +6997,27 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>REQ070</t>
+          <t>Interview 1</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Category rename: replace native prompt() with app dialog</t>
+          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6240,7 +7027,7 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>Client's current POS practice; not in the paper.</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr"/>
@@ -6256,27 +7043,27 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>REQ033, REQ093</t>
+          <t>Report Formats sheet (CREDIT terms)</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
+          <t>Credit sales follow-up (who owes what, mark as paid)</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -6286,7 +7073,7 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>Not in the paper; ask the client if the main office tracks collections instead.</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr"/>
@@ -6302,22 +7089,22 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>REQ099</t>
+          <t>Report Formats sheet (daily Sales section)</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>'Payment not received' as its own hold type</t>
+          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6330,7 +7117,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H79" s="11" t="inlineStr"/>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>Both were 0.00 on the sample day; ask if it's used.</t>
+        </is>
+      </c>
       <c r="I79" s="11" t="inlineStr"/>
       <c r="J79" s="11" t="inlineStr">
         <is>
@@ -6344,22 +7135,22 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>REQ026</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Checkout pick-up notice mentions bringing the original prescription</t>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
@@ -6391,17 +7182,17 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>REQ009</t>
+          <t>REQ013, REQ068</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Show quantity in stock on catalog cards</t>
+          <t>Dosage/usage notes field on products</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6433,17 +7224,17 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>REQ040</t>
+          <t>REQ049</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Profile picture in Account Settings</t>
+          <t>Supplier column in the inventory batch table</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
@@ -6475,12 +7266,12 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>REQNF028</t>
+          <t>REQ103, REQ107</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
+          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
@@ -6498,7 +7289,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H83" s="11" t="inlineStr"/>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
+        </is>
+      </c>
       <c r="I83" s="11" t="inlineStr"/>
       <c r="J83" s="11" t="inlineStr">
         <is>
@@ -6517,17 +7312,17 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>REQ047</t>
+          <t>REQ116</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
+          <t>Customer Accounts: list of the customer's orders</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -6540,11 +7335,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H84" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H84" s="11" t="inlineStr"/>
       <c r="I84" s="11" t="inlineStr"/>
       <c r="J84" s="11" t="inlineStr">
         <is>
@@ -6563,17 +7354,17 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>REQNF017</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>README with setup steps; fix the error message that points to it</t>
+          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -6609,17 +7400,17 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>REQ001</t>
+          <t>REQ070</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Normalize phone number at registration</t>
+          <t>Category rename: replace native prompt() with app dialog</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -6655,17 +7446,17 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>REQ008; Interview 1</t>
+          <t>REQ033, REQ093</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Store announcement banner (e.g. closure days)</t>
+          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -6678,7 +7469,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H87" s="11" t="inlineStr"/>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I87" s="11" t="inlineStr"/>
       <c r="J87" s="11" t="inlineStr">
         <is>
@@ -6697,17 +7492,17 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>REQ039, Fig 2.10, C16</t>
+          <t>REQ099</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+          <t>'Payment not received' as its own hold type</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
@@ -6739,17 +7534,17 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>System roles (-)</t>
+          <t>REQ026</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+          <t>Checkout pick-up notice mentions bringing the original prescription</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -6776,22 +7571,22 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Whole paper + system (-)</t>
+          <t>REQ009</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+          <t>Show quantity in stock on catalog cards</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -6818,22 +7613,22 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>REQ040</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>Profile picture in Account Settings</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -6846,11 +7641,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H91" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H91" s="11" t="inlineStr"/>
       <c r="I91" s="11" t="inlineStr"/>
       <c r="J91" s="11" t="inlineStr">
         <is>
@@ -6864,22 +7655,22 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>REQNF028</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
@@ -6892,11 +7683,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H92" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H92" s="11" t="inlineStr"/>
       <c r="I92" s="11" t="inlineStr"/>
       <c r="J92" s="11" t="inlineStr">
         <is>
@@ -6910,22 +7697,22 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Scope and Limitations p.7</t>
+          <t>REQ047</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -6940,7 +7727,7 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>From the first review.</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr"/>
@@ -6956,22 +7743,22 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Decision-dependent</t>
+          <t>REQNF017</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+          <t>README with setup steps; fix the error message that points to it</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -6986,7 +7773,7 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>From the first review.</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr"/>
@@ -7002,22 +7789,22 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>REQ001</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>Normalize phone number at registration</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -7030,7 +7817,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H95" s="11" t="inlineStr"/>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I95" s="11" t="inlineStr"/>
       <c r="J95" s="11" t="inlineStr">
         <is>
@@ -7044,22 +7835,22 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Scope (p.6)</t>
+          <t>REQ008; Interview 1</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>Store announcement banner (e.g. closure days)</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -7086,22 +7877,22 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.22-23)</t>
+          <t>REQ039, Fig 2.10, C16</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -7128,17 +7919,17 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.32)</t>
+          <t>System roles (-)</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -7170,17 +7961,17 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Whole paper + system (-)</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
@@ -7217,17 +8008,17 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Modules FEFO p.41</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Add the 2-month Bad Order step (C7).</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -7240,7 +8031,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H100" s="11" t="inlineStr"/>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I100" s="11" t="inlineStr"/>
       <c r="J100" s="11" t="inlineStr">
         <is>
@@ -7259,17 +8054,17 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Technical Background p.35-37; Budget p.99</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -7282,7 +8077,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H101" s="11" t="inlineStr"/>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I101" s="11" t="inlineStr"/>
       <c r="J101" s="11" t="inlineStr">
         <is>
@@ -7301,17 +8100,17 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Scope p.6; Product Browsing REQ009</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -7324,7 +8123,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H102" s="11" t="inlineStr"/>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I102" s="11" t="inlineStr"/>
       <c r="J102" s="11" t="inlineStr">
         <is>
@@ -7343,17 +8146,17 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.36-38)</t>
+          <t>Scope and Limitations p.7</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -7366,7 +8169,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H103" s="11" t="inlineStr"/>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I103" s="11" t="inlineStr"/>
       <c r="J103" s="11" t="inlineStr">
         <is>
@@ -7385,17 +8192,17 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.38)</t>
+          <t>Decision-dependent</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -7408,7 +8215,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H104" s="11" t="inlineStr"/>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I104" s="11" t="inlineStr"/>
       <c r="J104" s="11" t="inlineStr">
         <is>
@@ -7427,12 +8238,12 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Modules: Price Management (p.42)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
@@ -7469,12 +8280,12 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+          <t>Scope (p.6)</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
@@ -7511,12 +8322,12 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.97-98)</t>
+          <t>Theoretical Framework (p.22-23)</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
@@ -7553,12 +8364,12 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Methodology: sprint plan (p.32)</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
@@ -7595,12 +8406,12 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
@@ -7637,12 +8448,12 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>References (p.100)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
@@ -7679,12 +8490,12 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>References (p.10 / refs)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
@@ -7721,12 +8532,12 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>References (p.17 / refs)</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
@@ -7763,12 +8574,12 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Appendices (p.124)</t>
+          <t>Technical Background: Software (p.36-38)</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
@@ -7805,12 +8616,12 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+          <t>Technical Background: Software (p.38)</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Regenerate page numbers after all edits.</t>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
@@ -7836,18 +8647,438 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="11" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>Modules: Price Management (p.42)</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr"/>
+      <c r="I115" s="11" t="inlineStr"/>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr"/>
+      <c r="I116" s="11" t="inlineStr"/>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities (p.97-98)</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr"/>
+      <c r="I117" s="11" t="inlineStr"/>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="11" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H118" s="11" t="inlineStr"/>
+      <c r="I118" s="11" t="inlineStr"/>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr"/>
+      <c r="I119" s="11" t="inlineStr"/>
+      <c r="J119" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>References (p.100)</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr"/>
+      <c r="I120" s="11" t="inlineStr"/>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>References (p.10 / refs)</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr"/>
+      <c r="I121" s="11" t="inlineStr"/>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>References (p.17 / refs)</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H122" s="11" t="inlineStr"/>
+      <c r="I122" s="11" t="inlineStr"/>
+      <c r="J122" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>Appendices (p.124)</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr"/>
+      <c r="I123" s="11" t="inlineStr"/>
+      <c r="J123" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G124" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H124" s="11" t="inlineStr"/>
+      <c r="I124" s="11" t="inlineStr"/>
+      <c r="J124" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J114"/>
-  <conditionalFormatting sqref="J2:J114">
+  <autoFilter ref="A1:J124"/>
+  <conditionalFormatting sqref="J2:J124">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -21314,7 +22545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -21564,29 +22795,41 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Scope and Limitations p.7</t>
+          <t>Scope p.6; Product Browsing REQ009</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>Scope and Limitations p.7</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t>Decision-dependent</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B22"/>
+  <autoFilter ref="A1:B23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21597,765 +22840,357 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Client report</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>What the client asked</t>
+          <t>Section / columns</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>Where it's covered</t>
+          <t>System data today</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>To-Do</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Daily Sales (PDF)</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Price lock: one person changes prices, can lower then restore, changes monitored</t>
+          <t>Header: store name, date range 12:00:01 AM - 11:59:59 PM</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>To-Do: price lock item; REQ071-073</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>Reports module</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>1, 4</t>
+          <t>Daily Sales (PDF)</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Void / cancel with lock, reason, receipt number, stock restore, exchange</t>
+          <t>Sales: Date, No. of Orders, Total, Discount/Deduction, Grand Total, Less VAT, VATable Sales, VAT 12%, VAT Exempt Sales</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>To-Do: walk-in void; receipt numbers</t>
+          <t>posSales, orders, wholesaleOrders totals</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Covered (rules added from Interview 4)</t>
+          <t>No discounts; no VAT fields (sample day: all VAT-exempt)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Discount decision; VAT question to client</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Daily Sales (PDF)</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Reports with batch + expiry, summarized, copy-paste into office Excel</t>
+          <t>Pay-In, Pay-Out, TOTAL</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>To-Do: Reports module</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>Not recorded</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Pay-in/pay-out decision</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Daily Sales (PDF)</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>'Keep' a punched walk-in order until the customer confirms</t>
+          <t>Retail Sales: Date, No. of Items, Total Amount</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>To-Do: park/hold sale</t>
+          <t>posSales + online orders</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Added now (Decision)</t>
-        </is>
-      </c>
+          <t>OK once combined</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Daily Sales (PDF)</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Small thermal receipt printer</t>
+          <t>Wholesale Sales: Date, No. of Items, Total Amount</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>To-Do: receipt printing</t>
+          <t>wholesaleOrders</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Covered</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Daily Sales (PDF)</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Usable on the manager's phone</t>
+          <t>Payment Method: Bank Transfer, Cash, Credit, G-Cash, Terminal - orders + amount</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>REQNF003 test pass</t>
+          <t>posSales.paymentMethod (cash/card/e-wallet only)</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>No Bank Transfer/Credit; wholesale has no payment method</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Payment method + terms item</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Daily Sales (PDF)</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Not connected to BIR or government; confidential</t>
+          <t>Item Sold: Item, No. of Items, Total Amount, Discount (sorted by qty)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>To-Do: 'not an official receipt' relabel; Limitations edit</t>
+          <t>sale line items</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Added now</t>
-        </is>
-      </c>
+          <t>OK (no discount)</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Customer File (Excel, daily)</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Announce closure days to buyers</t>
+          <t>Customer Name, Date+time, SI#, Batch No, Exp, Qty, Item, Sales Price, Total Amount, Terms of Payment; subtotal per customer</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>To-Do: announcement banner (REQ008)</t>
+          <t>sale line items</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Added now</t>
+          <t>No batch/expiry per line, no SI#, no walk-in customer name, no terms</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Batch per sale; SI#; walk-in name; payment terms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Monthly Inventory (Excel)</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Free goods: near-expiry RX only to doctors, vitamins to all</t>
+          <t>One sheet per category (Generics, Medical Supplies, Grocery, Drugstore per pc, Branded): Product, POS stock, Physical count, Costing, Retail, Wholesale, Batch #, Expiry</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>To-Do: wholesale free-of-cost (note)</t>
+          <t>stockBatches + reconciliation counts + product prices</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Added now (note)</t>
+          <t>Categories differ; needs reconciliation export by category</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Categories item; Reports module</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Monthly Return to POS (Excel)</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Multi-branch / Manila branch use</t>
+          <t>Item, Batch, Expiry, Customer, DR#, Date Purchased, Date Returned, Qty, Amount, Total</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Limitations p.7 (single branch)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Out of scope</t>
+          <t>Wholesale exchange/return not built; no DR#/SI# on the original sale</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale exchange; SI#</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Monthly Supplier Purchases (Excel)</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Sales Staff = POS only</t>
+          <t>Supplier Name, Order Date, Receipt #, Product, Brand, Packs, Batch #, Expiry, Qty, Price, Amount, Total; separate Drugstore and Grocery sheets</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>REQ121 decision</t>
+          <t>stockBatches (supplier, batch, expiry, qty, date)</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>No receipt #, unit cost, pack on receiving</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Receiving fields item</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Observations</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Wholesale not online; retail price only online</t>
+          <t>Their old POS shows negative stock (-1); several expiries are typed into product names (e.g. '4/28'); one batch cell can list several expiries</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>REQ088 (wholesale price visibility)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Wholesale documents: LTO + business permit, latest copies</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>REQ086 expiry tracking</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>POS receipt printed; BIR receipt with VAT only on request</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>'Not an official receipt' item; Limitations edit</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Added now</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Send the sales invoice format</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Client item</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Price change needs reason and date (option or free note, e.g. 'approved by boss')</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Price lock item</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Customer file per wholesale buyer; reorder past purchases</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Wholesale history item (reorder added)</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Added now (reorder)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Daily sales (per customer, items, batch, expiry); monthly purchases (batch, expiry, purchase date, receipt no., supplier); monthly inventory; pull-out; returns</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Reports module; supplier DR number field</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Added now (DR number)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Wholesale returns as item exchange, no money back</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Wholesale exchange item</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Free-of-cost for wholesale only</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Wholesale free-of-cost item</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Lalamove only; payment first, no COD; customer pays rider</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>REQ020; Terms rewrite</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Rider details recorded</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Delivery notes item (note)</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Added now (note)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Daily cash remitted to main office</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Reports module (totals by payment method)</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>Added now (note)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Live chat on the website</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Live chat decision</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>3, 4</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>No third-party payment; QR Ph direct, verified on the spot</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>REQ028 QR image</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Wrong item delivered: exchange, no refund; no cancellation after payment; failed-delivery fees on customer</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Terms rewrite</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Added now</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Report export must look like the client's sample</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Client item; Reports module</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Export the dashboard</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Reports module (Dashboard Export button)</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>See history of what came from each supplier</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Supplier history item</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Added now</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>See wholesale permit expiry</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>REQ086</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Audit log shows who added stock/products</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>REQ122 completeness</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Void restricted: a second person must see it</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>Walk-in void item (note)</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Added now (note)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Hands-on before go-live</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>User manual + training item</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Added now</t>
+          <t>Our system blocks negative stock and keeps one expiry per batch - good defense talking points; data needs cleaning before import</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Catalog import item</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D34"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
+          <t>DECIDED: build it with OpenAI via a Netlify Function (panel's recommended feature). Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr"/>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Orders access was added on purpose on 2026-10-01.</t>
+          <t>DECIDED: trim to POS + catalog view; Walk-in history inside POS. Orders access was added on purpose on 2026-10-01.</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr"/>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -4553,7 +4553,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: live on verification queue + customer order page only; reword REQNF005 for the rest.</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="inlineStr"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
@@ -4567,7 +4571,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -4595,7 +4599,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: Netlify (already set up).</t>
+        </is>
+      </c>
       <c r="I22" s="11" t="inlineStr"/>
       <c r="J22" s="11" t="inlineStr">
         <is>
@@ -4609,7 +4617,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -4639,13 +4647,13 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Not in the paper; client gives boss-approved discounts today.</t>
+          <t>Client confirmed: no discounts. Not in the paper; client gives boss-approved discounts today.</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4663,7 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -4685,13 +4693,13 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
+          <t>DECIDED: yes, once the client sends the catalog. Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr"/>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -6955,7 +6963,7 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
@@ -6983,11 +6991,15 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H76" s="11" t="inlineStr"/>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: leave as is; state in Limitations.</t>
+        </is>
+      </c>
       <c r="I76" s="11" t="inlineStr"/>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -6997,7 +7009,7 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -7027,13 +7039,13 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Client's current POS practice; not in the paper.</t>
+          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr"/>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7055,7 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
@@ -7073,13 +7085,13 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Not in the paper; ask the client if the main office tracks collections instead.</t>
+          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr"/>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7101,7 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -7119,13 +7131,13 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Both were 0.00 on the sample day; ask if it's used.</t>
+          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr"/>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8229,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DECIDED: build it with OpenAI via a Netlify Function (panel's recommended feature). See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr"/>
@@ -9079,7 +9091,7 @@
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Open,In progress,Done,Dropped"</formula1>
+      <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22126,17 +22138,17 @@
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Not hosted; local http-server via start-server.bat</t>
+          <t>Netlify (set up); local http-server for testing</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Netlify blocked by billing. Options: Firebase Hosting (free, HTTPS) and update the paper, or present locally and move hosting to Limitations.</t>
+          <t>DECIDED: stay on Netlify. Budget row must match the chosen plan; Netlify Functions host the OpenAI call.</t>
         </is>
       </c>
     </row>
@@ -22234,17 +22246,17 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Not integrated</t>
+          <t>Not integrated yet</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>Change system</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Needs a server-side function to keep the API key secret.</t>
+          <t>DECIDED: OpenAI through a Netlify Function so the key stays secret. Budget: add OpenAI usage.</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -15,23 +15,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Stack" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Edits" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Formats" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Asks" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manuscript Pass" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removals (Letter)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Formats" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Asks" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manuscript Pass" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$J$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Contradictions'!$A$1:$E$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Tech Stack'!$A$1:$E$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Paper Edits'!$A$1:$B$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report Formats'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Interview Asks'!$A$1:$D$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Manuscript Pass'!$A$1:$F$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Figures'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Removals (Letter)'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Report Formats'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Interview Asks'!$A$1:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Manuscript Pass'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Figures'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -129,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,6 +146,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -763,7 +768,7 @@
         </is>
       </c>
       <c r="B20">
-        <f>COUNTIF('To-Do'!J:J,"Open")</f>
+        <f>COUNTIF('To-Do'!K:K,"Open")</f>
         <v/>
       </c>
     </row>
@@ -900,6 +905,367 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Client report</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Section / columns</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>System data today</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>To-Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Daily Sales (PDF)</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Header: store name, date range 12:00:01 AM - 11:59:59 PM</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>Reports module</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Daily Sales (PDF)</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Sales: Date, No. of Orders, Total, Discount/Deduction, Grand Total, Less VAT, VATable Sales, VAT 12%, VAT Exempt Sales</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>posSales, orders, wholesaleOrders totals</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>No discounts; no VAT fields (sample day: all VAT-exempt)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Discount decision; VAT question to client</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Daily Sales (PDF)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Pay-In, Pay-Out, TOTAL</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Not recorded</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Pay-in/pay-out decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Daily Sales (PDF)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Retail Sales: Date, No. of Items, Total Amount</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>posSales + online orders</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>OK once combined</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Daily Sales (PDF)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale Sales: Date, No. of Items, Total Amount</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>wholesaleOrders</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Daily Sales (PDF)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Payment Method: Bank Transfer, Cash, Credit, G-Cash, Terminal - orders + amount</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>posSales.paymentMethod (cash/card/e-wallet only)</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>No Bank Transfer/Credit; wholesale has no payment method</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Payment method + terms item</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Daily Sales (PDF)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Item Sold: Item, No. of Items, Total Amount, Discount (sorted by qty)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>sale line items</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>OK (no discount)</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Customer File (Excel, daily)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Customer Name, Date+time, SI#, Batch No, Exp, Qty, Item, Sales Price, Total Amount, Terms of Payment; subtotal per customer</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>sale line items</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>No batch/expiry per line, no SI#, no walk-in customer name, no terms</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Batch per sale; SI#; walk-in name; payment terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Monthly Inventory (Excel)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>One sheet per category (Generics, Medical Supplies, Grocery, Drugstore per pc, Branded): Product, POS stock, Physical count, Costing, Retail, Wholesale, Batch #, Expiry</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>stockBatches + reconciliation counts + product prices</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Categories differ; needs reconciliation export by category</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Categories item; Reports module</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Monthly Return to POS (Excel)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Item, Batch, Expiry, Customer, DR#, Date Purchased, Date Returned, Qty, Amount, Total</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale exchange/return not built; no DR#/SI# on the original sale</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale exchange; SI#</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Monthly Supplier Purchases (Excel)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Supplier Name, Order Date, Receipt #, Product, Brand, Packs, Batch #, Expiry, Qty, Price, Amount, Total; separate Drugstore and Grocery sheets</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>stockBatches (supplier, batch, expiry, qty, date)</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>No receipt #, unit cost, pack on receiving</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Receiving fields item</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Observations</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Their old POS shows negative stock (-1); several expiries are typed into product names (e.g. '4/28'); one batch cell can list several expiries</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Our system blocks negative stock and keeps one expiry per batch - good defense talking points; data needs cleaning before import</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Catalog import item</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1668,7 +2034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3227,7 +3593,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3606,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3617,8 +3983,9 @@
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3664,10 +4031,15 @@
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
+          <t>Paper impact</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3708,8 +4080,13 @@
         </is>
       </c>
       <c r="H2" s="11" t="inlineStr"/>
-      <c r="I2" s="11" t="inlineStr"/>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr"/>
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3754,8 +4131,13 @@
           <t>DECIDED: build it with OpenAI via a Netlify Function (panel's recommended feature). Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr"/>
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3796,8 +4178,13 @@
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr"/>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3842,8 +4229,13 @@
           <t>Title feature.</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3888,8 +4280,13 @@
           <t>Client's one remaining ask (Interview 4). Build to the 4 client samples (see Report Formats sheet); Excel output must paste cleanly into the main office's own sheets (Interviews 1, 2, 4); daily sales should total by payment method to match the daily cash remittance (Interview 2).</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3930,8 +4327,13 @@
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr"/>
-      <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3972,8 +4374,13 @@
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr"/>
-      <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4018,8 +4425,13 @@
           <t>Need the image from the client.</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr"/>
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4060,8 +4472,13 @@
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr"/>
-      <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4106,8 +4523,13 @@
           <t>Client is not BIR-connected by choice and issues BIR/VAT receipts manually on request.</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4152,8 +4574,13 @@
           <t>Panel may read the Terms during the demo.</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4198,8 +4625,13 @@
           <t>Every client report lists batch + expiry per sold line; today FEFO deducts the right batch but the sale doesn't remember which. Blocks the Reports module.</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr"/>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4244,8 +4676,13 @@
           <t>Replaces the separate 'receipt numbers' item; voids reference it.</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4290,8 +4727,13 @@
           <t>Credit was ₱57,534 of ₱81,181 on the sample day.</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4336,8 +4778,13 @@
           <t>Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr"/>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr"/>
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4382,8 +4829,13 @@
           <t>From the first review.</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr"/>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr"/>
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4424,8 +4876,13 @@
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr"/>
-      <c r="I18" s="11" t="inlineStr"/>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr"/>
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4466,8 +4923,13 @@
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr"/>
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4512,8 +4974,13 @@
           <t>DECIDED: trim to POS + catalog view; Walk-in history inside POS. Orders access was added on purpose on 2026-10-01.</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr"/>
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4558,8 +5025,13 @@
           <t>DECIDED: live on verification queue + customer order page only; reword REQNF005 for the rest.</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4604,8 +5076,13 @@
           <t>DECIDED: Netlify (already set up).</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4650,8 +5127,13 @@
           <t>Client confirmed: no discounts. Not in the paper; client gives boss-approved discounts today.</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>None (not in paper)</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -4696,8 +5178,13 @@
           <t>DECIDED: yes, once the client sends the catalog. Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr"/>
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -4738,8 +5225,13 @@
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr"/>
-      <c r="I25" s="11" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4780,8 +5272,13 @@
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr"/>
-      <c r="I26" s="11" t="inlineStr"/>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr"/>
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4822,8 +5319,13 @@
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr"/>
-      <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4868,8 +5370,13 @@
           <t>From the first review.</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr"/>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr"/>
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4914,8 +5421,13 @@
           <t>From the first review.</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr"/>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr"/>
+      <c r="K29" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4956,8 +5468,13 @@
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr"/>
-      <c r="I30" s="11" t="inlineStr"/>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr"/>
+      <c r="K30" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5002,8 +5519,13 @@
           <t>Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr"/>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5044,8 +5566,13 @@
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr"/>
-      <c r="I32" s="11" t="inlineStr"/>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr"/>
+      <c r="K32" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5086,8 +5613,13 @@
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr"/>
-      <c r="I33" s="11" t="inlineStr"/>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5128,8 +5660,13 @@
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr"/>
-      <c r="I34" s="11" t="inlineStr"/>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5170,8 +5707,13 @@
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr"/>
-      <c r="I35" s="11" t="inlineStr"/>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5212,8 +5754,13 @@
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr"/>
-      <c r="I36" s="11" t="inlineStr"/>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr"/>
+      <c r="K36" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5258,8 +5805,13 @@
           <t>From the first review.</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr"/>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr"/>
+      <c r="K37" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5304,8 +5856,13 @@
           <t>EmailJS free tier: 200/month.</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr"/>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr"/>
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5346,8 +5903,13 @@
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr"/>
-      <c r="I39" s="11" t="inlineStr"/>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr"/>
+      <c r="K39" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5388,8 +5950,13 @@
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr"/>
-      <c r="I40" s="11" t="inlineStr"/>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5430,8 +5997,13 @@
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr"/>
-      <c r="I41" s="11" t="inlineStr"/>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5476,8 +6048,13 @@
           <t>Required column in the monthly purchases report.</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr"/>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5522,8 +6099,13 @@
           <t>Shown to the client during the prototype walkthrough.</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr"/>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5568,8 +6150,13 @@
           <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr"/>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5614,8 +6201,13 @@
           <t>Customer File groups every sale by customer name.</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr"/>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr"/>
+      <c r="K45" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5660,8 +6252,13 @@
           <t>Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr"/>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr"/>
+      <c r="K46" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5706,8 +6303,13 @@
           <t>Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr"/>
-      <c r="J47" s="11" t="inlineStr">
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr"/>
+      <c r="K47" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5748,8 +6350,13 @@
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr"/>
-      <c r="I48" s="11" t="inlineStr"/>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr"/>
+      <c r="K48" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5790,8 +6397,13 @@
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr"/>
-      <c r="I49" s="11" t="inlineStr"/>
-      <c r="J49" s="11" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5832,8 +6444,13 @@
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr"/>
-      <c r="I50" s="11" t="inlineStr"/>
-      <c r="J50" s="11" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr"/>
+      <c r="K50" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5874,8 +6491,13 @@
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr"/>
-      <c r="I51" s="11" t="inlineStr"/>
-      <c r="J51" s="11" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr"/>
+      <c r="K51" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5920,8 +6542,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr"/>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5966,8 +6593,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr"/>
-      <c r="J53" s="11" t="inlineStr">
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr"/>
+      <c r="K53" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6012,8 +6644,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr"/>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6058,8 +6695,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr"/>
-      <c r="J55" s="11" t="inlineStr">
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr"/>
+      <c r="K55" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6104,8 +6746,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I56" s="11" t="inlineStr"/>
-      <c r="J56" s="11" t="inlineStr">
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6150,8 +6797,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I57" s="11" t="inlineStr"/>
-      <c r="J57" s="11" t="inlineStr">
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr"/>
+      <c r="K57" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6196,8 +6848,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr"/>
-      <c r="J58" s="11" t="inlineStr">
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr"/>
+      <c r="K58" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6242,8 +6899,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I59" s="11" t="inlineStr"/>
-      <c r="J59" s="11" t="inlineStr">
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr"/>
+      <c r="K59" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6288,8 +6950,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr"/>
-      <c r="J60" s="11" t="inlineStr">
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr"/>
+      <c r="K60" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6334,8 +7001,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr"/>
-      <c r="J61" s="11" t="inlineStr">
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr"/>
+      <c r="K61" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6380,8 +7052,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr"/>
-      <c r="J62" s="11" t="inlineStr">
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr"/>
+      <c r="K62" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6426,8 +7103,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr"/>
-      <c r="J63" s="11" t="inlineStr">
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr"/>
+      <c r="K63" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6472,8 +7154,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr"/>
-      <c r="J64" s="11" t="inlineStr">
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr"/>
+      <c r="K64" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6518,8 +7205,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr"/>
-      <c r="J65" s="11" t="inlineStr">
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr"/>
+      <c r="K65" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6564,8 +7256,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I66" s="11" t="inlineStr"/>
-      <c r="J66" s="11" t="inlineStr">
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr"/>
+      <c r="K66" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6610,8 +7307,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I67" s="11" t="inlineStr"/>
-      <c r="J67" s="11" t="inlineStr">
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr"/>
+      <c r="K67" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6656,8 +7358,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr"/>
-      <c r="J68" s="11" t="inlineStr">
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6698,8 +7405,13 @@
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr"/>
-      <c r="I69" s="11" t="inlineStr"/>
-      <c r="J69" s="11" t="inlineStr">
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6740,8 +7452,13 @@
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr"/>
-      <c r="I70" s="11" t="inlineStr"/>
-      <c r="J70" s="11" t="inlineStr">
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr"/>
+      <c r="K70" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6782,8 +7499,13 @@
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr"/>
-      <c r="I71" s="11" t="inlineStr"/>
-      <c r="J71" s="11" t="inlineStr">
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6824,8 +7546,13 @@
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr"/>
-      <c r="I72" s="11" t="inlineStr"/>
-      <c r="J72" s="11" t="inlineStr">
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J72" s="11" t="inlineStr"/>
+      <c r="K72" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6866,8 +7593,13 @@
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr"/>
-      <c r="I73" s="11" t="inlineStr"/>
-      <c r="J73" s="11" t="inlineStr">
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6908,8 +7640,13 @@
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr"/>
-      <c r="I74" s="11" t="inlineStr"/>
-      <c r="J74" s="11" t="inlineStr">
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6950,8 +7687,13 @@
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr"/>
-      <c r="I75" s="11" t="inlineStr"/>
-      <c r="J75" s="11" t="inlineStr">
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr"/>
+      <c r="K75" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6996,8 +7738,13 @@
           <t>DECIDED: leave as is; state in Limitations.</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr"/>
-      <c r="J76" s="11" t="inlineStr">
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES - letter (REQ088 to Limitations)</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="inlineStr"/>
+      <c r="K76" s="11" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -7042,8 +7789,13 @@
           <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr"/>
-      <c r="J77" s="11" t="inlineStr">
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>None (not in paper)</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="inlineStr"/>
+      <c r="K77" s="11" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -7088,8 +7840,13 @@
           <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
         </is>
       </c>
-      <c r="I78" s="11" t="inlineStr"/>
-      <c r="J78" s="11" t="inlineStr">
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>None (not in paper)</t>
+        </is>
+      </c>
+      <c r="J78" s="11" t="inlineStr"/>
+      <c r="K78" s="11" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -7134,8 +7891,13 @@
           <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr"/>
-      <c r="J79" s="11" t="inlineStr">
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>None (not in paper)</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr"/>
+      <c r="K79" s="11" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -7176,8 +7938,13 @@
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr"/>
-      <c r="I80" s="11" t="inlineStr"/>
-      <c r="J80" s="11" t="inlineStr">
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J80" s="11" t="inlineStr"/>
+      <c r="K80" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7218,8 +7985,13 @@
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr"/>
-      <c r="I81" s="11" t="inlineStr"/>
-      <c r="J81" s="11" t="inlineStr">
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr"/>
+      <c r="K81" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7260,8 +8032,13 @@
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr"/>
-      <c r="I82" s="11" t="inlineStr"/>
-      <c r="J82" s="11" t="inlineStr">
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="inlineStr"/>
+      <c r="K82" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7306,8 +8083,13 @@
           <t>Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
         </is>
       </c>
-      <c r="I83" s="11" t="inlineStr"/>
-      <c r="J83" s="11" t="inlineStr">
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="inlineStr"/>
+      <c r="K83" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7348,8 +8130,13 @@
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr"/>
-      <c r="I84" s="11" t="inlineStr"/>
-      <c r="J84" s="11" t="inlineStr">
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr"/>
+      <c r="K84" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7394,8 +8181,13 @@
           <t>From the first review.</t>
         </is>
       </c>
-      <c r="I85" s="11" t="inlineStr"/>
-      <c r="J85" s="11" t="inlineStr">
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr"/>
+      <c r="K85" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7440,8 +8232,13 @@
           <t>From the first review.</t>
         </is>
       </c>
-      <c r="I86" s="11" t="inlineStr"/>
-      <c r="J86" s="11" t="inlineStr">
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="inlineStr"/>
+      <c r="K86" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7486,8 +8283,13 @@
           <t>From the first review.</t>
         </is>
       </c>
-      <c r="I87" s="11" t="inlineStr"/>
-      <c r="J87" s="11" t="inlineStr">
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="inlineStr"/>
+      <c r="K87" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7528,8 +8330,13 @@
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr"/>
-      <c r="I88" s="11" t="inlineStr"/>
-      <c r="J88" s="11" t="inlineStr">
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J88" s="11" t="inlineStr"/>
+      <c r="K88" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7570,8 +8377,13 @@
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr"/>
-      <c r="I89" s="11" t="inlineStr"/>
-      <c r="J89" s="11" t="inlineStr">
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr"/>
+      <c r="K89" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7612,8 +8424,13 @@
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr"/>
-      <c r="I90" s="11" t="inlineStr"/>
-      <c r="J90" s="11" t="inlineStr">
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J90" s="11" t="inlineStr"/>
+      <c r="K90" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7654,8 +8471,13 @@
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr"/>
-      <c r="I91" s="11" t="inlineStr"/>
-      <c r="J91" s="11" t="inlineStr">
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="inlineStr"/>
+      <c r="K91" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7696,8 +8518,13 @@
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr"/>
-      <c r="I92" s="11" t="inlineStr"/>
-      <c r="J92" s="11" t="inlineStr">
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr"/>
+      <c r="K92" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7742,8 +8569,13 @@
           <t>From the first review.</t>
         </is>
       </c>
-      <c r="I93" s="11" t="inlineStr"/>
-      <c r="J93" s="11" t="inlineStr">
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr"/>
+      <c r="K93" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7788,8 +8620,13 @@
           <t>From the first review.</t>
         </is>
       </c>
-      <c r="I94" s="11" t="inlineStr"/>
-      <c r="J94" s="11" t="inlineStr">
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr"/>
+      <c r="K94" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7834,8 +8671,13 @@
           <t>From the first review.</t>
         </is>
       </c>
-      <c r="I95" s="11" t="inlineStr"/>
-      <c r="J95" s="11" t="inlineStr">
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr"/>
+      <c r="K95" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7876,8 +8718,13 @@
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr"/>
-      <c r="I96" s="11" t="inlineStr"/>
-      <c r="J96" s="11" t="inlineStr">
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr"/>
+      <c r="K96" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7918,8 +8765,13 @@
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr"/>
-      <c r="I97" s="11" t="inlineStr"/>
-      <c r="J97" s="11" t="inlineStr">
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr"/>
+      <c r="K97" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7960,8 +8812,13 @@
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr"/>
-      <c r="I98" s="11" t="inlineStr"/>
-      <c r="J98" s="11" t="inlineStr">
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr"/>
+      <c r="K98" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8002,8 +8859,13 @@
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr"/>
-      <c r="I99" s="11" t="inlineStr"/>
-      <c r="J99" s="11" t="inlineStr">
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr"/>
+      <c r="K99" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8048,8 +8910,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I100" s="11" t="inlineStr"/>
-      <c r="J100" s="11" t="inlineStr">
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="inlineStr"/>
+      <c r="K100" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8094,8 +8961,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I101" s="11" t="inlineStr"/>
-      <c r="J101" s="11" t="inlineStr">
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr"/>
+      <c r="K101" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8140,8 +9012,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I102" s="11" t="inlineStr"/>
-      <c r="J102" s="11" t="inlineStr">
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>Adds</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr"/>
+      <c r="K102" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8186,8 +9063,13 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I103" s="11" t="inlineStr"/>
-      <c r="J103" s="11" t="inlineStr">
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Adds</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr"/>
+      <c r="K103" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8232,8 +9114,13 @@
           <t>DECIDED: build it with OpenAI via a Netlify Function (panel's recommended feature). See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I104" s="11" t="inlineStr"/>
-      <c r="J104" s="11" t="inlineStr">
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr"/>
+      <c r="K104" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8274,8 +9161,13 @@
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr"/>
-      <c r="I105" s="11" t="inlineStr"/>
-      <c r="J105" s="11" t="inlineStr">
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr"/>
+      <c r="K105" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8316,8 +9208,13 @@
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr"/>
-      <c r="I106" s="11" t="inlineStr"/>
-      <c r="J106" s="11" t="inlineStr">
+      <c r="I106" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr"/>
+      <c r="K106" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8358,8 +9255,13 @@
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr"/>
-      <c r="I107" s="11" t="inlineStr"/>
-      <c r="J107" s="11" t="inlineStr">
+      <c r="I107" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr"/>
+      <c r="K107" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8400,8 +9302,13 @@
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr"/>
-      <c r="I108" s="11" t="inlineStr"/>
-      <c r="J108" s="11" t="inlineStr">
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr"/>
+      <c r="K108" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8442,8 +9349,13 @@
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr"/>
-      <c r="I109" s="11" t="inlineStr"/>
-      <c r="J109" s="11" t="inlineStr">
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr"/>
+      <c r="K109" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8484,8 +9396,13 @@
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr"/>
-      <c r="I110" s="11" t="inlineStr"/>
-      <c r="J110" s="11" t="inlineStr">
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr"/>
+      <c r="K110" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8526,8 +9443,13 @@
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr"/>
-      <c r="I111" s="11" t="inlineStr"/>
-      <c r="J111" s="11" t="inlineStr">
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr"/>
+      <c r="K111" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8568,8 +9490,13 @@
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr"/>
-      <c r="I112" s="11" t="inlineStr"/>
-      <c r="J112" s="11" t="inlineStr">
+      <c r="I112" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J112" s="11" t="inlineStr"/>
+      <c r="K112" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8610,8 +9537,13 @@
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr"/>
-      <c r="I113" s="11" t="inlineStr"/>
-      <c r="J113" s="11" t="inlineStr">
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>Adds</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr"/>
+      <c r="K113" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8652,8 +9584,13 @@
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr"/>
-      <c r="I114" s="11" t="inlineStr"/>
-      <c r="J114" s="11" t="inlineStr">
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr"/>
+      <c r="K114" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8694,8 +9631,13 @@
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr"/>
-      <c r="I115" s="11" t="inlineStr"/>
-      <c r="J115" s="11" t="inlineStr">
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr"/>
+      <c r="K115" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8736,8 +9678,13 @@
         </is>
       </c>
       <c r="H116" s="11" t="inlineStr"/>
-      <c r="I116" s="11" t="inlineStr"/>
-      <c r="J116" s="11" t="inlineStr">
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr"/>
+      <c r="K116" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8778,8 +9725,13 @@
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr"/>
-      <c r="I117" s="11" t="inlineStr"/>
-      <c r="J117" s="11" t="inlineStr">
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr"/>
+      <c r="K117" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8820,8 +9772,13 @@
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr"/>
-      <c r="I118" s="11" t="inlineStr"/>
-      <c r="J118" s="11" t="inlineStr">
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J118" s="11" t="inlineStr"/>
+      <c r="K118" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8862,8 +9819,13 @@
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr"/>
-      <c r="I119" s="11" t="inlineStr"/>
-      <c r="J119" s="11" t="inlineStr">
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="inlineStr"/>
+      <c r="K119" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8904,8 +9866,13 @@
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr"/>
-      <c r="I120" s="11" t="inlineStr"/>
-      <c r="J120" s="11" t="inlineStr">
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr"/>
+      <c r="K120" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8946,8 +9913,13 @@
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr"/>
-      <c r="I121" s="11" t="inlineStr"/>
-      <c r="J121" s="11" t="inlineStr">
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="inlineStr"/>
+      <c r="K121" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8988,8 +9960,13 @@
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr"/>
-      <c r="I122" s="11" t="inlineStr"/>
-      <c r="J122" s="11" t="inlineStr">
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J122" s="11" t="inlineStr"/>
+      <c r="K122" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -9030,8 +10007,13 @@
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr"/>
-      <c r="I123" s="11" t="inlineStr"/>
-      <c r="J123" s="11" t="inlineStr">
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J123" s="11" t="inlineStr"/>
+      <c r="K123" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -9072,16 +10054,21 @@
         </is>
       </c>
       <c r="H124" s="11" t="inlineStr"/>
-      <c r="I124" s="11" t="inlineStr"/>
-      <c r="J124" s="11" t="inlineStr">
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J124" s="11" t="inlineStr"/>
+      <c r="K124" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J124"/>
-  <conditionalFormatting sqref="J2:J124">
+  <autoFilter ref="A1:K124"/>
+  <conditionalFormatting sqref="K2:K124">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -9090,7 +10077,7 @@
     <dataValidation sqref="B2:B124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9193,7 +10180,7 @@
           <t>Register with full name, email, contact no., password</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -9246,7 +10233,7 @@
           <t>Email verification code; activate only after verification</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -9303,7 +10290,7 @@
           <t>CAPTCHA on registration and login</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -9356,7 +10343,7 @@
           <t>Lock account 2 min after 5 failed logins</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -9413,7 +10400,7 @@
           <t>Email OTP when logging in from an unrecognized device</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -9470,7 +10457,7 @@
           <t>Show Terms and Conditions; require acceptance</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -9523,7 +10510,7 @@
           <t>Password recovery via time-limited reset link</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -9580,7 +10567,7 @@
           <t>Home page with products, announcements, promotions, navigation</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -9637,7 +10624,7 @@
           <t>Catalog by category with name, price, stock availability</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -9694,7 +10681,7 @@
           <t>Filter by category, price range, stock status</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -9751,7 +10738,7 @@
           <t>Keyword / product-name search</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -9808,7 +10795,7 @@
           <t>'No products found' message</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -9861,7 +10848,7 @@
           <t>Product page: name, description, price, stock, dosage/usage notes, images</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -9918,7 +10905,7 @@
           <t>Persistent cart per logged-in customer</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -9975,7 +10962,7 @@
           <t>Adjust quantities / remove items</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10028,7 +11015,7 @@
           <t>Running total updates on change</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10081,7 +11068,7 @@
           <t>Collect delivery address before submission</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10134,7 +11121,7 @@
           <t>Save default delivery address</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10191,7 +11178,7 @@
           <t>Block submission without address</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10244,7 +11231,7 @@
           <t>Notice: delivery fee paid to Lalamove rider</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10301,7 +11288,7 @@
           <t>RX pre-order requires prescription photo</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10354,7 +11341,7 @@
           <t>Full QR PH payment + screenshot before submission</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10407,7 +11394,7 @@
           <t>RX pre-orders are pick-up only</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10460,7 +11447,7 @@
           <t>Submitted as 'Pending Prescription Verification'; not prepared until staff approve the prescription</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -10517,7 +11504,7 @@
           <t>Notify approved/ready for pick-up, or rejected with reason</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -10574,7 +11561,7 @@
           <t>Notice: original prescription must be presented at pick-up</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -10631,7 +11618,7 @@
           <t>Customer can view RX pre-order status in My Orders</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10684,7 +11671,7 @@
           <t>Show branch QR PH code and account details</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -10741,7 +11728,7 @@
           <t>Require payment screenshot upload</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10794,7 +11781,7 @@
           <t>Hold order pending verification until admin confirms</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10847,7 +11834,7 @@
           <t>Statuses: pending payment, payment verified, confirmed, dispatched, delivered, payment rejected</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -10904,7 +11891,7 @@
           <t>View full order details</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -10957,7 +11944,7 @@
           <t>View/download system receipt for completed orders</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -11014,7 +12001,7 @@
           <t>Customer monitors delivery progress</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -11071,7 +12058,7 @@
           <t>Live chat for guests and customers</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -11128,7 +12115,7 @@
           <t>AI-powered responses (OpenAI) for common inquiries</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -11185,7 +12172,7 @@
           <t>Escalate to staff when needed</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -11242,7 +12229,7 @@
           <t>Notify staff of new/escalated chats</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -11299,7 +12286,7 @@
           <t>In-platform and email notifications for order/payment/delivery updates</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -11356,7 +12343,7 @@
           <t>Update name, address, contact no., profile picture</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -11413,7 +12400,7 @@
           <t>Confirm current password before setting new one</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -11466,7 +12453,7 @@
           <t>Enable/disable email notifications</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -11523,7 +12510,7 @@
           <t>Staff log in with credentials created by Branch Manager; role permissions applied</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -11576,7 +12563,7 @@
           <t>Staff OTP only on unrecognized device</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -11633,7 +12620,7 @@
           <t>Staff lockout after 5 failed attempts</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -11686,7 +12673,7 @@
           <t>Staff password reset link</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -11739,7 +12726,7 @@
           <t>Daily sales, active orders, low stock, near expiry, pending verifications, quick navigation</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -11796,7 +12783,7 @@
           <t>Notify BM + Technical of new orders, payments, stock, expiry, wholesale updates, chat</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -11853,7 +12840,7 @@
           <t>Inventory list per product by batch, with supplier details</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -11910,7 +12897,7 @@
           <t>Consistent stock across concurrent transactions</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -11963,7 +12950,7 @@
           <t>Record write-offs</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12016,7 +13003,7 @@
           <t>Reason required for write-off</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12069,7 +13056,7 @@
           <t>Create PO: supplier, products, quantities, date; Pending</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12122,7 +13109,7 @@
           <t>Link delivery to existing PO when receiving</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12175,7 +13162,7 @@
           <t>Auto-compare received vs PO quantities</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12228,7 +13215,7 @@
           <t>Discrepancy report + PO status Discrepancy</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12281,7 +13268,7 @@
           <t>Received when matched; acknowledgment to close Discrepancy</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12334,7 +13321,7 @@
           <t>Discrepancy reports by date range, PDF/Excel</t>
         </is>
       </c>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="D59" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -12391,7 +13378,7 @@
           <t>Input physical counts</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12444,7 +13431,7 @@
           <t>Auto variance calculation</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12497,7 +13484,7 @@
           <t>Branch Manager finalizes; variance reason in Audit Log</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D62" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -12554,7 +13541,7 @@
           <t>Record deliveries: product, qty, batch, expiry, supplier</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12607,7 +13594,7 @@
           <t>Stock added immediately on confirmation</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12660,7 +13647,7 @@
           <t>Bulk stock upload via Excel/CSV template</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12713,7 +13700,7 @@
           <t>FEFO across all transactions</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12766,7 +13753,7 @@
           <t>Flag batches within 6 months; remove from sellable; wholesale free-of-cost only</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -12823,7 +13810,7 @@
           <t>Within 2 months: Bad Order, disposal alert, auto-deduct</t>
         </is>
       </c>
-      <c r="D68" s="14" t="inlineStr">
+      <c r="D68" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -12880,7 +13867,7 @@
           <t>Create/edit/remove products incl. dosage notes, costing, retail, wholesale, image</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D69" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -12937,7 +13924,7 @@
           <t>Supplier records linked to products</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -12990,7 +13977,7 @@
           <t>Add, rename, remove categories</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D71" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -13047,7 +14034,7 @@
           <t>Price changes restricted to Branch Manager</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D72" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -13104,7 +14091,7 @@
           <t>Confirm price change before saving</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
+      <c r="D73" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -13157,7 +14144,7 @@
           <t>Audit log: previous price, new price, timestamp</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -13214,7 +14201,7 @@
           <t>Searchable, filterable order queue</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D75" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -13267,7 +14254,7 @@
           <t>Confirm, update, or hold orders</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -13320,7 +14307,7 @@
           <t>FEFO deduction on confirmation</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -13373,7 +14360,7 @@
           <t>Dedicated RX pre-order queue with prescription + payment proof</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D78" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -13430,7 +14417,7 @@
           <t>Approve after checking prescription: FEFO reservation, Ready for Pick-up, notify</t>
         </is>
       </c>
-      <c r="D79" s="13" t="inlineStr">
+      <c r="D79" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -13487,7 +14474,7 @@
           <t>Mandatory reason to reject; reason in customer notification</t>
         </is>
       </c>
-      <c r="D80" s="14" t="inlineStr">
+      <c r="D80" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -13544,7 +14531,7 @@
           <t>RX never assignable to delivery</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D81" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -13597,7 +14584,7 @@
           <t>Record staff, timestamp, action per verification</t>
         </is>
       </c>
-      <c r="D82" s="14" t="inlineStr">
+      <c r="D82" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -13654,7 +14641,7 @@
           <t>Technical + Sales Staff process walk-in sales (OTC + RX)</t>
         </is>
       </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -13707,7 +14694,7 @@
           <t>Void with reason, restore stock, audit log, record exchange + price difference</t>
         </is>
       </c>
-      <c r="D84" s="14" t="inlineStr">
+      <c r="D84" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -13764,7 +14751,7 @@
           <t>RX Verified checkbox + optional notes, no upload</t>
         </is>
       </c>
-      <c r="D85" s="14" t="inlineStr">
+      <c r="D85" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -13821,7 +14808,7 @@
           <t>Wholesale accounts with contact, business type, agreed pricing</t>
         </is>
       </c>
-      <c r="D86" s="13" t="inlineStr">
+      <c r="D86" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -13878,7 +14865,7 @@
           <t>Upload/update LTO and Business Permit</t>
         </is>
       </c>
-      <c r="D87" s="13" t="inlineStr">
+      <c r="D87" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -13935,7 +14922,7 @@
           <t>Record wholesale POs linked to account with wholesale pricing</t>
         </is>
       </c>
-      <c r="D88" s="12" t="inlineStr">
+      <c r="D88" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -13988,7 +14975,7 @@
           <t>Wholesale prices admin-only; not shown on retail site</t>
         </is>
       </c>
-      <c r="D89" s="13" t="inlineStr">
+      <c r="D89" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -14045,7 +15032,7 @@
           <t>Purchase history per wholesale account</t>
         </is>
       </c>
-      <c r="D90" s="14" t="inlineStr">
+      <c r="D90" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -14102,7 +15089,7 @@
           <t>Wholesale item exchanges with FEFO + audit log</t>
         </is>
       </c>
-      <c r="D91" s="14" t="inlineStr">
+      <c r="D91" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -14159,7 +15146,7 @@
           <t>Free-of-cost near-expiry distributions, zero cost, reason in audit log</t>
         </is>
       </c>
-      <c r="D92" s="13" t="inlineStr">
+      <c r="D92" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -14216,7 +15203,7 @@
           <t>Retail/walk-in receipt; wholesale sales invoice with buyer details</t>
         </is>
       </c>
-      <c r="D93" s="13" t="inlineStr">
+      <c r="D93" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -14273,7 +15260,7 @@
           <t>Receipt on payment verification, downloadable in My Orders</t>
         </is>
       </c>
-      <c r="D94" s="13" t="inlineStr">
+      <c r="D94" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -14330,7 +15317,7 @@
           <t>Verification queue of orders with proof</t>
         </is>
       </c>
-      <c r="D95" s="12" t="inlineStr">
+      <c r="D95" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -14383,7 +15370,7 @@
           <t>Confirm, or hold with issue type</t>
         </is>
       </c>
-      <c r="D96" s="12" t="inlineStr">
+      <c r="D96" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -14436,7 +15423,7 @@
           <t>On Hold - Invalid Screenshot + notify re-upload</t>
         </is>
       </c>
-      <c r="D97" s="12" t="inlineStr">
+      <c r="D97" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -14489,7 +15476,7 @@
           <t>On Hold - Underpayment, record outstanding, notify</t>
         </is>
       </c>
-      <c r="D98" s="12" t="inlineStr">
+      <c r="D98" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -14542,7 +15529,7 @@
           <t>On Hold - Overpayment, excess as unapplied value</t>
         </is>
       </c>
-      <c r="D99" s="15" t="inlineStr">
+      <c r="D99" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -14599,7 +15586,7 @@
           <t>On Hold - Payment Not Received, reason, notify</t>
         </is>
       </c>
-      <c r="D100" s="13" t="inlineStr">
+      <c r="D100" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -14656,7 +15643,7 @@
           <t>Auto-close after 7 days; verified payment kept as credit</t>
         </is>
       </c>
-      <c r="D101" s="12" t="inlineStr">
+      <c r="D101" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -14713,7 +15700,7 @@
           <t>Status to confirmed on approval</t>
         </is>
       </c>
-      <c r="D102" s="12" t="inlineStr">
+      <c r="D102" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -14766,7 +15753,7 @@
           <t>Notify customer on verification</t>
         </is>
       </c>
-      <c r="D103" s="13" t="inlineStr">
+      <c r="D103" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -14823,7 +15810,7 @@
           <t>Compile name, address, contact, schedule, order ID; one-click copy</t>
         </is>
       </c>
-      <c r="D104" s="13" t="inlineStr">
+      <c r="D104" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -14880,7 +15867,7 @@
           <t>Mark Dispatched and enter Lalamove tracking URL</t>
         </is>
       </c>
-      <c r="D105" s="12" t="inlineStr">
+      <c r="D105" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -14933,7 +15920,7 @@
           <t>Reflect status to customer; customer 'Order Received' finalizes as Delivered</t>
         </is>
       </c>
-      <c r="D106" s="15" t="inlineStr">
+      <c r="D106" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -14990,7 +15977,7 @@
           <t>Auto Dispatched -&gt; Delivered after 3 days</t>
         </is>
       </c>
-      <c r="D107" s="12" t="inlineStr">
+      <c r="D107" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -15043,7 +16030,7 @@
           <t>Optional internal delivery notes</t>
         </is>
       </c>
-      <c r="D108" s="14" t="inlineStr">
+      <c r="D108" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -15100,7 +16087,7 @@
           <t>Staff view customer and AI conversations</t>
         </is>
       </c>
-      <c r="D109" s="14" t="inlineStr">
+      <c r="D109" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -15157,7 +16144,7 @@
           <t>Staff respond to customers</t>
         </is>
       </c>
-      <c r="D110" s="14" t="inlineStr">
+      <c r="D110" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -15214,7 +16201,7 @@
           <t>Mark threads resolved</t>
         </is>
       </c>
-      <c r="D111" s="14" t="inlineStr">
+      <c r="D111" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -15271,7 +16258,7 @@
           <t>Export daily sales reports (from Order Processing)</t>
         </is>
       </c>
-      <c r="D112" s="14" t="inlineStr">
+      <c r="D112" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -15328,7 +16315,7 @@
           <t>Export monthly inventory + purchase reports (from Inventory)</t>
         </is>
       </c>
-      <c r="D113" s="14" t="inlineStr">
+      <c r="D113" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -15385,7 +16372,7 @@
           <t>Pull-out reports by date range</t>
         </is>
       </c>
-      <c r="D114" s="14" t="inlineStr">
+      <c r="D114" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -15442,7 +16429,7 @@
           <t>Wholesale exchange reports by period</t>
         </is>
       </c>
-      <c r="D115" s="14" t="inlineStr">
+      <c r="D115" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -15495,7 +16482,7 @@
           <t>All reports in PDF or Excel</t>
         </is>
       </c>
-      <c r="D116" s="13" t="inlineStr">
+      <c r="D116" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -15548,7 +16535,7 @@
           <t>View profiles: status, registration date, order history</t>
         </is>
       </c>
-      <c r="D117" s="13" t="inlineStr">
+      <c r="D117" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -15605,7 +16592,7 @@
           <t>Deactivate without deleting</t>
         </is>
       </c>
-      <c r="D118" s="12" t="inlineStr">
+      <c r="D118" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -15658,7 +16645,7 @@
           <t>BM creates, modifies, revokes staff accounts</t>
         </is>
       </c>
-      <c r="D119" s="13" t="inlineStr">
+      <c r="D119" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -15715,7 +16702,7 @@
           <t>BM assigns roles that set accessible modules</t>
         </is>
       </c>
-      <c r="D120" s="12" t="inlineStr">
+      <c r="D120" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -15768,7 +16755,7 @@
           <t>Technical Staff cannot access Staff Management or Price Management</t>
         </is>
       </c>
-      <c r="D121" s="13" t="inlineStr">
+      <c r="D121" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -15825,7 +16812,7 @@
           <t>Sales Staff: walk-in orders + catalog viewing only</t>
         </is>
       </c>
-      <c r="D122" s="15" t="inlineStr">
+      <c r="D122" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -15882,7 +16869,7 @@
           <t>Log price changes, voids, wholesale exchanges, write-offs with user, time, record, before/after, reason</t>
         </is>
       </c>
-      <c r="D123" s="13" t="inlineStr">
+      <c r="D123" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -15939,7 +16926,7 @@
           <t>Audit log accessible to BM and Technical Staff</t>
         </is>
       </c>
-      <c r="D124" s="12" t="inlineStr">
+      <c r="D124" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -15992,7 +16979,7 @@
           <t>Entries can't be edited or deleted</t>
         </is>
       </c>
-      <c r="D125" s="12" t="inlineStr">
+      <c r="D125" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -16045,7 +17032,7 @@
           <t>Consistent, organized layout</t>
         </is>
       </c>
-      <c r="D126" s="12" t="inlineStr">
+      <c r="D126" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -16098,7 +17085,7 @@
           <t>Meaningful feedback messages</t>
         </is>
       </c>
-      <c r="D127" s="12" t="inlineStr">
+      <c r="D127" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -16151,7 +17138,7 @@
           <t>Works on desktop, laptop, tablet, phone</t>
         </is>
       </c>
-      <c r="D128" s="16" t="inlineStr">
+      <c r="D128" s="17" t="inlineStr">
         <is>
           <t>Not verified</t>
         </is>
@@ -16208,7 +17195,7 @@
           <t>Standard operations load in reasonable time</t>
         </is>
       </c>
-      <c r="D129" s="16" t="inlineStr">
+      <c r="D129" s="17" t="inlineStr">
         <is>
           <t>Not verified</t>
         </is>
@@ -16265,7 +17252,7 @@
           <t>Inventory/order changes appear without manual refresh</t>
         </is>
       </c>
-      <c r="D130" s="15" t="inlineStr">
+      <c r="D130" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -16322,7 +17309,7 @@
           <t>Reports in reasonable time</t>
         </is>
       </c>
-      <c r="D131" s="17" t="inlineStr">
+      <c r="D131" s="18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16375,7 +17362,7 @@
           <t>Chrome, Firefox, Edge, Safari</t>
         </is>
       </c>
-      <c r="D132" s="16" t="inlineStr">
+      <c r="D132" s="17" t="inlineStr">
         <is>
           <t>Not verified</t>
         </is>
@@ -16432,7 +17419,7 @@
           <t>Integrates OpenAI, EmailJS, QR PH</t>
         </is>
       </c>
-      <c r="D133" s="13" t="inlineStr">
+      <c r="D133" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -16489,7 +17476,7 @@
           <t>Passwords securely hashed, never exposed</t>
         </is>
       </c>
-      <c r="D134" s="12" t="inlineStr">
+      <c r="D134" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -16542,7 +17529,7 @@
           <t>Encrypted connection</t>
         </is>
       </c>
-      <c r="D135" s="13" t="inlineStr">
+      <c r="D135" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -16599,7 +17586,7 @@
           <t>RBAC: customers can't reach admin; each staff role limited</t>
         </is>
       </c>
-      <c r="D136" s="13" t="inlineStr">
+      <c r="D136" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -16656,7 +17643,7 @@
           <t>No patient data sent to OpenAI</t>
         </is>
       </c>
-      <c r="D137" s="17" t="inlineStr">
+      <c r="D137" s="18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16713,7 +17700,7 @@
           <t>Hosted with uptime + recovery</t>
         </is>
       </c>
-      <c r="D138" s="14" t="inlineStr">
+      <c r="D138" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -16770,7 +17757,7 @@
           <t>Descriptive error messages</t>
         </is>
       </c>
-      <c r="D139" s="12" t="inlineStr">
+      <c r="D139" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -16823,7 +17810,7 @@
           <t>Supports growth without structural change</t>
         </is>
       </c>
-      <c r="D140" s="12" t="inlineStr">
+      <c r="D140" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -16876,7 +17863,7 @@
           <t>New branches addable later</t>
         </is>
       </c>
-      <c r="D141" s="12" t="inlineStr">
+      <c r="D141" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -16929,7 +17916,7 @@
           <t>Modular code with documentation</t>
         </is>
       </c>
-      <c r="D142" s="13" t="inlineStr">
+      <c r="D142" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -16986,7 +17973,7 @@
           <t>Admins manage products/users/inventory without a developer</t>
         </is>
       </c>
-      <c r="D143" s="12" t="inlineStr">
+      <c r="D143" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17039,7 +18026,7 @@
           <t>Deployable elsewhere without restructuring</t>
         </is>
       </c>
-      <c r="D144" s="12" t="inlineStr">
+      <c r="D144" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17092,7 +18079,7 @@
           <t>Data export in PDF and Excel</t>
         </is>
       </c>
-      <c r="D145" s="13" t="inlineStr">
+      <c r="D145" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -17149,7 +18136,7 @@
           <t>Usable with basic digital literacy</t>
         </is>
       </c>
-      <c r="D146" s="16" t="inlineStr">
+      <c r="D146" s="17" t="inlineStr">
         <is>
           <t>Not verified</t>
         </is>
@@ -17202,7 +18189,7 @@
           <t>Any modern browser, no install</t>
         </is>
       </c>
-      <c r="D147" s="12" t="inlineStr">
+      <c r="D147" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17255,7 +18242,7 @@
           <t>New features without rebuild</t>
         </is>
       </c>
-      <c r="D148" s="12" t="inlineStr">
+      <c r="D148" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17308,7 +18295,7 @@
           <t>Future courier/payment/SMS integration</t>
         </is>
       </c>
-      <c r="D149" s="12" t="inlineStr">
+      <c r="D149" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17361,7 +18348,7 @@
           <t>Data Privacy Act 2012</t>
         </is>
       </c>
-      <c r="D150" s="13" t="inlineStr">
+      <c r="D150" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -17418,7 +18405,7 @@
           <t>English throughout</t>
         </is>
       </c>
-      <c r="D151" s="12" t="inlineStr">
+      <c r="D151" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17471,7 +18458,7 @@
           <t>Peso with 2 decimals and commas</t>
         </is>
       </c>
-      <c r="D152" s="12" t="inlineStr">
+      <c r="D152" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17524,7 +18511,7 @@
           <t>Dates MM/DD/YYYY, 12-hour AM/PM</t>
         </is>
       </c>
-      <c r="D153" s="13" t="inlineStr">
+      <c r="D153" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -17581,7 +18568,7 @@
           <t>Clear, professional language</t>
         </is>
       </c>
-      <c r="D154" s="13" t="inlineStr">
+      <c r="D154" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -17701,7 +18688,7 @@
           <t>Guest, Sales Staff</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17733,7 +18720,7 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17765,7 +18752,7 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -17797,7 +18784,7 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17825,7 +18812,7 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -17857,7 +18844,7 @@
           <t>(no actor connected)</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -17889,7 +18876,7 @@
           <t>Sales Staff, Technical Staff</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17917,7 +18904,7 @@
           <t>Sales, Technical, Registered User</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -17949,7 +18936,7 @@
           <t>Sales, Technical, Registered User</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -17981,7 +18968,7 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18009,7 +18996,7 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18037,7 +19024,7 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18065,7 +19052,7 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18093,7 +19080,7 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18121,7 +19108,7 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -18153,7 +19140,7 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18181,7 +19168,7 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -18213,7 +19200,7 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18245,7 +19232,7 @@
           <t>Branch Manager</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -18277,7 +19264,7 @@
           <t>Branch Manager</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18305,7 +19292,7 @@
           <t>Branch Manager</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18333,7 +19320,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18361,7 +19348,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -18393,7 +19380,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18421,7 +19408,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -18453,7 +19440,7 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -18481,7 +19468,7 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18509,7 +19496,7 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18537,7 +19524,7 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -18565,7 +19552,7 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18593,7 +19580,7 @@
           <t>Staff, Registered User</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -18625,7 +19612,7 @@
           <t>Staff, Registered User</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18653,7 +19640,7 @@
           <t>Staff, Registered User</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18681,7 +19668,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -18713,7 +19700,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18741,7 +19728,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18769,7 +19756,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18797,7 +19784,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -18829,7 +19816,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18861,7 +19848,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18889,7 +19876,7 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18921,7 +19908,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -18949,7 +19936,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -18981,7 +19968,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19009,7 +19996,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -19041,7 +20028,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19069,7 +20056,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19101,7 +20088,7 @@
           <t>Sales Staff, Technical Staff</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19129,7 +20116,7 @@
           <t>Sales/Technical</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19161,7 +20148,7 @@
           <t>Sales/Technical</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -19193,7 +20180,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -19225,7 +20212,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19253,7 +20240,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19281,7 +20268,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19309,7 +20296,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D56" s="14" t="inlineStr">
+      <c r="D56" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -19337,7 +20324,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19369,7 +20356,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D58" s="18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19401,7 +20388,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D59" s="18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19433,7 +20420,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="D60" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -19465,7 +20452,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19497,7 +20484,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19525,7 +20512,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19557,7 +20544,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -19585,7 +20572,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -19613,7 +20600,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D66" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -19645,7 +20632,7 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19673,7 +20660,7 @@
           <t>Branch Manager</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -19705,7 +20692,7 @@
           <t>Branch Manager</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19737,7 +20724,7 @@
           <t>Branch Manager</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19769,7 +20756,7 @@
           <t>Branch Manager</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D71" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19867,7 +20854,7 @@
           <t>Same (js/auth.js:94)</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19900,7 +20887,7 @@
           <t>Same (js/auth.js:57)</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -19933,7 +20920,7 @@
           <t>Not built</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -19970,7 +20957,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20007,7 +20994,7 @@
           <t>reCAPTCHA check, rejecting attempts while locked, blocking deactivated accounts, sending unverified customers to email verification</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20044,7 +21031,7 @@
           <t>Terms modal opens when the checkbox is ticked (before submit); duplicate email is caught by Firebase at account creation; code sent after</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20081,7 +21068,7 @@
           <t>Retry or Resend link (js/verify-email.js)</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -20118,7 +21105,7 @@
           <t>Goes straight to the shop, already signed in</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20155,7 +21142,7 @@
           <t>Login account is created first with emailVerified:false; unverified customers are redirected to verification on login</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -20192,7 +21179,7 @@
           <t>Same, plus choosing which cart items to check out</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -20229,7 +21216,7 @@
           <t>Same (js/checkout.js)</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -20262,7 +21249,7 @@
           <t>RX detected when checkout opens; address section hidden; pick-up only</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20299,7 +21286,7 @@
           <t>Required on the payment page for RX orders</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20336,7 +21323,7 @@
           <t>Same ('placed' = Order Pending Verification)</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -20373,7 +21360,7 @@
           <t>Only an on-screen confirmation with the order number; no notification</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -20410,7 +21397,7 @@
           <t>Login required to check out, delivery schedule, store credit discount, live stock re-check before submitting</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20447,7 +21434,7 @@
           <t>Stock is deducted first; if stock ran out the order goes on an Out of Stock hold instead</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20484,7 +21471,7 @@
           <t>RX orders skip courier booking and go straight to Ready for Pick-up</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20521,7 +21508,7 @@
           <t>Not built (payment approval only)</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -20558,7 +21545,7 @@
           <t>Admin pastes the link and marks Dispatched in one step; customer can't see the link</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -20595,7 +21582,7 @@
           <t>Same (js/admin-online-orders.js:561; js/order-details.js)</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -20628,7 +21615,7 @@
           <t>Every resolution returns to staff (resubmission or Release Hold)</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20665,7 +21652,7 @@
           <t>Approved immediately; excess added to store credit</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20702,7 +21689,7 @@
           <t>Closed automatically after 7 days, with verified payment kept as credit</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20739,7 +21726,7 @@
           <t>Fully credit-covered orders (no screenshot), Release Hold by staff</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20776,7 +21763,7 @@
           <t>Same (js/admin-inventory.js:994)</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -20809,7 +21796,7 @@
           <t>Same, except receiving is not written to the audit log</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -20846,7 +21833,7 @@
           <t>Partial stock added, PO marked Discrepancy, acknowledgment required to close</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20883,7 +21870,7 @@
           <t>Both exist (manual Receive Stock, Excel/CSV upload)</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -20920,7 +21907,7 @@
           <t>Flagged automatically as Wholesale Only (only when Inventory opens) + alert; no pull-out action choice</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -20957,7 +21944,7 @@
           <t>Not built</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -20994,7 +21981,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21031,7 +22018,7 @@
           <t>Accounts searchable; create with LTO/permit upload (js/admin-wholesale-accounts.js:270)</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -21064,7 +22051,7 @@
           <t>Documents viewable; no expiry tracking</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -21101,7 +22088,7 @@
           <t>Not built</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -21138,7 +22125,7 @@
           <t>Near-expiry stock is used first automatically; price can be typed as 0 but there is no free-of-cost option</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -21175,7 +22162,7 @@
           <t>Confirm + FEFO deduction + audit entry; no sales invoice</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -21212,7 +22199,7 @@
           <t>Same, plus a review screen with Edit/Confirm, payment method and change</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
@@ -21249,7 +22236,7 @@
           <t>No RX check in POS</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -21286,7 +22273,7 @@
           <t>Receipt shown on screen only</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -21323,7 +22310,7 @@
           <t>Not built</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -21360,7 +22347,7 @@
           <t>Not built</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -21397,7 +22384,7 @@
           <t>Not built</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -21434,7 +22421,7 @@
           <t>Not built</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -21471,7 +22458,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E46" s="18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22852,357 +23839,423 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Client report</t>
+          <t>Change</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>Section / columns</t>
+          <t>Paper location</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>System data today</t>
+          <t>What gets removed / narrowed</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>How to avoid the letter</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>To-Do</t>
+          <t>Recommendation</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Daily Sales (PDF)</t>
+          <t>Promotions on the home page</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Header: store name, date range 12:00:01 AM - 11:59:59 PM</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>'promotions' dropped</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Build a simple promotions/announcements banner (same component as the store-closure banner)</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>Reports module</t>
+          <t>Build - no letter (S)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Daily Sales (PDF)</t>
+          <t>'Payment Rejected' order status</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Sales: Date, No. of Orders, Total, Discount/Deduction, Grand Total, Less VAT, VATable Sales, VAT 12%, VAT Exempt Sales</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>posSales, orders, wholesaleOrders totals</t>
+          <t>Status list replaced; 'Payment Rejected' no longer exists</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>No discounts; no VAT fields (sample day: all VAT-exempt)</t>
+          <t>Show invalid-payment holds to the customer as 'Payment Rejected - re-upload needed'</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Discount decision; VAT question to client</t>
+          <t>Build - no letter (S)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Daily Sales (PDF)</t>
+          <t>Per-account agreed wholesale pricing</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Pay-In, Pay-Out, TOTAL</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Agreed price per buyer replaced by one wholesale price per product</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Not recorded</t>
+          <t>Add an optional agreed price per buyer per product, used as the default on their orders</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Pay-in/pay-out decision</t>
+          <t>Build - no letter (M)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Daily Sales (PDF)</t>
+          <t>'On Hold - Overpayment'</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Retail Sales: Date, No. of Items, Total Amount</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6, 2.11</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>posSales + online orders</t>
+          <t>Overpayment hold type removed (system approves and credits instead)</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>OK once combined</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr"/>
+          <t>Ask the adviser whether this is a refinement (excess still kept as unapplied value, as REQ098 requires). Otherwise change the system to hold overpaid orders until staff apply the excess</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Ask adviser</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Daily Sales (PDF)</t>
+          <t>Real-time updates everywhere</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Wholesale Sales: Date, No. of Items, Total Amount</t>
+          <t>REQNF005 p.63</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>wholesaleOrders</t>
+          <t>Limited to the verification queue and customer order page</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr"/>
+          <t>Use live updates on all order and inventory screens</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Reconsider the decision - build (M), no letter</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Daily Sales (PDF)</t>
+          <t>Wholesale prices admin-only</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Payment Method: Bank Transfer, Cash, Credit, G-Cash, Terminal - orders + amount</t>
+          <t>REQ088 p.57</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>posSales.paymentMethod (cash/card/e-wallet only)</t>
+          <t>Moved to Limitations (prices are hidden on screen but readable in the database)</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>No Bank Transfer/Credit; wholesale has no payment method</t>
+          <t>Move costing/wholesale prices to a staff-only collection</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Payment method + terms item</t>
+          <t>Build if time (M); otherwise letter</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Daily Sales (PDF)</t>
+          <t>Push notifications</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Item Sold: Item, No. of Items, Total Amount, Discount (sorted by qty)</t>
+          <t>Theoretical Framework p.23</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>sale line items</t>
+          <t>'Instantaneous push notifications' reworded to in-app alerts</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>OK (no discount)</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr"/>
+          <t>Add browser notifications for staff alerts</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Ask adviser (framework wording, not a requirement)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Customer File (Excel, daily)</t>
+          <t>Chart.js inventory analytics</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Customer Name, Date+time, SI#, Batch No, Exp, Qty, Item, Sales Price, Total Amount, Terms of Payment; subtotal per customer</t>
+          <t>Technical Background p.35-37</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>sale line items</t>
+          <t>Inventory movement charts not provided</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>No batch/expiry per line, no SI#, no walk-in customer name, no terms</t>
+          <t>Add an inventory movement chart to the dashboard</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Batch per sale; SI#; walk-in name; payment terms</t>
+          <t>Build - no letter (S)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Monthly Inventory (Excel)</t>
+          <t>Price locking</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>One sheet per category (Generics, Medical Supplies, Grocery, Drugstore per pc, Branded): Product, POS stock, Physical count, Costing, Retail, Wholesale, Batch #, Expiry</t>
+          <t>Modules p.42</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>stockBatches + reconciliation counts + product prices</t>
+          <t>'Allows price locking' reworded</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Categories differ; needs reconciliation export by category</t>
+          <t>Add a lock/unlock toggle per product for the Branch Manager</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Categories item; Reports module</t>
+          <t>Build - no letter (S)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Monthly Return to POS (Excel)</t>
+          <t>OpenAI API</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Item, Batch, Expiry, Customer, DR#, Date Purchased, Date Returned, Qty, Amount, Total</t>
+          <t>9 places: pp.3, 4, 24, 26, 34, 35, 37-38, 63</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Replaced by a free provider (Gemini via Firebase AI Logic, if approved)</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Wholesale exchange/return not built; no DR#/SI# on the original sale</t>
+          <t>Keep OpenAI (paid, prepaid credit)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Wholesale exchange; SI#</t>
+          <t>Ask adviser - tool replacement, not a feature removal</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Monthly Supplier Purchases (Excel)</t>
+          <t>DataTable library</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Supplier Name, Order Date, Receipt #, Product, Brand, Packs, Batch #, Expiry, Qty, Price, Amount, Total; separate Drugstore and Grocery sheets</t>
+          <t>Technical Background p.35, 37</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>stockBatches (supplier, batch, expiry, qty, date)</t>
+          <t>Removed (custom tables used)</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>No receipt #, unit cost, pack on receiving</t>
+          <t>Use the DataTables library on the main tables</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Receiving fields item</t>
+          <t>Ask adviser - tool change</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Observations</t>
+          <t>Firebase Storage for images</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Their old POS shows negative stock (-1); several expiries are typed into product names (e.g. '4/28'); one batch cell can list several expiries</t>
+          <t>Technical Background p.35-36</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Replaced by Cloudinary</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Our system blocks negative stock and keeps one expiry per batch - good defense talking points; data needs cleaning before import</t>
+          <t>Move uploads to Firebase Storage (needs the paid Blaze plan)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Catalog import item</t>
+          <t>Ask adviser - tool replacement</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>EmailJS for password reset</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background p.36</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Replaced by Firebase Auth's own reset email</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Send reset links through EmailJS</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Ask adviser - tool replacement (minor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Who the system serves</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Scope p.6; Conceptual Framework p.25</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>'Wholesale clients' and 'main office' as users; wholesale buyers registering/ordering online</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>None - the original text is inaccurate (wholesale is staff-recorded per the client)</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Ask adviser - correction of an error</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
@@ -3972,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: build it with OpenAI via a Netlify Function (panel's recommended feature). Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
+          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -4899,22 +4899,22 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Objectives / evaluation (p.5-6, 21-24)</t>
+          <t>Removals (Letter) sheet</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
+          <t>Letter to the panel: OpenAI -&gt; Gemini (free), Firebase Storage -&gt; Cloudinary, DataTable -&gt; custom tables, password reset via Firebase Auth, overpayment approve-and-credit, corrections to scope/conceptual framework</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -4922,10 +4922,14 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>One letter covers all remaining removals; send before the paper edits.</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr"/>
@@ -4941,42 +4945,38 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>REQ121</t>
+          <t>Objectives / evaluation (p.5-6, 21-24)</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
+          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: trim to POS + catalog view; Walk-in history inside POS. Orders access was added on purpose on 2026-10-01.</t>
-        </is>
-      </c>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr"/>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr"/>
@@ -4997,12 +4997,12 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>REQNF005</t>
+          <t>REQ121</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Live updates without refresh on verification queue + customer order page</t>
+          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: live on verification queue + customer order page only; reword REQNF005 for the rest.</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DECIDED: trim to POS + catalog view; Walk-in history inside POS. Orders access was added on purpose on 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr"/>
@@ -5048,22 +5048,22 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>REQNF010, REQNF013</t>
+          <t>REQNF005</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
+          <t>Live updates without refresh on all order and inventory screens (staff + customer)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: Netlify (already set up).</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>DECIDED (revised): build everywhere to avoid a removal letter.</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr"/>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Discount/Deductions columns); Interview 2</t>
+          <t>REQNF010, REQNF013</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Discount / deduction per sale or line, with reason and audit entry</t>
+          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -5124,18 +5124,18 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Client confirmed: no discounts. Not in the paper; client gives boss-approved discounts today.</t>
+          <t>DECIDED: Netlify (already set up).</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Methodology p.30 ('actual client data'); Report Formats sheet</t>
+          <t>Report Formats sheet (Discount/Deductions columns); Interview 2</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Load the client's real March-end catalog (prices, batches, expiry) from their workbook via the existing upload templates</t>
+          <t>Discount / deduction per sale or line, with reason and audit entry</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -5175,18 +5175,18 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: yes, once the client sends the catalog. Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
+          <t>Client confirmed: no discounts. Not in the paper; client gives boss-approved discounts today.</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -5196,27 +5196,27 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>Methodology p.30 ('actual client data'); Report Formats sheet</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
+          <t>Load the client's real March-end catalog (prices, batches, expiry) from their workbook via the existing upload templates</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -5224,7 +5224,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: yes, once the client sends the catalog. Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
+        </is>
+      </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5233,7 +5237,7 @@
       <c r="J25" s="11" t="inlineStr"/>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5257,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
+          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -5295,12 +5299,12 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -5337,22 +5341,22 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
+          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -5365,11 +5369,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H28" s="11" t="inlineStr"/>
       <c r="I28" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>REQ002</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
+          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -5444,22 +5444,22 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
+          <t>REQ002</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Unrecognized-device OTP for customers and staff</t>
+          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -5467,7 +5467,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5491,17 +5495,17 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>REQ086, REQ089, REQ091, REQ092</t>
+          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
+          <t>Unrecognized-device OTP for customers and staff</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -5514,11 +5518,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
-        </is>
-      </c>
+      <c r="H31" s="11" t="inlineStr"/>
       <c r="I31" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5542,17 +5542,17 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>REQ090, REQ114, Fig 2.15</t>
+          <t>REQ086, REQ089, REQ091, REQ092</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
+          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -5565,7 +5565,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
+        </is>
+      </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5589,12 +5593,12 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>REQ067, C7</t>
+          <t>REQ090, REQ114, Fig 2.15</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
+          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
@@ -5636,12 +5640,12 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
+          <t>REQ067, C7</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
+          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -5651,7 +5655,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -5683,12 +5687,12 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>REQ084</t>
+          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>POS: RX Verified checkbox + optional notes</t>
+          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -5730,17 +5734,17 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>REQ061, C5</t>
+          <t>REQ084</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
+          <t>POS: RX Verified checkbox + optional notes</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -5777,17 +5781,17 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>REQNF025, REQNF029</t>
+          <t>REQ061, C5</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
+          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -5800,11 +5804,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H37" s="11" t="inlineStr"/>
       <c r="I37" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5828,22 +5828,22 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>REQ039, REQ042</t>
+          <t>REQNF025, REQNF029</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
+          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>EmailJS free tier: 200/month.</t>
+          <t>From the first review.</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>REQ122</t>
+          <t>REQ039, REQ042</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
+          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -5902,7 +5902,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>EmailJS free tier: 200/month.</t>
+        </is>
+      </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5926,22 +5930,22 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>REQ014</t>
+          <t>REQ122</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Save cart to the customer's account</t>
+          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -5973,17 +5977,17 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>REQNF003, REQNF007</t>
+          <t>REQ014</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Phone/tablet and cross-browser test pass</t>
+          <t>Save cart to the customer's account</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -6020,17 +6024,17 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Interviews 2, 4</t>
+          <t>REQNF003, REQNF007</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
+          <t>Phone/tablet and cross-browser test pass</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Not verified</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -6043,11 +6047,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
-        <is>
-          <t>Required column in the monthly purchases report.</t>
-        </is>
-      </c>
+      <c r="H42" s="11" t="inlineStr"/>
       <c r="I42" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6071,12 +6071,12 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Interview 4 walkthrough</t>
+          <t>Interviews 2, 4</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Supplier history: everything received from each supplier</t>
+          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Shown to the client during the prototype walkthrough.</t>
+          <t>Required column in the monthly purchases report.</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Methodology p.30; Interview 4</t>
+          <t>Interview 4 walkthrough</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>User manual + hands-on training + handover to the branch</t>
+          <t>Supplier history: everything received from each supplier</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
+          <t>Shown to the client during the prototype walkthrough.</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
+          <t>Methodology p.30; Interview 4</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
+          <t>User manual + hands-on training + handover to the branch</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Customer File groups every sale by customer name.</t>
+          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -6224,17 +6224,17 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Supplier sheets)</t>
+          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
+          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
+          <t>Customer File groups every sale by customer name.</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
@@ -6275,17 +6275,17 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
+          <t>Report Formats sheet (Supplier sheets)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies, Grocery</t>
+          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
+          <t>Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -6326,17 +6326,17 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Project Context (p.1)</t>
+          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies, Grocery</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -6349,7 +6349,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
+        </is>
+      </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6373,22 +6377,22 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.24)</t>
+          <t>REQ085, REQ087</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Optional agreed price per wholesale buyer per product, used as default on their orders</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -6396,10 +6400,14 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr"/>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Keeps per-account pricing (no letter).</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr"/>
@@ -6420,22 +6428,22 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output) (p.27)</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>Cut database reads: stop loading whole collections on every page (Firestore free-plan daily read cap ~50k)</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
@@ -6443,7 +6451,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Needed before real use with the client's ~1,000-product catalog.</t>
+        </is>
+      </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6462,17 +6474,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles (p.45-46)</t>
+          <t>Project Context (p.1)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
@@ -6493,7 +6505,7 @@
       <c r="H51" s="11" t="inlineStr"/>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr"/>
@@ -6509,22 +6521,22 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>REQ007 / Technical Background p.35-36</t>
+          <t>Theoretical Framework (p.24)</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -6537,14 +6549,10 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H52" s="11" t="inlineStr"/>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr"/>
@@ -6560,22 +6568,22 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>REQ008 p.47; Modules p.38</t>
+          <t>Conceptual Framework (Output) (p.27)</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -6588,14 +6596,10 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I53" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H53" s="11" t="inlineStr"/>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr"/>
@@ -6611,22 +6615,22 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>REQ031 p.50</t>
+          <t>Modules: Staff roles (p.45-46)</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -6639,14 +6643,10 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H54" s="11" t="inlineStr"/>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr"/>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>REQ073 p.55</t>
+          <t>REQ007 / Technical Background p.35-36</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -6746,9 +6746,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr"/>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087 p.57; Modules p.44</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Default wholesale price per product, adjustable per order (C9).</t>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+          <t>REQ073 p.55</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -6848,9 +6848,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I58" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr"/>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>REQ121 p.61</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -6950,9 +6950,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I60" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr"/>
@@ -6973,12 +6973,12 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 text p.67</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
@@ -7001,9 +7001,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr"/>
@@ -7024,12 +7024,12 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 diagram</t>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.5 text p.72</t>
+          <t>REQ121 p.61</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 / 2.7 diagrams</t>
+          <t>Fig 2.2 text p.67</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.8 diagram + text p.76-77</t>
+          <t>Fig 2.2 diagram</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -7228,12 +7228,12 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 diagram + text p.78-79</t>
+          <t>Fig 2.5 text p.72</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.10 diagram</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 diagram + text p.82-83</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -7381,17 +7381,17 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover (i)</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -7404,7 +7404,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H69" s="11" t="inlineStr"/>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -7428,22 +7432,22 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -7451,7 +7455,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H70" s="11" t="inlineStr"/>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -7475,17 +7483,17 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>Fig 2.11 diagram + text p.82-83</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -7498,7 +7506,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H71" s="11" t="inlineStr"/>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -7522,12 +7534,12 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input) (p.25)</t>
+          <t>Title page / cover (i)</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -7546,9 +7558,9 @@
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr"/>
-      <c r="I72" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr"/>
@@ -7569,12 +7581,12 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.30-35)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
@@ -7584,7 +7596,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -7616,12 +7628,12 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -7663,12 +7675,12 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Conceptual Framework (Input) (p.25)</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
@@ -7687,9 +7699,9 @@
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr"/>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr"/>
@@ -7705,48 +7717,44 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>REQ088</t>
+          <t>Methodology: sprint plan (p.30-35)</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Hide costing/wholesale prices from public reads</t>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H76" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: leave as is; state in Limitations.</t>
-        </is>
-      </c>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES - letter (REQ088 to Limitations)</t>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr"/>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr"/>
       <c r="K76" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7756,48 +7764,44 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Interview 1</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H77" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr"/>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr"/>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7807,48 +7811,44 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (CREDIT terms)</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Credit sales follow-up (who owes what, mark as paid)</t>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H78" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="inlineStr"/>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr"/>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7863,22 +7863,22 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (daily Sales section)</t>
+          <t>REQ088</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
+          <t>Hide costing/wholesale prices from public reads</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -7888,18 +7888,18 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
+          <t>DECIDED (revised): build it to avoid a removal letter.</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr"/>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7909,27 +7909,27 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Interview 1</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
@@ -7937,16 +7937,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H80" s="11" t="inlineStr"/>
+      <c r="H80" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
+        </is>
+      </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr"/>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -7961,12 +7965,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>REQ013, REQ068</t>
+          <t>Report Formats sheet (CREDIT terms)</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Dosage/usage notes field on products</t>
+          <t>Credit sales follow-up (who owes what, mark as paid)</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -7976,7 +7980,7 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -7984,16 +7988,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H81" s="11" t="inlineStr"/>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
+        </is>
+      </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr"/>
       <c r="K81" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8008,17 +8016,17 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>REQ049</t>
+          <t>Report Formats sheet (daily Sales section)</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Supplier column in the inventory batch table</t>
+          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
@@ -8031,16 +8039,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H82" s="11" t="inlineStr"/>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
+        </is>
+      </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr"/>
       <c r="K82" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8050,22 +8062,22 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>REQ103, REQ107</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -8078,11 +8090,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H83" s="11" t="inlineStr">
-        <is>
-          <t>Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
-        </is>
-      </c>
+      <c r="H83" s="11" t="inlineStr"/>
       <c r="I83" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8106,17 +8114,17 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>REQ116</t>
+          <t>REQ013, REQ068</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Customer Accounts: list of the customer's orders</t>
+          <t>Dosage/usage notes field on products</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -8153,17 +8161,17 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>REQ049</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
+          <t>Supplier column in the inventory batch table</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -8176,11 +8184,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H85" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H85" s="11" t="inlineStr"/>
       <c r="I85" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8204,17 +8208,17 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>REQ070</t>
+          <t>REQ103, REQ107</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Category rename: replace native prompt() with app dialog</t>
+          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -8229,7 +8233,7 @@
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -8255,12 +8259,12 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>REQ033, REQ093</t>
+          <t>REQ116</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
+          <t>Customer Accounts: list of the customer's orders</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
@@ -8278,11 +8282,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H87" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H87" s="11" t="inlineStr"/>
       <c r="I87" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8306,17 +8306,17 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>REQ099</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>'Payment not received' as its own hold type</t>
+          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
@@ -8329,7 +8329,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H88" s="11" t="inlineStr"/>
+      <c r="H88" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8353,17 +8357,17 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>REQ026</t>
+          <t>REQ070</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Checkout pick-up notice mentions bringing the original prescription</t>
+          <t>Category rename: replace native prompt() with app dialog</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -8376,7 +8380,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H89" s="11" t="inlineStr"/>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8400,12 +8408,12 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>REQ009</t>
+          <t>REQ033, REQ093</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Show quantity in stock on catalog cards</t>
+          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -8423,7 +8431,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H90" s="11" t="inlineStr"/>
+      <c r="H90" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8447,17 +8459,17 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>REQ040</t>
+          <t>REQ099</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Profile picture in Account Settings</t>
+          <t>'Payment not received' as its own hold type</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -8494,12 +8506,12 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>REQNF028</t>
+          <t>REQ026</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
+          <t>Checkout pick-up notice mentions bringing the original prescription</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -8541,17 +8553,17 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>REQ047</t>
+          <t>REQ009</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
+          <t>Show quantity in stock on catalog cards</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -8564,11 +8576,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H93" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H93" s="11" t="inlineStr"/>
       <c r="I93" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8592,12 +8600,12 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>REQNF017</t>
+          <t>REQ040</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>README with setup steps; fix the error message that points to it</t>
+          <t>Profile picture in Account Settings</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -8615,11 +8623,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H94" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H94" s="11" t="inlineStr"/>
       <c r="I94" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8643,17 +8647,17 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>REQ001</t>
+          <t>REQNF028</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Normalize phone number at registration</t>
+          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -8666,11 +8670,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H95" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H95" s="11" t="inlineStr"/>
       <c r="I95" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8694,17 +8694,17 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>REQ008; Interview 1</t>
+          <t>REQ047</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Store announcement banner (e.g. closure days)</t>
+          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -8717,7 +8717,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H96" s="11" t="inlineStr"/>
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8741,12 +8745,12 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>REQ039, Fig 2.10, C16</t>
+          <t>REQNF017</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+          <t>README with setup steps; fix the error message that points to it</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
@@ -8764,7 +8768,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H97" s="11" t="inlineStr"/>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8788,17 +8796,17 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>System roles (-)</t>
+          <t>REQ001</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+          <t>Normalize phone number at registration</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -8811,7 +8819,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H98" s="11" t="inlineStr"/>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>From the first review.</t>
+        </is>
+      </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8830,22 +8842,22 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Whole paper + system (-)</t>
+          <t>REQ008; Interview 1</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -8861,7 +8873,7 @@
       <c r="H99" s="11" t="inlineStr"/>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr"/>
@@ -8877,22 +8889,22 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>REQ031</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -8907,12 +8919,12 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Keeps the paper's status name (no letter).</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr"/>
@@ -8928,22 +8940,22 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>Technical Background p.35-37</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -8958,12 +8970,12 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I101" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>Keeps the Chart.js claim (no letter).</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr"/>
@@ -8979,22 +8991,22 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Scope p.6; Product Browsing REQ009</t>
+          <t>Modules p.42</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
+          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -9009,12 +9021,12 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Keeps 'price locking' (no letter).</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr"/>
@@ -9030,22 +9042,22 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Scope and Limitations p.7</t>
+          <t>Theoretical Framework p.23</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -9060,12 +9072,12 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Keeps the 'push notifications' claim (no letter).</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr"/>
@@ -9081,22 +9093,22 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Decision-dependent</t>
+          <t>REQ039, Fig 2.10, C16</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -9109,14 +9121,10 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H104" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: build it with OpenAI via a Netlify Function (panel's recommended feature). See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H104" s="11" t="inlineStr"/>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr"/>
@@ -9132,17 +9140,17 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>System roles (-)</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
@@ -9163,7 +9171,7 @@
       <c r="H105" s="11" t="inlineStr"/>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J105" s="11" t="inlineStr"/>
@@ -9179,17 +9187,17 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Scope (p.6)</t>
+          <t>Whole paper + system (-)</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
@@ -9208,9 +9216,9 @@
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr"/>
-      <c r="I106" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J106" s="11" t="inlineStr"/>
@@ -9231,17 +9239,17 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.22-23)</t>
+          <t>Modules FEFO p.41</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>Add the 2-month Bad Order step (C7).</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -9254,10 +9262,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H107" s="11" t="inlineStr"/>
-      <c r="I107" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J107" s="11" t="inlineStr"/>
@@ -9278,17 +9290,17 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.32)</t>
+          <t>Technical Background p.35-37; Budget p.99</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -9301,10 +9313,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H108" s="11" t="inlineStr"/>
-      <c r="I108" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I108" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J108" s="11" t="inlineStr"/>
@@ -9325,17 +9341,17 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Scope p.6; Product Browsing REQ009</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -9348,10 +9364,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H109" s="11" t="inlineStr"/>
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J109" s="11" t="inlineStr"/>
@@ -9372,17 +9392,17 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Scope and Limitations p.7</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
@@ -9395,10 +9415,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H110" s="11" t="inlineStr"/>
-      <c r="I110" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J110" s="11" t="inlineStr"/>
@@ -9419,17 +9443,17 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Decision-dependent</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
@@ -9442,10 +9466,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H111" s="11" t="inlineStr"/>
-      <c r="I111" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr"/>
@@ -9466,12 +9494,12 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
@@ -9490,9 +9518,9 @@
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr"/>
-      <c r="I112" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J112" s="11" t="inlineStr"/>
@@ -9513,12 +9541,12 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.36-38)</t>
+          <t>Scope (p.6)</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
@@ -9537,9 +9565,9 @@
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr"/>
-      <c r="I113" s="11" t="inlineStr">
-        <is>
-          <t>Adds</t>
+      <c r="I113" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J113" s="11" t="inlineStr"/>
@@ -9560,12 +9588,12 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.38)</t>
+          <t>Theoretical Framework (p.22-23)</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
@@ -9584,9 +9612,9 @@
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr"/>
-      <c r="I114" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I114" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J114" s="11" t="inlineStr"/>
@@ -9607,12 +9635,12 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Modules: Price Management (p.42)</t>
+          <t>Methodology: sprint plan (p.32)</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
@@ -9631,9 +9659,9 @@
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr"/>
-      <c r="I115" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr"/>
@@ -9654,12 +9682,12 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
@@ -9701,12 +9729,12 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.97-98)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
@@ -9725,9 +9753,9 @@
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr"/>
-      <c r="I117" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I117" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J117" s="11" t="inlineStr"/>
@@ -9748,12 +9776,12 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
@@ -9772,9 +9800,9 @@
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr"/>
-      <c r="I118" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J118" s="11" t="inlineStr"/>
@@ -9795,12 +9823,12 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
@@ -9819,9 +9847,9 @@
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr"/>
-      <c r="I119" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J119" s="11" t="inlineStr"/>
@@ -9842,12 +9870,12 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>References (p.100)</t>
+          <t>Technical Background: Software (p.36-38)</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
@@ -9868,7 +9896,7 @@
       <c r="H120" s="11" t="inlineStr"/>
       <c r="I120" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr"/>
@@ -9889,12 +9917,12 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>References (p.10 / refs)</t>
+          <t>Technical Background: Software (p.38)</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
@@ -9936,12 +9964,12 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>References (p.17 / refs)</t>
+          <t>Modules: Price Management (p.42)</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -9960,9 +9988,9 @@
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr"/>
-      <c r="I122" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr"/>
@@ -9983,12 +10011,12 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Appendices (p.124)</t>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
@@ -10030,12 +10058,12 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+          <t>Calendar of Activities (p.97-98)</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Regenerate page numbers after all edits.</t>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
@@ -10066,18 +10094,347 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="11" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr"/>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="inlineStr"/>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr"/>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J126" s="11" t="inlineStr"/>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>References (p.100)</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr"/>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="inlineStr"/>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>References (p.10 / refs)</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr"/>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="inlineStr"/>
+      <c r="K128" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>References (p.17 / refs)</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr"/>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="inlineStr"/>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>Appendices (p.124)</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr"/>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J130" s="11" t="inlineStr"/>
+      <c r="K130" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr"/>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J131" s="11" t="inlineStr"/>
+      <c r="K131" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K124"/>
-  <conditionalFormatting sqref="K2:K124">
+  <autoFilter ref="A1:K131"/>
+  <conditionalFormatting sqref="K2:K131">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23243,7 +23600,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: OpenAI through a Netlify Function so the key stays secret. Budget: add OpenAI usage.</t>
+          <t>DECIDED: Gemini via Firebase AI Logic (free tier, no server needed); Groq as fallback. In the panel letter.</t>
         </is>
       </c>
     </row>
@@ -23899,7 +24256,7 @@
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>Build - no letter (S)</t>
+          <t>Building - no letter (S)</t>
         </is>
       </c>
     </row>
@@ -23926,7 +24283,7 @@
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Build - no letter (S)</t>
+          <t>Building - no letter (S)</t>
         </is>
       </c>
     </row>
@@ -23953,7 +24310,7 @@
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Build - no letter (M)</t>
+          <t>Building - no letter (M)</t>
         </is>
       </c>
     </row>
@@ -23980,7 +24337,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Ask adviser</t>
+          <t>In letter (as a refinement the client approved)</t>
         </is>
       </c>
     </row>
@@ -24007,7 +24364,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Reconsider the decision - build (M), no letter</t>
+          <t>Building - no letter (M)</t>
         </is>
       </c>
     </row>
@@ -24034,7 +24391,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Build if time (M); otherwise letter</t>
+          <t>Building - no letter (M)</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24418,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Ask adviser (framework wording, not a requirement)</t>
+          <t>Building - no letter (S)</t>
         </is>
       </c>
     </row>
@@ -24088,7 +24445,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Build - no letter (S)</t>
+          <t>Building - no letter (S)</t>
         </is>
       </c>
     </row>
@@ -24115,7 +24472,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Build - no letter (S)</t>
+          <t>Building - no letter (S)</t>
         </is>
       </c>
     </row>
@@ -24142,7 +24499,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Ask adviser - tool replacement, not a feature removal</t>
+          <t>In letter (same letter as the other tool swaps)</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24526,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Ask adviser - tool change</t>
+          <t>In letter</t>
         </is>
       </c>
     </row>
@@ -24196,7 +24553,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Ask adviser - tool replacement</t>
+          <t>In letter</t>
         </is>
       </c>
     </row>
@@ -24223,7 +24580,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Ask adviser - tool replacement (minor)</t>
+          <t>In letter</t>
         </is>
       </c>
     </row>
@@ -24250,7 +24607,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Ask adviser - correction of an error</t>
+          <t>In letter (correction)</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Title feature.</t>
+          <t>DONE e1e200b. Title feature.</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
@@ -4237,7 +4237,7 @@
       <c r="J5" s="11" t="inlineStr"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Client is not BIR-connected by choice and issues BIR/VAT receipts manually on request.</t>
+          <t>DONE e1e200b. Client is not BIR-connected by choice and issues BIR/VAT receipts manually on request.</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -4531,7 +4531,7 @@
       <c r="J11" s="11" t="inlineStr"/>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Every client report lists batch + expiry per sold line; today FEFO deducts the right batch but the sale doesn't remember which. Blocks the Reports module.</t>
+          <t>DONE e1e200b. Every client report lists batch + expiry per sold line; today FEFO deducts the right batch but the sale doesn't remember which. Blocks the Reports module.</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -4633,7 +4633,7 @@
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Replaces the separate 'receipt numbers' item; voids reference it.</t>
+          <t>DONE e1e200b. Replaces the separate 'receipt numbers' item; voids reference it.</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -4684,7 +4684,7 @@
       <c r="J14" s="11" t="inlineStr"/>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Credit was ₱57,534 of ₱81,181 on the sample day.</t>
+          <t>DONE e1e200b. Credit was ₱57,534 of ₱81,181 on the sample day.</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -4735,7 +4735,7 @@
       <c r="J15" s="11" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE e1e200b (system part; REQ098 paper wording still to do). From the first review.</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -4837,7 +4837,7 @@
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>Customer File groups every sale by customer name.</t>
+          <t>DONE e1e200b. Customer File groups every sale by customer name.</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
@@ -6260,7 +6260,7 @@
       <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
+          <t>DONE e1e200b: unit cost + receipt/DR no. added; pack size stays in the product name as the branch does today. Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -6311,7 +6311,7 @@
       <c r="J47" s="11" t="inlineStr"/>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
+          <t>DONE e1e200b: also storefront links/filters now follow Manage Categories. Existing Firebase projects keep their current categories - add the client's in Manage Categories.. Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -6362,7 +6362,7 @@
       <c r="J48" s="11" t="inlineStr"/>
       <c r="K48" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -8382,7 +8382,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -8393,7 +8393,7 @@
       <c r="J89" s="11" t="inlineStr"/>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -4373,7 +4373,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>DONE customer order page shows a 'Track with Lalamove' card once dispatched.</t>
+        </is>
+      </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -4382,7 +4386,7 @@
       <c r="J8" s="11" t="inlineStr"/>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4475,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>DONE header search on every shop page -&gt; catalog keyword search (name, generic, brand, description); price range + availability filters.</t>
+        </is>
+      </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -4480,7 +4488,7 @@
       <c r="J10" s="11" t="inlineStr"/>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -3568,7 +3568,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Get from the client: the QR Ph image and the sales invoice format (sample reports received). Ask them: are all sales VAT-exempt (sample shows VATable 0.00), is pay-in/pay-out used, who tracks credit collections, which categories to use, may we load the real catalog for the demo?</t>
+          <t>Get from the client: the QR Ph image, the sales invoice format, and the store details for the footer (hotline, email, hours, address, FDA LTO No. - fill js/store-info.js); have them review the Terms/Privacy text. Ask them: are all sales VAT-exempt (sample shows VATable 0.00), is pay-in/pay-out used, who tracks credit collections, which categories to use, may we load the real catalog for the demo?</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Get from the client: the QR Ph image and the sales invoice format (sample reports received). Ask them: are all sales VAT-exempt (sample shows VATable 0.00), is pay-in/pay-out used, who tracks credit collections, which categories to use, may we load the real catalog for the demo?</t>
+          <t>Get from the client: the QR Ph image, the sales invoice format, and the store details for the footer (hotline, email, hours, address, FDA LTO No. - fill js/store-info.js); have them review the Terms/Privacy text. Ask them: are all sales VAT-exempt (sample shows VATable 0.00), is pay-in/pay-out used, who tracks credit collections, which categories to use, may we load the real catalog for the demo?</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Panel may read the Terms during the demo.</t>
+          <t>DONE js/legal-content.js used by the sign-up pop-up and new legal.html; written to the client's policies + Data Privacy Act. CLIENT MUST REVIEW before go-live. Panel may read the Terms during the demo.</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -4590,7 +4590,7 @@
       <c r="J12" s="11" t="inlineStr"/>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE footer rebuilt from js/store-info.js (real About text, links to legal.html; contact/LTO lines hidden until the client confirms them); chat links hidden until chat is built; payment page Terms link fixed. From the first review.</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -5872,7 +5872,7 @@
       <c r="J38" s="11" t="inlineStr"/>
       <c r="K38" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -4883,7 +4883,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>DONE BM-only prices in the form, batch import and quick-add (others' products saved Inactive + 'Price pending'); reason required and logged; enforced in firestore.rules - PUBLISH THE RULES in the Firebase console.</t>
+        </is>
+      </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -4892,7 +4896,7 @@
       <c r="J18" s="11" t="inlineStr"/>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9033,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Keeps 'price locking' (no letter).</t>
+          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -9040,7 +9044,7 @@
       <c r="J102" s="11" t="inlineStr"/>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10838,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Terms rewritten to the branch's policies (client to review). (was: -)</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -11046,9 +11050,9 @@
           <t>Filter by category, price range, stock status</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -11058,12 +11062,12 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Category filter and price sort only; no price-range or stock-status filter.</t>
+          <t>Fixed: price range + availability filters. (was: Category filter and price sort only; no price-range or stock-status filter.)</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -11103,9 +11107,9 @@
           <t>Keyword / product-name search</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -11115,12 +11119,12 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Header search box is not wired to anything on any page.</t>
+          <t>Fixed: header search works on every page. (was: Header search box is not wired to anything on any page.)</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -12366,9 +12370,9 @@
           <t>Customer monitors delivery progress</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -12378,12 +12382,12 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>Status timeline shows, but the Lalamove tracking link staff paste is never shown to the customer.</t>
+          <t>Fixed: customer sees the Lalamove tracking link. (was: Status timeline shows, but the Lalamove tracking link staff paste is never shown to the customer.)</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -14118,9 +14122,9 @@
           <t>Flag batches within 6 months; remove from sellable; wholesale free-of-cost only</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
@@ -14130,12 +14134,12 @@
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>The flag only runs when someone opens the Inventory page. Until then, near-expiry batches stay sellable online and at the POS. Free-of-cost distribution is not a recorded transaction type (see REQ091).</t>
+          <t>Fixed: retail stock excludes near-expiry batches by date on every load and sale; expired stock never sold. (was: The flag only runs when someone opens the Inventory page. Until then, near-expiry batches stay sellable online and at the POS. Free-of-cost distribution is not a recorded transaction type (see REQ091).)</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
@@ -14342,9 +14346,9 @@
           <t>Add, rename, remove categories</t>
         </is>
       </c>
-      <c r="D71" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
@@ -14354,12 +14358,12 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>Rename uses the browser's native prompt(), the only native dialog left.</t>
+          <t>Fixed: rename uses the app dialog; delete can move products. (was: Rename uses the browser's native prompt(), the only native dialog left.)</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -14399,9 +14403,9 @@
           <t>Price changes restricted to Branch Manager</t>
         </is>
       </c>
-      <c r="D72" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -14411,12 +14415,12 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>Only editing an existing product is locked. Any staff (incl. Sales Staff) can set prices when creating or batch-importing a product, and the database rules let any staff write prices.</t>
+          <t>Fixed: BM-only prices everywhere, enforced in database rules (publish rules). (was: Only editing an existing product is locked. Any staff (incl. Sales Staff) can set prices when creating or batch-importing a product, and the database rules let any staff write prices.)</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
@@ -14468,7 +14472,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Confirm step now also asks for a reason. (was: -)</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -14509,9 +14513,9 @@
           <t>Audit log: previous price, new price, timestamp</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
-        <is>
-          <t>Matches</t>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -14521,7 +14525,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>Matches the paper, but the client asked for a reason with each change (Interview 2) and none is captured.</t>
+          <t>System now logs the reason too; paper REQ073 wording should add 'reason'. (was: Matches the paper, but the client asked for a reason with each change (Interview 2) and none is captured.)</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr">
@@ -15580,7 +15584,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>Walk-in and online receipts exist; no wholesale sales invoice. Receipts show no batch numbers or expiry dates, which the Project Context (p.1) names as the old POS's main gap.</t>
+          <t>Walk-in/online receipts now carry SI No.; sales record batch + expiry per line; wholesale sales invoice still missing. (was: Walk-in and online receipts exist; no wholesale sales invoice. Receipts show no batch numbers or expiry dates, which the Project Context (p.1) names as the old POS's main gap.)</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -16118,9 +16122,9 @@
           <t>Notify customer on verification</t>
         </is>
       </c>
-      <c r="D103" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
@@ -16130,12 +16134,12 @@
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>Works for normal approvals; missing for overpayment approvals (see REQ098).</t>
+          <t>Fixed: overpayment approval now notifies the customer. (was: Works for normal approvals; missing for overpayment approvals (see REQ098).)</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
@@ -17120,9 +17124,9 @@
           <t>Technical Staff cannot access Staff Management or Price Management</t>
         </is>
       </c>
-      <c r="D121" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D121" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
@@ -17132,12 +17136,12 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>Staff Management is blocked. Price: see REQ071 (Technical Staff can set prices on new products).</t>
+          <t>Fixed with REQ071. (was: Staff Management is blocked. Price: see REQ071 (Technical Staff can set prices on new products).)</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
@@ -18713,9 +18717,9 @@
           <t>Data Privacy Act 2012</t>
         </is>
       </c>
-      <c r="D150" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D150" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
@@ -18725,12 +18729,12 @@
       </c>
       <c r="F150" s="11" t="inlineStr">
         <is>
-          <t>Terms/Privacy shown at registration, but footer Privacy Policy and Terms links go nowhere.</t>
+          <t>Privacy Policy rewritten for the Data Privacy Act and linked from every footer (client to review). (was: Terms/Privacy shown at registration, but footer Privacy Policy and Terms links go nowhere.)</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H150" s="11" t="inlineStr">
@@ -18933,9 +18937,9 @@
           <t>Clear, professional language</t>
         </is>
       </c>
-      <c r="D154" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D154" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
@@ -18945,12 +18949,12 @@
       </c>
       <c r="F154" s="11" t="inlineStr">
         <is>
-          <t>Footer says 'Amson about description sample text'.</t>
+          <t>Filler text removed from the footer. (was: Footer says 'Amson about description sample text'.)</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -4262,7 +4262,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Client's one remaining ask (Interview 4). Build to the 4 client samples (see Report Formats sheet); Excel output must paste cleanly into the main office's own sheets (Interviews 1, 2, 4); daily sales should total by payment method to match the daily cash remittance (Interview 2).</t>
+          <t>PARTIAL aece0e7: all 6 Export buttons now produce real PDF/Excel tables of what's on screen; the client's 4 report formats are still to build. Client's one remaining ask (Interview 4). Build to the 4 client samples (see Report Formats sheet); Excel output must paste cleanly into the main office's own sheets (Interviews 1, 2, 4); daily sales should total by payment method to match the daily cash remittance (Interview 2).</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
+          <t>DONE 57f4d80: BM/Technical void completed sales from POS Today's Sales or Walk-in Orders: reason, SI No., stock restored to the same batches, exchange note + price difference, audit entry. Still open: second-person approval (client rule) and exchange as a real stock movement. Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -4794,7 +4794,7 @@
       <c r="J16" s="11" t="inlineStr"/>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: trim to POS + catalog view; Walk-in history inside POS. Orders access was added on purpose on 2026-10-01.</t>
+          <t>DONE 57f4d80: POS (with Today's Sales) + read-only catalog; lands on POS after login. Orders access was added on purpose on 2026-10-01.</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
@@ -5045,7 +5045,7 @@
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout; 'not an official receipt' line.</t>
+        </is>
+      </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5731,7 +5735,7 @@
       <c r="J35" s="11" t="inlineStr"/>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5773,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>DONE 57f4d80: checkbox + notes, required for RX items, saved on the sale.</t>
+        </is>
+      </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5778,7 +5786,7 @@
       <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -15063,9 +15071,9 @@
           <t>Void with reason, restore stock, audit log, record exchange + price difference</t>
         </is>
       </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -15075,7 +15083,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>No void function at all.</t>
+          <t>57f4d80: void for completed walk-in sales by BM/Technical (Admin too): reason, original SI No., stock back to the exact batches, optional exchange note + price difference, audit entry. Not yet: second-person approval; exchange item is a note, not a stock movement. (was: No void function at all.)</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -15120,9 +15128,9 @@
           <t>RX Verified checkbox + optional notes, no upload</t>
         </is>
       </c>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
@@ -15132,12 +15140,12 @@
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>Not in POS.</t>
+          <t>57f4d80: RX Verified checkbox + optional notes in POS, required when the cart has RX items. (was: Not in POS.)</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -16627,9 +16635,9 @@
           <t>Export daily sales reports (from Order Processing)</t>
         </is>
       </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
@@ -16639,7 +16647,7 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>Online Orders Export downloads a blank PDF. Dashboard Sales Analytics export works but is not the daily sales report the client described (per customer, items with batch + expiry).</t>
+          <t>aece0e7: Online Orders Export now gives real PDF/Excel of the listed orders. Client's daily sales format still to build. (was: Online Orders Export downloads a blank PDF. Dashboard Sales Analytics export works but is not the daily sales report the client described (per customer, items with batch + expiry).)</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
@@ -16684,9 +16692,9 @@
           <t>Export monthly inventory + purchase reports (from Inventory)</t>
         </is>
       </c>
-      <c r="D113" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
@@ -16696,7 +16704,7 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>Inventory Export downloads a blank PDF.</t>
+          <t>aece0e7: Inventory Export now gives real PDF/Excel by batch (expiry, supplier, receipt/DR no., unit cost, date received). Client's monthly format still to build. (was: Inventory Export downloads a blank PDF.)</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
@@ -16863,7 +16871,7 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>Only Sales Analytics exports (PDF + Excel). Five other Export buttons give blank PDFs (Dashboard, Inventory, Online Orders, Suppliers, Audit Log).</t>
+          <t>aece0e7: all 6 Export buttons now give real PDF or Excel. Client report formats still to build. (was: Only Sales Analytics exports (PDF + Excel). Five other Export buttons give blank PDFs (Dashboard, Inventory, Online Orders, Suppliers, Audit Log).)</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr">
@@ -17181,9 +17189,9 @@
           <t>Sales Staff: walk-in orders + catalog viewing only</t>
         </is>
       </c>
-      <c r="D122" s="16" t="inlineStr">
-        <is>
-          <t>Deviates</t>
+      <c r="D122" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -17193,12 +17201,12 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Sales Staff can also open Dashboard, Orders, Products (with editing), and Notifications. Orders access was added deliberately on 2026-10-01 for the Walk-in Orders tab.</t>
+          <t>57f4d80: Sales Staff limited to POS (with Today's Sales) + read-only catalog. (was: Sales Staff can also open Dashboard, Orders, Products (with editing), and Notifications. Orders access was added deliberately on 2026-10-01 for the Walk-in Orders tab.)</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
@@ -18460,7 +18468,7 @@
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>Only Sales Analytics exports.</t>
+          <t>aece0e7: every Export button offers PDF or Excel. (was: Only Sales Analytics exports.)</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr">
@@ -19477,9 +19485,9 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -19489,7 +19497,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Five blank-PDF exports.</t>
+          <t>aece0e7: exports are real PDF/Excel; client report formats still to build.</t>
         </is>
       </c>
     </row>
@@ -20517,9 +20525,9 @@
           <t>Sales/Technical</t>
         </is>
       </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
@@ -20529,7 +20537,7 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>No print button / thermal format.</t>
+          <t>57f4d80: Print button with 58mm receipt layout.</t>
         </is>
       </c>
     </row>
@@ -20549,9 +20557,9 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -20561,7 +20569,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Not built.</t>
+          <t>57f4d80: void with required reason.</t>
         </is>
       </c>
     </row>
@@ -22639,24 +22647,20 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Receipt shown on screen only</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>57f4d80: Print button, 58mm layout</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>Thermal print layout.</t>
-        </is>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -22676,22 +22680,22 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>57f4d80: void built</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>Change paper</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>Build REQ083; add the void branch to the diagram.</t>
+          <t>Add the void branch to the diagram.</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -4326,7 +4326,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>DONE 082ec92: RX filter, Reject Prescription with reason (7-day re-upload hold), 'ready for pick-up' notice, verifier recorded + audit.</t>
+        </is>
+      </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -4335,7 +4339,7 @@
       <c r="J7" s="11" t="inlineStr"/>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5434,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE d9fc96b: locks itself after one run; SI counter now staff-only in rules (publish rules). From the first review.</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -5441,7 +5445,7 @@
       <c r="J29" s="11" t="inlineStr"/>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5583,7 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
+          <t>DONE 5cad255: history, sales invoice PDF, free-of-cost, LTO/permit validity. Not built: reorder from a past order. Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
@@ -5590,7 +5594,7 @@
       <c r="J32" s="11" t="inlineStr"/>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5828,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>DONE 06574da: others save counts; BM finalizes; variance reason required and logged.</t>
+        </is>
+      </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5833,7 +5841,7 @@
       <c r="J37" s="11" t="inlineStr"/>
       <c r="K37" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6028,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>DONE 77336f3.</t>
+        </is>
+      </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6029,7 +6041,7 @@
       <c r="J41" s="11" t="inlineStr"/>
       <c r="K41" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6128,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Required column in the monthly purchases report.</t>
+          <t>DONE e1e200b. Required column in the monthly purchases report.</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -6127,7 +6139,7 @@
       <c r="J43" s="11" t="inlineStr"/>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6581,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr"/>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>DONE 06574da: system now matches (BM-only finalize).</t>
+        </is>
+      </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6578,7 +6594,7 @@
       <c r="J52" s="11" t="inlineStr"/>
       <c r="K52" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6632,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr"/>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>DONE footer links to legal.html on every page.</t>
+        </is>
+      </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6625,7 +6645,7 @@
       <c r="J53" s="11" t="inlineStr"/>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6683,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
+        </is>
+      </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -6672,7 +6696,7 @@
       <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8157,7 +8181,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H84" s="11" t="inlineStr"/>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>DONE 06574da.</t>
+        </is>
+      </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8166,7 +8194,7 @@
       <c r="J84" s="11" t="inlineStr"/>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8232,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H85" s="11" t="inlineStr"/>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>DONE 06574da.</t>
+        </is>
+      </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8213,7 +8245,7 @@
       <c r="J85" s="11" t="inlineStr"/>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8285,7 @@
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
+          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -8264,7 +8296,7 @@
       <c r="J86" s="11" t="inlineStr"/>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8334,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H87" s="11" t="inlineStr"/>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>DONE 847c877.</t>
+        </is>
+      </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8311,7 +8347,7 @@
       <c r="J87" s="11" t="inlineStr"/>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8387,7 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE 847c877. From the first review.</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -8362,7 +8398,7 @@
       <c r="J88" s="11" t="inlineStr"/>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8453,7 +8489,7 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE 082ec92. From the first review.</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -8464,7 +8500,7 @@
       <c r="J90" s="11" t="inlineStr"/>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8538,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H91" s="11" t="inlineStr"/>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>DONE 847c877.</t>
+        </is>
+      </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8511,7 +8551,7 @@
       <c r="J91" s="11" t="inlineStr"/>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8589,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H92" s="11" t="inlineStr"/>
+      <c r="H92" s="11" t="inlineStr">
+        <is>
+          <t>DONE 082ec92.</t>
+        </is>
+      </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8558,7 +8602,7 @@
       <c r="J92" s="11" t="inlineStr"/>
       <c r="K92" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8640,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H93" s="11" t="inlineStr"/>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>DONE 06574da.</t>
+        </is>
+      </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8605,7 +8653,7 @@
       <c r="J93" s="11" t="inlineStr"/>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8691,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H94" s="11" t="inlineStr"/>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>DONE 77336f3.</t>
+        </is>
+      </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8652,7 +8704,7 @@
       <c r="J94" s="11" t="inlineStr"/>
       <c r="K94" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8742,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H95" s="11" t="inlineStr"/>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>DONE 847c877.</t>
+        </is>
+      </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8699,7 +8755,7 @@
       <c r="J95" s="11" t="inlineStr"/>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8795,7 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -8750,7 +8806,7 @@
       <c r="J96" s="11" t="inlineStr"/>
       <c r="K96" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8846,7 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE 77336f3. From the first review.</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -8801,7 +8857,7 @@
       <c r="J97" s="11" t="inlineStr"/>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8897,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE d9fc96b. From the first review.</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -8852,7 +8908,7 @@
       <c r="J98" s="11" t="inlineStr"/>
       <c r="K98" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8995,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Keeps the paper's status name (no letter).</t>
+          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -8950,7 +9006,7 @@
       <c r="J100" s="11" t="inlineStr"/>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11001,9 +11057,9 @@
           <t>Catalog by category with name, price, stock availability</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -11013,12 +11069,12 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Cards show name/price and an Out of Stock badge, but not the quantity available (only on the product page).</t>
+          <t>06574da: catalog cards show the quantity in stock. (was: Cards show name/price and an Out of Stock badge, but not the quantity available (only on the product page).)</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -11225,9 +11281,9 @@
           <t>Product page: name, description, price, stock, dosage/usage notes, images</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -11237,12 +11293,12 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>No dosage/usage notes field exists anywhere.</t>
+          <t>06574da: Dosage / Usage notes field shown on the product page and quick view. (was: No dosage/usage notes field exists anywhere.)</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -11282,9 +11338,9 @@
           <t>Persistent cart per logged-in customer</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>Deviates</t>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -11294,12 +11350,12 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Cart is stored in the browser, so it follows the device, not the account.</t>
+          <t>77336f3: signed-in cart saved on the account and merged with any guest cart at sign-in. (was: Cart is stored in the browser, so it follows the device, not the account.)</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -11824,9 +11880,9 @@
           <t>Submitted as 'Pending Prescription Verification'; not prepared until staff approve the prescription</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -11836,12 +11892,12 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>RX orders use the same 'Order Pending Verification' status as normal orders; prescription approval is not a separate step.</t>
+          <t>082ec92: RX orders show 'Pending Prescription Verification' and aren't prepared until staff approve the prescription. (was: RX orders use the same 'Order Pending Verification' status as normal orders; prescription approval is not a separate step.)</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -11881,9 +11937,9 @@
           <t>Notify approved/ready for pick-up, or rejected with reason</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -11893,12 +11949,12 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Approval sends 'Payment confirmed' only; there is no rejection path at all.</t>
+          <t>082ec92: approval sends 'ready for pick-up'; rejection sends the reason. (was: Approval sends 'Payment confirmed' only; there is no rejection path at all.)</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -11938,9 +11994,9 @@
           <t>Notice: original prescription must be presented at pick-up</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -11950,12 +12006,12 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Checkout pick-up notice does not mention the original prescription (only the later pick-up notification does).</t>
+          <t>082ec92: checkout and payment pages say to bring the original prescription. (was: Checkout pick-up notice does not mention the original prescription (only the later pick-up notification does).)</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -12321,9 +12377,9 @@
           <t>View/download system receipt for completed orders</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -12333,12 +12389,12 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Receipt downloadable for any order (even unpaid); PDF shows only final total, not subtotal/credit applied.</t>
+          <t>082ec92: receipt only after verification; PDF shows subtotal and store credit applied. (was: Receipt downloadable for any order (even unpaid); PDF shows only final total, not subtotal/credit applied.)</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -12720,9 +12776,9 @@
           <t>Update name, address, contact no., profile picture</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
@@ -12732,12 +12788,12 @@
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>No profile picture.</t>
+          <t>77336f3: profile photo upload in Account Settings. (was: No profile picture.)</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -13172,7 +13228,7 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>Covers orders, payments, stock, expiry, PO discrepancies. No wholesale order updates or chat. Also shown to Sales Staff.</t>
+          <t>57f4d80: no longer shown to Sales Staff. Still missing wholesale-order and chat notifications. (was: Covers orders, payments, stock, expiry, PO discrepancies. No wholesale order updates or chat. Also shown to Sales Staff.)</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -13217,9 +13273,9 @@
           <t>Inventory list per product by batch, with supplier details</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -13229,12 +13285,12 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>Batch table has no supplier column.</t>
+          <t>06574da: batch table has a Supplier column (with receipt/DR no.). (was: Batch table has no supplier column.)</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -13861,9 +13917,9 @@
           <t>Branch Manager finalizes; variance reason in Audit Log</t>
         </is>
       </c>
-      <c r="D62" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -13873,12 +13929,12 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>Any staff with Inventory access can finalize; no variance reason is asked or logged (only a count of adjusted batches).</t>
+          <t>06574da: only the Branch Manager finalizes; others save the count; variance reason required and logged with each batch's change. (was: Any staff with Inventory access can finalize; no variance reason is asked or logged (only a count of adjusted batches).)</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
@@ -14244,9 +14300,9 @@
           <t>Create/edit/remove products incl. dosage notes, costing, retail, wholesale, image</t>
         </is>
       </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
@@ -14256,12 +14312,12 @@
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>No dosage notes field.</t>
+          <t>06574da: dosage notes field added to the product form. (was: No dosage notes field.)</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -14737,9 +14793,9 @@
           <t>Dedicated RX pre-order queue with prescription + payment proof</t>
         </is>
       </c>
-      <c r="D78" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -14749,12 +14805,12 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>RX orders appear in the general Payment Verification queue with the photo shown; no dedicated queue or filter.</t>
+          <t>082ec92: RX filter + RX badge in the verification queue, prescription and payment shown together. (was: RX orders appear in the general Payment Verification queue with the photo shown; no dedicated queue or filter.)</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
@@ -14794,9 +14850,9 @@
           <t>Approve after checking prescription: FEFO reservation, Ready for Pick-up, notify</t>
         </is>
       </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -14806,12 +14862,12 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>Approving payment moves RX orders straight to Ready for Pick-up, but the notification says 'Payment confirmed', not 'Ready for pick-up'.</t>
+          <t>082ec92: approval reserves stock (FEFO), sets Ready for Pick-up and notifies 'ready for pick-up'. (was: Approving payment moves RX orders straight to Ready for Pick-up, but the notification says 'Payment confirmed', not 'Ready for pick-up'.)</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
@@ -14851,9 +14907,9 @@
           <t>Mandatory reason to reject; reason in customer notification</t>
         </is>
       </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -14863,12 +14919,12 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>No reject action exists for prescriptions.</t>
+          <t>082ec92: Reject Prescription with required reason + message; customer can re-upload within 7 days. (was: No reject action exists for prescriptions.)</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr">
@@ -14961,9 +15017,9 @@
           <t>Record staff, timestamp, action per verification</t>
         </is>
       </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -14973,12 +15029,12 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>Who approved is not stored.</t>
+          <t>082ec92: every approval/hold/rejection stores who, when and what (verification field) + audit entry for RX. (was: Who approved is not stored.)</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
@@ -15242,9 +15298,9 @@
           <t>Upload/update LTO and Business Permit</t>
         </is>
       </c>
-      <c r="D87" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
@@ -15254,12 +15310,12 @@
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>Upload works; no document expiry date or 'expired' flag (shown in Interview 4 walkthrough and Activity 2.13).</t>
+          <t>5cad255: LTO and Business Permit valid-until dates; cards flag expired/expiring; orders blocked while expired. (was: Upload works; no document expiry date or 'expired' flag (shown in Interview 4 walkthrough and Activity 2.13).)</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
@@ -15409,9 +15465,9 @@
           <t>Purchase history per wholesale account</t>
         </is>
       </c>
-      <c r="D90" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -15421,12 +15477,12 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Orders are saved (wholesaleOrders) but there is no history view.</t>
+          <t>5cad255: Purchase History per wholesale account, with invoice download. (was: Orders are saved (wholesaleOrders) but there is no history view.)</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -15523,9 +15579,9 @@
           <t>Free-of-cost near-expiry distributions, zero cost, reason in audit log</t>
         </is>
       </c>
-      <c r="D92" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -15535,12 +15591,12 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>A unit price of 0 is possible, but there is no free-of-cost option, reason, or dedicated audit entry.</t>
+          <t>5cad255: free-of-cost option (prices 0), required reason, own audit entry, noted on the invoice. (was: A unit price of 0 is possible, but there is no free-of-cost option, reason, or dedicated audit entry.)</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
@@ -15580,9 +15636,9 @@
           <t>Retail/walk-in receipt; wholesale sales invoice with buyer details</t>
         </is>
       </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
@@ -15592,12 +15648,12 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>Walk-in/online receipts now carry SI No.; sales record batch + expiry per line; wholesale sales invoice still missing. (was: Walk-in and online receipts exist; no wholesale sales invoice. Receipts show no batch numbers or expiry dates, which the Project Context (p.1) names as the old POS's main gap.)</t>
+          <t>5cad255: wholesale sales invoice PDF with buyer details, batch and expiry per line; walk-in/online receipts carry SI No. (was: Walk-in and online receipts exist; no wholesale sales invoice. Receipts show no batch numbers or expiry dates, which the Project Context (p.1) names as the old POS's main gap.)</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
@@ -15637,9 +15693,9 @@
           <t>Receipt on payment verification, downloadable in My Orders</t>
         </is>
       </c>
-      <c r="D94" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -15649,12 +15705,12 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>Available before verification too.</t>
+          <t>082ec92: receipt only downloadable once payment is verified (SI No. assigned). (was: Available before verification too.)</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -15963,9 +16019,9 @@
           <t>On Hold - Payment Not Received, reason, notify</t>
         </is>
       </c>
-      <c r="D100" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D100" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -15975,12 +16031,12 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Exists only as a reason under 'Invalid payment', not as its own hold type.</t>
+          <t>847c877: 'Payment not received' is its own hold type; customer sees 'Payment Rejected - Re-upload Needed'. (was: Exists only as a reason under 'Invalid payment', not as its own hold type.)</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
@@ -16187,9 +16243,9 @@
           <t>Compile name, address, contact, schedule, order ID; one-click copy</t>
         </is>
       </c>
-      <c r="D104" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
@@ -16199,12 +16255,12 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Separate copy buttons for address/name/contact/notes. Preferred schedule and order ID are not shown; no 'copy all'.</t>
+          <t>06574da: approved modal shows order no. and preferred schedule, with a Copy All button. (was: Separate copy buttons for address/name/contact/notes. Preferred schedule and order ID are not shown; no 'copy all'.)</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
@@ -16309,7 +16365,7 @@
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Customer sees status, but not the tracking link. Customer confirmation sets 'Received' (a separate step after 'Delivered').</t>
+          <t>Tracking link now shown to the customer. Remaining difference is wording: customer confirmation sets 'Received' after 'Delivered' (fix in paper). (was: Customer sees status, but not the tracking link. Customer confirmation sets 'Received' (a separate step after 'Delivered').)</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr">
@@ -16407,9 +16463,9 @@
           <t>Optional internal delivery notes</t>
         </is>
       </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D108" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
@@ -16419,12 +16475,12 @@
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>Not built.</t>
+          <t>06574da: optional internal delivery notes saved on dispatch. (was: Not built.)</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
@@ -16912,9 +16968,9 @@
           <t>View profiles: status, registration date, order history</t>
         </is>
       </c>
-      <c r="D117" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
@@ -16924,12 +16980,12 @@
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>Shows total order count, not the order list.</t>
+          <t>847c877: customer profile lists their orders with status. (was: Shows total order count, not the order list.)</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
@@ -17022,9 +17078,9 @@
           <t>BM creates, modifies, revokes staff accounts</t>
         </is>
       </c>
-      <c r="D119" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D119" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
@@ -17034,12 +17090,12 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>Works (revoke = deactivate). New staff accounts skip the shared name/email/password validators, and editing an Administrator silently changes it to Branch Manager (js/admin-staff-management.js:181).</t>
+          <t>847c877: staff form uses the shared name/email/password rules; Administrator no longer demoted on edit. (was: Works (revoke = deactivate). New staff accounts skip the shared name/email/password validators, and editing an Administrator silently changes it to Branch Manager (js/admin-staff-management.js:181).)</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
@@ -17258,7 +17314,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Logs price changes, write-offs, reconciliation, wholesale orders, account changes. Stock receiving is not logged (Fig 2.12 shows it). Voids and exchanges don't exist yet. Before/after values are free text, reasons mostly missing, IP shown as '-'.</t>
+          <t>Now also logs stock receiving, voids (reason), RX approvals/rejections, free-of-cost distributions and reconciliation variances with reason. Still free-text before/after; IP shown as '-'. (was: Logs price changes, write-offs, reconciliation, wholesale orders, account changes. Stock receiving is not logged (Fig 2.12 shows it). Voids and exchanges don't exist yet. Before/after values are free text, reasons mostly missing, IP shown as '-'.)</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
@@ -18293,9 +18349,9 @@
           <t>Modular code with documentation</t>
         </is>
       </c>
-      <c r="D142" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D142" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
@@ -18305,12 +18361,12 @@
       </c>
       <c r="F142" s="11" t="inlineStr">
         <is>
-          <t>Modular, but no README or setup documentation (an error message even points to a missing README.md).</t>
+          <t>77336f3: README with setup, services, rules publishing, roles and deployment. (was: Modular, but no README or setup documentation (an error message even points to a missing README.md).)</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H142" s="11" t="inlineStr">
@@ -18888,9 +18944,9 @@
           <t>Dates MM/DD/YYYY, 12-hour AM/PM</t>
         </is>
       </c>
-      <c r="D153" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D153" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
@@ -18900,12 +18956,12 @@
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
-          <t>Several screens use 'Oct 18, 2026' or 'October 2026'; the audit log uses a 2-digit hour.</t>
+          <t>847c877: one MM/DD/YYYY + 12-hour formatter on every screen, receipt and export. (was: Several screens use 'Oct 18, 2026' or 'October 2026'; the audit log uses a 2-digit hour.)</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
@@ -19129,9 +19185,9 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -19141,7 +19197,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>Search box not wired; no price/stock filters.</t>
+          <t>Header search + price/stock filters.</t>
         </is>
       </c>
     </row>
@@ -19545,9 +19601,9 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -19557,7 +19613,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>REQ061 says BM finalizes - see C5.</t>
+          <t>06574da: BM finalizes; variance reason logged.</t>
         </is>
       </c>
     </row>
@@ -19609,9 +19665,9 @@
           <t>Branch Manager</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -19621,7 +19677,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Non-BM can set prices on new products.</t>
+          <t>BM-only prices everywhere (publish rules).</t>
         </is>
       </c>
     </row>
@@ -19725,9 +19781,9 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -19737,7 +19793,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>Cart is per browser, not per account.</t>
+          <t>77336f3: cart saved on the account.</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19853,7 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Named 'Submit Prescription Pre-Order' in Fig 2.4.</t>
+          <t>082ec92: approve/reject built. Name still differs from Fig 2.4 ('Submit Prescription Pre-Order') - paper edit.</t>
         </is>
       </c>
     </row>
@@ -19901,9 +19957,9 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -19911,7 +19967,11 @@
           <t>REQ010-011</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr"/>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Header search + price/stock filters.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -20045,9 +20105,9 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -20057,7 +20117,7 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>No separate prescription approval/rejection.</t>
+          <t>082ec92: separate prescription approval/rejection with reason.</t>
         </is>
       </c>
     </row>
@@ -20161,9 +20221,9 @@
           <t>Registered User</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -20173,7 +20233,7 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Tracking link not shown.</t>
+          <t>Tracking link shown once dispatched.</t>
         </is>
       </c>
     </row>
@@ -20373,9 +20433,9 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -20385,7 +20445,7 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>BM finalize + reason missing.</t>
+          <t>06574da: BM finalizes; variance reason logged.</t>
         </is>
       </c>
     </row>
@@ -20673,9 +20733,9 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -20683,7 +20743,11 @@
           <t>REQ111-115</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr"/>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>aece0e7: exports are real PDF/Excel; client report formats still to build.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -20977,9 +21041,9 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -20989,7 +21053,7 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>No order history list.</t>
+          <t>847c877: order history listed in the profile.</t>
         </is>
       </c>
     </row>
@@ -21037,9 +21101,9 @@
           <t>Branch Manager</t>
         </is>
       </c>
-      <c r="D68" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -21049,7 +21113,7 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>Non-BM staff can set prices on new/imported products.</t>
+          <t>BM-only prices everywhere (publish rules).</t>
         </is>
       </c>
     </row>
@@ -21882,17 +21946,17 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Not built (payment approval only)</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>082ec92: approve or reject (reason) before preparation; notify customer</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -21919,7 +21983,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Admin pastes the link and marks Dispatched in one step; customer can't see the link</t>
+          <t>Customer now sees the tracking link; marking Dispatched with the link is still one step</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -22170,17 +22234,17 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Same, except receiving is not written to the audit log</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>Receiving is now written to the audit log</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -22425,17 +22489,17 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Documents viewable; no expiry tracking</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>5cad255: LTO/permit valid-until dates; expired documents block the order</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -22462,17 +22526,17 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>5cad255: Purchase History per buyer</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
@@ -22499,17 +22563,17 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Near-expiry stock is used first automatically; price can be typed as 0 but there is no free-of-cost option</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>5cad255: free-of-cost option with reason and audit entry</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -22536,17 +22600,17 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Confirm + FEFO deduction + audit entry; no sales invoice</t>
-        </is>
-      </c>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>5cad255: sales invoice PDF with buyer, batch and expiry</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -22610,17 +22674,17 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>No RX check in POS</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>57f4d80: RX Verified checkbox + notes in POS</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
@@ -3972,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout; 'not an official receipt' line.</t>
+          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout. The 'not an official receipt' line was removed from POS and online receipts on 2026-10-21 at the team's request.</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Project Context (p.1)</t>
+          <t>Dashboard module p.40; Interview 4 (dashboard export)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>Dashboard Sales Analytics: show which dates the Today/Week/Month/Year view covers, and add a picker to choose a specific day, week, month or year (with previous/next)</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -6534,7 +6534,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr"/>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
+        </is>
+      </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6558,12 +6562,12 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.24)</t>
+          <t>Project Context (p.1)</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -6581,11 +6585,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>DONE 06574da: system now matches (BM-only finalize).</t>
-        </is>
-      </c>
+      <c r="H52" s="11" t="inlineStr"/>
       <c r="I52" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6594,7 +6594,7 @@
       <c r="J52" s="11" t="inlineStr"/>
       <c r="K52" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6609,12 +6609,12 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output) (p.27)</t>
+          <t>Theoretical Framework (p.24)</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>DONE footer links to legal.html on every page.</t>
+          <t>DONE 06574da: system now matches (BM-only finalize).</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -6655,17 +6655,17 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles (p.45-46)</t>
+          <t>Conceptual Framework (Output) (p.27)</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
+          <t>DONE footer links to legal.html on every page.</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr"/>
@@ -6706,22 +6706,22 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>REQ007 / Technical Background p.35-36</t>
+          <t>Modules: Staff roles (p.45-46)</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -6747,7 +6747,7 @@
       <c r="J55" s="11" t="inlineStr"/>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>REQ008 p.47; Modules p.38</t>
+          <t>REQ007 / Technical Background p.35-36</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -6790,9 +6790,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I56" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr"/>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>REQ031 p.50</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>REQ073 p.55</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -6892,9 +6892,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr"/>
@@ -6915,12 +6915,12 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+          <t>REQ073 p.55</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087 p.57; Modules p.44</t>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Default wholesale price per product, adjustable per order (C9).</t>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -6994,9 +6994,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I60" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr"/>
@@ -7017,12 +7017,12 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -7096,9 +7096,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I62" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr"/>
@@ -7119,12 +7119,12 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>REQ121 p.61</t>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 text p.67</t>
+          <t>REQ121 p.61</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 diagram</t>
+          <t>Fig 2.2 text p.67</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.5 text p.72</t>
+          <t>Fig 2.2 diagram</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 / 2.7 diagrams</t>
+          <t>Fig 2.5 text p.72</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.8 diagram + text p.76-77</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 diagram + text p.78-79</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.10 diagram</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 diagram + text p.82-83</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
@@ -7578,17 +7578,17 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover (i)</t>
+          <t>Fig 2.11 diagram + text p.82-83</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
@@ -7601,7 +7601,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H72" s="11" t="inlineStr"/>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -7625,12 +7629,12 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Title page / cover (i)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
@@ -7640,7 +7644,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -7672,12 +7676,12 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -7687,7 +7691,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr">
@@ -7719,12 +7723,12 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input) (p.25)</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
@@ -7743,9 +7747,9 @@
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr"/>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr"/>
@@ -7766,12 +7770,12 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.30-35)</t>
+          <t>Conceptual Framework (Input) (p.25)</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -7790,9 +7794,9 @@
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr"/>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr"/>
@@ -7813,12 +7817,12 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Methodology: sprint plan (p.30-35)</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
@@ -7865,7 +7869,7 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -7902,42 +7906,38 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>REQ088</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Hide costing/wholesale prices from public reads</t>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H79" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED (revised): build it to avoid a removal letter.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="inlineStr"/>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr"/>
@@ -7958,17 +7958,17 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Interview 1</t>
+          <t>REQ088</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
+          <t>Hide costing/wholesale prices from public reads</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
@@ -7983,18 +7983,18 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
+          <t>DECIDED (revised): build it to avoid a removal letter.</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr"/>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (CREDIT terms)</t>
+          <t>Interview 1</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Credit sales follow-up (who owes what, mark as paid)</t>
+          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
+          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (daily Sales section)</t>
+          <t>Report Formats sheet (CREDIT terms)</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
+          <t>Credit sales follow-up (who owes what, mark as paid)</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
+          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -8106,22 +8106,22 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Report Formats sheet (daily Sales section)</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -8134,16 +8134,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H83" s="11" t="inlineStr"/>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
+        </is>
+      </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
       <c r="K83" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8153,22 +8157,22 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>REQ013, REQ068</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Dosage/usage notes field on products</t>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -8181,11 +8185,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H84" s="11" t="inlineStr">
-        <is>
-          <t>DONE 06574da.</t>
-        </is>
-      </c>
+      <c r="H84" s="11" t="inlineStr"/>
       <c r="I84" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8194,7 +8194,7 @@
       <c r="J84" s="11" t="inlineStr"/>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8209,17 +8209,17 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>REQ049</t>
+          <t>REQ013, REQ068</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Supplier column in the inventory batch table</t>
+          <t>Dosage/usage notes field on products</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>REQ103, REQ107</t>
+          <t>REQ049</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
+          <t>Supplier column in the inventory batch table</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>REQ116</t>
+          <t>REQ103, REQ107</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Customer Accounts: list of the customer's orders</t>
+          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -8362,17 +8362,17 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>REQ116</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
+          <t>Customer Accounts: list of the customer's orders</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877. From the first review.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -8413,17 +8413,17 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>REQ070</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Category rename: replace native prompt() with app dialog</t>
+          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
+          <t>DONE 847c877. From the first review.</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -8464,17 +8464,17 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>REQ033, REQ093</t>
+          <t>REQ070</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
+          <t>Category rename: replace native prompt() with app dialog</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92. From the first review.</t>
+          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>REQ099</t>
+          <t>REQ033, REQ093</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>'Payment not received' as its own hold type</t>
+          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 082ec92. From the first review.</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>REQ026</t>
+          <t>REQ099</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Checkout pick-up notice mentions bringing the original prescription</t>
+          <t>'Payment not received' as its own hold type</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>REQ009</t>
+          <t>REQ026</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Show quantity in stock on catalog cards</t>
+          <t>Checkout pick-up notice mentions bringing the original prescription</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DONE 082ec92.</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -8668,17 +8668,17 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>REQ040</t>
+          <t>REQ009</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Profile picture in Account Settings</t>
+          <t>Show quantity in stock on catalog cards</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -8719,17 +8719,17 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>REQNF028</t>
+          <t>REQ040</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
+          <t>Profile picture in Account Settings</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 77336f3.</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -8770,17 +8770,17 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>REQ047</t>
+          <t>REQNF028</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
+          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -8821,17 +8821,17 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>REQNF017</t>
+          <t>REQ047</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>README with setup steps; fix the error message that points to it</t>
+          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3. From the first review.</t>
+          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -8872,17 +8872,17 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>REQ001</t>
+          <t>REQNF017</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Normalize phone number at registration</t>
+          <t>README with setup steps; fix the error message that points to it</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b. From the first review.</t>
+          <t>DONE 77336f3. From the first review.</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -8923,17 +8923,17 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>REQ008; Interview 1</t>
+          <t>REQ001</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
+          <t>Normalize phone number at registration</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -8946,7 +8946,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H99" s="11" t="inlineStr"/>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>DONE d9fc96b. From the first review.</t>
+        </is>
+      </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8955,7 +8959,7 @@
       <c r="J99" s="11" t="inlineStr"/>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8970,17 +8974,17 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>REQ031</t>
+          <t>REQ008; Interview 1</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
+          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -8993,11 +8997,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H100" s="11" t="inlineStr">
-        <is>
-          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
-        </is>
-      </c>
+      <c r="H100" s="11" t="inlineStr"/>
       <c r="I100" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -9006,7 +9006,7 @@
       <c r="J100" s="11" t="inlineStr"/>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9021,17 +9021,17 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37</t>
+          <t>REQ031</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
+          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Keeps the Chart.js claim (no letter).</t>
+          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -9057,7 +9057,7 @@
       <c r="J101" s="11" t="inlineStr"/>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9072,12 +9072,12 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Modules p.42</t>
+          <t>Technical Background p.35-37</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
+          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
+          <t>Keeps the Chart.js claim (no letter).</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -9108,7 +9108,7 @@
       <c r="J102" s="11" t="inlineStr"/>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework p.23</t>
+          <t>Modules p.42</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
+          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Keeps the 'push notifications' claim (no letter).</t>
+          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -9159,7 +9159,7 @@
       <c r="J103" s="11" t="inlineStr"/>
       <c r="K103" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9174,12 +9174,12 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>REQ039, Fig 2.10, C16</t>
+          <t>Theoretical Framework p.23</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
@@ -9197,7 +9197,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H104" s="11" t="inlineStr"/>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>Keeps the 'push notifications' claim (no letter).</t>
+        </is>
+      </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -9221,17 +9225,17 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>System roles (-)</t>
+          <t>REQ039, Fig 2.10, C16</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -9263,17 +9267,17 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Whole paper + system (-)</t>
+          <t>System roles (-)</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
@@ -9294,7 +9298,7 @@
       <c r="H106" s="11" t="inlineStr"/>
       <c r="I106" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J106" s="11" t="inlineStr"/>
@@ -9310,22 +9314,22 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>Whole paper + system (-)</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -9338,11 +9342,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H107" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H107" s="11" t="inlineStr"/>
       <c r="I107" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>Modules FEFO p.41</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>Add the 2-month Bad Order step (C7).</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
@@ -9394,9 +9394,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I108" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J108" s="11" t="inlineStr"/>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Scope p.6; Product Browsing REQ009</t>
+          <t>Technical Background p.35-37; Budget p.99</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
@@ -9445,9 +9445,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I109" s="11" t="inlineStr">
-        <is>
-          <t>Adds</t>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J109" s="11" t="inlineStr"/>
@@ -9468,12 +9468,12 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Scope and Limitations p.7</t>
+          <t>Scope p.6; Product Browsing REQ009</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Decision-dependent</t>
+          <t>Scope and Limitations p.7</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+          <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr"/>
@@ -9570,17 +9570,17 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Decision-dependent</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
@@ -9593,7 +9593,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H112" s="11" t="inlineStr"/>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -9617,12 +9621,12 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Scope (p.6)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
@@ -9641,9 +9645,9 @@
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr"/>
-      <c r="I113" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J113" s="11" t="inlineStr"/>
@@ -9664,12 +9668,12 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.22-23)</t>
+          <t>Scope (p.6)</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
@@ -9711,12 +9715,12 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.32)</t>
+          <t>Theoretical Framework (p.22-23)</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
@@ -9735,9 +9739,9 @@
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr"/>
-      <c r="I115" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr"/>
@@ -9758,12 +9762,12 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Methodology: sprint plan (p.32)</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
@@ -9805,12 +9809,12 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
@@ -9829,9 +9833,9 @@
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr"/>
-      <c r="I117" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J117" s="11" t="inlineStr"/>
@@ -9857,7 +9861,7 @@
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
@@ -9899,12 +9903,12 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
@@ -9946,12 +9950,12 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.36-38)</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
@@ -9970,9 +9974,9 @@
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr"/>
-      <c r="I120" s="11" t="inlineStr">
-        <is>
-          <t>Adds</t>
+      <c r="I120" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr"/>
@@ -9993,12 +9997,12 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.38)</t>
+          <t>Technical Background: Software (p.36-38)</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
@@ -10019,7 +10023,7 @@
       <c r="H121" s="11" t="inlineStr"/>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr"/>
@@ -10040,12 +10044,12 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Modules: Price Management (p.42)</t>
+          <t>Technical Background: Software (p.38)</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -10064,9 +10068,9 @@
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr"/>
-      <c r="I122" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr"/>
@@ -10087,12 +10091,12 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+          <t>Modules: Price Management (p.42)</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
@@ -10111,9 +10115,9 @@
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr"/>
-      <c r="I123" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J123" s="11" t="inlineStr"/>
@@ -10134,12 +10138,12 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.97-98)</t>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
@@ -10181,12 +10185,12 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Calendar of Activities (p.97-98)</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
@@ -10233,7 +10237,7 @@
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
@@ -10275,12 +10279,12 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>References (p.100)</t>
+          <t>Budgetary Estimate (p.99)</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
@@ -10322,12 +10326,12 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>References (p.10 / refs)</t>
+          <t>References (p.100)</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
@@ -10369,12 +10373,12 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>References (p.17 / refs)</t>
+          <t>References (p.10 / refs)</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
@@ -10416,12 +10420,12 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Appendices (p.124)</t>
+          <t>References (p.17 / refs)</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
@@ -10463,12 +10467,12 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+          <t>Appendices (p.124)</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Regenerate page numbers after all edits.</t>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
@@ -10499,18 +10503,65 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="11" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr"/>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J132" s="11" t="inlineStr"/>
+      <c r="K132" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K131"/>
-  <conditionalFormatting sqref="K2:K131">
+  <autoFilter ref="A1:K132"/>
+  <conditionalFormatting sqref="K2:K132">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
+          <t>DONE 80b3988: widget, built-in answers, Gemini via Firebase AI Logic, daily AI limit with usage shown, staff console (reply, take over, hand back, resolve), staff alert. Enable AI Logic in the Firebase console and publish rules. Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -4139,7 +4139,7 @@
       <c r="J3" s="11" t="inlineStr"/>
       <c r="K3" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
+          <t>DONE cb08e78: date range shown; Day/Week/Month/Year with previous/next and a date picker; exports name the period. Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -6547,7 +6547,7 @@
       <c r="J51" s="11" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+          <t>DONE 80b3988: widget, built-in answers, Gemini via Firebase AI Logic, daily AI limit with usage shown, staff console (reply, take over, hand back, resolve), staff alert. Enable AI Logic in the Firebase console and publish rules. See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -9606,7 +9606,7 @@
       <c r="J112" s="11" t="inlineStr"/>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -12542,9 +12542,9 @@
           <t>Live chat for guests and customers</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -12554,12 +12554,12 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Buttons exist but go nowhere.</t>
+          <t>80b3988: chat widget on every shop page for guests and customers. (was: Buttons exist but go nowhere.)</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -12599,9 +12599,9 @@
           <t>AI-powered responses (OpenAI) for common inquiries</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>Not built. A browser-only app cannot hide an OpenAI key, so this needs a server function (e.g. Firebase Cloud Functions, Blaze plan).</t>
+          <t>80b3988: AI replies from Gemini (Firebase AI Logic, free tier) instead of OpenAI, plus built-in answers for common questions. Paper names OpenAI - in the panel letter. (was: Not built. A browser-only app cannot hide an OpenAI key, so this needs a server function (e.g. Firebase Cloud Functions, Blaze plan).)</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -12656,9 +12656,9 @@
           <t>Escalate to staff when needed</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -12668,12 +12668,12 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Not built.</t>
+          <t>80b3988: hands off to staff when asked, when the assistant is unsure, or when the daily AI limit is reached. (was: Not built.)</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
@@ -12713,9 +12713,9 @@
           <t>Notify staff of new/escalated chats</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Not built.</t>
+          <t>80b3988: waiting chats show in the staff notification bell and the Live Chat page. (was: Not built.)</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>57f4d80: no longer shown to Sales Staff. Still missing wholesale-order and chat notifications. (was: Covers orders, payments, stock, expiry, PO discrepancies. No wholesale order updates or chat. Also shown to Sales Staff.)</t>
+          <t>No longer shown to Sales Staff; waiting chats now included (80b3988). Still missing wholesale-order notifications. (was: Covers orders, payments, stock, expiry, PO discrepancies. No wholesale order updates or chat. Also shown to Sales Staff.)</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -15190,7 +15190,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>57f4d80: void for completed walk-in sales by BM/Technical (Admin too): reason, original SI No., stock back to the exact batches, optional exchange note + price difference, audit entry. Not yet: second-person approval; exchange item is a note, not a stock movement. (was: No void function at all.)</t>
+          <t>57f4d80 + a771333: void the whole sale or specific items/quantities, with reason, SI No., stock back to the same batches, exchange note, audit entry. Not yet: second-person approval. (was: No void function at all.)</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -16571,9 +16571,9 @@
           <t>Staff view customer and AI conversations</t>
         </is>
       </c>
-      <c r="D109" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
@@ -16583,12 +16583,12 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>Sidebar link goes nowhere on all 12 admin pages.</t>
+          <t>80b3988: Admin -&gt; Live Chat lists every conversation, live. (was: Sidebar link goes nowhere on all 12 admin pages.)</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
@@ -16628,9 +16628,9 @@
           <t>Staff respond to customers</t>
         </is>
       </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D110" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
@@ -16640,12 +16640,12 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>Not built.</t>
+          <t>80b3988: staff reply, take over from the assistant, or hand back. (was: Not built.)</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
@@ -16685,9 +16685,9 @@
           <t>Mark threads resolved</t>
         </is>
       </c>
-      <c r="D111" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D111" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
@@ -16697,12 +16697,12 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>Not built.</t>
+          <t>80b3988: Mark resolved; a new customer message reopens it. (was: Not built.)</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
@@ -17915,7 +17915,7 @@
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>EmailJS works; QR PH is a static image (missing, see REQ028); OpenAI not integrated.</t>
+          <t>EmailJS works; AI is Gemini via Firebase AI Logic (paper: OpenAI); QR Ph image still missing. (was: EmailJS works; QR PH is a static image (missing, see REQ028); OpenAI not integrated.)</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
@@ -19296,9 +19296,9 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -19308,7 +19308,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Dead buttons.</t>
+          <t>80b3988</t>
         </is>
       </c>
     </row>
@@ -19328,9 +19328,9 @@
           <t>(no actor connected)</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Paper: bubble has no actor line in the overall diagram.</t>
+          <t>80b3988: built; Fig 2.2 still needs the actor line (paper edit).</t>
         </is>
       </c>
     </row>
@@ -19924,9 +19924,9 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -19934,7 +19934,11 @@
           <t>REQ035</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr"/>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>80b3988</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -20912,9 +20916,9 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -20924,7 +20928,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>Connected here, but not in Fig 2.2.</t>
+          <t>80b3988</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -9595,7 +9595,7 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>DONE 80b3988: widget, built-in answers, Gemini via Firebase AI Logic, daily AI limit with usage shown, staff console (reply, take over, hand back, resolve), staff alert. Enable AI Logic in the Firebase console and publish rules. See Contradictions / Paper Edits</t>
+          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -9606,7 +9606,7 @@
       <c r="J112" s="11" t="inlineStr"/>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -4277,7 +4277,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>PARTIAL aece0e7: all 6 Export buttons now produce real PDF/Excel tables of what's on screen; the client's 4 report formats are still to build. Client's one remaining ask (Interview 4). Build to the 4 client samples (see Report Formats sheet); Excel output must paste cleanly into the main office's own sheets (Interviews 1, 2, 4); daily sales should total by payment method to match the daily cash remittance (Interview 2).</t>
+          <t>DONE bf16804: Reports page with Daily Sales, Customer File, Monthly Inventory, Supplier Purchases, Pull-Out and PO Discrepancy in the branch's formats; preview, PDF, Excel. Not yet: Return to POS / wholesale exchange report (needs the exchange feature). Discount, VAT and pay-in/pay-out columns show 0 (client: no discounts; VAT-exempt as in their sample). PARTIAL aece0e7: all 6 Export buttons now produce real PDF/Excel tables of what's on screen; the client's 4 report formats are still to build. Client's one remaining ask (Interview 4). Build to the 4 client samples (see Report Formats sheet); Excel output must paste cleanly into the main office's own sheets (Interviews 1, 2, 4); daily sales should total by payment method to match the daily cash remittance (Interview 2).</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -4288,7 +4288,7 @@
       <c r="J6" s="11" t="inlineStr"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>DECIDED (revised): build everywhere to avoid a removal letter.</t>
+          <t>DONE 21e505b: orders (staff + customer), inventory, POS today's sales, chat.</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -5100,7 +5100,7 @@
       <c r="J22" s="11" t="inlineStr"/>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>DONE d2a957b: automatic write-off with reason, audit entry, disposal alert, Mark disposed.</t>
+        </is>
+      </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5688,7 +5692,7 @@
       <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -13805,9 +13809,9 @@
           <t>Discrepancy reports by date range, PDF/Excel</t>
         </is>
       </c>
-      <c r="D59" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
@@ -13817,12 +13821,12 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>No discrepancy report export.</t>
+          <t>bf16804: Reports -&gt; Purchase Order Discrepancy Report, date range, PDF/Excel. (was: No discrepancy report export.)</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -14294,9 +14298,9 @@
           <t>Within 2 months: Bad Order, disposal alert, auto-deduct</t>
         </is>
       </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -14306,12 +14310,12 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>No 2-month Bad Order handling.</t>
+          <t>d2a957b: within 2 months (or expired) the batch becomes Bad Order: remaining units written off automatically (write-off + audit entry), disposal alert until staff Mark disposed. (was: No 2-month Bad Order handling.)</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
@@ -16742,9 +16746,9 @@
           <t>Export daily sales reports (from Order Processing)</t>
         </is>
       </c>
-      <c r="D112" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D112" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
@@ -16754,12 +16758,12 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>aece0e7: Online Orders Export now gives real PDF/Excel of the listed orders. Client's daily sales format still to build. (was: Online Orders Export downloads a blank PDF. Dashboard Sales Analytics export works but is not the daily sales report the client described (per customer, items with batch + expiry).)</t>
+          <t>bf16804: Reports -&gt; Daily Sales Report in the branch's format (sales, retail, wholesale, payment method, items sold) + Customer File; shortcut on Orders. (was: Online Orders Export downloads a blank PDF. Dashboard Sales Analytics export works but is not the daily sales report the client described (per customer, items with batch + expiry).)</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
@@ -16799,9 +16803,9 @@
           <t>Export monthly inventory + purchase reports (from Inventory)</t>
         </is>
       </c>
-      <c r="D113" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D113" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
@@ -16811,12 +16815,12 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>aece0e7: Inventory Export now gives real PDF/Excel by batch (expiry, supplier, receipt/DR no., unit cost, date received). Client's monthly format still to build. (was: Inventory Export downloads a blank PDF.)</t>
+          <t>bf16804: Reports -&gt; Monthly Inventory (sheet per category, POS vs physical, prices, batch, expiry) + Supplier Purchases; shortcut on Inventory. (was: Inventory Export downloads a blank PDF.)</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
@@ -16856,9 +16860,9 @@
           <t>Pull-out reports by date range</t>
         </is>
       </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D114" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
@@ -16868,12 +16872,12 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Not built (write-offs are recorded, so data exists).</t>
+          <t>bf16804: Reports -&gt; Pull-Out Report (write-offs incl. automatic Bad Order) by date range. (was: Not built (write-offs are recorded, so data exists).)</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">
@@ -16966,9 +16970,9 @@
           <t>All reports in PDF or Excel</t>
         </is>
       </c>
-      <c r="D116" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D116" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
@@ -16978,12 +16982,12 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>aece0e7: all 6 Export buttons now give real PDF or Excel. Client report formats still to build. (was: Only Sales Analytics exports (PDF + Excel). Five other Export buttons give blank PDFs (Dashboard, Inventory, Online Orders, Suppliers, Audit Log).)</t>
+          <t>bf16804: every report previews on screen and downloads as PDF or Excel. (was: Only Sales Analytics exports (PDF + Excel). Five other Export buttons give blank PDFs (Dashboard, Inventory, Online Orders, Suppliers, Audit Log).)</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H116" s="11" t="inlineStr"/>
@@ -17736,9 +17740,9 @@
           <t>Inventory/order changes appear without manual refresh</t>
         </is>
       </c>
-      <c r="D130" s="16" t="inlineStr">
-        <is>
-          <t>Deviates</t>
+      <c r="D130" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
@@ -17748,12 +17752,12 @@
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>Users must reload to see new orders or stock changes.</t>
+          <t>21e505b: online orders, inventory, POS today's sales, customer order list and order page, and chat update live. Dashboard tiles refresh on load. (was: Users must reload to see new orders or stock changes.)</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H130" s="11" t="inlineStr">
@@ -17793,9 +17797,9 @@
           <t>Reports in reasonable time</t>
         </is>
       </c>
-      <c r="D131" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
@@ -17805,7 +17809,7 @@
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>Reports not built yet.</t>
+          <t>Reports query only the chosen period's sales, write-offs and POs. (was: Reports not built yet.)</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
@@ -18563,9 +18567,9 @@
           <t>Data export in PDF and Excel</t>
         </is>
       </c>
-      <c r="D145" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D145" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
@@ -18575,12 +18579,12 @@
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>aece0e7: every Export button offers PDF or Excel. (was: Only Sales Analytics exports.)</t>
+          <t>Every report and Export button gives PDF or Excel. (was: Only Sales Analytics exports.)</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
@@ -19592,9 +19596,9 @@
           <t>Technical Staff</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -19604,7 +19608,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>aece0e7: exports are real PDF/Excel; client report formats still to build.</t>
+          <t>bf16804: Reports page.</t>
         </is>
       </c>
     </row>
@@ -20428,9 +20432,9 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -20440,7 +20444,7 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>6-month flag yes; 2-month Bad Order missing.</t>
+          <t>6-month Wholesale Only + 2-month Bad Order (d2a957b).</t>
         </is>
       </c>
     </row>
@@ -20788,9 +20792,9 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -20800,7 +20804,7 @@
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>aece0e7: exports are real PDF/Excel; client report formats still to build.</t>
+          <t>bf16804: Reports page in the client's formats.</t>
         </is>
       </c>
     </row>
@@ -22437,17 +22441,17 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>d2a957b: built; diagram box should say 'Write off batch (Bad Order)', not FEFO deduction</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -5632,7 +5632,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>DONE Purchase History -&gt; Exchange: return to batch, FEFO replacement, value rule, audit, exchange document; Return / Exchange report.</t>
+        </is>
+      </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5641,7 +5645,7 @@
       <c r="J33" s="11" t="inlineStr"/>
       <c r="K33" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6187,7 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>Shown to the client during the prototype walkthrough.</t>
+          <t>DONE Reports -&gt; Supplier Purchases (per supplier, per month). Shown to the client during the prototype walkthrough.</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
@@ -6194,7 +6198,7 @@
       <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6442,7 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Keeps per-account pricing (no letter).</t>
+          <t>DONE saved from Process Order, listed in Edit account, default on orders. Keeps per-account pricing (no letter).</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
@@ -6449,7 +6453,7 @@
       <c r="J49" s="11" t="inlineStr"/>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6593,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr"/>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
+        </is>
+      </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6598,7 +6606,7 @@
       <c r="J52" s="11" t="inlineStr"/>
       <c r="K52" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9009,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H100" s="11" t="inlineStr"/>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
+        </is>
+      </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -9010,7 +9022,7 @@
       <c r="J100" s="11" t="inlineStr"/>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9264,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H105" s="11" t="inlineStr"/>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
+        </is>
+      </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -9261,7 +9277,7 @@
       <c r="J105" s="11" t="inlineStr"/>
       <c r="K105" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10134,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H123" s="11" t="inlineStr"/>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
+        </is>
+      </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
           <t>REMOVES / narrows - see Removals (Letter)</t>
@@ -10127,7 +10147,7 @@
       <c r="J123" s="11" t="inlineStr"/>
       <c r="K123" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11055,9 +11075,9 @@
           <t>Home page with products, announcements, promotions, navigation</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -11067,12 +11087,12 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Featured products and categories exist; no announcements or promotions section.</t>
+          <t>Announcement / promotion banner on every shop page, edited in Settings by the BM or Technical Staff. (was: Featured products and categories exist; no announcements or promotions section.)</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -12786,7 +12806,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>In-platform bell works; no email notifications are sent (EmailJS is only used for OTP). No notification at all when an order is placed (Fig 2.10 'Send Order Submission Notification').</t>
+          <t>In-platform notifications for order placed, payment confirmed, holds, prescription results, ready for pick-up. Email notifications not built. (was: In-platform bell works; no email notifications are sent (EmailJS is only used for OTP). No notification at all when an order is placed (Fig 2.10 'Send Order Submission Notification').)</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -13271,9 +13291,9 @@
           <t>Notify BM + Technical of new orders, payments, stock, expiry, wholesale updates, chat</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -13283,12 +13303,12 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>No longer shown to Sales Staff; waiting chats now included (80b3988). Still missing wholesale-order notifications. (was: Covers orders, payments, stock, expiry, PO discrepancies. No wholesale order updates or chat. Also shown to Sales Staff.)</t>
+          <t>Staff bell: orders, payments, stock, expiry, Bad Order disposal, PO discrepancies, wholesale document expiry, waiting chats. (was: Covers orders, payments, stock, expiry, PO discrepancies. No wholesale order updates or chat. Also shown to Sales Staff.)</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -15182,9 +15202,9 @@
           <t>Void with reason, restore stock, audit log, record exchange + price difference</t>
         </is>
       </c>
-      <c r="D84" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -15194,12 +15214,12 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>57f4d80 + a771333: void the whole sale or specific items/quantities, with reason, SI No., stock back to the same batches, exchange note, audit entry. Not yet: second-person approval. (was: No void function at all.)</t>
+          <t>Full or item-level voids with reason, SI No., stock back to the same batches, exchange note, audit entry; Technical Staff voids need a Branch Manager's email + password approval (client rule). (was: No void function at all.)</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
@@ -15296,9 +15316,9 @@
           <t>Wholesale accounts with contact, business type, agreed pricing</t>
         </is>
       </c>
-      <c r="D86" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D86" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
@@ -15308,12 +15328,12 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>No per-account agreed pricing; price comes from the product's wholesale price and can be edited per order.</t>
+          <t>Agreed price per buyer per product (saved from Process Order, reviewed in Edit), used as the default on their orders. (was: No per-account agreed pricing; price comes from the product's wholesale price and can be edited per order.)</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>Change paper</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
@@ -15422,7 +15442,7 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>POs recorded against the buyer with their agreed prices as defaults. (was: -)</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr">
@@ -15577,9 +15597,9 @@
           <t>Wholesale item exchanges with FEFO + audit log</t>
         </is>
       </c>
-      <c r="D91" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
@@ -15589,12 +15609,12 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>Not built.</t>
+          <t>Wholesale exchange from Purchase History: return to the original batch, FEFO replacement, equal-or-higher value (buyer pays the difference), reason, audit entry, exchange document (EX-#####). (was: Not built.)</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -16917,9 +16937,9 @@
           <t>Wholesale exchange reports by period</t>
         </is>
       </c>
-      <c r="D115" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D115" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
@@ -16929,12 +16949,12 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>Not built; depends on REQ090.</t>
+          <t>Reports -&gt; Return / Exchange Report (the branch's 'Return to POS' sheet + replacement and difference). (was: Not built; depends on REQ090.)</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr"/>
@@ -21044,9 +21064,9 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D64" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -21054,7 +21074,11 @@
           <t>REQ090</t>
         </is>
       </c>
-      <c r="F64" s="11" t="inlineStr"/>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>Purchase History -&gt; Exchange.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -21072,9 +21096,9 @@
           <t>Technical Staff (+BM)</t>
         </is>
       </c>
-      <c r="D65" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -21082,7 +21106,11 @@
           <t>REQ090</t>
         </is>
       </c>
-      <c r="F65" s="11" t="inlineStr"/>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>Return to batch + FEFO replacement in one transaction.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
@@ -21857,17 +21885,17 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Only an on-screen confirmation with the order number; no notification</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Order-placed notice in the customer's bell</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -22840,17 +22868,17 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Built from Purchase History</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -22877,17 +22905,17 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Returned units back to their batch + FEFO replacement</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
@@ -22914,17 +22942,17 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Audit entry + exchange document; diagram should say 'Generate Wholesale Exchange Document'</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -9113,7 +9113,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Keeps the Chart.js claim (no letter).</t>
+          <t>DONE Dashboard: stock in vs stock out per day/week/month/year. Keeps the Chart.js claim (no letter).</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -9124,7 +9124,7 @@
       <c r="J102" s="11" t="inlineStr"/>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>Keeps the 'push notifications' claim (no letter).</t>
+          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -9226,7 +9226,7 @@
       <c r="J104" s="11" t="inlineStr"/>
       <c r="K104" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H115" s="11" t="inlineStr"/>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
+        </is>
+      </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
           <t>REMOVES / narrows - see Removals (Letter)</t>
@@ -9767,7 +9771,7 @@
       <c r="J115" s="11" t="inlineStr"/>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9950,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H119" s="11" t="inlineStr"/>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: dashboard now has the inventory movement chart.</t>
+        </is>
+      </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
           <t>REMOVES / narrows - see Removals (Letter)</t>
@@ -9955,7 +9963,7 @@
       <c r="J119" s="11" t="inlineStr"/>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -5940,7 +5940,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>EmailJS free tier: 200/month.</t>
+          <t>DONE EmailJS order template (ID to paste in js/emailjs-config.js) + on/off toggle in Account Settings. EmailJS free tier: 200/month.</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -5951,7 +5951,7 @@
       <c r="J39" s="11" t="inlineStr"/>
       <c r="K39" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -12802,9 +12802,9 @@
           <t>In-platform and email notifications for order/payment/delivery updates</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>In-platform notifications for order placed, payment confirmed, holds, prescription results, ready for pick-up. Email notifications not built. (was: In-platform bell works; no email notifications are sent (EmailJS is only used for OTP). No notification at all when an order is placed (Fig 2.10 'Send Order Submission Notification').)</t>
+          <t>In-platform + EmailJS email for order placed, payment confirmed, holds, prescription results, dispatched (tracking link), ready for pick-up, credit. Needs the order template ID in js/emailjs-config.js. (was: In-platform bell works; no email notifications are sent (EmailJS is only used for OTP). No notification at all when an order is placed (Fig 2.10 'Send Order Submission Notification').)</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
@@ -12969,9 +12969,9 @@
           <t>Enable/disable email notifications</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -12981,12 +12981,12 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>No toggle (and no email notifications yet).</t>
+          <t>Account Settings -&gt; Notifications: email updates on/off. (was: No toggle (and no email notifications yet).)</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -157,9 +157,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -167,6 +164,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5534,7 +5534,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>DONE 7ede9d4: emailed code on new browsers, customers and staff; recognized devices in Account Settings.</t>
+        </is>
+      </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5543,7 +5547,7 @@
       <c r="J31" s="11" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10916,29 +10920,29 @@
           <t>Email OTP when logging in from an unrecognized device</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>js/device-trust.js; js/auth.js</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>No device recognition or login OTP exists.</t>
+          <t>Built (7ede9d4): new browser gets an emailed 6-digit code (10 min, 5 tries, resend after 60 s); recognized devices in Account Settings. Checked in the browser, not by database rules.</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Also in Fig 2.3 (Verify OTP) and Activity 2.8; OTP + EmailJS code already exists (js/otp.js) to reuse.</t>
+          <t>Paper may add: the device check runs in the browser.</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -12350,7 +12354,7 @@
           <t>Statuses: pending payment, payment verified, confirmed, dispatched, delivered, payment rejected</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -12631,7 +12635,7 @@
           <t>AI-powered responses (OpenAI) for common inquiries</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -13079,31 +13083,27 @@
           <t>Staff OTP only on unrecognized device</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>js/device-trust.js; js/admin-header.js</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>Not built (same as REQ005).</t>
+          <t>Built with REQ005 (7ede9d4); admin pages send an unconfirmed device back to login.</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>Do together with REQ005.</t>
-        </is>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr"/>
       <c r="I45" s="11" t="inlineStr">
         <is>
           <t>Med</t>
@@ -16045,7 +16045,7 @@
           <t>On Hold - Overpayment, excess as unapplied value</t>
         </is>
       </c>
-      <c r="D99" s="16" t="inlineStr">
+      <c r="D99" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -16436,7 +16436,7 @@
           <t>Reflect status to customer; customer 'Order Received' finalizes as Delivered</t>
         </is>
       </c>
-      <c r="D106" s="16" t="inlineStr">
+      <c r="D106" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -17654,7 +17654,7 @@
           <t>Works on desktop, laptop, tablet, phone</t>
         </is>
       </c>
-      <c r="D128" s="17" t="inlineStr">
+      <c r="D128" s="16" t="inlineStr">
         <is>
           <t>Not verified</t>
         </is>
@@ -17711,7 +17711,7 @@
           <t>Standard operations load in reasonable time</t>
         </is>
       </c>
-      <c r="D129" s="17" t="inlineStr">
+      <c r="D129" s="16" t="inlineStr">
         <is>
           <t>Not verified</t>
         </is>
@@ -17878,7 +17878,7 @@
           <t>Chrome, Firefox, Edge, Safari</t>
         </is>
       </c>
-      <c r="D132" s="17" t="inlineStr">
+      <c r="D132" s="16" t="inlineStr">
         <is>
           <t>Not verified</t>
         </is>
@@ -18159,7 +18159,7 @@
           <t>No patient data sent to OpenAI</t>
         </is>
       </c>
-      <c r="D137" s="18" t="inlineStr">
+      <c r="D137" s="17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18216,7 +18216,7 @@
           <t>Hosted with uptime + recovery</t>
         </is>
       </c>
-      <c r="D138" s="15" t="inlineStr">
+      <c r="D138" s="18" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -18652,7 +18652,7 @@
           <t>Usable with basic digital literacy</t>
         </is>
       </c>
-      <c r="D146" s="17" t="inlineStr">
+      <c r="D146" s="16" t="inlineStr">
         <is>
           <t>Not verified</t>
         </is>
@@ -20104,9 +20104,9 @@
           <t>Staff, Registered User</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -20116,7 +20116,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Verify OTP not built.</t>
+          <t>Built (7ede9d4).</t>
         </is>
       </c>
     </row>
@@ -20884,7 +20884,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D58" s="18" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20916,7 +20916,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D59" s="18" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21453,22 +21453,22 @@
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Same (js/auth.js startDeviceVerification)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>Change system</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>REQ005/REQ044.</t>
+          <t>REQ005/REQ044, 7ede9d4.</t>
         </is>
       </c>
     </row>
@@ -21493,7 +21493,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21530,7 +21530,7 @@
           <t>reCAPTCHA check, rejecting attempts while locked, blocking deactivated accounts, sending unverified customers to email verification</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -21567,7 +21567,7 @@
           <t>Terms modal opens when the checkbox is ticked (before submit); duplicate email is caught by Firebase at account creation; code sent after</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -21641,7 +21641,7 @@
           <t>Goes straight to the shop, already signed in</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -21785,7 +21785,7 @@
           <t>RX detected when checkout opens; address section hidden; pick-up only</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -21822,7 +21822,7 @@
           <t>Required on the payment page for RX orders</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -21933,7 +21933,7 @@
           <t>Login required to check out, delivery schedule, store credit discount, live stock re-check before submitting</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -21970,7 +21970,7 @@
           <t>Stock is deducted first; if stock ran out the order goes on an Out of Stock hold instead</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -22007,7 +22007,7 @@
           <t>RX orders skip courier booking and go straight to Ready for Pick-up</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -22151,7 +22151,7 @@
           <t>Every resolution returns to staff (resubmission or Release Hold)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -22188,7 +22188,7 @@
           <t>Approved immediately; excess added to store credit</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -22225,7 +22225,7 @@
           <t>Closed automatically after 7 days, with verified payment kept as credit</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -22262,7 +22262,7 @@
           <t>Fully credit-covered orders (no screenshot), Release Hold by staff</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -22369,7 +22369,7 @@
           <t>Partial stock added, PO marked Discrepancy, acknowledgment required to close</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -22406,7 +22406,7 @@
           <t>Both exist (manual Receive Stock, Excel/CSV upload)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Deviates</t>
         </is>
@@ -22517,7 +22517,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22990,7 +22990,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -23397,12 +23397,12 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>No OTP yet.</t>
+          <t>System follows the text: a wrong code shows tries left, Resend sends a new one; 5 wrong codes sign the person out (does not feed the password lockout).</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Pick one when building REQ005/044; update the other.</t>
+          <t>Change the Fig 2.8 diagram: 'No' from Validate OTP goes back to Enter OTP / Request new OTP, not the failed-attempt counter.</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -21638,22 +21638,22 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Goes straight to the shop, already signed in</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>Deviates</t>
+          <t>Same: after registering, the code signs them out and opens Login with the email filled in</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Matches</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Change paper</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>C10.</t>
+          <t>C10 resolved.</t>
         </is>
       </c>
     </row>
@@ -23316,12 +23316,12 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Redirects straight to the shop (already signed in).</t>
+          <t>System now matches: after registration it goes to Login.</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Change paper (minor).</t>
+          <t>No change.</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
@@ -3972,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4757,22 +4757,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
+          <t>REQNF011, REQ121</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
+          <t>Database rules per staff role: Sales Staff limited to POS + read-only catalog in the rules too, not only in the page menus</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -4787,18 +4787,18 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: BM/Technical void completed sales from POS Today's Sales or Walk-in Orders: reason, SI No., stock restored to the same batches, exchange note + price difference, audit entry. Still open: second-person approval (client rule) and exchange as a real stock movement. Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
+          <t>Pages already block Sales Staff; someone with technical know-how could still write other collections directly.</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr"/>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4813,22 +4813,22 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>REQ098, REQ102, C2</t>
+          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
+          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b (system part; REQ098 paper wording still to do). From the first review.</t>
+          <t>DONE 57f4d80: BM/Technical void completed sales from POS Today's Sales or Walk-in Orders: reason, SI No., stock restored to the same batches, exchange note + price difference, audit entry. Still open: second-person approval (client rule) and exchange as a real stock movement. Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -4864,17 +4864,17 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
+          <t>REQ098, REQ102, C2</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
+          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>DONE BM-only prices in the form, batch import and quick-add (others' products saved Inactive + 'Price pending'); reason required and logged; enforced in firestore.rules - PUBLISH THE RULES in the Firebase console.</t>
+          <t>DONE e1e200b (system part; REQ098 paper wording still to do). From the first review.</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
@@ -4910,22 +4910,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Removals (Letter) sheet</t>
+          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Letter to the panel: OpenAI -&gt; Gemini (free), Firebase Storage -&gt; Cloudinary, DataTable -&gt; custom tables, password reset via Firebase Auth, overpayment approve-and-credit, corrections to scope/conceptual framework</t>
+          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -4940,18 +4940,18 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>One letter covers all remaining removals; send before the paper edits.</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE BM-only prices in the form, batch import and quick-add (others' products saved Inactive + 'Price pending'); reason required and logged; enforced in firestore.rules - PUBLISH THE RULES in the Firebase console.</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4966,22 +4966,22 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Objectives / evaluation (p.5-6, 21-24)</t>
+          <t>Removals (Letter) sheet</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
+          <t>Letter to the panel: OpenAI -&gt; Gemini (free), Firebase Storage -&gt; Cloudinary, DataTable -&gt; custom tables, password reset via Firebase Auth, overpayment approve-and-credit, corrections to scope/conceptual framework</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -4989,10 +4989,14 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr"/>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>One letter covers all remaining removals; send before the paper edits.</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr"/>
@@ -5008,48 +5012,44 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>REQ121</t>
+          <t>Objectives / evaluation (p.5-6, 21-24)</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
+          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>DONE 57f4d80: POS (with Today's Sales) + read-only catalog; lands on POS after login. Orders access was added on purpose on 2026-10-01.</t>
-        </is>
-      </c>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr"/>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5064,12 +5064,12 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>REQNF005</t>
+          <t>REQ121</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Live updates without refresh on all order and inventory screens (staff + customer)</t>
+          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>DONE 21e505b: orders (staff + customer), inventory, POS today's sales, chat.</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 57f4d80: POS (with Today's Sales) + read-only catalog; lands on POS after login. Orders access was added on purpose on 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr"/>
@@ -5110,27 +5110,27 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>REQNF010, REQNF013</t>
+          <t>REQNF005</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
+          <t>Live updates without refresh on all order and inventory screens (staff + customer)</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -5140,18 +5140,18 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: Netlify (already set up).</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>DONE 21e505b: orders (staff + customer), inventory, POS today's sales, chat.</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Discount/Deductions columns); Interview 2</t>
+          <t>REQNF010, REQNF013</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Discount / deduction per sale or line, with reason and audit entry</t>
+          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -5191,18 +5191,18 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Client confirmed: no discounts. Not in the paper; client gives boss-approved discounts today.</t>
+          <t>DECIDED: Netlify (already set up).</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Methodology p.30 ('actual client data'); Report Formats sheet</t>
+          <t>Report Formats sheet (Discount/Deductions columns); Interview 2</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Load the client's real March-end catalog (prices, batches, expiry) from their workbook via the existing upload templates</t>
+          <t>Discount / deduction per sale or line, with reason and audit entry</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -5242,18 +5242,18 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: yes, once the client sends the catalog. Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
+          <t>Client confirmed: no discounts. Not in the paper; client gives boss-approved discounts today.</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr"/>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -5263,27 +5263,27 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>Methodology p.30 ('actual client data'); Report Formats sheet</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
+          <t>Load the client's real March-end catalog (prices, batches, expiry) from their workbook via the existing upload templates</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -5291,7 +5291,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr"/>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: yes, once the client sends the catalog. Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
+        </is>
+      </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5300,7 +5304,7 @@
       <c r="J26" s="11" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5324,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
+          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -5362,12 +5366,12 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -5404,22 +5408,22 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
+          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -5432,11 +5436,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>DONE d9fc96b: locks itself after one run; SI counter now staff-only in rules (publish rules). From the first review.</t>
-        </is>
-      </c>
+      <c r="H29" s="11" t="inlineStr"/>
       <c r="I29" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5445,7 +5445,7 @@
       <c r="J29" s="11" t="inlineStr"/>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>REQ002</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
+          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE d9fc96b: locks itself after one run; SI counter now staff-only in rules (publish rules). From the first review.</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
@@ -5496,7 +5496,7 @@
       <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5511,22 +5511,22 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
+          <t>REQ002</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Unrecognized-device OTP for customers and staff</t>
+          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>DONE 7ede9d4: emailed code on new browsers, customers and staff; recognized devices in Account Settings.</t>
+          <t>From the first review.</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -5547,7 +5547,7 @@
       <c r="J31" s="11" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5562,17 +5562,17 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>REQ086, REQ089, REQ091, REQ092</t>
+          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
+          <t>Unrecognized-device OTP for customers and staff</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>DONE 5cad255: history, sales invoice PDF, free-of-cost, LTO/permit validity. Not built: reorder from a past order. Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
+          <t>DONE 7ede9d4: emailed code on new browsers, customers and staff; recognized devices in Account Settings.</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
@@ -5613,17 +5613,17 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>REQ090, REQ114, Fig 2.15</t>
+          <t>REQ086, REQ089, REQ091, REQ092</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
+          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>DONE Purchase History -&gt; Exchange: return to batch, FEFO replacement, value rule, audit, exchange document; Return / Exchange report.</t>
+          <t>DONE 5cad255: history, sales invoice PDF, free-of-cost, LTO/permit validity. Not built: reorder from a past order. Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>REQ067, C7</t>
+          <t>REQ090, REQ114, Fig 2.15</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
+          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>DONE d2a957b: automatic write-off with reason, audit entry, disposal alert, Mark disposed.</t>
+          <t>DONE Purchase History -&gt; Exchange: return to batch, FEFO replacement, value rule, audit, exchange document; Return / Exchange report.</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
+          <t>REQ067, C7</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
+          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout. The 'not an official receipt' line was removed from POS and online receipts on 2026-10-21 at the team's request.</t>
+          <t>DONE d2a957b: automatic write-off with reason, audit entry, disposal alert, Mark disposed.</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>REQ084</t>
+          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>POS: RX Verified checkbox + optional notes</t>
+          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: checkbox + notes, required for RX items, saved on the sale.</t>
+          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout. The 'not an official receipt' line was removed from POS and online receipts on 2026-10-21 at the team's request.</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -5817,17 +5817,17 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>REQ061, C5</t>
+          <t>REQ084</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
+          <t>POS: RX Verified checkbox + optional notes</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da: others save counts; BM finalizes; variance reason required and logged.</t>
+          <t>DONE 57f4d80: checkbox + notes, required for RX items, saved on the sale.</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -5868,17 +5868,17 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>REQNF025, REQNF029</t>
+          <t>REQ061, C5</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
+          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>DONE footer rebuilt from js/store-info.js (real About text, links to legal.html; contact/LTO lines hidden until the client confirms them); chat links hidden until chat is built; payment page Terms link fixed. From the first review.</t>
+          <t>DONE 06574da: others save counts; BM finalizes; variance reason required and logged.</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -5919,22 +5919,22 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>REQ039, REQ042</t>
+          <t>REQNF025, REQNF029</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
+          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>DONE EmailJS order template (ID to paste in js/emailjs-config.js) + on/off toggle in Account Settings. EmailJS free tier: 200/month.</t>
+          <t>DONE footer rebuilt from js/store-info.js (real About text, links to legal.html; contact/LTO lines hidden until the client confirms them); chat links hidden until chat is built; payment page Terms link fixed. From the first review.</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>REQ122</t>
+          <t>REQ039, REQ042</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
+          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -5993,7 +5993,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>DONE EmailJS order template (ID to paste in js/emailjs-config.js) + on/off toggle in Account Settings. EmailJS free tier: 200/month.</t>
+        </is>
+      </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6002,7 +6006,7 @@
       <c r="J40" s="11" t="inlineStr"/>
       <c r="K40" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6017,22 +6021,22 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>REQ014</t>
+          <t>REQ122</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Save cart to the customer's account</t>
+          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -6040,11 +6044,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>DONE 77336f3.</t>
-        </is>
-      </c>
+      <c r="H41" s="11" t="inlineStr"/>
       <c r="I41" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6053,7 +6053,7 @@
       <c r="J41" s="11" t="inlineStr"/>
       <c r="K41" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6068,17 +6068,17 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>REQNF003, REQNF007</t>
+          <t>REQ014</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Phone/tablet and cross-browser test pass</t>
+          <t>Save cart to the customer's account</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -6091,7 +6091,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>DONE 77336f3.</t>
+        </is>
+      </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6100,7 +6104,7 @@
       <c r="J42" s="11" t="inlineStr"/>
       <c r="K42" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6115,17 +6119,17 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Interviews 2, 4</t>
+          <t>REQNF003, REQNF007</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
+          <t>Phone/tablet and cross-browser test pass</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Not verified</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -6138,11 +6142,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>DONE e1e200b. Required column in the monthly purchases report.</t>
-        </is>
-      </c>
+      <c r="H43" s="11" t="inlineStr"/>
       <c r="I43" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6151,7 +6151,7 @@
       <c r="J43" s="11" t="inlineStr"/>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Interview 4 walkthrough</t>
+          <t>Interviews 2, 4</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Supplier history: everything received from each supplier</t>
+          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>DONE Reports -&gt; Supplier Purchases (per supplier, per month). Shown to the client during the prototype walkthrough.</t>
+          <t>DONE e1e200b. Required column in the monthly purchases report.</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Methodology p.30; Interview 4</t>
+          <t>Interview 4 walkthrough</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>User manual + hands-on training + handover to the branch</t>
+          <t>Supplier history: everything received from each supplier</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
+          <t>DONE Reports -&gt; Supplier Purchases (per supplier, per month). Shown to the client during the prototype walkthrough.</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -6253,7 +6253,7 @@
       <c r="J45" s="11" t="inlineStr"/>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
+          <t>Methodology p.30; Interview 4</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
+          <t>User manual + hands-on training + handover to the branch</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b. Customer File groups every sale by customer name.</t>
+          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
@@ -6304,7 +6304,7 @@
       <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6319,17 +6319,17 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Supplier sheets)</t>
+          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
+          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b: unit cost + receipt/DR no. added; pack size stays in the product name as the branch does today. Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
+          <t>DONE e1e200b. Customer File groups every sale by customer name.</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -6370,17 +6370,17 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
+          <t>Report Formats sheet (Supplier sheets)</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies, Grocery</t>
+          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b: also storefront links/filters now follow Manage Categories. Existing Firebase projects keep their current categories - add the client's in Manage Categories.. Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
+          <t>DONE e1e200b: unit cost + receipt/DR no. added; pack size stays in the product name as the branch does today. Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -6421,22 +6421,22 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087</t>
+          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Optional agreed price per wholesale buyer per product, used as default on their orders</t>
+          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies, Grocery</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>DONE saved from Process Order, listed in Edit account, default on orders. Keeps per-account pricing (no letter).</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE e1e200b: also storefront links/filters now follow Manage Categories. Existing Firebase projects keep their current categories - add the client's in Manage Categories.. Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr"/>
@@ -6472,12 +6472,12 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>REQ085, REQ087</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Cut database reads: stop loading whole collections on every page (Firestore free-plan daily read cap ~50k)</t>
+          <t>Optional agreed price per wholesale buyer per product, used as default on their orders</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -6497,18 +6497,18 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>Needed before real use with the client's ~1,000-product catalog.</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>DONE saved from Process Order, listed in Edit account, default on orders. Keeps per-account pricing (no letter).</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6523,22 +6523,22 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Dashboard module p.40; Interview 4 (dashboard export)</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Dashboard Sales Analytics: show which dates the Today/Week/Month/Year view covers, and add a picker to choose a specific day, week, month or year (with previous/next)</t>
+          <t>Cut database reads: stop loading whole collections on every page (Firestore free-plan daily read cap ~50k)</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>DONE cb08e78: date range shown; Day/Week/Month/Year with previous/next and a date picker; exports name the period. Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
+          <t>Needed before real use with the client's ~1,000-product catalog.</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -6559,7 +6559,7 @@
       <c r="J51" s="11" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6574,17 +6574,17 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Project Context (p.1)</t>
+          <t>Dashboard module p.40; Interview 4 (dashboard export)</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>Dashboard Sales Analytics: show which dates the Today/Week/Month/Year view covers, and add a picker to choose a specific day, week, month or year (with previous/next)</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
+          <t>DONE cb08e78: date range shown; Day/Week/Month/Year with previous/next and a date picker; exports name the period. Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -6625,17 +6625,17 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.24)</t>
+          <t>REQ048, Notification module</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Admin notification for pending wholesale orders (Pending -&gt; Released)</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da: system now matches (BM-only finalize).</t>
+          <t>DONE 274b8e0: wholesale orders start Pending; Mark Released in purchase history; staff notification.</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -6661,7 +6661,7 @@
       <c r="J53" s="11" t="inlineStr"/>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output) (p.27)</t>
+          <t>REQ111, Sales Report module</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>Daily Sales report: batch, expiry, date received and supplier per item sold</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>DONE footer links to legal.html on every page.</t>
+          <t>DONE 274b8e0: 'Item Sold by Batch' section.</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -6712,7 +6712,7 @@
       <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6722,17 +6722,17 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles (p.45-46)</t>
+          <t>Project Context (p.1)</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
+          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr"/>
@@ -6773,22 +6773,22 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>REQ007 / Technical Background p.35-36</t>
+          <t>Theoretical Framework (p.24)</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -6803,18 +6803,18 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE 06574da: system now matches (BM-only finalize).</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr"/>
       <c r="K56" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6824,22 +6824,22 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>REQ008 p.47; Modules p.38</t>
+          <t>Conceptual Framework (Output) (p.27)</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -6854,18 +6854,18 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I57" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE footer links to legal.html on every page.</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr"/>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6875,22 +6875,22 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>REQ031 p.50</t>
+          <t>Modules: Staff roles (p.45-46)</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
@@ -6905,18 +6905,18 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I58" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6931,12 +6931,12 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>REQ073 p.55</t>
+          <t>REQ007 / Technical Background p.35-36</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -7010,9 +7010,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I60" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr"/>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087 p.57; Modules p.44</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Default wholesale price per product, adjustable per order (C9).</t>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+          <t>REQ073 p.55</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -7112,9 +7112,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I62" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr"/>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>REQ121 p.61</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -7214,9 +7214,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr"/>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 text p.67</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -7265,9 +7265,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I65" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr"/>
@@ -7288,12 +7288,12 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 diagram</t>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.5 text p.72</t>
+          <t>REQ121 p.61</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 / 2.7 diagrams</t>
+          <t>Fig 2.2 text p.67</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.8 diagram + text p.76-77</t>
+          <t>Fig 2.2 diagram</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 diagram + text p.78-79</t>
+          <t>Fig 2.5 text p.72</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.10 diagram</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 diagram + text p.82-83</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover (i)</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -7668,7 +7668,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H73" s="11" t="inlineStr"/>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -7692,22 +7696,22 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr">
@@ -7715,7 +7719,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H74" s="11" t="inlineStr"/>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -7739,17 +7747,17 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>Fig 2.11 diagram + text p.82-83</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -7762,7 +7770,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H75" s="11" t="inlineStr"/>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -7786,12 +7798,12 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input) (p.25)</t>
+          <t>Title page / cover (i)</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -7810,9 +7822,9 @@
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr"/>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr"/>
@@ -7833,12 +7845,12 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.30-35)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
@@ -7848,7 +7860,7 @@
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -7880,12 +7892,12 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -7927,12 +7939,12 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Conceptual Framework (Input) (p.25)</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -7951,9 +7963,9 @@
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr"/>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr"/>
@@ -7969,42 +7981,38 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>REQ088</t>
+          <t>Methodology: sprint plan (p.30-35)</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Hide costing/wholesale prices from public reads</t>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H80" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED (revised): build it to avoid a removal letter.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H80" s="11" t="inlineStr"/>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr"/>
@@ -8020,48 +8028,44 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Interview 1</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H81" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr"/>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr"/>
       <c r="K81" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8071,48 +8075,44 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (CREDIT terms)</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Credit sales follow-up (who owes what, mark as paid)</t>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H82" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H82" s="11" t="inlineStr"/>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr"/>
       <c r="K82" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8127,22 +8127,22 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (daily Sales section)</t>
+          <t>REQ088</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
+          <t>Hide costing/wholesale prices from public reads</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -8152,18 +8152,18 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
+          <t>DECIDED (revised): build it to avoid a removal letter.</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
       <c r="K83" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8173,27 +8173,27 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Interview 1</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -8201,16 +8201,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H84" s="11" t="inlineStr"/>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
+        </is>
+      </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr"/>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8225,12 +8229,12 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>REQ013, REQ068</t>
+          <t>Report Formats sheet (CREDIT terms)</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Dosage/usage notes field on products</t>
+          <t>Credit sales follow-up (who owes what, mark as paid)</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
@@ -8240,7 +8244,7 @@
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -8250,18 +8254,18 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr"/>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8276,17 +8280,17 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>REQ049</t>
+          <t>Report Formats sheet (daily Sales section)</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Supplier column in the inventory batch table</t>
+          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -8301,18 +8305,18 @@
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr"/>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8322,22 +8326,22 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>REQ103, REQ107</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -8350,11 +8354,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H87" s="11" t="inlineStr">
-        <is>
-          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
-        </is>
-      </c>
+      <c r="H87" s="11" t="inlineStr"/>
       <c r="I87" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8363,7 +8363,7 @@
       <c r="J87" s="11" t="inlineStr"/>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8378,17 +8378,17 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>REQ116</t>
+          <t>REQ013, REQ068</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Customer Accounts: list of the customer's orders</t>
+          <t>Dosage/usage notes field on products</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -8429,17 +8429,17 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>REQ049</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
+          <t>Supplier column in the inventory batch table</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877. From the first review.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -8480,17 +8480,17 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>REQ070</t>
+          <t>REQ103, REQ107</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Category rename: replace native prompt() with app dialog</t>
+          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
+          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>REQ033, REQ093</t>
+          <t>REQ116</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
+          <t>Customer Accounts: list of the customer's orders</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92. From the first review.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -8582,17 +8582,17 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>REQ099</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>'Payment not received' as its own hold type</t>
+          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 847c877. From the first review.</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -8633,17 +8633,17 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>REQ026</t>
+          <t>REQ070</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Checkout pick-up notice mentions bringing the original prescription</t>
+          <t>Category rename: replace native prompt() with app dialog</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92.</t>
+          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -8684,12 +8684,12 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>REQ009</t>
+          <t>REQ033, REQ093</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Show quantity in stock on catalog cards</t>
+          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DONE 082ec92. From the first review.</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -8735,17 +8735,17 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>REQ040</t>
+          <t>REQ099</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Profile picture in Account Settings</t>
+          <t>'Payment not received' as its own hold type</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>REQNF028</t>
+          <t>REQ026</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
+          <t>Checkout pick-up notice mentions bringing the original prescription</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 082ec92.</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -8837,17 +8837,17 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>REQ047</t>
+          <t>REQ009</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
+          <t>Show quantity in stock on catalog cards</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>REQNF017</t>
+          <t>REQ040</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>README with setup steps; fix the error message that points to it</t>
+          <t>Profile picture in Account Settings</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3. From the first review.</t>
+          <t>DONE 77336f3.</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -8939,17 +8939,17 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>REQ001</t>
+          <t>REQNF028</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Normalize phone number at registration</t>
+          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b. From the first review.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -8990,17 +8990,17 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>REQ008; Interview 1</t>
+          <t>REQ047</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
+          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
+          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>REQ031</t>
+          <t>REQNF017</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
+          <t>README with setup steps; fix the error message that points to it</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
+          <t>DONE 77336f3. From the first review.</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37</t>
+          <t>REQ001</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
+          <t>Normalize phone number at registration</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>DONE Dashboard: stock in vs stock out per day/week/month/year. Keeps the Chart.js claim (no letter).</t>
+          <t>DONE d9fc96b. From the first review.</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Modules p.42</t>
+          <t>REQ008; Interview 1</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
+          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
+          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -9194,17 +9194,17 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework p.23</t>
+          <t>REQ031</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
+          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
+          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>REQ039, Fig 2.10, C16</t>
+          <t>Technical Background p.35-37</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
+          <t>DONE Dashboard: stock in vs stock out per day/week/month/year. Keeps the Chart.js claim (no letter).</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -9296,17 +9296,17 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>System roles (-)</t>
+          <t>Modules p.42</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -9319,7 +9319,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H106" s="11" t="inlineStr"/>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
+        </is>
+      </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -9328,7 +9332,7 @@
       <c r="J106" s="11" t="inlineStr"/>
       <c r="K106" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9338,22 +9342,22 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Whole paper + system (-)</t>
+          <t>Theoretical Framework p.23</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -9366,16 +9370,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H107" s="11" t="inlineStr"/>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
+        </is>
+      </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J107" s="11" t="inlineStr"/>
       <c r="K107" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9385,22 +9393,22 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>REQ039, Fig 2.10, C16</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -9415,18 +9423,18 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J108" s="11" t="inlineStr"/>
       <c r="K108" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9436,22 +9444,22 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>REQ004</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>Login lockout counter can be reset by anyone (public loginAttempts collection)</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -9466,12 +9474,12 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I109" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>Lockout works for normal use; a determined attacker could clear it. Mention as a limitation if not fixed.</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J109" s="11" t="inlineStr"/>
@@ -9487,22 +9495,22 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Scope p.6; Product Browsing REQ009</t>
+          <t>System roles (-)</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
@@ -9515,14 +9523,10 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H110" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H110" s="11" t="inlineStr"/>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J110" s="11" t="inlineStr"/>
@@ -9538,22 +9542,22 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Scope and Limitations p.7</t>
+          <t>Whole paper + system (-)</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
@@ -9566,14 +9570,10 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H111" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H111" s="11" t="inlineStr"/>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr"/>
@@ -9594,22 +9594,22 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Decision-dependent</t>
+          <t>REQ005, REQ044</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+          <t>New-device code is checked in the browser, not by the database rules</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+          <t>Stops normal use of a stolen password; a technical attacker could skip it. State this in Limitations.</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -9645,17 +9645,17 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Modules FEFO p.41</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>Add the 2-month Bad Order step (C7).</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -9668,7 +9668,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H113" s="11" t="inlineStr"/>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -9692,17 +9696,17 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Scope (p.6)</t>
+          <t>Technical Background p.35-37; Budget p.99</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -9715,7 +9719,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H114" s="11" t="inlineStr"/>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
           <t>REMOVES / narrows - see Removals (Letter)</t>
@@ -9739,17 +9747,17 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.22-23)</t>
+          <t>Scope p.6; Product Browsing REQ009</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -9764,18 +9772,18 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
-        </is>
-      </c>
-      <c r="I115" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr"/>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9790,17 +9798,17 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.32)</t>
+          <t>Scope and Limitations p.7</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
@@ -9813,10 +9821,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H116" s="11" t="inlineStr"/>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J116" s="11" t="inlineStr"/>
@@ -9837,17 +9849,17 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Decision-dependent</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
@@ -9860,7 +9872,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H117" s="11" t="inlineStr"/>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -9884,12 +9900,12 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
@@ -9908,9 +9924,9 @@
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr"/>
-      <c r="I118" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J118" s="11" t="inlineStr"/>
@@ -9931,12 +9947,12 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Scope (p.6)</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
@@ -9954,11 +9970,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H119" s="11" t="inlineStr">
-        <is>
-          <t>DONE No paper change needed: dashboard now has the inventory movement chart.</t>
-        </is>
-      </c>
+      <c r="H119" s="11" t="inlineStr"/>
       <c r="I119" s="12" t="inlineStr">
         <is>
           <t>REMOVES / narrows - see Removals (Letter)</t>
@@ -9967,7 +9979,7 @@
       <c r="J119" s="11" t="inlineStr"/>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9994,12 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Theoretical Framework (p.22-23)</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
@@ -10005,7 +10017,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H120" s="11" t="inlineStr"/>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
+        </is>
+      </c>
       <c r="I120" s="12" t="inlineStr">
         <is>
           <t>REMOVES / narrows - see Removals (Letter)</t>
@@ -10014,7 +10030,7 @@
       <c r="J120" s="11" t="inlineStr"/>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10029,12 +10045,12 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.36-38)</t>
+          <t>Methodology: sprint plan (p.32)</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
@@ -10055,7 +10071,7 @@
       <c r="H121" s="11" t="inlineStr"/>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr"/>
@@ -10076,12 +10092,12 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.38)</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -10123,12 +10139,12 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Modules: Price Management (p.42)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
@@ -10146,11 +10162,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H123" s="11" t="inlineStr">
-        <is>
-          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
-        </is>
-      </c>
+      <c r="H123" s="11" t="inlineStr"/>
       <c r="I123" s="12" t="inlineStr">
         <is>
           <t>REMOVES / narrows - see Removals (Letter)</t>
@@ -10159,7 +10171,7 @@
       <c r="J123" s="11" t="inlineStr"/>
       <c r="K123" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -10174,12 +10186,12 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
@@ -10197,16 +10209,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H124" s="11" t="inlineStr"/>
-      <c r="I124" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H124" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: dashboard now has the inventory movement chart.</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J124" s="11" t="inlineStr"/>
       <c r="K124" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10237,12 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.97-98)</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
@@ -10245,9 +10261,9 @@
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr"/>
-      <c r="I125" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I125" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J125" s="11" t="inlineStr"/>
@@ -10268,12 +10284,12 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background: Software (p.36-38)</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
@@ -10294,7 +10310,7 @@
       <c r="H126" s="11" t="inlineStr"/>
       <c r="I126" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J126" s="11" t="inlineStr"/>
@@ -10315,12 +10331,12 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background: Software (p.38)</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
@@ -10362,12 +10378,12 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>References (p.100)</t>
+          <t>Modules: Price Management (p.42)</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
@@ -10385,16 +10401,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H128" s="11" t="inlineStr"/>
-      <c r="I128" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
+        </is>
+      </c>
+      <c r="I128" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J128" s="11" t="inlineStr"/>
       <c r="K128" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10409,12 +10429,12 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>References (p.10 / refs)</t>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
@@ -10456,12 +10476,12 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>References (p.17 / refs)</t>
+          <t>Calendar of Activities (p.97-98)</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
@@ -10503,12 +10523,12 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Appendices (p.124)</t>
+          <t>Budgetary Estimate (p.99)</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
@@ -10550,12 +10570,12 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+          <t>Budgetary Estimate (p.99)</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Regenerate page numbers after all edits.</t>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
@@ -10586,18 +10606,253 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="11" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>References (p.100)</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr"/>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="inlineStr"/>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>References (p.10 / refs)</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr"/>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="inlineStr"/>
+      <c r="K134" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>References (p.17 / refs)</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr"/>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="inlineStr"/>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>Appendices (p.124)</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr"/>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="inlineStr"/>
+      <c r="K136" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr"/>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="inlineStr"/>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K132"/>
-  <conditionalFormatting sqref="K2:K132">
+  <autoFilter ref="A1:K137"/>
+  <conditionalFormatting sqref="K2:K137">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
@@ -3972,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4808,22 +4808,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
+          <t>REQ095-100, REQ098</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
+          <t>Bug check: store credit could be lost or added twice on expired holds; credit redeemed on an order was lost on invalid-payment holds; two staff approving at once deducted stock twice</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -4838,18 +4838,18 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: BM/Technical void completed sales from POS Today's Sales or Walk-in Orders: reason, SI No., stock restored to the same batches, exchange note + price difference, audit entry. Still open: second-person approval (client rule) and exchange as a real stock movement. Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
+          <t>DONE f0faaad.</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4859,27 +4859,27 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>REQ098, REQ102, C2</t>
+          <t>REQNF011, REQ002, REQ098</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
+          <t>Bug check: database rules let a customer create orders with any status/hold, start with store credit, rewrite a hold when resubmitting, or reset the order counter; deactivated staff kept access</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -4889,18 +4889,18 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b (system part; REQ098 paper wording still to do). From the first review.</t>
+          <t>DONE 5d41982 (publish firestore.rules).</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr"/>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4910,22 +4910,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
+          <t>REQNF011</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
+          <t>Bug check: customer- and staff-typed text (names, order numbers, notes) was put into admin pages as HTML</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -4940,18 +4940,18 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>DONE BM-only prices in the form, batch import and quick-add (others' products saved Inactive + 'Price pending'); reason required and logged; enforced in firestore.rules - PUBLISH THE RULES in the Firebase console.</t>
+          <t>DONE 72e7361.</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4961,27 +4961,27 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Removals (Letter) sheet</t>
+          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Letter to the panel: OpenAI -&gt; Gemini (free), Firebase Storage -&gt; Cloudinary, DataTable -&gt; custom tables, password reset via Firebase Auth, overpayment approve-and-credit, corrections to scope/conceptual framework</t>
+          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -4991,18 +4991,18 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>One letter covers all remaining removals; send before the paper edits.</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 57f4d80: BM/Technical void completed sales from POS Today's Sales or Walk-in Orders: reason, SI No., stock restored to the same batches, exchange note + price difference, audit entry. Still open: second-person approval (client rule) and exchange as a real stock movement. Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr"/>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5012,27 +5012,27 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Objectives / evaluation (p.5-6, 21-24)</t>
+          <t>REQ098, REQ102, C2</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
+          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -5040,7 +5040,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>DONE e1e200b (system part; REQ098 paper wording still to do). From the first review.</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -5049,7 +5053,7 @@
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5059,22 +5063,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>REQ121</t>
+          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
+          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -5084,17 +5088,17 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: POS (with Today's Sales) + read-only catalog; lands on POS after login. Orders access was added on purpose on 2026-10-01.</t>
+          <t>DONE BM-only prices in the form, batch import and quick-add (others' products saved Inactive + 'Price pending'); reason required and logged; enforced in firestore.rules - PUBLISH THE RULES in the Firebase console.</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr"/>
@@ -5110,37 +5114,37 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>REQNF005</t>
+          <t>Removals (Letter) sheet</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Live updates without refresh on all order and inventory screens (staff + customer)</t>
+          <t>Letter to the panel: OpenAI -&gt; Gemini (free), Firebase Storage -&gt; Cloudinary, DataTable -&gt; custom tables, password reset via Firebase Auth, overpayment approve-and-credit, corrections to scope/conceptual framework</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>DONE 21e505b: orders (staff + customer), inventory, POS today's sales, chat.</t>
+          <t>One letter covers all remaining removals; send before the paper edits.</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
@@ -5151,7 +5155,7 @@
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5161,42 +5165,38 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>REQNF010, REQNF013</t>
+          <t>Objectives / evaluation (p.5-6, 21-24)</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
+          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: Netlify (already set up).</t>
-        </is>
-      </c>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr"/>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr"/>
@@ -5212,27 +5212,27 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Discount/Deductions columns); Interview 2</t>
+          <t>REQ121</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Discount / deduction per sale or line, with reason and audit entry</t>
+          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -5242,18 +5242,18 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Client confirmed: no discounts. Not in the paper; client gives boss-approved discounts today.</t>
+          <t>DONE 57f4d80: POS (with Today's Sales) + read-only catalog; lands on POS after login. Orders access was added on purpose on 2026-10-01.</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr"/>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5263,22 +5263,22 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Methodology p.30 ('actual client data'); Report Formats sheet</t>
+          <t>REQNF005</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Load the client's real March-end catalog (prices, batches, expiry) from their workbook via the existing upload templates</t>
+          <t>Live updates without refresh on all order and inventory screens (staff + customer)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -5293,18 +5293,18 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: yes, once the client sends the catalog. Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>DONE 21e505b: orders (staff + customer), inventory, POS today's sales, chat.</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5314,22 +5314,22 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>REQNF010, REQNF013</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
+          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -5342,7 +5342,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: Netlify (already set up).</t>
+        </is>
+      </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5361,27 +5365,27 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>Report Formats sheet (Discount/Deductions columns); Interview 2</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
+          <t>Discount / deduction per sale or line, with reason and audit entry</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -5389,16 +5393,20 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Client confirmed: no discounts. Not in the paper; client gives boss-approved discounts today.</t>
+        </is>
+      </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr"/>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -5408,27 +5416,27 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Methodology p.30 ('actual client data'); Report Formats sheet</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+          <t>Load the client's real March-end catalog (prices, batches, expiry) from their workbook via the existing upload templates</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -5436,7 +5444,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: yes, once the client sends the catalog. Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
+        </is>
+      </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5445,7 +5457,7 @@
       <c r="J29" s="11" t="inlineStr"/>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -5455,22 +5467,22 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
+          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -5483,11 +5495,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>DONE d9fc96b: locks itself after one run; SI counter now staff-only in rules (publish rules). From the first review.</t>
-        </is>
-      </c>
+      <c r="H30" s="11" t="inlineStr"/>
       <c r="I30" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5496,7 +5504,7 @@
       <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5506,22 +5514,22 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>REQ002</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
+          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -5534,11 +5542,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>From the first review.</t>
-        </is>
-      </c>
+      <c r="H31" s="11" t="inlineStr"/>
       <c r="I31" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5557,27 +5561,27 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Unrecognized-device OTP for customers and staff</t>
+          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -5585,11 +5589,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>DONE 7ede9d4: emailed code on new browsers, customers and staff; recognized devices in Account Settings.</t>
-        </is>
-      </c>
+      <c r="H32" s="11" t="inlineStr"/>
       <c r="I32" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5598,7 +5598,7 @@
       <c r="J32" s="11" t="inlineStr"/>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5613,22 +5613,22 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>REQ086, REQ089, REQ091, REQ092</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
+          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>DONE 5cad255: history, sales invoice PDF, free-of-cost, LTO/permit validity. Not built: reorder from a past order. Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
+          <t>DONE d9fc96b: locks itself after one run; SI counter now staff-only in rules (publish rules). From the first review.</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>REQ090, REQ114, Fig 2.15</t>
+          <t>REQ002</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
+          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>DONE Purchase History -&gt; Exchange: return to batch, FEFO replacement, value rule, audit, exchange document; Return / Exchange report.</t>
+          <t>From the first review.</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -5700,7 +5700,7 @@
       <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5715,12 +5715,12 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>REQ067, C7</t>
+          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
+          <t>Unrecognized-device OTP for customers and staff</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>DONE d2a957b: automatic write-off with reason, audit entry, disposal alert, Mark disposed.</t>
+          <t>DONE 7ede9d4: emailed code on new browsers, customers and staff; recognized devices in Account Settings.</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -5766,22 +5766,22 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
+          <t>REQ086, REQ089, REQ091, REQ092</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
+          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout. The 'not an official receipt' line was removed from POS and online receipts on 2026-10-21 at the team's request.</t>
+          <t>DONE 5cad255: history, sales invoice PDF, free-of-cost, LTO/permit validity. Not built: reorder from a past order. Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>REQ084</t>
+          <t>REQ090, REQ114, Fig 2.15</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>POS: RX Verified checkbox + optional notes</t>
+          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: checkbox + notes, required for RX items, saved on the sale.</t>
+          <t>DONE Purchase History -&gt; Exchange: return to batch, FEFO replacement, value rule, audit, exchange document; Return / Exchange report.</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -5868,22 +5868,22 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>REQ061, C5</t>
+          <t>REQ067, C7</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
+          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da: others save counts; BM finalizes; variance reason required and logged.</t>
+          <t>DONE d2a957b: automatic write-off with reason, audit entry, disposal alert, Mark disposed.</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -5919,17 +5919,17 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>REQNF025, REQNF029</t>
+          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
+          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>DONE footer rebuilt from js/store-info.js (real About text, links to legal.html; contact/LTO lines hidden until the client confirms them); chat links hidden until chat is built; payment page Terms link fixed. From the first review.</t>
+          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout. The 'not an official receipt' line was removed from POS and online receipts on 2026-10-21 at the team's request.</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -5970,22 +5970,22 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>REQ039, REQ042</t>
+          <t>REQ084</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
+          <t>POS: RX Verified checkbox + optional notes</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>DONE EmailJS order template (ID to paste in js/emailjs-config.js) + on/off toggle in Account Settings. EmailJS free tier: 200/month.</t>
+          <t>DONE 57f4d80: checkbox + notes, required for RX items, saved on the sale.</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>REQ122</t>
+          <t>REQ061, C5</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
+          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -6044,7 +6044,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>DONE 06574da: others save counts; BM finalizes; variance reason required and logged.</t>
+        </is>
+      </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6053,7 +6057,7 @@
       <c r="J41" s="11" t="inlineStr"/>
       <c r="K41" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6068,17 +6072,17 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>REQ014</t>
+          <t>REQNF025, REQNF029</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Save cart to the customer's account</t>
+          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -6093,7 +6097,7 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3.</t>
+          <t>DONE footer rebuilt from js/store-info.js (real About text, links to legal.html; contact/LTO lines hidden until the client confirms them); chat links hidden until chat is built; payment page Terms link fixed. From the first review.</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
@@ -6119,22 +6123,22 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>REQNF003, REQNF007</t>
+          <t>REQ039, REQ042</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Phone/tablet and cross-browser test pass</t>
+          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -6142,7 +6146,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>DONE EmailJS order template (ID to paste in js/emailjs-config.js) + on/off toggle in Account Settings. EmailJS free tier: 200/month.</t>
+        </is>
+      </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6151,7 +6159,7 @@
       <c r="J43" s="11" t="inlineStr"/>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6166,22 +6174,22 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Interviews 2, 4</t>
+          <t>REQ122</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
+          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
@@ -6189,11 +6197,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>DONE e1e200b. Required column in the monthly purchases report.</t>
-        </is>
-      </c>
+      <c r="H44" s="11" t="inlineStr"/>
       <c r="I44" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6202,7 +6206,7 @@
       <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6217,17 +6221,17 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Interview 4 walkthrough</t>
+          <t>REQ014</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Supplier history: everything received from each supplier</t>
+          <t>Save cart to the customer's account</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -6242,7 +6246,7 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>DONE Reports -&gt; Supplier Purchases (per supplier, per month). Shown to the client during the prototype walkthrough.</t>
+          <t>DONE 77336f3.</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -6268,22 +6272,22 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Methodology p.30; Interview 4</t>
+          <t>REQNF003, REQNF007</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>User manual + hands-on training + handover to the branch</t>
+          <t>Phone/tablet and cross-browser test pass</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Not verified</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr">
@@ -6291,11 +6295,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
-        </is>
-      </c>
+      <c r="H46" s="11" t="inlineStr"/>
       <c r="I46" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
+          <t>Interviews 2, 4</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
+          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b. Customer File groups every sale by customer name.</t>
+          <t>DONE e1e200b. Required column in the monthly purchases report.</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -6370,17 +6370,17 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Supplier sheets)</t>
+          <t>Interview 4 walkthrough</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
+          <t>Supplier history: everything received from each supplier</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b: unit cost + receipt/DR no. added; pack size stays in the product name as the branch does today. Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
+          <t>DONE Reports -&gt; Supplier Purchases (per supplier, per month). Shown to the client during the prototype walkthrough.</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -6421,22 +6421,22 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
+          <t>Methodology p.30; Interview 4</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies, Grocery</t>
+          <t>User manual + hands-on training + handover to the branch</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b: also storefront links/filters now follow Manage Categories. Existing Firebase projects keep their current categories - add the client's in Manage Categories.. Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
+          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -6457,7 +6457,7 @@
       <c r="J49" s="11" t="inlineStr"/>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6472,22 +6472,22 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087</t>
+          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Optional agreed price per wholesale buyer per product, used as default on their orders</t>
+          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>DONE saved from Process Order, listed in Edit account, default on orders. Keeps per-account pricing (no letter).</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE e1e200b. Customer File groups every sale by customer name.</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr"/>
@@ -6523,12 +6523,12 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>Report Formats sheet (Supplier sheets)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Cut database reads: stop loading whole collections on every page (Firestore free-plan daily read cap ~50k)</t>
+          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Needed before real use with the client's ~1,000-product catalog.</t>
+          <t>DONE e1e200b: unit cost + receipt/DR no. added; pack size stays in the product name as the branch does today. Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -6559,7 +6559,7 @@
       <c r="J51" s="11" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6574,17 +6574,17 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Dashboard module p.40; Interview 4 (dashboard export)</t>
+          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Dashboard Sales Analytics: show which dates the Today/Week/Month/Year view covers, and add a picker to choose a specific day, week, month or year (with previous/next)</t>
+          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies, Grocery</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>DONE cb08e78: date range shown; Day/Week/Month/Year with previous/next and a date picker; exports name the period. Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
+          <t>DONE e1e200b: also storefront links/filters now follow Manage Categories. Existing Firebase projects keep their current categories - add the client's in Manage Categories.. Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -6625,22 +6625,22 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>REQ048, Notification module</t>
+          <t>REQ085, REQ087</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Admin notification for pending wholesale orders (Pending -&gt; Released)</t>
+          <t>Optional agreed price per wholesale buyer per product, used as default on their orders</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -6650,18 +6650,18 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>DONE 274b8e0: wholesale orders start Pending; Mark Released in purchase history; staff notification.</t>
-        </is>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>DONE saved from Process Order, listed in Edit account, default on orders. Keeps per-account pricing (no letter).</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr"/>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6676,22 +6676,22 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>REQ111, Sales Report module</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Daily Sales report: batch, expiry, date received and supplier per item sold</t>
+          <t>Cut database reads: stop loading whole collections on every page (Firestore free-plan daily read cap ~50k)</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>DONE 274b8e0: 'Item Sold by Batch' section.</t>
+          <t>Needed before real use with the client's ~1,000-product catalog.</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -6727,17 +6727,17 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Project Context (p.1)</t>
+          <t>Dashboard module p.40; Interview 4 (dashboard export)</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>Dashboard Sales Analytics: show which dates the Today/Week/Month/Year view covers, and add a picker to choose a specific day, week, month or year (with previous/next)</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
+          <t>DONE cb08e78: date range shown; Day/Week/Month/Year with previous/next and a date picker; exports name the period. Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -6778,17 +6778,17 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.24)</t>
+          <t>REQ048, Notification module</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Admin notification for pending wholesale orders (Pending -&gt; Released)</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da: system now matches (BM-only finalize).</t>
+          <t>DONE 274b8e0: wholesale orders start Pending; Mark Released in purchase history; staff notification.</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -6814,7 +6814,7 @@
       <c r="J56" s="11" t="inlineStr"/>
       <c r="K56" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6829,17 +6829,17 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output) (p.27)</t>
+          <t>REQ111, Sales Report module</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>Daily Sales report: batch, expiry, date received and supplier per item sold</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>DONE footer links to legal.html on every page.</t>
+          <t>DONE 274b8e0: 'Item Sold by Batch' section.</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -6865,7 +6865,7 @@
       <c r="J57" s="11" t="inlineStr"/>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6875,27 +6875,27 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles (p.45-46)</t>
+          <t>Various</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>Bug check: checkout, reports, inventory and wholesale fixes (RX orders always pick-up, price/availability re-check, exchanges in sales reports, write-off date, stock count variance, receiving saved all at once, invoice peso sign)</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
@@ -6905,18 +6905,18 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
+          <t>DONE d51639d, 0e7826e.</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6926,22 +6926,22 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>REQ007 / Technical Background p.35-36</t>
+          <t>Project Context (p.1)</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -6956,18 +6956,18 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr"/>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6977,22 +6977,22 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>REQ008 p.47; Modules p.38</t>
+          <t>Theoretical Framework (p.24)</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
@@ -7007,18 +7007,18 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I60" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 06574da: system now matches (BM-only finalize).</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr"/>
       <c r="K60" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7028,22 +7028,22 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>REQ031 p.50</t>
+          <t>Conceptual Framework (Output) (p.27)</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -7058,18 +7058,18 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I61" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE footer links to legal.html on every page.</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr"/>
       <c r="K61" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7079,22 +7079,22 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>REQ073 p.55</t>
+          <t>Modules: Staff roles (p.45-46)</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -7120,7 +7120,7 @@
       <c r="J62" s="11" t="inlineStr"/>
       <c r="K62" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+          <t>REQ007 / Technical Background p.35-36</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087 p.57; Modules p.44</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Default wholesale price per product, adjustable per order (C9).</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+          <t>REQ073 p.55</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>REQ121 p.61</t>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 text p.67</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -7418,9 +7418,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I68" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr"/>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 diagram</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
@@ -7469,9 +7469,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr"/>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.5 text p.72</t>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 / 2.7 diagrams</t>
+          <t>REQ121 p.61</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.8 diagram + text p.76-77</t>
+          <t>Fig 2.2 text p.67</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -7645,12 +7645,12 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 diagram + text p.78-79</t>
+          <t>Fig 2.2 diagram</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.10 diagram</t>
+          <t>Fig 2.5 text p.72</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 diagram + text p.82-83</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
@@ -7798,17 +7798,17 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover (i)</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -7821,7 +7821,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H76" s="11" t="inlineStr"/>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -7845,22 +7849,22 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -7868,7 +7872,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H77" s="11" t="inlineStr"/>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -7892,17 +7900,17 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -7915,7 +7923,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H78" s="11" t="inlineStr"/>
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -7939,17 +7951,17 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input) (p.25)</t>
+          <t>Fig 2.11 diagram + text p.82-83</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -7962,10 +7974,14 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H79" s="11" t="inlineStr"/>
-      <c r="I79" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr"/>
@@ -7986,12 +8002,12 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.30-35)</t>
+          <t>Title page / cover (i)</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -8033,12 +8049,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -8048,7 +8064,7 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -8080,12 +8096,12 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -8122,42 +8138,38 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>REQ088</t>
+          <t>Conceptual Framework (Input) (p.25)</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Hide costing/wholesale prices from public reads</t>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H83" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED (revised): build it to avoid a removal letter.</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr"/>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
@@ -8173,48 +8185,44 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Interview 1</t>
+          <t>Methodology: sprint plan (p.30-35)</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H84" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H84" s="11" t="inlineStr"/>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr"/>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8224,48 +8232,44 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (CREDIT terms)</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Credit sales follow-up (who owes what, mark as paid)</t>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H85" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr"/>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr"/>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8275,22 +8279,22 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (daily Sales section)</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -8300,23 +8304,19 @@
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H86" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H86" s="11" t="inlineStr"/>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr"/>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8326,27 +8326,27 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>REQ088</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+          <t>Hide costing/wholesale prices from public reads</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -8354,7 +8354,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H87" s="11" t="inlineStr"/>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED (revised): build it to avoid a removal letter.</t>
+        </is>
+      </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8378,12 +8382,12 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>REQ013, REQ068</t>
+          <t>Interview 1</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Dosage/usage notes field on products</t>
+          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
@@ -8393,7 +8397,7 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr">
@@ -8403,18 +8407,18 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr"/>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8429,22 +8433,22 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>REQ049</t>
+          <t>Report Formats sheet (CREDIT terms)</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Supplier column in the inventory batch table</t>
+          <t>Credit sales follow-up (who owes what, mark as paid)</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -8454,18 +8458,18 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr"/>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8480,17 +8484,17 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>REQ103, REQ107</t>
+          <t>Report Formats sheet (daily Sales section)</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
+          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -8505,18 +8509,18 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
+          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr"/>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8526,22 +8530,22 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>REQ116</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Customer Accounts: list of the customer's orders</t>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -8554,11 +8558,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H91" s="11" t="inlineStr">
-        <is>
-          <t>DONE 847c877.</t>
-        </is>
-      </c>
+      <c r="H91" s="11" t="inlineStr"/>
       <c r="I91" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -8567,7 +8567,7 @@
       <c r="J91" s="11" t="inlineStr"/>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8582,17 +8582,17 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>REQ013, REQ068</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
+          <t>Dosage/usage notes field on products</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877. From the first review.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -8633,17 +8633,17 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>REQ070</t>
+          <t>REQ049</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Category rename: replace native prompt() with app dialog</t>
+          <t>Supplier column in the inventory batch table</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -8684,12 +8684,12 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>REQ033, REQ093</t>
+          <t>REQ103, REQ107</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
+          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92. From the first review.</t>
+          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>REQ099</t>
+          <t>REQ116</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>'Payment not received' as its own hold type</t>
+          <t>Customer Accounts: list of the customer's orders</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
@@ -8786,17 +8786,17 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>REQ026</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Checkout pick-up notice mentions bringing the original prescription</t>
+          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92.</t>
+          <t>DONE 847c877. From the first review.</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -8837,17 +8837,17 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>REQ009</t>
+          <t>REQ070</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Show quantity in stock on catalog cards</t>
+          <t>Category rename: replace native prompt() with app dialog</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -8888,17 +8888,17 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>REQ040</t>
+          <t>REQ033, REQ093</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Profile picture in Account Settings</t>
+          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3.</t>
+          <t>DONE 082ec92. From the first review.</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>REQNF028</t>
+          <t>REQ099</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
+          <t>'Payment not received' as its own hold type</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
@@ -8990,17 +8990,17 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>REQ047</t>
+          <t>REQ026</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
+          <t>Checkout pick-up notice mentions bringing the original prescription</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
+          <t>DONE 082ec92.</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>REQNF017</t>
+          <t>REQ009</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>README with setup steps; fix the error message that points to it</t>
+          <t>Show quantity in stock on catalog cards</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3. From the first review.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>REQ001</t>
+          <t>REQ040</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Normalize phone number at registration</t>
+          <t>Profile picture in Account Settings</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b. From the first review.</t>
+          <t>DONE 77336f3.</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -9143,17 +9143,17 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>REQ008; Interview 1</t>
+          <t>REQNF028</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
+          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -9194,17 +9194,17 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>REQ031</t>
+          <t>REQ047</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
+          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
+          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37</t>
+          <t>REQNF017</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
+          <t>README with setup steps; fix the error message that points to it</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>DONE Dashboard: stock in vs stock out per day/week/month/year. Keeps the Chart.js claim (no letter).</t>
+          <t>DONE 77336f3. From the first review.</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -9296,17 +9296,17 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Modules p.42</t>
+          <t>REQ001</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
+          <t>Normalize phone number at registration</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
+          <t>DONE d9fc96b. From the first review.</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework p.23</t>
+          <t>REQ008; Interview 1</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
+          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
+          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -9398,17 +9398,17 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>REQ039, Fig 2.10, C16</t>
+          <t>REQ031</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
+          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -9449,17 +9449,17 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>REQ004</t>
+          <t>Technical Background p.35-37</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Login lockout counter can be reset by anyone (public loginAttempts collection)</t>
+          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Lockout works for normal use; a determined attacker could clear it. Mention as a limitation if not fixed.</t>
+          <t>DONE Dashboard: stock in vs stock out per day/week/month/year. Keeps the Chart.js claim (no letter).</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -9485,7 +9485,7 @@
       <c r="J109" s="11" t="inlineStr"/>
       <c r="K109" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9500,17 +9500,17 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>System roles (-)</t>
+          <t>Modules p.42</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
@@ -9523,7 +9523,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H110" s="11" t="inlineStr"/>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
+        </is>
+      </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -9532,7 +9536,7 @@
       <c r="J110" s="11" t="inlineStr"/>
       <c r="K110" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9542,22 +9546,22 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Whole paper + system (-)</t>
+          <t>Theoretical Framework p.23</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
@@ -9570,16 +9574,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H111" s="11" t="inlineStr"/>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
+        </is>
+      </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr"/>
       <c r="K111" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9589,27 +9597,27 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044</t>
+          <t>REQ039, Fig 2.10, C16</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>New-device code is checked in the browser, not by the database rules</t>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
@@ -9619,18 +9627,18 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>Stops normal use of a stolen password; a technical attacker could skip it. State this in Limitations.</t>
+          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J112" s="11" t="inlineStr"/>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9640,22 +9648,22 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>REQ004</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>Login lockout counter can be reset by anyone (public loginAttempts collection)</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -9670,12 +9678,12 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Lockout works for normal use; a determined attacker could clear it. Mention as a limitation if not fixed.</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J113" s="11" t="inlineStr"/>
@@ -9691,22 +9699,22 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>System roles (-)</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -9719,14 +9727,10 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H114" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I114" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H114" s="11" t="inlineStr"/>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J114" s="11" t="inlineStr"/>
@@ -9742,22 +9746,22 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Scope p.6; Product Browsing REQ009</t>
+          <t>Whole paper + system (-)</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -9770,14 +9774,10 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H115" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H115" s="11" t="inlineStr"/>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr"/>
@@ -9798,22 +9798,22 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Scope and Limitations p.7</t>
+          <t>REQ005, REQ044</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+          <t>New-device code is checked in the browser, not by the database rules</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr">
@@ -9823,12 +9823,12 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Stops normal use of a stolen password; a technical attacker could skip it. State this in Limitations.</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J116" s="11" t="inlineStr"/>
@@ -9849,17 +9849,17 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Decision-dependent</t>
+          <t>REQ090</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+          <t>Known, not fixed: two wholesale exchanges on the same order line at the same second can mix up which batch a later return goes back to (stock totals stay right)</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+          <t>Rare; same-second exchanges on one line.</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
@@ -9900,17 +9900,17 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>REQ125</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>Known, not fixed: if creating a staff account fails after the login is made, the email can't be reused until the login is removed in the Firebase console</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
@@ -9923,7 +9923,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H118" s="11" t="inlineStr"/>
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>Needs a server function to clean up; note in the user manual.</t>
+        </is>
+      </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -9947,17 +9951,17 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Scope (p.6)</t>
+          <t>Modules FEFO p.41</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>Add the 2-month Bad Order step (C7).</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
@@ -9970,10 +9974,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H119" s="11" t="inlineStr"/>
-      <c r="I119" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J119" s="11" t="inlineStr"/>
@@ -9994,17 +10002,17 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.22-23)</t>
+          <t>Technical Background p.35-37; Budget p.99</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
@@ -10019,7 +10027,7 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
+          <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I120" s="12" t="inlineStr">
@@ -10030,7 +10038,7 @@
       <c r="J120" s="11" t="inlineStr"/>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -10045,17 +10053,17 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.32)</t>
+          <t>Scope p.6; Product Browsing REQ009</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr">
@@ -10068,10 +10076,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H121" s="11" t="inlineStr"/>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr"/>
@@ -10092,17 +10104,17 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Scope and Limitations p.7</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr">
@@ -10115,10 +10127,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H122" s="11" t="inlineStr"/>
+      <c r="H122" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr"/>
@@ -10139,17 +10155,17 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Decision-dependent</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
@@ -10162,10 +10178,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H123" s="11" t="inlineStr"/>
-      <c r="I123" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J123" s="11" t="inlineStr"/>
@@ -10186,12 +10206,12 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
@@ -10209,20 +10229,16 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H124" s="11" t="inlineStr">
-        <is>
-          <t>DONE No paper change needed: dashboard now has the inventory movement chart.</t>
-        </is>
-      </c>
-      <c r="I124" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H124" s="11" t="inlineStr"/>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J124" s="11" t="inlineStr"/>
       <c r="K124" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -10237,12 +10253,12 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Scope (p.6)</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
@@ -10284,12 +10300,12 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.36-38)</t>
+          <t>Theoretical Framework (p.22-23)</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
@@ -10307,16 +10323,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H126" s="11" t="inlineStr"/>
-      <c r="I126" s="11" t="inlineStr">
-        <is>
-          <t>Adds</t>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
+        </is>
+      </c>
+      <c r="I126" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J126" s="11" t="inlineStr"/>
       <c r="K126" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10331,12 +10351,12 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.38)</t>
+          <t>Methodology: sprint plan (p.32)</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
@@ -10378,12 +10398,12 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Modules: Price Management (p.42)</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
@@ -10401,20 +10421,16 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H128" s="11" t="inlineStr">
-        <is>
-          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
-        </is>
-      </c>
-      <c r="I128" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H128" s="11" t="inlineStr"/>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J128" s="11" t="inlineStr"/>
       <c r="K128" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -10429,12 +10445,12 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
@@ -10453,9 +10469,9 @@
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr"/>
-      <c r="I129" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I129" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J129" s="11" t="inlineStr"/>
@@ -10476,12 +10492,12 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.97-98)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
@@ -10499,16 +10515,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H130" s="11" t="inlineStr"/>
-      <c r="I130" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: dashboard now has the inventory movement chart.</t>
+        </is>
+      </c>
+      <c r="I130" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J130" s="11" t="inlineStr"/>
       <c r="K130" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10523,12 +10543,12 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
@@ -10547,9 +10567,9 @@
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr"/>
-      <c r="I131" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J131" s="11" t="inlineStr"/>
@@ -10570,12 +10590,12 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background: Software (p.36-38)</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
@@ -10596,7 +10616,7 @@
       <c r="H132" s="11" t="inlineStr"/>
       <c r="I132" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J132" s="11" t="inlineStr"/>
@@ -10617,12 +10637,12 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>References (p.100)</t>
+          <t>Technical Background: Software (p.38)</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
@@ -10664,12 +10684,12 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>References (p.10 / refs)</t>
+          <t>Modules: Price Management (p.42)</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
@@ -10687,16 +10707,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H134" s="11" t="inlineStr"/>
-      <c r="I134" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
+        </is>
+      </c>
+      <c r="I134" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J134" s="11" t="inlineStr"/>
       <c r="K134" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10711,12 +10735,12 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>References (p.17 / refs)</t>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
@@ -10758,12 +10782,12 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Appendices (p.124)</t>
+          <t>Calendar of Activities (p.97-98)</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
@@ -10805,12 +10829,12 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+          <t>Budgetary Estimate (p.99)</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>Regenerate page numbers after all edits.</t>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
@@ -10841,18 +10865,300 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="11" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr"/>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="inlineStr"/>
+      <c r="K138" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>References (p.100)</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr"/>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="inlineStr"/>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>References (p.10 / refs)</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr"/>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr"/>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>References (p.17 / refs)</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr"/>
+      <c r="I141" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J141" s="11" t="inlineStr"/>
+      <c r="K141" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>Appendices (p.124)</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G142" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H142" s="11" t="inlineStr"/>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J142" s="11" t="inlineStr"/>
+      <c r="K142" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr"/>
+      <c r="I143" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J143" s="11" t="inlineStr"/>
+      <c r="K143" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K137"/>
-  <conditionalFormatting sqref="K2:K137">
+  <autoFilter ref="A1:K143"/>
+  <conditionalFormatting sqref="K2:K143">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -9900,7 +9900,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>REQ125</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
@@ -3972,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K143"/>
+  <dimension ref="A1:K144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9951,17 +9951,17 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>Technical Background (Chart.js 'inventory movement data'), Dashboard module</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>Inventory Movement chart removed from the dashboard at the team's request (2026-10-21)</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Removed</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I119" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+          <t>Paper: drop 'inventory movement data' from the Chart.js line, or note it in the panel letter; stock in/out is still in the Inventory page and reports.</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J119" s="11" t="inlineStr"/>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>Modules FEFO p.41</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>Add the 2-month Bad Order step (C7).</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
@@ -10030,9 +10030,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I120" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr"/>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Scope p.6; Product Browsing REQ009</t>
+          <t>Technical Background p.35-37; Budget p.99</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
@@ -10081,9 +10081,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I121" s="11" t="inlineStr">
-        <is>
-          <t>Adds</t>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr"/>
@@ -10104,12 +10104,12 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Scope and Limitations p.7</t>
+          <t>Scope p.6; Product Browsing REQ009</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -10155,12 +10155,12 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Decision-dependent</t>
+          <t>Scope and Limitations p.7</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+          <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J123" s="11" t="inlineStr"/>
@@ -10206,17 +10206,17 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Decision-dependent</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr">
@@ -10229,7 +10229,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H124" s="11" t="inlineStr"/>
+      <c r="H124" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -10253,12 +10257,12 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Scope (p.6)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
@@ -10277,9 +10281,9 @@
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr"/>
-      <c r="I125" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J125" s="11" t="inlineStr"/>
@@ -10300,12 +10304,12 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.22-23)</t>
+          <t>Scope (p.6)</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
@@ -10323,11 +10327,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H126" s="11" t="inlineStr">
-        <is>
-          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
-        </is>
-      </c>
+      <c r="H126" s="11" t="inlineStr"/>
       <c r="I126" s="12" t="inlineStr">
         <is>
           <t>REMOVES / narrows - see Removals (Letter)</t>
@@ -10336,7 +10336,7 @@
       <c r="J126" s="11" t="inlineStr"/>
       <c r="K126" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -10351,12 +10351,12 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.32)</t>
+          <t>Theoretical Framework (p.22-23)</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
@@ -10374,16 +10374,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H127" s="11" t="inlineStr"/>
-      <c r="I127" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
+        </is>
+      </c>
+      <c r="I127" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J127" s="11" t="inlineStr"/>
       <c r="K127" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10398,12 +10402,12 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Methodology: sprint plan (p.32)</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
@@ -10445,12 +10449,12 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
@@ -10469,9 +10473,9 @@
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr"/>
-      <c r="I129" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J129" s="11" t="inlineStr"/>
@@ -10497,7 +10501,7 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
@@ -10515,11 +10519,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H130" s="11" t="inlineStr">
-        <is>
-          <t>DONE No paper change needed: dashboard now has the inventory movement chart.</t>
-        </is>
-      </c>
+      <c r="H130" s="11" t="inlineStr"/>
       <c r="I130" s="12" t="inlineStr">
         <is>
           <t>REMOVES / narrows - see Removals (Letter)</t>
@@ -10528,7 +10528,7 @@
       <c r="J130" s="11" t="inlineStr"/>
       <c r="K130" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -10543,12 +10543,12 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
@@ -10566,7 +10566,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H131" s="11" t="inlineStr"/>
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: dashboard now has the inventory movement chart.</t>
+        </is>
+      </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
           <t>REMOVES / narrows - see Removals (Letter)</t>
@@ -10575,7 +10579,7 @@
       <c r="J131" s="11" t="inlineStr"/>
       <c r="K131" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10590,12 +10594,12 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.36-38)</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
@@ -10614,9 +10618,9 @@
         </is>
       </c>
       <c r="H132" s="11" t="inlineStr"/>
-      <c r="I132" s="11" t="inlineStr">
-        <is>
-          <t>Adds</t>
+      <c r="I132" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J132" s="11" t="inlineStr"/>
@@ -10637,12 +10641,12 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.38)</t>
+          <t>Technical Background: Software (p.36-38)</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
@@ -10663,7 +10667,7 @@
       <c r="H133" s="11" t="inlineStr"/>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J133" s="11" t="inlineStr"/>
@@ -10684,12 +10688,12 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Modules: Price Management (p.42)</t>
+          <t>Technical Background: Software (p.38)</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
@@ -10707,20 +10711,16 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H134" s="11" t="inlineStr">
-        <is>
-          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
-        </is>
-      </c>
-      <c r="I134" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H134" s="11" t="inlineStr"/>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J134" s="11" t="inlineStr"/>
       <c r="K134" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -10735,12 +10735,12 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+          <t>Modules: Price Management (p.42)</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
@@ -10758,16 +10758,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H135" s="11" t="inlineStr"/>
-      <c r="I135" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
+        </is>
+      </c>
+      <c r="I135" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J135" s="11" t="inlineStr"/>
       <c r="K135" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10782,12 +10786,12 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.97-98)</t>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
@@ -10829,12 +10833,12 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Calendar of Activities (p.97-98)</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
@@ -10881,7 +10885,7 @@
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
@@ -10923,12 +10927,12 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>References (p.100)</t>
+          <t>Budgetary Estimate (p.99)</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
@@ -10970,12 +10974,12 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>References (p.10 / refs)</t>
+          <t>References (p.100)</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
@@ -11017,12 +11021,12 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>References (p.17 / refs)</t>
+          <t>References (p.10 / refs)</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
@@ -11064,12 +11068,12 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Appendices (p.124)</t>
+          <t>References (p.17 / refs)</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
@@ -11111,12 +11115,12 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+          <t>Appendices (p.124)</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>Regenerate page numbers after all edits.</t>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
@@ -11147,18 +11151,65 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="11" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G144" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H144" s="11" t="inlineStr"/>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J144" s="11" t="inlineStr"/>
+      <c r="K144" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K143"/>
-  <conditionalFormatting sqref="K2:K143">
+  <autoFilter ref="A1:K144"/>
+  <conditionalFormatting sqref="K2:K144">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$167</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
@@ -3972,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K144"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5472,22 +5472,22 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>Live chat module</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
+          <t>Decide the live chat health approach with Amson / their pharmacist: label matching (now), staff-assigned condition shelves, or Shopee-style ingredient info with guardrails</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -5495,7 +5495,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Label matching can suggest a pain reliever for any pain (e.g. foot pain -&gt; Biogesic). Paper wording must stay honest: suggestions, not advice.</t>
+        </is>
+      </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5524,7 +5528,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
+          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -5566,12 +5570,12 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -5608,22 +5612,22 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
+          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -5636,11 +5640,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>DONE d9fc96b: locks itself after one run; SI counter now staff-only in rules (publish rules). From the first review.</t>
-        </is>
-      </c>
+      <c r="H33" s="11" t="inlineStr"/>
       <c r="I33" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5649,7 +5649,7 @@
       <c r="J33" s="11" t="inlineStr"/>
       <c r="K33" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>REQ002</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
+          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE d9fc96b: locks itself after one run; SI counter now staff-only in rules (publish rules). From the first review.</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -5700,7 +5700,7 @@
       <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5715,22 +5715,22 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
+          <t>REQ002</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Unrecognized-device OTP for customers and staff</t>
+          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>DONE 7ede9d4: emailed code on new browsers, customers and staff; recognized devices in Account Settings.</t>
+          <t>From the first review.</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -5751,7 +5751,7 @@
       <c r="J35" s="11" t="inlineStr"/>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5766,17 +5766,17 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>REQ086, REQ089, REQ091, REQ092</t>
+          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
+          <t>Unrecognized-device OTP for customers and staff</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>DONE 5cad255: history, sales invoice PDF, free-of-cost, LTO/permit validity. Not built: reorder from a past order. Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
+          <t>DONE 7ede9d4: emailed code on new browsers, customers and staff; recognized devices in Account Settings.</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -5817,17 +5817,17 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>REQ090, REQ114, Fig 2.15</t>
+          <t>REQ086, REQ089, REQ091, REQ092</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
+          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>DONE Purchase History -&gt; Exchange: return to batch, FEFO replacement, value rule, audit, exchange document; Return / Exchange report.</t>
+          <t>DONE 5cad255: history, sales invoice PDF, free-of-cost, LTO/permit validity. Not built: reorder from a past order. Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>REQ067, C7</t>
+          <t>REQ090, REQ114, Fig 2.15</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
+          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>DONE d2a957b: automatic write-off with reason, audit entry, disposal alert, Mark disposed.</t>
+          <t>DONE Purchase History -&gt; Exchange: return to batch, FEFO replacement, value rule, audit, exchange document; Return / Exchange report.</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
+          <t>REQ067, C7</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
+          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout. The 'not an official receipt' line was removed from POS and online receipts on 2026-10-21 at the team's request.</t>
+          <t>DONE d2a957b: automatic write-off with reason, audit entry, disposal alert, Mark disposed.</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>REQ084</t>
+          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>POS: RX Verified checkbox + optional notes</t>
+          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: checkbox + notes, required for RX items, saved on the sale.</t>
+          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout. The 'not an official receipt' line was removed from POS and online receipts on 2026-10-21 at the team's request.</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
@@ -6021,17 +6021,17 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>REQ061, C5</t>
+          <t>REQ084</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
+          <t>POS: RX Verified checkbox + optional notes</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da: others save counts; BM finalizes; variance reason required and logged.</t>
+          <t>DONE 57f4d80: checkbox + notes, required for RX items, saved on the sale.</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -6072,17 +6072,17 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>REQNF025, REQNF029</t>
+          <t>REQ061, C5</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
+          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>DONE footer rebuilt from js/store-info.js (real About text, links to legal.html; contact/LTO lines hidden until the client confirms them); chat links hidden until chat is built; payment page Terms link fixed. From the first review.</t>
+          <t>DONE 06574da: others save counts; BM finalizes; variance reason required and logged.</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
@@ -6123,22 +6123,22 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>REQ039, REQ042</t>
+          <t>REQNF025, REQNF029</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
+          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>DONE EmailJS order template (ID to paste in js/emailjs-config.js) + on/off toggle in Account Settings. EmailJS free tier: 200/month.</t>
+          <t>DONE footer rebuilt from js/store-info.js (real About text, links to legal.html; contact/LTO lines hidden until the client confirms them); chat links hidden until chat is built; payment page Terms link fixed. From the first review.</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>REQ122</t>
+          <t>REQ039, REQ042</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
+          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -6197,7 +6197,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>DONE EmailJS order template (ID to paste in js/emailjs-config.js) + on/off toggle in Account Settings. EmailJS free tier: 200/month.</t>
+        </is>
+      </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6206,7 +6210,7 @@
       <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6221,22 +6225,22 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>REQ014</t>
+          <t>REQ122</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Save cart to the customer's account</t>
+          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -6244,11 +6248,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>DONE 77336f3.</t>
-        </is>
-      </c>
+      <c r="H45" s="11" t="inlineStr"/>
       <c r="I45" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6257,7 +6257,7 @@
       <c r="J45" s="11" t="inlineStr"/>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6272,17 +6272,17 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>REQNF003, REQNF007</t>
+          <t>REQ014</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Phone/tablet and cross-browser test pass</t>
+          <t>Save cart to the customer's account</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -6295,7 +6295,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>DONE 77336f3.</t>
+        </is>
+      </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6304,7 +6308,7 @@
       <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6319,17 +6323,17 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Interviews 2, 4</t>
+          <t>REQNF003, REQNF007</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
+          <t>Phone/tablet and cross-browser test pass</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Not verified</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -6342,11 +6346,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>DONE e1e200b. Required column in the monthly purchases report.</t>
-        </is>
-      </c>
+      <c r="H47" s="11" t="inlineStr"/>
       <c r="I47" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6355,7 +6355,7 @@
       <c r="J47" s="11" t="inlineStr"/>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6370,12 +6370,12 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Interview 4 walkthrough</t>
+          <t>Interviews 2, 4</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Supplier history: everything received from each supplier</t>
+          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>DONE Reports -&gt; Supplier Purchases (per supplier, per month). Shown to the client during the prototype walkthrough.</t>
+          <t>DONE e1e200b. Required column in the monthly purchases report.</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Methodology p.30; Interview 4</t>
+          <t>Interview 4 walkthrough</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>User manual + hands-on training + handover to the branch</t>
+          <t>Supplier history: everything received from each supplier</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
+          <t>DONE Reports -&gt; Supplier Purchases (per supplier, per month). Shown to the client during the prototype walkthrough.</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -6457,7 +6457,7 @@
       <c r="J49" s="11" t="inlineStr"/>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6472,12 +6472,12 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
+          <t>Methodology p.30; Interview 4</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
+          <t>User manual + hands-on training + handover to the branch</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b. Customer File groups every sale by customer name.</t>
+          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
@@ -6508,7 +6508,7 @@
       <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6523,17 +6523,17 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Supplier sheets)</t>
+          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
+          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b: unit cost + receipt/DR no. added; pack size stays in the product name as the branch does today. Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
+          <t>DONE e1e200b. Customer File groups every sale by customer name.</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -6574,17 +6574,17 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
+          <t>Report Formats sheet (Supplier sheets)</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies, Grocery</t>
+          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b: also storefront links/filters now follow Manage Categories. Existing Firebase projects keep their current categories - add the client's in Manage Categories.. Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
+          <t>DONE e1e200b: unit cost + receipt/DR no. added; pack size stays in the product name as the branch does today. Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -6625,22 +6625,22 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087</t>
+          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Optional agreed price per wholesale buyer per product, used as default on their orders</t>
+          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies, Grocery</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>DONE saved from Process Order, listed in Edit account, default on orders. Keeps per-account pricing (no letter).</t>
-        </is>
-      </c>
-      <c r="I53" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE e1e200b: also storefront links/filters now follow Manage Categories. Existing Firebase projects keep their current categories - add the client's in Manage Categories.. Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr"/>
@@ -6676,12 +6676,12 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>REQ085, REQ087</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Cut database reads: stop loading whole collections on every page (Firestore free-plan daily read cap ~50k)</t>
+          <t>Optional agreed price per wholesale buyer per product, used as default on their orders</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -6701,18 +6701,18 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>Needed before real use with the client's ~1,000-product catalog.</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>DONE saved from Process Order, listed in Edit account, default on orders. Keeps per-account pricing (no letter).</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6727,22 +6727,22 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Dashboard module p.40; Interview 4 (dashboard export)</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Dashboard Sales Analytics: show which dates the Today/Week/Month/Year view covers, and add a picker to choose a specific day, week, month or year (with previous/next)</t>
+          <t>Cut database reads: stop loading whole collections on every page (Firestore free-plan daily read cap ~50k)</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>DONE cb08e78: date range shown; Day/Week/Month/Year with previous/next and a date picker; exports name the period. Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
+          <t>Needed before real use with the client's ~1,000-product catalog.</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -6763,7 +6763,7 @@
       <c r="J55" s="11" t="inlineStr"/>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6778,17 +6778,17 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>REQ048, Notification module</t>
+          <t>Dashboard module p.40; Interview 4 (dashboard export)</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Admin notification for pending wholesale orders (Pending -&gt; Released)</t>
+          <t>Dashboard Sales Analytics: show which dates the Today/Week/Month/Year view covers, and add a picker to choose a specific day, week, month or year (with previous/next)</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>DONE 274b8e0: wholesale orders start Pending; Mark Released in purchase history; staff notification.</t>
+          <t>DONE cb08e78: date range shown; Day/Week/Month/Year with previous/next and a date picker; exports name the period. Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -6814,7 +6814,7 @@
       <c r="J56" s="11" t="inlineStr"/>
       <c r="K56" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>REQ111, Sales Report module</t>
+          <t>REQ048, Notification module</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Daily Sales report: batch, expiry, date received and supplier per item sold</t>
+          <t>Admin notification for pending wholesale orders (Pending -&gt; Released)</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>DONE 274b8e0: 'Item Sold by Batch' section.</t>
+          <t>DONE 274b8e0: wholesale orders start Pending; Mark Released in purchase history; staff notification.</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -6880,12 +6880,12 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>REQ111, Sales Report module</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Bug check: checkout, reports, inventory and wholesale fixes (RX orders always pick-up, price/availability re-check, exchanges in sales reports, write-off date, stock count variance, receiving saved all at once, invoice peso sign)</t>
+          <t>Daily Sales report: batch, expiry, date received and supplier per item sold</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>DONE d51639d, 0e7826e.</t>
+          <t>DONE 274b8e0: 'Item Sold by Batch' section.</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -6931,22 +6931,22 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Project Context (p.1)</t>
+          <t>Various</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>Bug check: checkout, reports, inventory and wholesale fixes (RX orders always pick-up, price/availability re-check, exchanges in sales reports, write-off date, stock count variance, receiving saved all at once, invoice peso sign)</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
+          <t>DONE d51639d, 0e7826e.</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -6967,7 +6967,7 @@
       <c r="J59" s="11" t="inlineStr"/>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6982,17 +6982,17 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.24)</t>
+          <t>Shopping cart module, REQ014-016</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Buy Now goes to the cart page; Add to Cart / Buy Now no longer lose items on the next page</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da: system now matches (BM-only finalize).</t>
+          <t>DONE 010449e, 62b3c79. Cart sync uses a saved-at time so the newest cart wins; Buy Now adds the item and opens the cart.</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -7033,17 +7033,17 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output) (p.27)</t>
+          <t>Inventory module, REQ061-063</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>Receive Stock: every field required; supplier must be chosen (no 'No supplier')</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>DONE footer links to legal.html on every page.</t>
+          <t>DONE 1581610. Same rules for the form, Excel upload and PO delivery.</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -7079,22 +7079,22 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles (p.45-46)</t>
+          <t>Inventory module, FEFO (REQ064-066)</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>Batch numbers: same product + batch + expiry adds to that batch; same batch with a different expiry is refused; Bad Order batches can't be received again</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
+          <t>DONE df65830, a15c428. Team asked for unique batch numbers; agreed on this common practice since each batch has one expiry. Deliveries listed per batch.</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr"/>
@@ -7130,22 +7130,22 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>REQ007 / Technical Background p.35-36</t>
+          <t>Report Formats (client's month-end report), REQ111</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+          <t>Monthly Inventory report: Supplier column and an EXPIRED sheet (batches that expired in the month)</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -7160,18 +7160,18 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE 59f740f. Team request 2026-10-21.</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr"/>
       <c r="K63" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7181,22 +7181,22 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>REQ008 p.47; Modules p.38</t>
+          <t>POS module, REQ070-072</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
+          <t>POS: Reference No. required for GCash, bank transfer and card terminal payments</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
@@ -7211,18 +7211,18 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I64" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 2a52561. Saved on the sale, shown on receipt and reports.</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr"/>
       <c r="K64" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7232,22 +7232,22 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>REQ031 p.50</t>
+          <t>Audit log, REQNF011</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+          <t>Audit log covers every stock and order movement (receive, write-off, PO, walk-in sale, order status changes, customer received/auto-delivered)</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -7262,18 +7262,18 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I65" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 2a52561. Team request 2026-10-21.</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr"/>
       <c r="K65" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7283,27 +7283,27 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>REQ073 p.55</t>
+          <t>Live chat module</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+          <t>Live chat: order cards ('My orders') and 'what we carry for this' product cards for symptoms, with a fixed caution and a pharmacist hand-off</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
@@ -7313,18 +7313,18 @@
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE d45e61b, 128d7d2. Products are matched by words on their labels (dosage notes); Gemini only reads the question, it never names a medicine.</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr"/>
       <c r="K66" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7334,22 +7334,22 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+          <t>Tech Stack (free plans)</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+          <t>Before go-live: serve smaller Cloudinary images and shrink uploads; cut Firestore reads</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Keeps Cloudinary and Firestore on the free plans as visits grow. Offered, not built yet.</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr"/>
@@ -7385,22 +7385,22 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087 p.57; Modules p.44</t>
+          <t>Project Context (p.1)</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Default wholesale price per product, adjustable per order (C9).</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
@@ -7415,18 +7415,18 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I68" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr"/>
       <c r="K68" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7436,22 +7436,22 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+          <t>Theoretical Framework (p.24)</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -7466,18 +7466,18 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I69" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 06574da: system now matches (BM-only finalize).</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr"/>
       <c r="K69" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7487,22 +7487,22 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+          <t>Conceptual Framework (Output) (p.27)</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
@@ -7517,18 +7517,18 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE footer links to legal.html on every page.</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr"/>
       <c r="K70" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7538,22 +7538,22 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>REQ121 p.61</t>
+          <t>Modules: Staff roles (p.45-46)</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -7579,7 +7579,7 @@
       <c r="J71" s="11" t="inlineStr"/>
       <c r="K71" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7594,17 +7594,17 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 text p.67</t>
+          <t>REQ001 registration, Scope and Limitations</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+          <t>Phone number verification by SMS code: on hold (every SMS costs money; Amson doesn't want to spend)</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Paper: state in Limitations (number format checked, not ownership) and in Recommendations (SMS OTP).</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 diagram</t>
+          <t>Chapter 3 evaluation (Objective 4)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+          <t>Evaluation survey questionnaires: Branch Manager, Technical Staff, Sales Staff and User forms, mapped to TAM + ISO/IEC 25010</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE Claude Docs, 2026-10-22. In Claude Docs ('Survey Questionnaires (Admin and User)'); maintainability covered by the developers' testing (no IT expert form).</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
@@ -7681,7 +7681,7 @@
       <c r="J73" s="11" t="inlineStr"/>
       <c r="K73" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7696,12 +7696,12 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.5 text p.72</t>
+          <t>REQ007 / Technical Background p.35-36</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 / 2.7 diagrams</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
@@ -7775,9 +7775,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr"/>
@@ -7798,12 +7798,12 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.8 diagram + text p.76-77</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -7826,9 +7826,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr"/>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 diagram + text p.78-79</t>
+          <t>REQ073 p.55</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.10 diagram</t>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 diagram + text p.82-83</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -7979,9 +7979,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr"/>
@@ -8002,17 +8002,17 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover (i)</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
@@ -8025,10 +8025,14 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H80" s="11" t="inlineStr"/>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H80" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr"/>
@@ -8049,22 +8053,22 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -8072,7 +8076,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H81" s="11" t="inlineStr"/>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -8096,17 +8104,17 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>REQ121 p.61</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
@@ -8119,7 +8127,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H82" s="11" t="inlineStr"/>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -8143,17 +8155,17 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input) (p.25)</t>
+          <t>Fig 2.2 text p.67</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -8166,10 +8178,14 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H83" s="11" t="inlineStr"/>
-      <c r="I83" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
@@ -8190,17 +8206,17 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.30-35)</t>
+          <t>Fig 2.2 diagram</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -8213,7 +8229,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H84" s="11" t="inlineStr"/>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -8237,17 +8257,17 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Fig 2.5 text p.72</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -8260,7 +8280,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H85" s="11" t="inlineStr"/>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -8284,17 +8308,17 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -8307,7 +8331,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H86" s="11" t="inlineStr"/>
+      <c r="H86" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -8326,42 +8354,42 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>REQ088</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Hide costing/wholesale prices from public reads</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>DECIDED (revised): build it to avoid a removal letter.</t>
+          <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr"/>
@@ -8377,48 +8405,48 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Interview 1</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
+          <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr"/>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8428,48 +8456,48 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (CREDIT terms)</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Credit sales follow-up (who owes what, mark as paid)</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
+          <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr"/>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8479,22 +8507,22 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (daily Sales section)</t>
+          <t>Fig 2.11 diagram + text p.82-83</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -8504,23 +8532,23 @@
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
+          <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr"/>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8530,17 +8558,17 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Title page / cover (i)</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
@@ -8555,13 +8583,13 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr"/>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr"/>
@@ -8577,48 +8605,44 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>REQ013, REQ068</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Dosage/usage notes field on products</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H92" s="11" t="inlineStr">
-        <is>
-          <t>DONE 06574da.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H92" s="11" t="inlineStr"/>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr"/>
       <c r="K92" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8628,22 +8652,22 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>REQ049</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Supplier column in the inventory batch table</t>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -8653,23 +8677,19 @@
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H93" s="11" t="inlineStr">
-        <is>
-          <t>DONE 06574da.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="inlineStr"/>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr"/>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8679,22 +8699,22 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>REQ103, REQ107</t>
+          <t>Conceptual Framework (Input) (p.25)</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -8704,23 +8724,19 @@
       </c>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H94" s="11" t="inlineStr">
-        <is>
-          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H94" s="11" t="inlineStr"/>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr"/>
       <c r="K94" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8730,22 +8746,22 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>REQ116</t>
+          <t>Methodology: sprint plan (p.30-35)</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Customer Accounts: list of the customer's orders</t>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -8755,23 +8771,19 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H95" s="11" t="inlineStr">
-        <is>
-          <t>DONE 847c877.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr"/>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr"/>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8781,22 +8793,22 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -8806,23 +8818,19 @@
       </c>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H96" s="11" t="inlineStr">
-        <is>
-          <t>DONE 847c877. From the first review.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H96" s="11" t="inlineStr"/>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr"/>
       <c r="K96" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8832,22 +8840,22 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>REQ070</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Category rename: replace native prompt() with app dialog</t>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -8857,23 +8865,19 @@
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H97" s="11" t="inlineStr">
-        <is>
-          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr"/>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr"/>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8888,12 +8892,12 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>REQ033, REQ093</t>
+          <t>REQ088</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
+          <t>Hide costing/wholesale prices from public reads</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -8903,7 +8907,7 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -8913,7 +8917,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92. From the first review.</t>
+          <t>DECIDED (revised): build it to avoid a removal letter.</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -8924,7 +8928,7 @@
       <c r="J98" s="11" t="inlineStr"/>
       <c r="K98" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8939,22 +8943,22 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>REQ099</t>
+          <t>Interview 1</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>'Payment not received' as its own hold type</t>
+          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -8964,18 +8968,18 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr"/>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -8990,22 +8994,22 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>REQ026</t>
+          <t>Report Formats sheet (CREDIT terms)</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Checkout pick-up notice mentions bringing the original prescription</t>
+          <t>Credit sales follow-up (who owes what, mark as paid)</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
@@ -9015,18 +9019,18 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92.</t>
+          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr"/>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -9041,17 +9045,17 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>REQ009</t>
+          <t>Report Formats sheet (daily Sales section)</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Show quantity in stock on catalog cards</t>
+          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -9066,18 +9070,18 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr"/>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -9087,22 +9091,22 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>REQ040</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Profile picture in Account Settings</t>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -9115,11 +9119,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H102" s="11" t="inlineStr">
-        <is>
-          <t>DONE 77336f3.</t>
-        </is>
-      </c>
+      <c r="H102" s="11" t="inlineStr"/>
       <c r="I102" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -9128,7 +9128,7 @@
       <c r="J102" s="11" t="inlineStr"/>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9143,17 +9143,17 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>REQNF028</t>
+          <t>REQ013, REQ068</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
+          <t>Dosage/usage notes field on products</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -9194,17 +9194,17 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>REQ047</t>
+          <t>REQ049</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
+          <t>Supplier column in the inventory batch table</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -9245,17 +9245,17 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>REQNF017</t>
+          <t>REQ103, REQ107</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>README with setup steps; fix the error message that points to it</t>
+          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3. From the first review.</t>
+          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -9296,17 +9296,17 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>REQ001</t>
+          <t>REQ116</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Normalize phone number at registration</t>
+          <t>Customer Accounts: list of the customer's orders</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b. From the first review.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>REQ008; Interview 1</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
+          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
+          <t>DONE 847c877. From the first review.</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -9398,17 +9398,17 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>REQ031</t>
+          <t>REQ070</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
+          <t>Category rename: replace native prompt() with app dialog</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
+          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -9449,17 +9449,17 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37</t>
+          <t>REQ033, REQ093</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
+          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>DONE Dashboard: stock in vs stock out per day/week/month/year. Keeps the Chart.js claim (no letter).</t>
+          <t>DONE 082ec92. From the first review.</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -9500,17 +9500,17 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Modules p.42</t>
+          <t>REQ099</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
+          <t>'Payment not received' as its own hold type</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -9551,17 +9551,17 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework p.23</t>
+          <t>REQ026</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
+          <t>Checkout pick-up notice mentions bringing the original prescription</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
+          <t>DONE 082ec92.</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -9602,17 +9602,17 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>REQ039, Fig 2.10, C16</t>
+          <t>REQ009</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+          <t>Show quantity in stock on catalog cards</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -9653,17 +9653,17 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>REQ004</t>
+          <t>REQ040</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Login lockout counter can be reset by anyone (public loginAttempts collection)</t>
+          <t>Profile picture in Account Settings</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Lockout works for normal use; a determined attacker could clear it. Mention as a limitation if not fixed.</t>
+          <t>DONE 77336f3.</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -9689,7 +9689,7 @@
       <c r="J113" s="11" t="inlineStr"/>
       <c r="K113" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9704,17 +9704,17 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>System roles (-)</t>
+          <t>REQNF028</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -9727,7 +9727,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H114" s="11" t="inlineStr"/>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>DONE 847c877.</t>
+        </is>
+      </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -9736,7 +9740,7 @@
       <c r="J114" s="11" t="inlineStr"/>
       <c r="K114" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9746,22 +9750,22 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Whole paper + system (-)</t>
+          <t>REQ047</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -9774,16 +9778,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H115" s="11" t="inlineStr"/>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
+        </is>
+      </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr"/>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9793,27 +9801,27 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044</t>
+          <t>REQNF017</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>New-device code is checked in the browser, not by the database rules</t>
+          <t>README with setup steps; fix the error message that points to it</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr">
@@ -9823,18 +9831,18 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>Stops normal use of a stolen password; a technical attacker could skip it. State this in Limitations.</t>
+          <t>DONE 77336f3. From the first review.</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J116" s="11" t="inlineStr"/>
       <c r="K116" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9844,22 +9852,22 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>REQ090</t>
+          <t>REQ001</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Known, not fixed: two wholesale exchanges on the same order line at the same second can mix up which batch a later return goes back to (stock totals stay right)</t>
+          <t>Normalize phone number at registration</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
@@ -9874,18 +9882,18 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Rare; same-second exchanges on one line.</t>
+          <t>DONE d9fc96b. From the first review.</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J117" s="11" t="inlineStr"/>
       <c r="K117" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9895,22 +9903,22 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>REQ008; Interview 1</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Known, not fixed: if creating a staff account fails after the login is made, the email can't be reused until the login is removed in the Firebase console</t>
+          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
@@ -9925,18 +9933,18 @@
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>Needs a server function to clean up; note in the user manual.</t>
+          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
         </is>
       </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J118" s="11" t="inlineStr"/>
       <c r="K118" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9946,22 +9954,22 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (Chart.js 'inventory movement data'), Dashboard module</t>
+          <t>REQ031</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Inventory Movement chart removed from the dashboard at the team's request (2026-10-21)</t>
+          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
@@ -9976,18 +9984,18 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Paper: drop 'inventory movement data' from the Chart.js line, or note it in the panel letter; stock in/out is still in the Inventory page and reports.</t>
-        </is>
-      </c>
-      <c r="I119" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J119" s="11" t="inlineStr"/>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9997,22 +10005,22 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>Technical Background p.35-37</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
@@ -10027,18 +10035,18 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Built (stock in vs out), then removed at the team's request 2026-10-21 - see the Removals sheet. Keeps the Chart.js claim (no letter).</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr"/>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -10048,22 +10056,22 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>Modules p.42</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr">
@@ -10078,18 +10086,18 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I121" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr"/>
       <c r="K121" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10099,22 +10107,22 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Scope p.6; Product Browsing REQ009</t>
+          <t>Theoretical Framework p.23</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
+          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr">
@@ -10129,18 +10137,18 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr"/>
       <c r="K122" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10150,22 +10158,22 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Scope and Limitations p.7</t>
+          <t>REQ039, Fig 2.10, C16</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
@@ -10180,18 +10188,18 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J123" s="11" t="inlineStr"/>
       <c r="K123" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10201,22 +10209,22 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Decision-dependent</t>
+          <t>REQ004</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+          <t>Login lockout counter can be reset by anyone (public loginAttempts collection)</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr">
@@ -10231,12 +10239,12 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+          <t>Lockout works for normal use; a determined attacker could clear it. Mention as a limitation if not fixed.</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J124" s="11" t="inlineStr"/>
@@ -10252,22 +10260,22 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Inventory module</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>Inventory list: drop the 'Never received' placeholder rows</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr">
@@ -10280,16 +10288,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H125" s="11" t="inlineStr"/>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>DONE 66b8b2e. Products never stocked no longer show as empty batch rows.</t>
+        </is>
+      </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J125" s="11" t="inlineStr"/>
       <c r="K125" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10299,22 +10311,22 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Scope (p.6)</t>
+          <t>REQ001 registration validation</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>Name fields allow periods and dashes (Ma. Clara, Juan P. Cruz, Jr., Anne-Marie)</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr">
@@ -10327,16 +10339,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H126" s="11" t="inlineStr"/>
-      <c r="I126" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>DONE 010449e, 8ce4aa0. Same rule on register, account settings, staff and admin settings.</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J126" s="11" t="inlineStr"/>
       <c r="K126" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10346,22 +10362,22 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.22-23)</t>
+          <t>Checkout module, REQ019</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>Checkout: Same Day Delivery wording and a notice that the Lalamove fee is paid to the rider</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr">
@@ -10376,12 +10392,12 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
-        </is>
-      </c>
-      <c r="I127" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 010449e.</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J127" s="11" t="inlineStr"/>
@@ -10397,22 +10413,22 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.32)</t>
+          <t>EmailJS (Technical Background)</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>Settings: Email Test button that shows EmailJS's reply</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr">
@@ -10425,16 +10441,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H128" s="11" t="inlineStr"/>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>DONE 4eca895. Found the order template was missing To Email {{to_email}} - set it in the EmailJS dashboard before go-live.</t>
+        </is>
+      </c>
       <c r="I128" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J128" s="11" t="inlineStr"/>
       <c r="K128" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10444,22 +10464,22 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Shopping cart module</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>Cart page: 'You May Also Like' product suggestions under the cart items</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr">
@@ -10472,16 +10492,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H129" s="11" t="inlineStr"/>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>DONE 1581610. Team request 2026-10-21 (like Shopee).</t>
+        </is>
+      </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J129" s="11" t="inlineStr"/>
       <c r="K129" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10491,22 +10515,22 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Notification module</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Notifications: filter by Orders / Stock / Live Chat, newest first, mark read per filter</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr">
@@ -10519,16 +10543,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H130" s="11" t="inlineStr"/>
-      <c r="I130" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>DONE 1581610. Team request 2026-10-21.</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J130" s="11" t="inlineStr"/>
       <c r="K130" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10538,22 +10566,22 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Inventory module</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>Inventory: 'Quantity' renamed to 'Available Inventory' (table and export)</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr">
@@ -10568,12 +10596,12 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>DONE No paper change needed: dashboard now has the inventory movement chart.</t>
-        </is>
-      </c>
-      <c r="I131" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 1581610. Team request 2026-10-21.</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J131" s="11" t="inlineStr"/>
@@ -10589,22 +10617,22 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>All PDF exports</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>PDFs printed the peso sign as a broken character - now 'PHP'</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr">
@@ -10617,16 +10645,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H132" s="11" t="inlineStr"/>
-      <c r="I132" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>DONE a3f410b. jsPDF's built-in fonts have no peso sign.</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J132" s="11" t="inlineStr"/>
       <c r="K132" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10636,22 +10668,22 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.36-38)</t>
+          <t>Online order module</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>Online Orders: Reference No. and SI No. columns (searchable); order date and time shown in Payment Verification</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
@@ -10664,16 +10696,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H133" s="11" t="inlineStr"/>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>DONE 2a52561, 8d5a42e. Team request 2026-10-21.</t>
+        </is>
+      </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J133" s="11" t="inlineStr"/>
       <c r="K133" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10683,22 +10719,22 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.38)</t>
+          <t>Dashboard module, Reports module</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>Reports moved out of the Orders tab: all reports open from the dashboard Reports panel</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr">
@@ -10711,16 +10747,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H134" s="11" t="inlineStr"/>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>DONE 2a52561. Team request 2026-10-21. Paper: if the Orders module text mentions an export there, point it to Reports.</t>
+        </is>
+      </c>
       <c r="I134" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J134" s="11" t="inlineStr"/>
       <c r="K134" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10730,22 +10770,22 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Modules: Price Management (p.42)</t>
+          <t>Dashboard module, sequential SI</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+          <t>Dashboard: Find a Sale by SI No. (walk-in, online and wholesale)</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr">
@@ -10760,12 +10800,12 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
-        </is>
-      </c>
-      <c r="I135" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 8d5a42e. Every sale gets an SI No.; online orders keep their order/reference numbers too.</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J135" s="11" t="inlineStr"/>
@@ -10781,22 +10821,22 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+          <t>Go-live</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+          <t>Temporary Clear Test Data page (Branch Manager / Administrator) and its delete rule; both switch off 2026-11-15</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr">
@@ -10809,16 +10849,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H136" s="11" t="inlineStr"/>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>DONE 77fdd25, 112ce91 (publish firestore.rules to use it). Remove the page, its Settings card and the TEMPORARY rule block after go-live; not part of the paper.</t>
+        </is>
+      </c>
       <c r="I136" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J136" s="11" t="inlineStr"/>
       <c r="K136" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10828,17 +10872,17 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.97-98)</t>
+          <t>System roles (-)</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
@@ -10859,7 +10903,7 @@
       <c r="H137" s="11" t="inlineStr"/>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J137" s="11" t="inlineStr"/>
@@ -10875,17 +10919,17 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Whole paper + system (-)</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
@@ -10927,22 +10971,22 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>REQ005, REQ044</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+          <t>New-device code is checked in the browser, not by the database rules</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
@@ -10950,7 +10994,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H139" s="11" t="inlineStr"/>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>Stops normal use of a stolen password; a technical attacker could skip it. State this in Limitations.</t>
+        </is>
+      </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -10974,17 +11022,17 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>References (p.100)</t>
+          <t>REQ090</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+          <t>Known, not fixed: two wholesale exchanges on the same order line at the same second can mix up which batch a later return goes back to (stock totals stay right)</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr">
@@ -10997,7 +11045,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H140" s="11" t="inlineStr"/>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>Rare; same-second exchanges on one line.</t>
+        </is>
+      </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -11021,17 +11073,17 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>References (p.10 / refs)</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+          <t>Known, not fixed: if creating a staff account fails after the login is made, the email can't be reused until the login is removed in the Firebase console</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr">
@@ -11044,7 +11096,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H141" s="11" t="inlineStr"/>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>Needs a server function to clean up; note in the user manual.</t>
+        </is>
+      </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -11068,17 +11124,17 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>References (p.17 / refs)</t>
+          <t>Technical Background (Chart.js 'inventory movement data'), Dashboard module</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+          <t>Inventory Movement chart removed from the dashboard at the team's request (2026-10-21)</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Removed</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr">
@@ -11091,10 +11147,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H142" s="11" t="inlineStr"/>
-      <c r="I142" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H142" s="11" t="inlineStr">
+        <is>
+          <t>Paper: drop 'inventory movement data' from the Chart.js line, or note it in the panel letter; stock in/out is still in the Inventory page and reports.</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J142" s="11" t="inlineStr"/>
@@ -11115,17 +11175,17 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Appendices (p.124)</t>
+          <t>Modules FEFO p.41</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+          <t>Add the 2-month Bad Order step (C7).</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr">
@@ -11138,7 +11198,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H143" s="11" t="inlineStr"/>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -11162,17 +11226,17 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+          <t>Technical Background p.35-37; Budget p.99</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>Regenerate page numbers after all edits.</t>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr">
@@ -11185,10 +11249,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H144" s="11" t="inlineStr"/>
-      <c r="I144" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H144" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J144" s="11" t="inlineStr"/>
@@ -11198,18 +11266,1119 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="11" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>Scope p.6; Product Browsing REQ009</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>Adds</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr"/>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>Scope and Limitations p.7</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>Adds</t>
+        </is>
+      </c>
+      <c r="J146" s="11" t="inlineStr"/>
+      <c r="K146" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>Decision-dependent</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>Paper edit</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="inlineStr"/>
+      <c r="K147" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="11" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C148" s="11" t="inlineStr">
+        <is>
+          <t>Whole paper (-)</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G148" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H148" s="11" t="inlineStr"/>
+      <c r="I148" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J148" s="11" t="inlineStr"/>
+      <c r="K148" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
+        <is>
+          <t>Scope (p.6)</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H149" s="11" t="inlineStr"/>
+      <c r="I149" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J149" s="11" t="inlineStr"/>
+      <c r="K149" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="11" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C150" s="11" t="inlineStr">
+        <is>
+          <t>Theoretical Framework (p.22-23)</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F150" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G150" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H150" s="11" t="inlineStr">
+        <is>
+          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
+        </is>
+      </c>
+      <c r="I150" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J150" s="11" t="inlineStr"/>
+      <c r="K150" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr">
+        <is>
+          <t>Methodology: sprint plan (p.32)</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H151" s="11" t="inlineStr"/>
+      <c r="I151" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J151" s="11" t="inlineStr"/>
+      <c r="K151" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="11" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background (p.35)</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G152" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H152" s="11" t="inlineStr"/>
+      <c r="I152" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J152" s="11" t="inlineStr"/>
+      <c r="K152" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background (p.35-36)</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr"/>
+      <c r="I153" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J153" s="11" t="inlineStr"/>
+      <c r="K153" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background (p.35-36)</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G154" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H154" s="11" t="inlineStr"/>
+      <c r="I154" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J154" s="11" t="inlineStr"/>
+      <c r="K154" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background (p.35, 37)</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr"/>
+      <c r="I155" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J155" s="11" t="inlineStr"/>
+      <c r="K155" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="11" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C156" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background: Software (p.36-38)</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F156" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G156" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H156" s="11" t="inlineStr"/>
+      <c r="I156" s="11" t="inlineStr">
+        <is>
+          <t>Adds</t>
+        </is>
+      </c>
+      <c r="J156" s="11" t="inlineStr"/>
+      <c r="K156" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>Technical Background: Software (p.38)</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F157" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr"/>
+      <c r="I157" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J157" s="11" t="inlineStr"/>
+      <c r="K157" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="11" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="inlineStr">
+        <is>
+          <t>Modules: Price Management (p.42)</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F158" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G158" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H158" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
+        </is>
+      </c>
+      <c r="I158" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
+        </is>
+      </c>
+      <c r="J158" s="11" t="inlineStr"/>
+      <c r="K158" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="11" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C159" s="11" t="inlineStr">
+        <is>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F159" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G159" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H159" s="11" t="inlineStr"/>
+      <c r="I159" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J159" s="11" t="inlineStr"/>
+      <c r="K159" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="11" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C160" s="11" t="inlineStr">
+        <is>
+          <t>Calendar of Activities (p.97-98)</t>
+        </is>
+      </c>
+      <c r="D160" s="11" t="inlineStr">
+        <is>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F160" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G160" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H160" s="11" t="inlineStr"/>
+      <c r="I160" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J160" s="11" t="inlineStr"/>
+      <c r="K160" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="11" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C161" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F161" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G161" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H161" s="11" t="inlineStr"/>
+      <c r="I161" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J161" s="11" t="inlineStr"/>
+      <c r="K161" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C162" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D162" s="11" t="inlineStr">
+        <is>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F162" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G162" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H162" s="11" t="inlineStr"/>
+      <c r="I162" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J162" s="11" t="inlineStr"/>
+      <c r="K162" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="11" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C163" s="11" t="inlineStr">
+        <is>
+          <t>References (p.100)</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F163" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G163" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H163" s="11" t="inlineStr"/>
+      <c r="I163" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J163" s="11" t="inlineStr"/>
+      <c r="K163" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="11" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C164" s="11" t="inlineStr">
+        <is>
+          <t>References (p.10 / refs)</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+        </is>
+      </c>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F164" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G164" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H164" s="11" t="inlineStr"/>
+      <c r="I164" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J164" s="11" t="inlineStr"/>
+      <c r="K164" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C165" s="11" t="inlineStr">
+        <is>
+          <t>References (p.17 / refs)</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F165" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G165" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H165" s="11" t="inlineStr"/>
+      <c r="I165" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J165" s="11" t="inlineStr"/>
+      <c r="K165" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="11" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C166" s="11" t="inlineStr">
+        <is>
+          <t>Appendices (p.124)</t>
+        </is>
+      </c>
+      <c r="D166" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G166" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H166" s="11" t="inlineStr"/>
+      <c r="I166" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J166" s="11" t="inlineStr"/>
+      <c r="K166" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="11" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C167" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G167" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H167" s="11" t="inlineStr"/>
+      <c r="I167" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J167" s="11" t="inlineStr"/>
+      <c r="K167" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K144"/>
-  <conditionalFormatting sqref="K2:K144">
+  <autoFilter ref="A1:K167"/>
+  <conditionalFormatting sqref="K2:K167">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -25222,17 +26391,17 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Inventory movement charts not provided</t>
+          <t>Inventory movement chart removed from the dashboard at the team's request (2026-10-21)</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Add an inventory movement chart to the dashboard</t>
+          <t>Reword the Chart.js line to sales analytics (stock movement stays in the Inventory page and reports), or put the chart back</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Building - no letter (S)</t>
+          <t>In letter, unless the adviser accepts the reword</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -4177,7 +4177,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr"/>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>DONE chat is built (80b3988); keep the tick.</t>
+        </is>
+      </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -4186,7 +4190,7 @@
       <c r="J4" s="11" t="inlineStr"/>
       <c r="K4" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4853,7 @@
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4904,7 @@
       <c r="J18" s="11" t="inlineStr"/>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4955,7 @@
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5550,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>DONE chat is built; keep 'coordinated through live chat'.</t>
+        </is>
+      </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5555,7 +5563,7 @@
       <c r="J31" s="11" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6873,7 @@
       <c r="J57" s="11" t="inlineStr"/>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6924,7 @@
       <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6975,7 @@
       <c r="J59" s="11" t="inlineStr"/>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9127,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H102" s="11" t="inlineStr"/>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>DONE chat is built; keep the sentence.</t>
+        </is>
+      </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -9128,7 +9140,7 @@
       <c r="J102" s="11" t="inlineStr"/>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -6760,7 +6760,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Needed before real use with the client's ~1,000-product catalog.</t>
+          <t>DONE same commit as the Cloudinary/Firestore free-plan changes; reports and dashboard still read full history by design. Needed before real use with the client's ~1,000-product catalog.</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -6771,7 +6771,7 @@
       <c r="J55" s="11" t="inlineStr"/>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Keeps Cloudinary and Firestore on the free plans as visits grow. Offered, not built yet.</t>
+          <t>DONE resized delivery URLs (f_auto,q_auto,w_), photos shrunk before upload by kind; shop catalog cached 5 min in the browser, staff bell cached 2 min with status-filtered order/PO reads, Inventory and Orders read once via their live listeners. Keeps Cloudinary and Firestore on the free plans as visits grow. Offered, not built yet.</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -7383,7 +7383,7 @@
       <c r="J67" s="11" t="inlineStr"/>
       <c r="K67" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
@@ -3972,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>DONE same commit as the Cloudinary/Firestore free-plan changes; reports and dashboard still read full history by design. Needed before real use with the client's ~1,000-product catalog.</t>
+          <t>DONE 6bdc6a6; reports and dashboard still read full history by design. Needed before real use with the client's ~1,000-product catalog.</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>DONE resized delivery URLs (f_auto,q_auto,w_), photos shrunk before upload by kind; shop catalog cached 5 min in the browser, staff bell cached 2 min with status-filtered order/PO reads, Inventory and Orders read once via their live listeners. Keeps Cloudinary and Firestore on the free plans as visits grow. Offered, not built yet.</t>
+          <t>DONE 6bdc6a6: resized delivery URLs (f_auto,q_auto,w_), photos shrunk before upload by kind; shop catalog cached 5 min in the browser, staff bell cached 2 min with status-filtered order/PO reads, Inventory and Orders read once via their live listeners. Keeps Cloudinary and Firestore on the free plans as visits grow. Offered, not built yet.</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -7398,17 +7398,17 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Project Context (p.1)</t>
+          <t>Live chat module, Online order tracking</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>Live chat order cards: products with photos, progress tracker with dates, delivery or pick-up, what happens next, Track rider; live status; Gemini routes order questions the word list misses</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
+          <t>DONE d16bd76. Several orders show as short cards with Show details; follow-up buttons fit the status.</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.24)</t>
+          <t>Project Context (p.1)</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da: system now matches (BM-only finalize).</t>
+          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output) (p.27)</t>
+          <t>Theoretical Framework (p.24)</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>DONE footer links to legal.html on every page.</t>
+          <t>DONE 06574da: system now matches (BM-only finalize).</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -7546,17 +7546,17 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles (p.45-46)</t>
+          <t>Conceptual Framework (Output) (p.27)</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
+          <t>DONE footer links to legal.html on every page.</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr"/>
@@ -7597,22 +7597,22 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>REQ001 registration, Scope and Limitations</t>
+          <t>Modules: Staff roles (p.45-46)</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Phone number verification by SMS code: on hold (every SMS costs money; Amson doesn't want to spend)</t>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Paper: state in Limitations (number format checked, not ownership) and in Recommendations (SMS OTP).</t>
+          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -7638,7 +7638,7 @@
       <c r="J72" s="11" t="inlineStr"/>
       <c r="K72" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7653,17 +7653,17 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Chapter 3 evaluation (Objective 4)</t>
+          <t>REQ001 registration, Scope and Limitations</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Evaluation survey questionnaires: Branch Manager, Technical Staff, Sales Staff and User forms, mapped to TAM + ISO/IEC 25010</t>
+          <t>Phone number verification by SMS code: on hold (every SMS costs money; Amson doesn't want to spend)</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>DONE Claude Docs, 2026-10-22. In Claude Docs ('Survey Questionnaires (Admin and User)'); maintainability covered by the developers' testing (no IT expert form).</t>
+          <t>Paper: state in Limitations (number format checked, not ownership) and in Recommendations (SMS OTP).</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
@@ -7689,7 +7689,7 @@
       <c r="J73" s="11" t="inlineStr"/>
       <c r="K73" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7704,17 +7704,17 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>REQ007 / Technical Background p.35-36</t>
+          <t>Chapter 3 evaluation (Objective 4)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+          <t>Evaluation survey questionnaires: Branch Manager, Technical Staff, Sales Staff and User forms, mapped to TAM + ISO/IEC 25010</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE Claude Docs, 2026-10-22. In Claude Docs ('Survey Questionnaires (Admin and User)'); maintainability covered by the developers' testing (no IT expert form).</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -7740,7 +7740,7 @@
       <c r="J74" s="11" t="inlineStr"/>
       <c r="K74" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7755,12 +7755,12 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>REQ008 p.47; Modules p.38</t>
+          <t>REQ007 / Technical Background p.35-36</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
@@ -7783,9 +7783,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr"/>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>REQ031 p.50</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>REQ073 p.55</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
@@ -7885,9 +7885,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I77" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr"/>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+          <t>REQ073 p.55</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087 p.57; Modules p.44</t>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Default wholesale price per product, adjustable per order (C9).</t>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -7987,9 +7987,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I79" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr"/>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -8089,9 +8089,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr"/>
@@ -8112,12 +8112,12 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>REQ121 p.61</t>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 text p.67</t>
+          <t>REQ121 p.61</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 diagram</t>
+          <t>Fig 2.2 text p.67</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.5 text p.72</t>
+          <t>Fig 2.2 diagram</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 / 2.7 diagrams</t>
+          <t>Fig 2.5 text p.72</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.8 diagram + text p.76-77</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 diagram + text p.78-79</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.10 diagram</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 diagram + text p.82-83</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -8571,17 +8571,17 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover (i)</t>
+          <t>Fig 2.11 diagram + text p.82-83</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -8594,7 +8594,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H91" s="11" t="inlineStr"/>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -8618,12 +8622,12 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Title page / cover (i)</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -8633,7 +8637,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -8665,12 +8669,12 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
@@ -8680,7 +8684,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -8712,12 +8716,12 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input) (p.25)</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -8736,9 +8740,9 @@
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr"/>
-      <c r="I94" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr"/>
@@ -8759,12 +8763,12 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.30-35)</t>
+          <t>Conceptual Framework (Input) (p.25)</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
@@ -8783,9 +8787,9 @@
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr"/>
-      <c r="I95" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr"/>
@@ -8806,12 +8810,12 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Methodology: sprint plan (p.30-35)</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -8858,7 +8862,7 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
@@ -8895,42 +8899,38 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>REQ088</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Hide costing/wholesale prices from public reads</t>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H98" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED (revised): build it to avoid a removal letter.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr"/>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr"/>
@@ -8951,17 +8951,17 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Interview 1</t>
+          <t>REQ088</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
+          <t>Hide costing/wholesale prices from public reads</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -8976,18 +8976,18 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
+          <t>DECIDED (revised): build it to avoid a removal letter.</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr"/>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9002,12 +9002,12 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (CREDIT terms)</t>
+          <t>Interview 1</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Credit sales follow-up (who owes what, mark as paid)</t>
+          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
+          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (daily Sales section)</t>
+          <t>Report Formats sheet (CREDIT terms)</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
+          <t>Credit sales follow-up (who owes what, mark as paid)</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
+          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -9099,22 +9099,22 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Report Formats sheet (daily Sales section)</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -9129,18 +9129,18 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>DONE chat is built; keep the sentence.</t>
+          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr"/>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -9150,22 +9150,22 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>REQ013, REQ068</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Dosage/usage notes field on products</t>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DONE chat is built; keep the sentence.</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -9206,17 +9206,17 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>REQ049</t>
+          <t>REQ013, REQ068</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Supplier column in the inventory batch table</t>
+          <t>Dosage/usage notes field on products</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>REQ103, REQ107</t>
+          <t>REQ049</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
+          <t>Supplier column in the inventory batch table</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>REQ116</t>
+          <t>REQ103, REQ107</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Customer Accounts: list of the customer's orders</t>
+          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -9359,17 +9359,17 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>REQ116</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
+          <t>Customer Accounts: list of the customer's orders</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877. From the first review.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -9410,17 +9410,17 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>REQ070</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Category rename: replace native prompt() with app dialog</t>
+          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
+          <t>DONE 847c877. From the first review.</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -9461,17 +9461,17 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>REQ033, REQ093</t>
+          <t>REQ070</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
+          <t>Category rename: replace native prompt() with app dialog</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92. From the first review.</t>
+          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>REQ099</t>
+          <t>REQ033, REQ093</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>'Payment not received' as its own hold type</t>
+          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 082ec92. From the first review.</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>REQ026</t>
+          <t>REQ099</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Checkout pick-up notice mentions bringing the original prescription</t>
+          <t>'Payment not received' as its own hold type</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>REQ009</t>
+          <t>REQ026</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Show quantity in stock on catalog cards</t>
+          <t>Checkout pick-up notice mentions bringing the original prescription</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DONE 082ec92.</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -9665,17 +9665,17 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>REQ040</t>
+          <t>REQ009</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Profile picture in Account Settings</t>
+          <t>Show quantity in stock on catalog cards</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>REQNF028</t>
+          <t>REQ040</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
+          <t>Profile picture in Account Settings</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 77336f3.</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -9767,17 +9767,17 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>REQ047</t>
+          <t>REQNF028</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
+          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
@@ -9818,17 +9818,17 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>REQNF017</t>
+          <t>REQ047</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>README with setup steps; fix the error message that points to it</t>
+          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3. From the first review.</t>
+          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -9869,17 +9869,17 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>REQ001</t>
+          <t>REQNF017</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Normalize phone number at registration</t>
+          <t>README with setup steps; fix the error message that points to it</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b. From the first review.</t>
+          <t>DONE 77336f3. From the first review.</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
@@ -9920,17 +9920,17 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>REQ008; Interview 1</t>
+          <t>REQ001</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
+          <t>Normalize phone number at registration</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
+          <t>DONE d9fc96b. From the first review.</t>
         </is>
       </c>
       <c r="I118" s="11" t="inlineStr">
@@ -9971,17 +9971,17 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>REQ031</t>
+          <t>REQ008; Interview 1</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
+          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
+          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
@@ -10022,17 +10022,17 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37</t>
+          <t>REQ031</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
+          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
@@ -10047,18 +10047,18 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>Built (stock in vs out), then removed at the team's request 2026-10-21 - see the Removals sheet. Keeps the Chart.js claim (no letter).</t>
+          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr"/>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Modules p.42</t>
+          <t>Technical Background p.35-37</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
+          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
@@ -10098,18 +10098,18 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
+          <t>Built (stock in vs out), then removed at the team's request 2026-10-21 - see the Removals sheet. Keeps the Chart.js claim (no letter).</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr"/>
       <c r="K121" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework p.23</t>
+          <t>Modules p.42</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
+          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
+          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>REQ039, Fig 2.10, C16</t>
+          <t>Theoretical Framework p.23</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
+          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>REQ004</t>
+          <t>REQ039, Fig 2.10, C16</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Login lockout counter can be reset by anyone (public loginAttempts collection)</t>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>Lockout works for normal use; a determined attacker could clear it. Mention as a limitation if not fixed.</t>
+          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -10262,7 +10262,7 @@
       <c r="J124" s="11" t="inlineStr"/>
       <c r="K124" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10277,17 +10277,17 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Inventory module</t>
+          <t>REQ004</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Inventory list: drop the 'Never received' placeholder rows</t>
+          <t>Login lockout counter can be reset by anyone (public loginAttempts collection)</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>DONE 66b8b2e. Products never stocked no longer show as empty batch rows.</t>
+          <t>Lockout works for normal use; a determined attacker could clear it. Mention as a limitation if not fixed.</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
@@ -10313,7 +10313,7 @@
       <c r="J125" s="11" t="inlineStr"/>
       <c r="K125" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -10328,12 +10328,12 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>REQ001 registration validation</t>
+          <t>Inventory module</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Name fields allow periods and dashes (Ma. Clara, Juan P. Cruz, Jr., Anne-Marie)</t>
+          <t>Inventory list: drop the 'Never received' placeholder rows</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>DONE 010449e, 8ce4aa0. Same rule on register, account settings, staff and admin settings.</t>
+          <t>DONE 66b8b2e. Products never stocked no longer show as empty batch rows.</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Checkout module, REQ019</t>
+          <t>REQ001 registration validation</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Checkout: Same Day Delivery wording and a notice that the Lalamove fee is paid to the rider</t>
+          <t>Name fields allow periods and dashes (Ma. Clara, Juan P. Cruz, Jr., Anne-Marie)</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>DONE 010449e.</t>
+          <t>DONE 010449e, 8ce4aa0. Same rule on register, account settings, staff and admin settings.</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -10430,12 +10430,12 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>EmailJS (Technical Background)</t>
+          <t>Checkout module, REQ019</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Settings: Email Test button that shows EmailJS's reply</t>
+          <t>Checkout: Same Day Delivery wording and a notice that the Lalamove fee is paid to the rider</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>DONE 4eca895. Found the order template was missing To Email {{to_email}} - set it in the EmailJS dashboard before go-live.</t>
+          <t>DONE 010449e.</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Shopping cart module</t>
+          <t>EmailJS (Technical Background)</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Cart page: 'You May Also Like' product suggestions under the cart items</t>
+          <t>Settings: Email Test button that shows EmailJS's reply</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>DONE 1581610. Team request 2026-10-21 (like Shopee).</t>
+          <t>DONE 4eca895. Found the order template was missing To Email {{to_email}} - set it in the EmailJS dashboard before go-live.</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
@@ -10532,12 +10532,12 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Notification module</t>
+          <t>Shopping cart module</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Notifications: filter by Orders / Stock / Live Chat, newest first, mark read per filter</t>
+          <t>Cart page: 'You May Also Like' product suggestions under the cart items</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>DONE 1581610. Team request 2026-10-21.</t>
+          <t>DONE 1581610. Team request 2026-10-21 (like Shopee).</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Inventory module</t>
+          <t>Notification module</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Inventory: 'Quantity' renamed to 'Available Inventory' (table and export)</t>
+          <t>Notifications: filter by Orders / Stock / Live Chat, newest first, mark read per filter</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>All PDF exports</t>
+          <t>Inventory module</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>PDFs printed the peso sign as a broken character - now 'PHP'</t>
+          <t>Inventory: 'Quantity' renamed to 'Available Inventory' (table and export)</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>DONE a3f410b. jsPDF's built-in fonts have no peso sign.</t>
+          <t>DONE 1581610. Team request 2026-10-21.</t>
         </is>
       </c>
       <c r="I132" s="11" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Online order module</t>
+          <t>All PDF exports</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Online Orders: Reference No. and SI No. columns (searchable); order date and time shown in Payment Verification</t>
+          <t>PDFs printed the peso sign as a broken character - now 'PHP'</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>DONE 2a52561, 8d5a42e. Team request 2026-10-21.</t>
+          <t>DONE a3f410b. jsPDF's built-in fonts have no peso sign.</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
@@ -10736,12 +10736,12 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Dashboard module, Reports module</t>
+          <t>Online order module</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>Reports moved out of the Orders tab: all reports open from the dashboard Reports panel</t>
+          <t>Online Orders: Reference No. and SI No. columns (searchable); order date and time shown in Payment Verification</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>DONE 2a52561. Team request 2026-10-21. Paper: if the Orders module text mentions an export there, point it to Reports.</t>
+          <t>DONE 2a52561, 8d5a42e. Team request 2026-10-21.</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Dashboard module, sequential SI</t>
+          <t>Dashboard module, Reports module</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Dashboard: Find a Sale by SI No. (walk-in, online and wholesale)</t>
+          <t>Reports moved out of the Orders tab: all reports open from the dashboard Reports panel</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>DONE 8d5a42e. Every sale gets an SI No.; online orders keep their order/reference numbers too.</t>
+          <t>DONE 2a52561. Team request 2026-10-21. Paper: if the Orders module text mentions an export there, point it to Reports.</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Go-live</t>
+          <t>Dashboard module, sequential SI</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>Temporary Clear Test Data page (Branch Manager / Administrator) and its delete rule; both switch off 2026-11-15</t>
+          <t>Dashboard: Find a Sale by SI No. (walk-in, online and wholesale)</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>DONE 77fdd25, 112ce91 (publish firestore.rules to use it). Remove the page, its Settings card and the TEMPORARY rule block after go-live; not part of the paper.</t>
+          <t>DONE 8d5a42e. Every sale gets an SI No.; online orders keep their order/reference numbers too.</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
@@ -10889,17 +10889,17 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>System roles (-)</t>
+          <t>Go-live</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+          <t>Temporary Clear Test Data page (Branch Manager / Administrator) and its delete rule; both switch off 2026-11-15</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr">
@@ -10912,7 +10912,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H137" s="11" t="inlineStr"/>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>DONE 77fdd25, 112ce91 (publish firestore.rules to use it). Remove the page, its Settings card and the TEMPORARY rule block after go-live; not part of the paper.</t>
+        </is>
+      </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -10921,7 +10925,7 @@
       <c r="J137" s="11" t="inlineStr"/>
       <c r="K137" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10931,22 +10935,22 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Whole paper + system (-)</t>
+          <t>Tech Stack (free plans), REQNF013</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+          <t>Watch Firestore usage after go-live: Dashboard and Reports still read the full sales history on each visit</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
@@ -10959,10 +10963,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H138" s="11" t="inlineStr"/>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>Fine at one branch's volume; if the 50,000 reads/day limit gets close, limit them to the chosen period.</t>
+        </is>
+      </c>
       <c r="I138" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J138" s="11" t="inlineStr"/>
@@ -10978,27 +10986,27 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044</t>
+          <t>System roles (-)</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>New-device code is checked in the browser, not by the database rules</t>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
@@ -11006,14 +11014,10 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H139" s="11" t="inlineStr">
-        <is>
-          <t>Stops normal use of a stolen password; a technical attacker could skip it. State this in Limitations.</t>
-        </is>
-      </c>
+      <c r="H139" s="11" t="inlineStr"/>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J139" s="11" t="inlineStr"/>
@@ -11029,22 +11033,22 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>REQ090</t>
+          <t>Whole paper + system (-)</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>Known, not fixed: two wholesale exchanges on the same order line at the same second can mix up which batch a later return goes back to (stock totals stay right)</t>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr">
@@ -11057,11 +11061,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H140" s="11" t="inlineStr">
-        <is>
-          <t>Rare; same-second exchanges on one line.</t>
-        </is>
-      </c>
+      <c r="H140" s="11" t="inlineStr"/>
       <c r="I140" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -11085,12 +11085,12 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>REQ005, REQ044</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>Known, not fixed: if creating a staff account fails after the login is made, the email can't be reused until the login is removed in the Firebase console</t>
+          <t>New-device code is checked in the browser, not by the database rules</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Needs a server function to clean up; note in the user manual.</t>
+          <t>Stops normal use of a stolen password; a technical attacker could skip it. State this in Limitations.</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
@@ -11136,17 +11136,17 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (Chart.js 'inventory movement data'), Dashboard module</t>
+          <t>REQ090</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>Inventory Movement chart removed from the dashboard at the team's request (2026-10-21)</t>
+          <t>Known, not fixed: two wholesale exchanges on the same order line at the same second can mix up which batch a later return goes back to (stock totals stay right)</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="H142" s="11" t="inlineStr">
         <is>
-          <t>Paper: drop 'inventory movement data' from the Chart.js line, or note it in the panel letter; stock in/out is still in the Inventory page and reports.</t>
-        </is>
-      </c>
-      <c r="I142" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>Rare; same-second exchanges on one line.</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J142" s="11" t="inlineStr"/>
@@ -11187,17 +11187,17 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>Known, not fixed: if creating a staff account fails after the login is made, the email can't be reused until the login is removed in the Firebase console</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Needs a server function to clean up; note in the user manual.</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>Technical Background (Chart.js 'inventory movement data'), Dashboard module</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>Inventory Movement chart removed from the dashboard at the team's request (2026-10-21)</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Removed</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="H144" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Paper: drop 'inventory movement data' from the Chart.js line, or note it in the panel letter; stock in/out is still in the Inventory page and reports.</t>
         </is>
       </c>
       <c r="I144" s="12" t="inlineStr">
@@ -11289,12 +11289,12 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Scope p.6; Product Browsing REQ009</t>
+          <t>Modules FEFO p.41</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
+          <t>Add the 2-month Bad Order step (C7).</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J145" s="11" t="inlineStr"/>
@@ -11340,12 +11340,12 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>Scope and Limitations p.7</t>
+          <t>Technical Background p.35-37; Budget p.99</t>
         </is>
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
@@ -11368,9 +11368,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I146" s="11" t="inlineStr">
-        <is>
-          <t>Adds</t>
+      <c r="I146" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J146" s="11" t="inlineStr"/>
@@ -11391,12 +11391,12 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Decision-dependent</t>
+          <t>Scope p.6; Product Browsing REQ009</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
@@ -11416,12 +11416,12 @@
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+          <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J147" s="11" t="inlineStr"/>
@@ -11442,17 +11442,17 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Scope and Limitations p.7</t>
         </is>
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
@@ -11465,10 +11465,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H148" s="11" t="inlineStr"/>
+      <c r="H148" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J148" s="11" t="inlineStr"/>
@@ -11489,17 +11493,17 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Scope (p.6)</t>
+          <t>Decision-dependent</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr">
@@ -11512,10 +11516,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H149" s="11" t="inlineStr"/>
-      <c r="I149" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H149" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I149" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J149" s="11" t="inlineStr"/>
@@ -11536,12 +11544,12 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.22-23)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
@@ -11559,20 +11567,16 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H150" s="11" t="inlineStr">
-        <is>
-          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
-        </is>
-      </c>
-      <c r="I150" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H150" s="11" t="inlineStr"/>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J150" s="11" t="inlineStr"/>
       <c r="K150" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -11587,12 +11591,12 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.32)</t>
+          <t>Scope (p.6)</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
@@ -11611,9 +11615,9 @@
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr"/>
-      <c r="I151" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I151" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J151" s="11" t="inlineStr"/>
@@ -11634,12 +11638,12 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Theoretical Framework (p.22-23)</t>
         </is>
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
@@ -11657,16 +11661,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H152" s="11" t="inlineStr"/>
-      <c r="I152" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H152" s="11" t="inlineStr">
+        <is>
+          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
+        </is>
+      </c>
+      <c r="I152" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J152" s="11" t="inlineStr"/>
       <c r="K152" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11681,12 +11689,12 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Methodology: sprint plan (p.32)</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
@@ -11705,9 +11713,9 @@
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr"/>
-      <c r="I153" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I153" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J153" s="11" t="inlineStr"/>
@@ -11728,12 +11736,12 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
@@ -11752,9 +11760,9 @@
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr"/>
-      <c r="I154" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I154" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J154" s="11" t="inlineStr"/>
@@ -11775,12 +11783,12 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
@@ -11822,12 +11830,12 @@
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.36-38)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
@@ -11846,9 +11854,9 @@
         </is>
       </c>
       <c r="H156" s="11" t="inlineStr"/>
-      <c r="I156" s="11" t="inlineStr">
-        <is>
-          <t>Adds</t>
+      <c r="I156" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J156" s="11" t="inlineStr"/>
@@ -11869,12 +11877,12 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.38)</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
@@ -11893,9 +11901,9 @@
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr"/>
-      <c r="I157" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I157" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J157" s="11" t="inlineStr"/>
@@ -11916,12 +11924,12 @@
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>Modules: Price Management (p.42)</t>
+          <t>Technical Background: Software (p.36-38)</t>
         </is>
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
@@ -11939,20 +11947,16 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H158" s="11" t="inlineStr">
-        <is>
-          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
-        </is>
-      </c>
-      <c r="I158" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H158" s="11" t="inlineStr"/>
+      <c r="I158" s="11" t="inlineStr">
+        <is>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J158" s="11" t="inlineStr"/>
       <c r="K158" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -11967,12 +11971,12 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+          <t>Technical Background: Software (p.38)</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
@@ -12014,12 +12018,12 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.97-98)</t>
+          <t>Modules: Price Management (p.42)</t>
         </is>
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
@@ -12037,16 +12041,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H160" s="11" t="inlineStr"/>
-      <c r="I160" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H160" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
+        </is>
+      </c>
+      <c r="I160" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J160" s="11" t="inlineStr"/>
       <c r="K160" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -12061,12 +12069,12 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
@@ -12108,12 +12116,12 @@
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Calendar of Activities (p.97-98)</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
@@ -12155,12 +12163,12 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>References (p.100)</t>
+          <t>Budgetary Estimate (p.99)</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
@@ -12202,12 +12210,12 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>References (p.10 / refs)</t>
+          <t>Budgetary Estimate (p.99)</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
@@ -12249,12 +12257,12 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>References (p.17 / refs)</t>
+          <t>References (p.100)</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
@@ -12296,12 +12304,12 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>Appendices (p.124)</t>
+          <t>References (p.10 / refs)</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
@@ -12343,12 +12351,12 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+          <t>References (p.17 / refs)</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>Regenerate page numbers after all edits.</t>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
@@ -12379,18 +12387,112 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="11" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C168" s="11" t="inlineStr">
+        <is>
+          <t>Appendices (p.124)</t>
+        </is>
+      </c>
+      <c r="D168" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G168" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H168" s="11" t="inlineStr"/>
+      <c r="I168" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J168" s="11" t="inlineStr"/>
+      <c r="K168" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="11" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C169" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F169" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H169" s="11" t="inlineStr"/>
+      <c r="I169" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J169" s="11" t="inlineStr"/>
+      <c r="K169" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K167"/>
-  <conditionalFormatting sqref="K2:K167">
+  <autoFilter ref="A1:K169"/>
+  <conditionalFormatting sqref="K2:K169">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19573,7 +19675,7 @@
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>21e505b: online orders, inventory, POS today's sales, customer order list and order page, and chat update live. Dashboard tiles refresh on load. (was: Users must reload to see new orders or stock changes.)</t>
+          <t>21e505b: online orders, inventory, POS today's sales, customer order list and order page, chat and chat order cards update live. Dashboard tiles refresh on load; the shop catalog refreshes every 5 minutes (checkout re-checks stock live). (was: Users must reload to see new orders or stock changes.)</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr">

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -19675,7 +19675,7 @@
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>21e505b: online orders, inventory, POS today's sales, customer order list and order page, chat and chat order cards update live. Dashboard tiles refresh on load; the shop catalog refreshes every 5 minutes (checkout re-checks stock live). (was: Users must reload to see new orders or stock changes.)</t>
+          <t>21e505b: online orders, inventory, POS today's sales, customer order list and order page, chat, chat order cards, the staff bell (new orders, chats waiting) and the Dashboard order tiles update live. Sales and stock tiles refresh on load; the shop catalog refreshes every 5 minutes (checkout re-checks stock live). (was: Users must reload to see new orders or stock changes.)</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr">

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>One sheet per category (Generics, Medical Supplies, Grocery, Drugstore per pc, Branded): Product, POS stock, Physical count, Costing, Retail, Wholesale, Batch #, Expiry</t>
+          <t>One sheet per category (Generics, Medical Supplies, Drugstore per pc, Branded; no grocery since 2026-10-22): Product, POS stock, Physical count, Costing, Retail, Wholesale, Batch #, Expiry</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Supplier Name, Order Date, Receipt #, Product, Brand, Packs, Batch #, Expiry, Qty, Price, Amount, Total; separate Drugstore and Grocery sheets</t>
+          <t>Supplier Name, Order Date, Receipt #, Product, Brand, Packs, Batch #, Expiry, Qty, Price, Amount, Total; one Drugstore sheet (no grocery items since 2026-10-22)</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -3972,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K169"/>
+  <dimension ref="A1:K175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4056,17 +4056,17 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>Client items (-)</t>
+          <t>REQ009 product catalog, REQ061 (catalog data)</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Get from the client: the QR Ph image, the sales invoice format, and the store details for the footer (hotline, email, hours, address, FDA LTO No. - fill js/store-info.js); have them review the Terms/Privacy text. Ask them: are all sales VAT-exempt (sample shows VATable 0.00), is pay-in/pay-out used, who tracks credit collections, which categories to use, may we load the real catalog for the demo?</t>
+          <t>Upload Amson's April price list: 1,172 products in 6 files (999 Generics, 173 Medical Supplies) + read-me/checklist</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F2" s="11" t="inlineStr">
@@ -4079,7 +4079,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr"/>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>Files made 2026-10-22 from PRICELIST-APRIL-SEND-TO-CUSTOMER.xlsx; tested through the importer. Upload as the Branch Manager, each file once. Not committed (client data).</t>
+        </is>
+      </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -4098,27 +4102,27 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>REQ035-038, REQ108-110, REQNF008, REQNF012</t>
+          <t>REQ024 prescription items, REQ077</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Live chat (guest/customer widget, staff console, resolve threads; AI replies)</t>
+          <t>Pharmacist to check the Rx Required flag on all 1,172 products (set to YES unless a common OTC medicine; injectables and IV fluids always Rx)</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G3" s="11" t="inlineStr">
@@ -4128,7 +4132,7 @@
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>DONE 80b3988: widget, built-in answers, Gemini via Firebase AI Logic, daily AI limit with usage shown, staff console (reply, take over, hand back, resolve), staff alert. Enable AI Logic in the Firebase console and publish rules. Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
+          <t>'Rx check' sheet in the read-me workbook; untick in the review table before confirming.</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -4139,7 +4143,7 @@
       <c r="J3" s="11" t="inlineStr"/>
       <c r="K3" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4149,22 +4153,22 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>REQ061-066 receiving, FEFO</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>The proposed system gets a tick for 'AI-powered live chat'; keep only if chat is built.</t>
+          <t>Opening stock: current quantity per product and batch for Receive Stock (the price list has batch and expiry but no quantities)</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -4179,7 +4183,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>DONE chat is built (80b3988); keep the tick.</t>
+          <t>Once products are uploaded, export SKUs and we build the Receive Stock upload with batch, expiry and quantity.</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -4190,7 +4194,7 @@
       <c r="J4" s="11" t="inlineStr"/>
       <c r="K4" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4200,22 +4204,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>REQ066, Title, Obj. 2</t>
+          <t>Client items (-)</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Near-expiry stock removed from sale by date on every sale/catalog load, not only when Inventory is opened</t>
+          <t>Get from the client: the QR Ph image, the sales invoice format, and the store details for the footer (hotline, email, hours, address, FDA LTO No. - fill js/store-info.js); have them review the Terms/Privacy text. Ask them: are all sales VAT-exempt (sample shows VATable 0.00), is pay-in/pay-out used, who tracks credit collections, which categories to use, may we load the real catalog for the demo?</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -4228,11 +4232,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>DONE e1e200b. Title feature.</t>
-        </is>
-      </c>
+      <c r="H5" s="11" t="inlineStr"/>
       <c r="I5" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -4241,7 +4241,7 @@
       <c r="J5" s="11" t="inlineStr"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4251,22 +4251,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>REQ058, REQ111-115, REQNF020, Obj. 3</t>
+          <t>REQ035-038, REQ108-110, REQNF008, REQNF012</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Build the Reports module: daily sales (per customer, items with batch + expiry), monthly inventory + purchases (batch, expiry, date received, receipt no., supplier), pull-out, discrepancy; date range; PDF + Excel. Wire the 5 blank Export buttons to it.</t>
+          <t>Live chat (guest/customer widget, staff console, resolve threads; AI replies)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>DONE bf16804: Reports page with Daily Sales, Customer File, Monthly Inventory, Supplier Purchases, Pull-Out and PO Discrepancy in the branch's formats; preview, PDF, Excel. Not yet: Return to POS / wholesale exchange report (needs the exchange feature). Discount, VAT and pay-in/pay-out columns show 0 (client: no discounts; VAT-exempt as in their sample). PARTIAL aece0e7: all 6 Export buttons now produce real PDF/Excel tables of what's on screen; the client's 4 report formats are still to build. Client's one remaining ask (Interview 4). Build to the 4 client samples (see Report Formats sheet); Excel output must paste cleanly into the main office's own sheets (Interviews 1, 2, 4); daily sales should total by payment method to match the daily cash remittance (Interview 2).</t>
+          <t>DONE 80b3988: widget, built-in answers, Gemini via Firebase AI Logic, daily AI limit with usage shown, staff console (reply, take over, hand back, resolve), staff alert. Enable AI Logic in the Firebase console and publish rules. Decide: build (AI needs a server function) or scope down + Limitations. Affects Objective 1, Scope, Comparative Analysis.</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -4302,27 +4302,27 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>REQ024-025, REQ077-081, C3</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Prescription verification: approve/reject with mandatory reason, 'Ready for pick-up' notification, record who verified, RX filter in the queue</t>
+          <t>The proposed system gets a tick for 'AI-powered live chat'; keep only if chat is built.</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92: RX filter, Reject Prescription with reason (7-day re-upload hold), 'ready for pick-up' notice, verifier recorded + audit.</t>
+          <t>DONE chat is built (80b3988); keep the tick.</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>REQ034, REQ104-105</t>
+          <t>REQ066, Title, Obj. 2</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Show the Lalamove tracking link to the customer on their order page</t>
+          <t>Near-expiry stock removed from sale by date on every sale/catalog load, not only when Inventory is opened</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>DONE customer order page shows a 'Track with Lalamove' card once dispatched.</t>
+          <t>DONE e1e200b. Title feature.</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>REQ028</t>
+          <t>REQ058, REQ111-115, REQNF020, Obj. 3</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Add the client's real QR PH image (assets/payment-qr.png)</t>
+          <t>Build the Reports module: daily sales (per customer, items with batch + expiry), monthly inventory + purchases (batch, expiry, date received, receipt no., supplier), pull-out, discrepancy; date range; PDF + Excel. Wire the 5 blank Export buttons to it.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Need the image from the client.</t>
+          <t>DONE bf16804: Reports page with Daily Sales, Customer File, Monthly Inventory, Supplier Purchases, Pull-Out and PO Discrepancy in the branch's formats; preview, PDF, Excel. Not yet: Return to POS / wholesale exchange report (needs the exchange feature). Discount, VAT and pay-in/pay-out columns show 0 (client: no discounts; VAT-exempt as in their sample). PARTIAL aece0e7: all 6 Export buttons now produce real PDF/Excel tables of what's on screen; the client's 4 report formats are still to build. Client's one remaining ask (Interview 4). Build to the 4 client samples (see Report Formats sheet); Excel output must paste cleanly into the main office's own sheets (Interviews 1, 2, 4); daily sales should total by payment method to match the daily cash remittance (Interview 2).</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -4445,7 +4445,7 @@
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>REQ010-011</t>
+          <t>REQ024-025, REQ077-081, C3</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Wire product search (header box) + add price-range and stock-status filters</t>
+          <t>Prescription verification: approve/reject with mandatory reason, 'Ready for pick-up' notification, record who verified, RX filter in the queue</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>DONE header search on every shop page -&gt; catalog keyword search (name, generic, brand, description); price range + availability filters.</t>
+          <t>DONE 082ec92: RX filter, Reject Prescription with reason (7-day re-upload hold), 'ready for pick-up' notice, verifier recorded + audit.</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Purpose p.3; Interviews 1-2</t>
+          <t>REQ034, REQ104-105</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Stop calling system documents 'Official Receipt': relabel the online PDF (js/orders.js:263) and add 'This is not an official receipt' to all system receipts/invoices</t>
+          <t>Show the Lalamove tracking link to the customer on their order page</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b. Client is not BIR-connected by choice and issues BIR/VAT receipts manually on request.</t>
+          <t>DONE customer order page shows a 'Track with Lalamove' card once dispatched.</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>REQ006, REQNF025, Limitations p.7; Interviews 1-3</t>
+          <t>REQ028</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Rewrite Terms &amp; Privacy to the client's actual policies: no refunds (exchange only), no cancellation after payment, 7-day hold then closure with credit kept, delivery fee and failed-delivery fees paid by the customer to the rider, RX pick-up only with original prescription, QR Ph only, Data Privacy Act 2012. Remove 'refunds case-by-case' and 'request deletion' (system only deactivates). Replace placeholder support@amson.ph with a real contact.</t>
+          <t>Add the client's real QR PH image (assets/payment-qr.png)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>DONE js/legal-content.js used by the sign-up pop-up and new legal.html; written to the client's policies + Data Privacy Act. CLIENT MUST REVIEW before go-live. Panel may read the Terms during the demo.</t>
+          <t>Need the image from the client.</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -4598,7 +4598,7 @@
       <c r="J12" s="11" t="inlineStr"/>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet; REQ111; Interviews 2, 4</t>
+          <t>REQ010-011</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Record which batch (batch no. + expiry) each sold item came from, on every POS, online and wholesale sale</t>
+          <t>Wire product search (header box) + add price-range and stock-status filters</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b. Every client report lists batch + expiry per sold line; today FEFO deducts the right batch but the sale doesn't remember which. Blocks the Reports module.</t>
+          <t>DONE header search on every shop page -&gt; catalog keyword search (name, generic, brand, description); price range + availability filters.</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -4664,17 +4664,17 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (SI# 00008247...); Modules p.43</t>
+          <t>Purpose p.3; Interviews 1-2</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>One sequential Sales Invoice (SI#) number across walk-in, online and wholesale sales</t>
+          <t>Stop calling system documents 'Official Receipt': relabel the online PDF (js/orders.js:263) and add 'This is not an official receipt' to all system receipts/invoices</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b. Replaces the separate 'receipt numbers' item; voids reference it.</t>
+          <t>DONE e1e200b. Client is not BIR-connected by choice and issues BIR/VAT receipts manually on request.</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -4715,12 +4715,12 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Payment Method section, Terms of Payment)</t>
+          <t>REQ006, REQNF025, Limitations p.7; Interviews 1-3</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Payment method + terms on every sale: Cash, G-Cash/QR Ph, Bank Transfer, Terminal (card), Credit (pay later); add to wholesale orders, which record none today</t>
+          <t>Rewrite Terms &amp; Privacy to the client's actual policies: no refunds (exchange only), no cancellation after payment, 7-day hold then closure with credit kept, delivery fee and failed-delivery fees paid by the customer to the rider, RX pick-up only with original prescription, QR Ph only, Data Privacy Act 2012. Remove 'refunds case-by-case' and 'request deletion' (system only deactivates). Replace placeholder support@amson.ph with a real contact.</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b. Credit was ₱57,534 of ₱81,181 on the sample day.</t>
+          <t>DONE js/legal-content.js used by the sign-up pop-up and new legal.html; written to the client's policies + Data Privacy Act. CLIENT MUST REVIEW before go-live. Panel may read the Terms during the demo.</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>REQNF011, REQ121</t>
+          <t>Report Formats sheet; REQ111; Interviews 2, 4</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Database rules per staff role: Sales Staff limited to POS + read-only catalog in the rules too, not only in the page menus</t>
+          <t>Record which batch (batch no. + expiry) each sold item came from, on every POS, online and wholesale sale</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Pages already block Sales Staff; someone with technical know-how could still write other collections directly.</t>
+          <t>DONE e1e200b. Every client report lists batch + expiry per sold line; today FEFO deducts the right batch but the sale doesn't remember which. Blocks the Reports module.</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       <c r="J16" s="11" t="inlineStr"/>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>REQ095-100, REQ098</t>
+          <t>Report Formats sheet (SI# 00008247...); Modules p.43</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Bug check: store credit could be lost or added twice on expired holds; credit redeemed on an order was lost on invalid-payment holds; two staff approving at once deducted stock twice</t>
+          <t>One sequential Sales Invoice (SI#) number across walk-in, online and wholesale sales</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>DONE f0faaad.</t>
+          <t>DONE e1e200b. Replaces the separate 'receipt numbers' item; voids reference it.</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -4868,22 +4868,22 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>REQNF011, REQ002, REQ098</t>
+          <t>Report Formats sheet (Payment Method section, Terms of Payment)</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Bug check: database rules let a customer create orders with any status/hold, start with store credit, rewrite a hold when resubmitting, or reset the order counter; deactivated staff kept access</t>
+          <t>Payment method + terms on every sale: Cash, G-Cash/QR Ph, Bank Transfer, Terminal (card), Credit (pay later); add to wholesale orders, which record none today</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>DONE 5d41982 (publish firestore.rules).</t>
+          <t>DONE e1e200b. Credit was ₱57,534 of ₱81,181 on the sample day.</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
@@ -4919,22 +4919,22 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>REQNF011</t>
+          <t>REQNF011, REQ121</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Bug check: customer- and staff-typed text (names, order numbers, notes) was put into admin pages as HTML</t>
+          <t>Database rules per staff role: Sales Staff limited to POS + read-only catalog in the rules too, not only in the page menus</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>DONE 72e7361.</t>
+          <t>Pages already block Sales Staff; someone with technical know-how could still write other collections directly.</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -4955,7 +4955,7 @@
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4965,22 +4965,22 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
+          <t>REQ095-100, REQ098</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
+          <t>Bug check: store credit could be lost or added twice on expired holds; credit redeemed on an order was lost on invalid-payment holds; two staff approving at once deducted stock twice</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: BM/Technical void completed sales from POS Today's Sales or Walk-in Orders: reason, SI No., stock restored to the same batches, exchange note + price difference, audit entry. Still open: second-person approval (client rule) and exchange as a real stock movement. Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
+          <t>DONE f0faaad.</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr"/>
@@ -5016,27 +5016,27 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>REQ098, REQ102, C2</t>
+          <t>REQNF011, REQ002, REQ098</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
+          <t>Bug check: database rules let a customer create orders with any status/hold, start with store credit, rewrite a hold when resubmitting, or reset the order counter; deactivated staff kept access</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b (system part; REQ098 paper wording still to do). From the first review.</t>
+          <t>DONE 5d41982 (publish firestore.rules).</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr"/>
@@ -5067,22 +5067,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
+          <t>REQNF011</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
+          <t>Bug check: customer- and staff-typed text (names, order numbers, notes) was put into admin pages as HTML</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>DONE BM-only prices in the form, batch import and quick-add (others' products saved Inactive + 'Price pending'); reason required and logged; enforced in firestore.rules - PUBLISH THE RULES in the Firebase console.</t>
+          <t>DONE 72e7361.</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr"/>
@@ -5118,27 +5118,27 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Removals (Letter) sheet</t>
+          <t>REQ083, REQ122, Fig 2.6, Fig 2.14, C4</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Letter to the panel: OpenAI -&gt; Gemini (free), Firebase Storage -&gt; Cloudinary, DataTable -&gt; custom tables, password reset via Firebase Auth, overpayment approve-and-credit, corrections to scope/conceptual framework</t>
+          <t>Walk-in void: reason, original receipt no., automatic stock restore, optional exchange item + price difference, audit entry; restricted to authorized role</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -5148,18 +5148,18 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>One letter covers all remaining removals; send before the paper edits.</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 57f4d80: BM/Technical void completed sales from POS Today's Sales or Walk-in Orders: reason, SI No., stock restored to the same batches, exchange note + price difference, audit entry. Still open: second-person approval (client rule) and exchange as a real stock movement. Client's #1 pain point (Interview 4). Client rules: a void needs a second authorized person, not one junior staff member alone; exchange item must be equal or higher value (customer pays the difference, never refunded); restored stock must show online too.</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5169,27 +5169,27 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Objectives / evaluation (p.5-6, 21-24)</t>
+          <t>REQ098, REQ102, C2</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
+          <t>Fix overpayment approval: clear the old hold, send 'Payment confirmed' notification; reword REQ098</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -5197,7 +5197,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr"/>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>DONE e1e200b (system part; REQ098 paper wording still to do). From the first review.</t>
+        </is>
+      </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -5206,7 +5210,7 @@
       <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5216,22 +5220,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>REQ121</t>
+          <t>REQ071, REQ073, REQ120, REQNF011, C8</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
+          <t>Price lock: only Branch Manager sets prices on create/import too; enforce in database rules; add a reason to each price change</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -5241,17 +5245,17 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: POS (with Today's Sales) + read-only catalog; lands on POS after login. Orders access was added on purpose on 2026-10-01.</t>
+          <t>DONE BM-only prices in the form, batch import and quick-add (others' products saved Inactive + 'Price pending'); reason required and logged; enforced in firestore.rules - PUBLISH THE RULES in the Firebase console.</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr"/>
@@ -5267,37 +5271,37 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>REQNF005</t>
+          <t>Removals (Letter) sheet</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Live updates without refresh on all order and inventory screens (staff + customer)</t>
+          <t>Letter to the panel: OpenAI -&gt; Gemini (free), Firebase Storage -&gt; Cloudinary, DataTable -&gt; custom tables, password reset via Firebase Auth, overpayment approve-and-credit, corrections to scope/conceptual framework</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>DONE 21e505b: orders (staff + customer), inventory, POS today's sales, chat.</t>
+          <t>One letter covers all remaining removals; send before the paper edits.</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -5308,7 +5312,7 @@
       <c r="J26" s="11" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5318,42 +5322,38 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>REQNF010, REQNF013</t>
+          <t>Objectives / evaluation (p.5-6, 21-24)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
+          <t>Obj. 4 evaluates with TAM + ISO/IEC 25010, but there is no questionnaire, respondent group, sampling, scale, or statistical treatment yet. The final paper needs the instrument and a results chapter.</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: Netlify (already set up).</t>
-        </is>
-      </c>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr"/>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr"/>
@@ -5369,27 +5369,27 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Discount/Deductions columns); Interview 2</t>
+          <t>REQ085-088 wholesale pricing, Reports (costing)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Discount / deduction per sale or line, with reason and audit entry</t>
+          <t>Costing and wholesale prices: only 56 of 1,172 products have them (from the March report); the price list has retail only</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -5399,18 +5399,18 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Client confirmed: no discounts. Not in the paper; client gives boss-approved discounts today.</t>
+          <t>Branch Manager fills them in Edit Product, or send a list with costing/wholesale and we update by file.</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr"/>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5420,27 +5420,27 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Methodology p.30 ('actual client data'); Report Formats sheet</t>
+          <t>REQ121</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Load the client's real March-end catalog (prices, batches, expiry) from their workbook via the existing upload templates</t>
+          <t>Sales Staff access: trim to POS + catalog view, or reword REQ121</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: yes, once the client sends the catalog. Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
+          <t>DONE 57f4d80: POS (with Today's Sales) + read-only catalog; lands on POS after login. Orders access was added on purpose on 2026-10-01.</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -5461,7 +5461,7 @@
       <c r="J29" s="11" t="inlineStr"/>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5476,22 +5476,22 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Live chat module</t>
+          <t>REQNF005</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Decide the live chat health approach with Amson / their pharmacist: label matching (now), staff-assigned condition shelves, or Shopee-style ingredient info with guardrails</t>
+          <t>Live updates without refresh on all order and inventory screens (staff + customer)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -5501,18 +5501,18 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Label matching can suggest a pain reliever for any pain (e.g. foot pain -&gt; Biogesic). Paper wording must stay honest: suggestions, not advice.</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>DONE 21e505b: orders (staff + customer), inventory, POS today's sales, chat.</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>REQNF010, REQNF013</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
+          <t>Deployment: Firebase Hosting (HTTPS) or move hosting to Limitations</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>DONE chat is built; keep 'coordinated through live chat'.</t>
+          <t>DECIDED: Netlify (already set up).</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -5563,7 +5563,7 @@
       <c r="J31" s="11" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5573,27 +5573,27 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Limitations (p.7)</t>
+          <t>Report Formats sheet (Discount/Deductions columns); Interview 2</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
+          <t>Discount / deduction per sale or line, with reason and audit entry</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -5601,16 +5601,20 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Client confirmed: no discounts. Not in the paper; client gives boss-approved discounts today.</t>
+        </is>
+      </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr"/>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -5620,27 +5624,27 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Methodology p.30 ('actual client data'); Report Formats sheet</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
+          <t>Load the client's real March-end catalog (prices, batches, expiry) from their workbook via the existing upload templates</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -5648,7 +5652,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Client sent the April price list (2026-10-22): product upload files ready (item 149); opening stock quantities still needed (item 153). Makes the demo and the TAM evaluation realistic; check confidentiality with the client first.</t>
+        </is>
+      </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5667,29 +5675,29 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
+          <t>Live chat module</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Decide the live chat health approach with Amson / their pharmacist: label matching (now), staff-assigned condition shelves, or Shopee-style ingredient info with guardrails</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
           <t>Med</t>
@@ -5697,7 +5705,7 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: locks itself after one run; SI counter now staff-only in rules (publish rules). From the first review.</t>
+          <t>Label matching can suggest a pain reliever for any pain (e.g. foot pain -&gt; Biogesic). Paper wording must stay honest: suggestions, not advice.</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -5708,7 +5716,7 @@
       <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5718,22 +5726,22 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>REQ002</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
+          <t>'Retail item exchanges ... coordinated through live chat': if chat is cut, change this to phone/Messenger.</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -5748,7 +5756,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>From the first review.</t>
+          <t>DONE chat is built; keep 'coordinated through live chat'.</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -5759,7 +5767,7 @@
       <c r="J35" s="11" t="inlineStr"/>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5769,27 +5777,27 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
+          <t>Limitations (p.7)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Unrecognized-device OTP for customers and staff</t>
+          <t>Add new limitations if decided: hosting/deployment, live chat/AI, real-time refresh, OpenAI cost.</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
@@ -5797,11 +5805,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
-        <is>
-          <t>DONE 7ede9d4: emailed code on new browsers, customers and staff; recognized devices in Account Settings.</t>
-        </is>
-      </c>
+      <c r="H36" s="11" t="inlineStr"/>
       <c r="I36" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5810,7 +5814,7 @@
       <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5820,27 +5824,27 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>REQ086, REQ089, REQ091, REQ092</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
+          <t>Netlify listed for hosting with continuous integration; nothing is deployed (Netlify blocked by billing). Depends on the hosting decision.</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -5848,11 +5852,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>DONE 5cad255: history, sales invoice PDF, free-of-cost, LTO/permit validity. Not built: reorder from a past order. Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
-        </is>
-      </c>
+      <c r="H37" s="11" t="inlineStr"/>
       <c r="I37" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -5861,7 +5861,7 @@
       <c r="J37" s="11" t="inlineStr"/>
       <c r="K37" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5876,22 +5876,22 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>REQ090, REQ114, Fig 2.15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
+          <t>Remove or lock the Migrate Credit page (re-running it re-grants spent credit)</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>DONE Purchase History -&gt; Exchange: return to batch, FEFO replacement, value rule, audit, exchange document; Return / Exchange report.</t>
+          <t>DONE d9fc96b: locks itself after one run; SI counter now staff-only in rules (publish rules). From the first review.</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -5927,22 +5927,22 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>REQ067, C7</t>
+          <t>REQ002</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
+          <t>Close the email-verification bypass (code readable by customer; customer can set emailVerified)</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>DONE d2a957b: automatic write-off with reason, audit entry, disposal alert, Mark disposed.</t>
+          <t>From the first review.</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -5963,7 +5963,7 @@
       <c r="J39" s="11" t="inlineStr"/>
       <c r="K39" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
+          <t>REQ005, REQ044, Fig 2.3, Fig 2.8</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
+          <t>Unrecognized-device OTP for customers and staff</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout. The 'not an official receipt' line was removed from POS and online receipts on 2026-10-21 at the team's request.</t>
+          <t>DONE 7ede9d4: emailed code on new browsers, customers and staff; recognized devices in Account Settings.</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
@@ -6029,22 +6029,22 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>REQ084</t>
+          <t>REQ086, REQ089, REQ091, REQ092</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>POS: RX Verified checkbox + optional notes</t>
+          <t>Wholesale: purchase history per account (with reorder from a past order), wholesale sales invoice, free-of-cost option with reason, document expiry dates</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: checkbox + notes, required for RX items, saved on the sale.</t>
+          <t>DONE 5cad255: history, sales invoice PDF, free-of-cost, LTO/permit validity. Not built: reorder from a past order. Interview 1: free RX goods go only to medical doctors/hospitals; vitamins open to all. Interview 2: reorder what they bought weeks ago.</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -6080,22 +6080,22 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>REQ061, C5</t>
+          <t>REQ090, REQ114, Fig 2.15</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
+          <t>Wholesale exchange workflow (return + FEFO replacement + audit + exchange document)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da: others save counts; BM finalizes; variance reason required and logged.</t>
+          <t>DONE Purchase History -&gt; Exchange: return to batch, FEFO replacement, value rule, audit, exchange document; Return / Exchange report.</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
@@ -6131,22 +6131,22 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>REQNF025, REQNF029</t>
+          <t>REQ067, C7</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
+          <t>2-month Bad Order: auto-flag, disposal alert, auto-deduct with write-off record</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>DONE footer rebuilt from js/store-info.js (real About text, links to legal.html; contact/LTO lines hidden until the client confirms them); chat links hidden until chat is built; payment page Terms link fixed. From the first review.</t>
+          <t>DONE d2a957b: automatic write-off with reason, audit entry, disposal alert, Mark disposed.</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>REQ039, REQ042</t>
+          <t>Fig 2.6 Print Transaction Receipt, Modules p.44</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
+          <t>Receipt printing (thermal 58mm print layout) for POS sales</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>DONE EmailJS order template (ID to paste in js/emailjs-config.js) + on/off toggle in Account Settings. EmailJS free tier: 200/month.</t>
+          <t>DONE 57f4d80: Print button on every POS receipt; 58mm print layout. The 'not an official receipt' line was removed from POS and online receipts on 2026-10-21 at the team's request.</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
@@ -6233,22 +6233,22 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>REQ122</t>
+          <t>REQ084</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
+          <t>POS: RX Verified checkbox + optional notes</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -6256,7 +6256,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>DONE 57f4d80: checkbox + notes, required for RX items, saved on the sale.</t>
+        </is>
+      </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6265,7 +6269,7 @@
       <c r="J45" s="11" t="inlineStr"/>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6280,17 +6284,17 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>REQ014</t>
+          <t>REQ061, C5</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Save cart to the customer's account</t>
+          <t>Reconciliation: Branch Manager-only finalize + variance reason in audit log</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -6305,7 +6309,7 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3.</t>
+          <t>DONE 06574da: others save counts; BM finalizes; variance reason required and logged.</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
@@ -6331,17 +6335,17 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>REQNF003, REQNF007</t>
+          <t>REQNF025, REQNF029</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Phone/tablet and cross-browser test pass</t>
+          <t>Remove dead links and filler: Live Chat sidebar link, chat buttons, footer sample text, footer Privacy/Terms links</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -6354,7 +6358,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>DONE footer rebuilt from js/store-info.js (real About text, links to legal.html; contact/LTO lines hidden until the client confirms them); chat links hidden until chat is built; payment page Terms link fixed. From the first review.</t>
+        </is>
+      </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6363,7 +6371,7 @@
       <c r="J47" s="11" t="inlineStr"/>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6378,22 +6386,22 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Interviews 2, 4</t>
+          <t>REQ039, REQ042</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
+          <t>Email notifications for key order events + on/off toggle in Account Settings</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
@@ -6403,7 +6411,7 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b. Required column in the monthly purchases report.</t>
+          <t>DONE EmailJS order template (ID to paste in js/emailjs-config.js) + on/off toggle in Account Settings. EmailJS free tier: 200/month.</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -6429,22 +6437,22 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Interview 4 walkthrough</t>
+          <t>REQ122</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Supplier history: everything received from each supplier</t>
+          <t>Audit log completeness: structured before/after, reasons, more events (receiving, PO, product create/delete, RX verification)</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -6452,11 +6460,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>DONE Reports -&gt; Supplier Purchases (per supplier, per month). Shown to the client during the prototype walkthrough.</t>
-        </is>
-      </c>
+      <c r="H49" s="11" t="inlineStr"/>
       <c r="I49" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6465,7 +6469,7 @@
       <c r="J49" s="11" t="inlineStr"/>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6480,22 +6484,22 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Methodology p.30; Interview 4</t>
+          <t>REQ014</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>User manual + hands-on training + handover to the branch</t>
+          <t>Save cart to the customer's account</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
@@ -6505,7 +6509,7 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
+          <t>DONE 77336f3.</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
@@ -6516,7 +6520,7 @@
       <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6531,17 +6535,17 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
+          <t>REQNF003, REQNF007</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
+          <t>Phone/tablet and cross-browser test pass</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Not verified</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -6554,11 +6558,7 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>DONE e1e200b. Customer File groups every sale by customer name.</t>
-        </is>
-      </c>
+      <c r="H51" s="11" t="inlineStr"/>
       <c r="I51" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -6567,7 +6567,7 @@
       <c r="J51" s="11" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (Supplier sheets)</t>
+          <t>Interviews 2, 4</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
+          <t>Supplier receipt / DR number field on Receive Stock and PO receiving</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b: unit cost + receipt/DR no. added; pack size stays in the product name as the branch does today. Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
+          <t>DONE e1e200b. Required column in the monthly purchases report.</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -6633,17 +6633,17 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
+          <t>Interview 4 walkthrough</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies, Grocery</t>
+          <t>Supplier history: everything received from each supplier</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Deviates</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>DONE e1e200b: also storefront links/filters now follow Manage Categories. Existing Firebase projects keep their current categories - add the client's in Manage Categories.. Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
+          <t>DONE Reports -&gt; Supplier Purchases (per supplier, per month). Shown to the client during the prototype walkthrough.</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -6684,17 +6684,17 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087</t>
+          <t>Methodology p.30; Interview 4</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Optional agreed price per wholesale buyer per product, used as default on their orders</t>
+          <t>User manual + hands-on training + handover to the branch</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -6709,18 +6709,18 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>DONE saved from Process Order, listed in Edit account, default on orders. Keeps per-account pricing (no letter).</t>
-        </is>
-      </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>Client: 'kailangan pa namin gamayin, i-hands on pa namin to'.</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6735,22 +6735,22 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>Report Formats sheet (Customer File shows named walk-ins, e.g. EMPLOYEE)</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Cut database reads: stop loading whole collections on every page (Firestore free-plan daily read cap ~50k)</t>
+          <t>Optional customer name on walk-in sales (default 'Walk-in')</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>DONE 6bdc6a6; reports and dashboard still read full history by design. Needed before real use with the client's ~1,000-product catalog.</t>
+          <t>DONE e1e200b. Customer File groups every sale by customer name.</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -6786,17 +6786,17 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Dashboard module p.40; Interview 4 (dashboard export)</t>
+          <t>Report Formats sheet (Supplier sheets)</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Dashboard Sales Analytics: show which dates the Today/Week/Month/Year view covers, and add a picker to choose a specific day, week, month or year (with previous/next)</t>
+          <t>Unit cost, supplier receipt no., brand and pack on each stock receiving entry</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>DONE cb08e78: date range shown; Day/Week/Month/Year with previous/next and a date picker; exports name the period. Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
+          <t>DONE e1e200b: unit cost + receipt/DR no. added; pack size stays in the product name as the branch does today. Monthly purchases report needs cost per delivery, not just the product's current costing.</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -6837,17 +6837,17 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>REQ048, Notification module</t>
+          <t>Report Formats sheet (monthly sheets); js/products-data.js:401</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Admin notification for pending wholesale orders (Pending -&gt; Released)</t>
+          <t>Match the client's categories: Generics, Branded, Drugstore (per piece), Medical Supplies (no Grocery - client 2026-10-22)</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Deviates</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>DONE 274b8e0: wholesale orders start Pending; Mark Released in purchase history; staff notification.</t>
+          <t>DONE e1e200b: also storefront links/filters now follow Manage Categories. Existing Firebase projects keep their current categories - add the client's in Manage Categories.. Default categories are OTC/Vitamins/Personal Care/Health &amp; Wellness; the monthly report is one sheet per client category.</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -6888,22 +6888,22 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>REQ111, Sales Report module</t>
+          <t>REQ085, REQ087</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Daily Sales report: batch, expiry, date received and supplier per item sold</t>
+          <t>Optional agreed price per wholesale buyer per product, used as default on their orders</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>DONE 274b8e0: 'Item Sold by Batch' section.</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>DONE saved from Process Order, listed in Edit account, default on orders. Keeps per-account pricing (no letter).</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr"/>
@@ -6939,17 +6939,17 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Bug check: checkout, reports, inventory and wholesale fixes (RX orders always pick-up, price/availability re-check, exchanges in sales reports, write-off date, stock count variance, receiving saved all at once, invoice peso sign)</t>
+          <t>Cut database reads: stop loading whole collections on every page (Firestore free-plan daily read cap ~50k)</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>DONE d51639d, 0e7826e.</t>
+          <t>DONE 6bdc6a6; reports and dashboard still read full history by design. Needed before real use with the client's ~1,000-product catalog.</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -6990,17 +6990,17 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Shopping cart module, REQ014-016</t>
+          <t>Dashboard module p.40; Interview 4 (dashboard export)</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Buy Now goes to the cart page; Add to Cart / Buy Now no longer lose items on the next page</t>
+          <t>Dashboard Sales Analytics: show which dates the Today/Week/Month/Year view covers, and add a picker to choose a specific day, week, month or year (with previous/next)</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>DONE 010449e, 62b3c79. Cart sync uses a saved-at time so the newest cart wins; Buy Now adds the item and opens the cart.</t>
+          <t>DONE cb08e78: date range shown; Day/Week/Month/Year with previous/next and a date picker; exports name the period. Requested by the team 2026-10-21. Chart, totals and the export should all follow the picked period, and the export title should name it.</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -7041,17 +7041,17 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Inventory module, REQ061-063</t>
+          <t>REQ048, Notification module</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Receive Stock: every field required; supplier must be chosen (no 'No supplier')</t>
+          <t>Admin notification for pending wholesale orders (Pending -&gt; Released)</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>DONE 1581610. Same rules for the form, Excel upload and PO delivery.</t>
+          <t>DONE 274b8e0: wholesale orders start Pending; Mark Released in purchase history; staff notification.</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -7092,17 +7092,17 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Inventory module, FEFO (REQ064-066)</t>
+          <t>REQ111, Sales Report module</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Batch numbers: same product + batch + expiry adds to that batch; same batch with a different expiry is refused; Bad Order batches can't be received again</t>
+          <t>Daily Sales report: batch, expiry, date received and supplier per item sold</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>DONE df65830, a15c428. Team asked for unique batch numbers; agreed on this common practice since each batch has one expiry. Deliveries listed per batch.</t>
+          <t>DONE 274b8e0: 'Item Sold by Batch' section.</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -7143,22 +7143,22 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Report Formats (client's month-end report), REQ111</t>
+          <t>Various</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Monthly Inventory report: Supplier column and an EXPIRED sheet (batches that expired in the month)</t>
+          <t>Bug check: checkout, reports, inventory and wholesale fixes (RX orders always pick-up, price/availability re-check, exchanges in sales reports, write-off date, stock count variance, receiving saved all at once, invoice peso sign)</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>DONE 59f740f. Team request 2026-10-21.</t>
+          <t>DONE d51639d, 0e7826e.</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>POS module, REQ070-072</t>
+          <t>Shopping cart module, REQ014-016</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>POS: Reference No. required for GCash, bank transfer and card terminal payments</t>
+          <t>Buy Now goes to the cart page; Add to Cart / Buy Now no longer lose items on the next page</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>DONE 2a52561. Saved on the sale, shown on receipt and reports.</t>
+          <t>DONE 010449e, 62b3c79. Cart sync uses a saved-at time so the newest cart wins; Buy Now adds the item and opens the cart.</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Audit log, REQNF011</t>
+          <t>Inventory module, REQ061-063</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Audit log covers every stock and order movement (receive, write-off, PO, walk-in sale, order status changes, customer received/auto-delivered)</t>
+          <t>Receive Stock: every field required; supplier must be chosen (no 'No supplier')</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>DONE 2a52561. Team request 2026-10-21.</t>
+          <t>DONE 1581610. Same rules for the form, Excel upload and PO delivery.</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Live chat module</t>
+          <t>Inventory module, FEFO (REQ064-066)</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Live chat: order cards ('My orders') and 'what we carry for this' product cards for symptoms, with a fixed caution and a pharmacist hand-off</t>
+          <t>Batch numbers: same product + batch + expiry adds to that batch; same batch with a different expiry is refused; Bad Order batches can't be received again</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>DONE d45e61b, 128d7d2. Products are matched by words on their labels (dosage notes); Gemini only reads the question, it never names a medicine.</t>
+          <t>DONE df65830, a15c428. Team asked for unique batch numbers; agreed on this common practice since each batch has one expiry. Deliveries listed per batch.</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -7347,17 +7347,17 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Tech Stack (free plans)</t>
+          <t>Report Formats (client's month-end report), REQ111</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Before go-live: serve smaller Cloudinary images and shrink uploads; cut Firestore reads</t>
+          <t>Monthly Inventory report: Supplier column and an EXPIRED sheet (batches that expired in the month)</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>DONE 6bdc6a6: resized delivery URLs (f_auto,q_auto,w_), photos shrunk before upload by kind; shop catalog cached 5 min in the browser, staff bell cached 2 min with status-filtered order/PO reads, Inventory and Orders read once via their live listeners. Keeps Cloudinary and Firestore on the free plans as visits grow. Offered, not built yet.</t>
+          <t>DONE 59f740f. Team request 2026-10-21.</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Live chat module, Online order tracking</t>
+          <t>POS module, REQ070-072</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Live chat order cards: products with photos, progress tracker with dates, delivery or pick-up, what happens next, Track rider; live status; Gemini routes order questions the word list misses</t>
+          <t>POS: Reference No. required for GCash, bank transfer and card terminal payments</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>DONE d16bd76. Several orders show as short cards with Show details; follow-up buttons fit the status.</t>
+          <t>DONE 2a52561. Saved on the sale, shown on receipt and reports.</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -7449,17 +7449,17 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Project Context (p.1)</t>
+          <t>Audit log, REQNF011</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>Audit log covers every stock and order movement (receive, write-off, PO, walk-in sale, order status changes, customer received/auto-delivered)</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
+          <t>DONE 2a52561. Team request 2026-10-21.</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -7500,22 +7500,22 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.24)</t>
+          <t>Live chat module</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Live chat: order cards ('My orders') and 'what we carry for this' product cards for symptoms, with a fixed caution and a pharmacist hand-off</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da: system now matches (BM-only finalize).</t>
+          <t>DONE d45e61b, 128d7d2. Products are matched by words on their labels (dosage notes); Gemini only reads the question, it never names a medicine.</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output) (p.27)</t>
+          <t>Tech Stack (free plans)</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>Before go-live: serve smaller Cloudinary images and shrink uploads; cut Firestore reads</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>DONE footer links to legal.html on every page.</t>
+          <t>DONE 6bdc6a6: resized delivery URLs (f_auto,q_auto,w_), photos shrunk before upload by kind; shop catalog cached 5 min in the browser, staff bell cached 2 min with status-filtered order/PO reads, Inventory and Orders read once via their live listeners. Keeps Cloudinary and Firestore on the free plans as visits grow. Offered, not built yet.</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -7597,22 +7597,22 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles (p.45-46)</t>
+          <t>Live chat module, Online order tracking</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>Live chat order cards: products with photos, progress tracker with dates, delivery or pick-up, what happens next, Track rider; live status; Gemini routes order questions the word list misses</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
+          <t>DONE d16bd76. Several orders show as short cards with Show details; follow-up buttons fit the status.</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr"/>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>REQ001 registration, Scope and Limitations</t>
+          <t>Project Context (p.1)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Phone number verification by SMS code: on hold (every SMS costs money; Amson doesn't want to spend)</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -7678,18 +7678,18 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Paper: state in Limitations (number format checked, not ownership) and in Recommendations (SMS OTP).</t>
+          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr"/>
       <c r="K73" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7699,22 +7699,22 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Chapter 3 evaluation (Objective 4)</t>
+          <t>Theoretical Framework (p.24)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Evaluation survey questionnaires: Branch Manager, Technical Staff, Sales Staff and User forms, mapped to TAM + ISO/IEC 25010</t>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>DONE Claude Docs, 2026-10-22. In Claude Docs ('Survey Questionnaires (Admin and User)'); maintainability covered by the developers' testing (no IT expert form).</t>
+          <t>DONE 06574da: system now matches (BM-only finalize).</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr"/>
@@ -7750,22 +7750,22 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>REQ007 / Technical Background p.35-36</t>
+          <t>Conceptual Framework (Output) (p.27)</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -7780,18 +7780,18 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE footer links to legal.html on every page.</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr"/>
       <c r="K75" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7801,22 +7801,22 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>REQ008 p.47; Modules p.38</t>
+          <t>Modules: Staff roles (p.45-46)</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -7831,18 +7831,18 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr"/>
       <c r="K76" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7857,17 +7857,17 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>REQ031 p.50</t>
+          <t>REQ001 registration, Scope and Limitations</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+          <t>Phone number verification by SMS code: on hold (every SMS costs money; Amson doesn't want to spend)</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I77" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>Paper: state in Limitations (number format checked, not ownership) and in Recommendations (SMS OTP).</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr"/>
@@ -7908,17 +7908,17 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>REQ073 p.55</t>
+          <t>Chapter 3 evaluation (Objective 4)</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+          <t>Evaluation survey questionnaires: Branch Manager, Technical Staff, Sales Staff and User forms, mapped to TAM + ISO/IEC 25010</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE Claude Docs, 2026-10-22. In Claude Docs ('Survey Questionnaires (Admin and User)'); maintainability covered by the developers' testing (no IT expert form).</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -7944,7 +7944,7 @@
       <c r="J78" s="11" t="inlineStr"/>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7959,12 +7959,12 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+          <t>REQ007 / Technical Background p.35-36</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -8010,12 +8010,12 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087 p.57; Modules p.44</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Default wholesale price per product, adjustable per order (C9).</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+          <t>REQ073 p.55</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>REQ121 p.61</t>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 text p.67</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -8242,9 +8242,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I84" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I84" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr"/>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 diagram</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
@@ -8293,9 +8293,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I85" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr"/>
@@ -8316,12 +8316,12 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.5 text p.72</t>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 / 2.7 diagrams</t>
+          <t>REQ121 p.61</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.8 diagram + text p.76-77</t>
+          <t>Fig 2.2 text p.67</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 diagram + text p.78-79</t>
+          <t>Fig 2.2 diagram</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.10 diagram</t>
+          <t>Fig 2.5 text p.72</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 diagram + text p.82-83</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
@@ -8622,17 +8622,17 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover (i)</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
@@ -8645,7 +8645,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H92" s="11" t="inlineStr"/>
+      <c r="H92" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -8669,22 +8673,22 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -8692,7 +8696,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H93" s="11" t="inlineStr"/>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -8716,17 +8724,17 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -8739,7 +8747,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H94" s="11" t="inlineStr"/>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -8763,17 +8775,17 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input) (p.25)</t>
+          <t>Fig 2.11 diagram + text p.82-83</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -8786,10 +8798,14 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H95" s="11" t="inlineStr"/>
-      <c r="I95" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr"/>
@@ -8810,12 +8826,12 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.30-35)</t>
+          <t>Title page / cover (i)</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -8857,12 +8873,12 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
@@ -8872,7 +8888,7 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -8904,12 +8920,12 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -8946,42 +8962,38 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>REQ088</t>
+          <t>Conceptual Framework (Input) (p.25)</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Hide costing/wholesale prices from public reads</t>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H99" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED (revised): build it to avoid a removal letter.</t>
-        </is>
-      </c>
-      <c r="I99" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr"/>
+      <c r="I99" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr"/>
@@ -8997,48 +9009,44 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Interview 1</t>
+          <t>Methodology: sprint plan (p.30-35)</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H100" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr"/>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr"/>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9048,48 +9056,44 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (CREDIT terms)</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Credit sales follow-up (who owes what, mark as paid)</t>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H101" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr"/>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr"/>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9103,22 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Report Formats sheet (daily Sales section)</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -9124,23 +9128,19 @@
       </c>
       <c r="G102" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H102" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr"/>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr"/>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9150,22 +9150,22 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Price list</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
+          <t>Two price-list items have no price: Zardip Duo 40/5 (Telmisartan + Amlodipine) and Zincbos (Zinc Sulfate syrup)</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>DONE chat is built; keep the sentence.</t>
+          <t>Left out of the upload files; add by hand once priced.</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -9191,7 +9191,7 @@
       <c r="J103" s="11" t="inlineStr"/>
       <c r="K103" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9206,22 +9206,22 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>REQ013, REQ068</t>
+          <t>REQ088</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Dosage/usage notes field on products</t>
+          <t>Hide costing/wholesale prices from public reads</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DECIDED (revised): build it to avoid a removal letter.</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -9242,7 +9242,7 @@
       <c r="J104" s="11" t="inlineStr"/>
       <c r="K104" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -9257,22 +9257,22 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>REQ049</t>
+          <t>Interview 1</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Supplier column in the inventory batch table</t>
+          <t>Park/hold a walk-in sale ('keep') while serving the next customer</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
@@ -9282,18 +9282,18 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DECIDED: future work. Client's current POS practice; not in the paper.</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J105" s="11" t="inlineStr"/>
       <c r="K105" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -9308,22 +9308,22 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>REQ103, REQ107</t>
+          <t>Report Formats sheet (CREDIT terms)</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
+          <t>Credit sales follow-up (who owes what, mark as paid)</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr">
@@ -9333,18 +9333,18 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
+          <t>DECIDED: future work. Not in the paper; ask the client if the main office tracks collections instead.</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J106" s="11" t="inlineStr"/>
       <c r="K106" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -9359,17 +9359,17 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>REQ116</t>
+          <t>Report Formats sheet (daily Sales section)</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Customer Accounts: list of the customer's orders</t>
+          <t>Pay-in / pay-out (cash drawer in and out) recorded per day</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -9384,18 +9384,18 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DECIDED: future work. Both were 0.00 on the sample day; ask if it's used.</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J107" s="11" t="inlineStr"/>
       <c r="K107" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
+          <t>States the AI assistant won't give medical advice: keep only if chat is built.</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877. From the first review.</t>
+          <t>DONE chat is built; keep the sentence.</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -9461,17 +9461,17 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>REQ070</t>
+          <t>REQ013, REQ068</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Category rename: replace native prompt() with app dialog</t>
+          <t>Dosage/usage notes field on products</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>REQ033, REQ093</t>
+          <t>REQ049</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
+          <t>Supplier column in the inventory batch table</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92. From the first review.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>REQ099</t>
+          <t>REQ103, REQ107</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>'Payment not received' as its own hold type</t>
+          <t>Delivery: 'copy all' including preferred schedule + order no.; internal delivery notes</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 06574da. Use the notes for rider name/plate/number, which staff currently screenshot privately (Interviews 2-3).</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>REQ026</t>
+          <t>REQ116</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Checkout pick-up notice mentions bringing the original prescription</t>
+          <t>Customer Accounts: list of the customer's orders</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>DONE 082ec92.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -9665,17 +9665,17 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>REQ009</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Show quantity in stock on catalog cards</t>
+          <t>Staff creation uses shared validators; stop silent Administrator -&gt; Branch Manager change</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da.</t>
+          <t>DONE 847c877. From the first review.</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>REQ040</t>
+          <t>REQ070</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Profile picture in Account Settings</t>
+          <t>Category rename: replace native prompt() with app dialog</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3.</t>
+          <t>DONE category tools commit: rename uses the app dialog; deleting a category can move its products. From the first review.</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -9767,12 +9767,12 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>REQNF028</t>
+          <t>REQ033, REQ093</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
+          <t>Receipt only after verification; show subtotal/credit applied on PDF</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>DONE 847c877.</t>
+          <t>DONE 082ec92. From the first review.</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
@@ -9818,17 +9818,17 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>REQ047</t>
+          <t>REQ099</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
+          <t>'Payment not received' as its own hold type</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -9869,17 +9869,17 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>REQNF017</t>
+          <t>REQ026</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>README with setup steps; fix the error message that points to it</t>
+          <t>Checkout pick-up notice mentions bringing the original prescription</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>DONE 77336f3. From the first review.</t>
+          <t>DONE 082ec92.</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
@@ -9920,17 +9920,17 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>REQ001</t>
+          <t>REQ009</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Normalize phone number at registration</t>
+          <t>Show quantity in stock on catalog cards</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b. From the first review.</t>
+          <t>DONE 06574da.</t>
         </is>
       </c>
       <c r="I118" s="11" t="inlineStr">
@@ -9971,12 +9971,12 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>REQ008; Interview 1</t>
+          <t>REQ040</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
+          <t>Profile picture in Account Settings</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
+          <t>DONE 77336f3.</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>REQ031</t>
+          <t>REQNF028</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
+          <t>One date formatter (MM/DD/YYYY, 12-hour) across all screens</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
+          <t>DONE 847c877.</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
@@ -10073,17 +10073,17 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37</t>
+          <t>REQ047</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
+          <t>Dashboard 'Active Online Orders' excludes delivered/closed</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr">
@@ -10098,18 +10098,18 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Built (stock in vs out), then removed at the team's request 2026-10-21 - see the Removals sheet. Keeps the Chart.js claim (no letter).</t>
+          <t>DONE d9fc96b: counts verified + dispatched only. From the first review.</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>None (not in paper)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr"/>
       <c r="K121" s="11" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Modules p.42</t>
+          <t>REQNF017</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
+          <t>README with setup steps; fix the error message that points to it</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
+          <t>DONE 77336f3. From the first review.</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
@@ -10175,17 +10175,17 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework p.23</t>
+          <t>REQ001</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
+          <t>Normalize phone number at registration</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
+          <t>DONE d9fc96b. From the first review.</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>REQ039, Fig 2.10, C16</t>
+          <t>REQ008; Interview 1</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
+          <t>Store announcements + promotions banner, editable by staff (e.g. closure days)</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
+          <t>DONE Settings -&gt; Store Announcement; shown under the header on shop pages.</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -10277,12 +10277,12 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>REQ004</t>
+          <t>REQ031</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Login lockout counter can be reset by anyone (public loginAttempts collection)</t>
+          <t>Show invalid-payment holds to customers as 'Payment Rejected - re-upload needed'</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Lockout works for normal use; a determined attacker could clear it. Mention as a limitation if not fixed.</t>
+          <t>DONE d9fc96b: customer badges show Payment Rejected / Balance Due / Out of Stock / Prescription Rejected. Keeps the paper's status name (no letter).</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
@@ -10313,7 +10313,7 @@
       <c r="J125" s="11" t="inlineStr"/>
       <c r="K125" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10328,17 +10328,17 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Inventory module</t>
+          <t>Technical Background p.35-37</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Inventory list: drop the 'Never received' placeholder rows</t>
+          <t>Inventory movement chart on the dashboard (stock in/out over the period)</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr">
@@ -10353,18 +10353,18 @@
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>DONE 66b8b2e. Products never stocked no longer show as empty batch rows.</t>
+          <t>Built (stock in vs out), then removed at the team's request 2026-10-21 - see the Removals sheet. Keeps the Chart.js claim (no letter).</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (not in paper)</t>
         </is>
       </c>
       <c r="J126" s="11" t="inlineStr"/>
       <c r="K126" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Dropped</t>
         </is>
       </c>
     </row>
@@ -10379,17 +10379,17 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>REQ001 registration validation</t>
+          <t>Modules p.42</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Name fields allow periods and dashes (Ma. Clara, Juan P. Cruz, Jr., Anne-Marie)</t>
+          <t>Price lock/unlock toggle per product (Branch Manager only)</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>DONE 010449e, 8ce4aa0. Same rule on register, account settings, staff and admin settings.</t>
+          <t>DONE Lock/Unlock prices button for the Branch Manager in Edit Product. Keeps 'price locking' (no letter).</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -10430,17 +10430,17 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Checkout module, REQ019</t>
+          <t>Theoretical Framework p.23</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Checkout: Same Day Delivery wording and a notice that the Lalamove fee is paid to the rider</t>
+          <t>Browser notifications for staff alerts (new order, pending payment, expiry, low stock)</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>DONE 010449e.</t>
+          <t>DONE Notifications -&gt; Turn on desktop alerts; each new alert pops up once. Keeps the 'push notifications' claim (no letter).</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>EmailJS (Technical Background)</t>
+          <t>REQ039, Fig 2.10, C16</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Settings: Email Test button that shows EmailJS's reply</t>
+          <t>Order-placed notification in the customer's bell (no database rule change needed if derived from order status)</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>DONE 4eca895. Found the order template was missing To Email {{to_email}} - set it in the EmailJS dashboard before go-live.</t>
+          <t>DONE written at checkout (rule allows only the customer's own 'order_placed' notice).</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
@@ -10532,17 +10532,17 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Shopping cart module</t>
+          <t>REQ004</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Cart page: 'You May Also Like' product suggestions under the cart items</t>
+          <t>Login lockout counter can be reset by anyone (public loginAttempts collection)</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>DONE 1581610. Team request 2026-10-21 (like Shopee).</t>
+          <t>Lockout works for normal use; a determined attacker could clear it. Mention as a limitation if not fixed.</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -10568,7 +10568,7 @@
       <c r="J130" s="11" t="inlineStr"/>
       <c r="K130" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -10583,12 +10583,12 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Notification module</t>
+          <t>Inventory module</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Notifications: filter by Orders / Stock / Live Chat, newest first, mark read per filter</t>
+          <t>Inventory list: drop the 'Never received' placeholder rows</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>DONE 1581610. Team request 2026-10-21.</t>
+          <t>DONE 66b8b2e. Products never stocked no longer show as empty batch rows.</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Inventory module</t>
+          <t>REQ001 registration validation</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Inventory: 'Quantity' renamed to 'Available Inventory' (table and export)</t>
+          <t>Name fields allow periods and dashes (Ma. Clara, Juan P. Cruz, Jr., Anne-Marie)</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>DONE 1581610. Team request 2026-10-21.</t>
+          <t>DONE 010449e, 8ce4aa0. Same rule on register, account settings, staff and admin settings.</t>
         </is>
       </c>
       <c r="I132" s="11" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>All PDF exports</t>
+          <t>Checkout module, REQ019</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>PDFs printed the peso sign as a broken character - now 'PHP'</t>
+          <t>Checkout: Same Day Delivery wording and a notice that the Lalamove fee is paid to the rider</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>DONE a3f410b. jsPDF's built-in fonts have no peso sign.</t>
+          <t>DONE 010449e.</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
@@ -10736,12 +10736,12 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Online order module</t>
+          <t>EmailJS (Technical Background)</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>Online Orders: Reference No. and SI No. columns (searchable); order date and time shown in Payment Verification</t>
+          <t>Settings: Email Test button that shows EmailJS's reply</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>DONE 2a52561, 8d5a42e. Team request 2026-10-21.</t>
+          <t>DONE 4eca895. Found the order template was missing To Email {{to_email}} - set it in the EmailJS dashboard before go-live.</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Dashboard module, Reports module</t>
+          <t>Shopping cart module</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Reports moved out of the Orders tab: all reports open from the dashboard Reports panel</t>
+          <t>Cart page: 'You May Also Like' product suggestions under the cart items</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>DONE 2a52561. Team request 2026-10-21. Paper: if the Orders module text mentions an export there, point it to Reports.</t>
+          <t>DONE 1581610. Team request 2026-10-21 (like Shopee).</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Dashboard module, sequential SI</t>
+          <t>Notification module</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>Dashboard: Find a Sale by SI No. (walk-in, online and wholesale)</t>
+          <t>Notifications: filter by Orders / Stock / Live Chat, newest first, mark read per filter</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>DONE 8d5a42e. Every sale gets an SI No.; online orders keep their order/reference numbers too.</t>
+          <t>DONE 1581610. Team request 2026-10-21.</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Go-live</t>
+          <t>Inventory module</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>Temporary Clear Test Data page (Branch Manager / Administrator) and its delete rule; both switch off 2026-11-15</t>
+          <t>Inventory: 'Quantity' renamed to 'Available Inventory' (table and export)</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>DONE 77fdd25, 112ce91 (publish firestore.rules to use it). Remove the page, its Settings card and the TEMPORARY rule block after go-live; not part of the paper.</t>
+          <t>DONE 1581610. Team request 2026-10-21.</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
@@ -10940,17 +10940,17 @@
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Tech Stack (free plans), REQNF013</t>
+          <t>All PDF exports</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>Watch Firestore usage after go-live: Dashboard and Reports still read the full sales history on each visit</t>
+          <t>PDFs printed the peso sign as a broken character - now 'PHP'</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="H138" s="11" t="inlineStr">
         <is>
-          <t>Fine at one branch's volume; if the 50,000 reads/day limit gets close, limit them to the chosen period.</t>
+          <t>DONE a3f410b. jsPDF's built-in fonts have no peso sign.</t>
         </is>
       </c>
       <c r="I138" s="11" t="inlineStr">
@@ -10976,7 +10976,7 @@
       <c r="J138" s="11" t="inlineStr"/>
       <c r="K138" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -10991,17 +10991,17 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>System roles (-)</t>
+          <t>Online order module</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
+          <t>Online Orders: Reference No. and SI No. columns (searchable); order date and time shown in Payment Verification</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr">
@@ -11014,7 +11014,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H139" s="11" t="inlineStr"/>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>DONE 2a52561, 8d5a42e. Team request 2026-10-21.</t>
+        </is>
+      </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
           <t>None</t>
@@ -11023,7 +11027,7 @@
       <c r="J139" s="11" t="inlineStr"/>
       <c r="K139" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11033,22 +11037,22 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>Whole paper + system (-)</t>
+          <t>Dashboard module, Reports module</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
+          <t>Reports moved out of the Orders tab: all reports open from the dashboard Reports panel</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr">
@@ -11061,16 +11065,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H140" s="11" t="inlineStr"/>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>DONE 2a52561. Team request 2026-10-21. Paper: if the Orders module text mentions an export there, point it to Reports.</t>
+        </is>
+      </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J140" s="11" t="inlineStr"/>
       <c r="K140" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11080,27 +11088,27 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>REQ005, REQ044</t>
+          <t>Dashboard module, sequential SI</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>New-device code is checked in the browser, not by the database rules</t>
+          <t>Dashboard: Find a Sale by SI No. (walk-in, online and wholesale)</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
@@ -11110,18 +11118,18 @@
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Stops normal use of a stolen password; a technical attacker could skip it. State this in Limitations.</t>
+          <t>DONE 8d5a42e. Every sale gets an SI No.; online orders keep their order/reference numbers too.</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J141" s="11" t="inlineStr"/>
       <c r="K141" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11131,22 +11139,22 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>REQ090</t>
+          <t>Go-live</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>Known, not fixed: two wholesale exchanges on the same order line at the same second can mix up which batch a later return goes back to (stock totals stay right)</t>
+          <t>Temporary Clear Test Data page (Branch Manager / Administrator) and its delete rule; both switch off 2026-11-15</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr">
@@ -11161,18 +11169,18 @@
       </c>
       <c r="H142" s="11" t="inlineStr">
         <is>
-          <t>Rare; same-second exchanges on one line.</t>
+          <t>DONE 77fdd25, 112ce91 (publish firestore.rules to use it). Remove the page, its Settings card and the TEMPORARY rule block after go-live; not part of the paper.</t>
         </is>
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J142" s="11" t="inlineStr"/>
       <c r="K142" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11182,22 +11190,22 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>REQ118</t>
+          <t>Tech Stack (free plans), REQNF013</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>Known, not fixed: if creating a staff account fails after the login is made, the email can't be reused until the login is removed in the Firebase console</t>
+          <t>Watch Firestore usage after go-live: Dashboard and Reports still read the full sales history on each visit</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr">
@@ -11212,12 +11220,12 @@
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Needs a server function to clean up; note in the user manual.</t>
+          <t>Fine at one branch's volume; if the 50,000 reads/day limit gets close, limit them to the chosen period.</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J143" s="11" t="inlineStr"/>
@@ -11233,22 +11241,22 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (Chart.js 'inventory movement data'), Dashboard module</t>
+          <t>Report Formats (Supplier Purchases, Monthly Inventory), Scope p.6</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>Inventory Movement chart removed from the dashboard at the team's request (2026-10-21)</t>
+          <t>No grocery / non-medical items (client, 2026-10-22): Grocery removed from the default categories; Supplier Purchases is one sheet</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr">
@@ -11263,18 +11271,18 @@
       </c>
       <c r="H144" s="11" t="inlineStr">
         <is>
-          <t>Paper: drop 'inventory movement data' from the Chart.js line, or note it in the panel letter; stock in/out is still in the Inventory page and reports.</t>
-        </is>
-      </c>
-      <c r="I144" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+          <t>DONE 19118db. Delete a 'Grocery' category already in Firebase via Manage Categories.</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J144" s="11" t="inlineStr"/>
       <c r="K144" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11284,22 +11292,22 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Modules FEFO p.41</t>
+          <t>System roles (-)</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>Add the 2-month Bad Order step (C7).</t>
+          <t>The system also has a legacy 'Administrator' role that the paper never mentions. Hide it from the UI or document it.</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
@@ -11312,14 +11320,10 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H145" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
+      <c r="H145" s="11" t="inlineStr"/>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J145" s="11" t="inlineStr"/>
@@ -11335,22 +11339,22 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>Technical Background p.35-37; Budget p.99</t>
+          <t>Whole paper + system (-)</t>
         </is>
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
+          <t>'QR PH' in the paper and most screens, 'QR Ph' on the payment page image text. The official name is 'QR Ph'; pick one everywhere.</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr">
@@ -11363,14 +11367,10 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H146" s="11" t="inlineStr">
-        <is>
-          <t>See Contradictions / Paper Edits</t>
-        </is>
-      </c>
-      <c r="I146" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H146" s="11" t="inlineStr"/>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J146" s="11" t="inlineStr"/>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Scope p.6; Product Browsing REQ009</t>
+          <t>REQ005, REQ044</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
+          <t>New-device code is checked in the browser, not by the database rules</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
@@ -11416,12 +11416,12 @@
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Stops normal use of a stolen password; a technical attacker could skip it. State this in Limitations.</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J147" s="11" t="inlineStr"/>
@@ -11442,17 +11442,17 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Scope and Limitations p.7</t>
+          <t>REQ090</t>
         </is>
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
+          <t>Known, not fixed: two wholesale exchanges on the same order line at the same second can mix up which batch a later return goes back to (stock totals stay right)</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="H148" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>Rare; same-second exchanges on one line.</t>
         </is>
       </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
-          <t>Adds</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J148" s="11" t="inlineStr"/>
@@ -11493,17 +11493,17 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Decision-dependent</t>
+          <t>REQ118</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
+          <t>Known, not fixed: if creating a staff account fails after the login is made, the email can't be reused until the login is removed in the Firebase console</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+          <t>Needs a server function to clean up; note in the user manual.</t>
         </is>
       </c>
       <c r="I149" s="11" t="inlineStr">
@@ -11544,17 +11544,17 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Technical Background (Chart.js 'inventory movement data'), Dashboard module</t>
         </is>
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
+          <t>Inventory Movement chart removed from the dashboard at the team's request (2026-10-21)</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Removed</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr">
@@ -11567,10 +11567,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H150" s="11" t="inlineStr"/>
-      <c r="I150" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H150" s="11" t="inlineStr">
+        <is>
+          <t>Paper: drop 'inventory movement data' from the Chart.js line, or note it in the panel letter; stock in/out is still in the Inventory page and reports.</t>
+        </is>
+      </c>
+      <c r="I150" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J150" s="11" t="inlineStr"/>
@@ -11591,17 +11595,17 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Scope (p.6)</t>
+          <t>Modules FEFO p.41</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
+          <t>Add the 2-month Bad Order step (C7).</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
@@ -11614,10 +11618,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H151" s="11" t="inlineStr"/>
-      <c r="I151" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H151" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J151" s="11" t="inlineStr"/>
@@ -11638,17 +11646,17 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.22-23)</t>
+          <t>Technical Background p.35-37; Budget p.99</t>
         </is>
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
+          <t>Cloudinary instead of Firebase Storage; Choices.js added; DataTable removed; hosting per decision (Tech Stack sheet).</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
@@ -11663,7 +11671,7 @@
       </c>
       <c r="H152" s="11" t="inlineStr">
         <is>
-          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
+          <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
       <c r="I152" s="12" t="inlineStr">
@@ -11674,7 +11682,7 @@
       <c r="J152" s="11" t="inlineStr"/>
       <c r="K152" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -11689,17 +11697,17 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.32)</t>
+          <t>Scope p.6; Product Browsing REQ009</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
+          <t>The client also sells medical supplies (grocery items are dropped, client 2026-10-22); the paper only mentions OTC/prescription medicines. Mention medical supplies.</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
@@ -11712,10 +11720,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H153" s="11" t="inlineStr"/>
+      <c r="H153" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J153" s="11" t="inlineStr"/>
@@ -11736,17 +11748,17 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35)</t>
+          <t>Scope and Limitations p.7</t>
         </is>
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
+          <t>Add: system receipts/invoices are internal records, not BIR-registered official receipts; BIR/VAT receipts stay manual on request; no BIR or government integration (client policy, Interview 1).</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
@@ -11759,10 +11771,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H154" s="11" t="inlineStr"/>
+      <c r="H154" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I154" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J154" s="11" t="inlineStr"/>
@@ -11783,17 +11799,17 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Decision-dependent</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
+          <t>Live chat/AI (Obj. 1, Scope, Framework, REQ035-038, REQ108-110, NF008, NF012); real-time refresh (NF005); hosting (NF013); wholesale price visibility (REQ088).</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr">
@@ -11806,10 +11822,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H155" s="11" t="inlineStr"/>
-      <c r="I155" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H155" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED: build it on Gemini via Firebase AI Logic (free tier), swappable to Groq; FAQ answers without AI calls; staff handoff when the free limit is hit. Verify the project's limit in AI Studio first. See Contradictions / Paper Edits</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J155" s="11" t="inlineStr"/>
@@ -11830,12 +11850,12 @@
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35-36)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
+          <t>Spelling consistency: 'Fulfilment' on the cover vs 'fulfillment' elsewhere.</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
@@ -11854,9 +11874,9 @@
         </is>
       </c>
       <c r="H156" s="11" t="inlineStr"/>
-      <c r="I156" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I156" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J156" s="11" t="inlineStr"/>
@@ -11877,12 +11897,12 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Technical Background (p.35, 37)</t>
+          <t>Scope (p.6)</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
+          <t>'Intended to serve retail customers, wholesale clients, branch staff, and main office management': wholesale clients and the main office never log in. Reword to 'staff record wholesale transactions; reports are submitted to the main office'.</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
@@ -11924,12 +11944,12 @@
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.36-38)</t>
+          <t>Theoretical Framework (p.22-23)</t>
         </is>
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
+          <t>Mentions 'instantaneous push notifications for near-expiry supplies'; the system has an in-app notification bell, not push notifications. Reword.</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
@@ -11947,16 +11967,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H158" s="11" t="inlineStr"/>
-      <c r="I158" s="11" t="inlineStr">
-        <is>
-          <t>Adds</t>
+      <c r="H158" s="11" t="inlineStr">
+        <is>
+          <t>DONE Desktop alerts now built; wording can stay (or say 'desktop alerts').</t>
+        </is>
+      </c>
+      <c r="I158" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J158" s="11" t="inlineStr"/>
       <c r="K158" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11971,12 +11995,12 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>Technical Background: Software (p.38)</t>
+          <t>Methodology: sprint plan (p.32)</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
+          <t>Phase 4 (customer side) lists the 'one-click copy feature for delivery details' under My Orders; that's an admin Delivery feature (also listed in Phase 6). Remove it from Phase 4.</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
@@ -12018,12 +12042,12 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>Modules: Price Management (p.42)</t>
+          <t>Technical Background (p.35)</t>
         </is>
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
+          <t>Say 'Cloud Firestore' instead of 'real-time database', and Cloudinary instead of Firebase cloud storage for images.</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
@@ -12041,20 +12065,16 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H160" s="11" t="inlineStr">
-        <is>
-          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
-        </is>
-      </c>
-      <c r="I160" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="H160" s="11" t="inlineStr"/>
+      <c r="I160" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J160" s="11" t="inlineStr"/>
       <c r="K160" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -12069,12 +12089,12 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
+          <t>EmailJS listed for order confirmations and password reset links: password reset is Firebase Auth; order emails depend on REQ039.</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
@@ -12093,9 +12113,9 @@
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr"/>
-      <c r="I161" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I161" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J161" s="11" t="inlineStr"/>
@@ -12116,12 +12136,12 @@
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.97-98)</t>
+          <t>Technical Background (p.35-36)</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
+          <t>Chart.js listed for 'inventory movement data': dashboard charts are sales only (inventory uses count tiles). Reword or add an inventory chart.</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
@@ -12140,9 +12160,9 @@
         </is>
       </c>
       <c r="H162" s="11" t="inlineStr"/>
-      <c r="I162" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I162" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J162" s="11" t="inlineStr"/>
@@ -12163,12 +12183,12 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background (p.35, 37)</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
+          <t>DataTable listed; tables are custom-built. Remove or reword.</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
@@ -12187,9 +12207,9 @@
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr"/>
-      <c r="I163" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I163" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J163" s="11" t="inlineStr"/>
@@ -12210,12 +12230,12 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>Budgetary Estimate (p.99)</t>
+          <t>Technical Background: Software (p.36-38)</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+          <t>Missing tools actually used: Cloudinary (images), Choices.js (searchable dropdowns), Bootstrap Icons, Google Fonts (Roboto), Git/GitHub (version control), Node.js http-server (local serving).</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
@@ -12236,7 +12256,7 @@
       <c r="H164" s="11" t="inlineStr"/>
       <c r="I164" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>Adds</t>
         </is>
       </c>
       <c r="J164" s="11" t="inlineStr"/>
@@ -12257,12 +12277,12 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>References (p.100)</t>
+          <t>Technical Background: Software (p.38)</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+          <t>Canva is listed for mockups, but the Gantt chart says 'Creation of Figma'. Use one tool name.</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
@@ -12304,12 +12324,12 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>References (p.10 / refs)</t>
+          <t>Modules: Price Management (p.42)</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+          <t>'Allows price locking': the lock is the Branch Manager-only rule (no separate lock switch). Reword, or add a lock toggle.</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
@@ -12327,16 +12347,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H166" s="11" t="inlineStr"/>
-      <c r="I166" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="H166" s="11" t="inlineStr">
+        <is>
+          <t>DONE No paper change needed: the Branch Manager has a Lock/Unlock prices toggle per product.</t>
+        </is>
+      </c>
+      <c r="I166" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J166" s="11" t="inlineStr"/>
       <c r="K166" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -12351,12 +12375,12 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>References (p.17 / refs)</t>
+          <t>Wireframes (Figs 2.16-2.21) (p.92-95)</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+          <t>Not compared yet. Replace with real screenshots, or keep them labelled as early wireframes.</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
@@ -12398,12 +12422,12 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>Appendices (p.124)</t>
+          <t>Calendar of Activities (p.97-98)</t>
         </is>
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+          <t>Add rows for work actually done (POS, inventory, payment verification, wholesale, reports, testing) and mark 'System Deployment' per the hosting decision.</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
@@ -12445,12 +12469,12 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+          <t>Budgetary Estimate (p.99)</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>Regenerate page numbers after all edits.</t>
+          <t>Total ₱31,790.08 checks out. Missing: Cloudinary (free), OpenAI API (pay-per-use, if chat is built), thermal printer (if printing is in scope).</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
@@ -12481,18 +12505,300 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="11" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C170" s="11" t="inlineStr">
+        <is>
+          <t>Budgetary Estimate (p.99)</t>
+        </is>
+      </c>
+      <c r="D170" s="11" t="inlineStr">
+        <is>
+          <t>Domain name ₱841.08 and Firebase Blaze ₱200: keep only if actually bought/used. Netlify is listed as free, but deployment was blocked by billing; make these consistent.</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F170" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G170" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H170" s="11" t="inlineStr"/>
+      <c r="I170" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J170" s="11" t="inlineStr"/>
+      <c r="K170" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="11" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C171" s="11" t="inlineStr">
+        <is>
+          <t>References (p.100)</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>Davis reference is written 'Fred D. Davis. (1989)'; APA is 'Davis, F. D. (1989).'</t>
+        </is>
+      </c>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F171" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H171" s="11" t="inlineStr"/>
+      <c r="I171" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J171" s="11" t="inlineStr"/>
+      <c r="K171" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="11" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C172" s="11" t="inlineStr">
+        <is>
+          <t>References (p.10 / refs)</t>
+        </is>
+      </c>
+      <c r="D172" s="11" t="inlineStr">
+        <is>
+          <t>'The Generics Pharmacy (TGP) Sumulong Case Study (2024)' is cited without an author; check the APA author/organization format.</t>
+        </is>
+      </c>
+      <c r="E172" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F172" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G172" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H172" s="11" t="inlineStr"/>
+      <c r="I172" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J172" s="11" t="inlineStr"/>
+      <c r="K172" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="11" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C173" s="11" t="inlineStr">
+        <is>
+          <t>References (p.17 / refs)</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>Sardjono et al. (2023) is described as an Agile-based study, but its listed title is about Track and Trace in Pharma 4.0. Verify the source matches the summary.</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G173" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H173" s="11" t="inlineStr"/>
+      <c r="I173" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J173" s="11" t="inlineStr"/>
+      <c r="K173" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="11" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C174" s="11" t="inlineStr">
+        <is>
+          <t>Appendices (p.124)</t>
+        </is>
+      </c>
+      <c r="D174" s="11" t="inlineStr">
+        <is>
+          <t>List of Appendices says 'PayMongo Pricing' / 'Lalamove API Instruction'; the appendix pages say 'PayMongo Pricing Limitation' / 'Lalamove API Limitation'. Match titles.</t>
+        </is>
+      </c>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F174" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G174" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H174" s="11" t="inlineStr"/>
+      <c r="I174" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J174" s="11" t="inlineStr"/>
+      <c r="K174" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="inlineStr">
+        <is>
+          <t>Table of Contents / List of Figures (p.iv-vi)</t>
+        </is>
+      </c>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>Regenerate page numbers after all edits.</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>Manuscript pass</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H175" s="11" t="inlineStr"/>
+      <c r="I175" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
+        </is>
+      </c>
+      <c r="J175" s="11" t="inlineStr"/>
+      <c r="K175" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K169"/>
-  <conditionalFormatting sqref="K2:K169">
+  <autoFilter ref="A1:K175"/>
+  <conditionalFormatting sqref="K2:K175">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Client,Decision,System,System + paper,Paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -26226,7 +26532,7 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>The client also sells medical supplies and grocery items (monthly report); the paper only mentions OTC/prescription medicines. Mention them, or exclude them on purpose.</t>
+          <t>The client also sells medical supplies (grocery items are dropped, client 2026-10-22); the paper only mentions OTC/prescription medicines. Mention medical supplies.</t>
         </is>
       </c>
     </row>

--- a/docs/AMSON-Deviation-Register.xlsx
+++ b/docs/AMSON-Deviation-Register.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To-Do'!$A$1:$K$176</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Requirements'!$A$1:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Use Cases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Activity Diagrams'!$A$1:$G$46</definedName>
@@ -3972,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K175"/>
+  <dimension ref="A1:K176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7653,17 +7653,17 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Project Context (p.1)</t>
+          <t>REQNF011, REQNF005, REQ064-067</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
+          <t>Code review of 2026-10-22 work: temporary delete rule narrowed to what Clear Test Data clears; staff can no longer delete counters (SI sequence) or store settings; bell keeps re-reading stock alerts on busy days; chat order list retries after errors and on account change; Inventory re-runs expiry rules on every refresh from live data and recovers a dropped listener; one UTC cutoff for the go-live page; cheaper counts</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -7678,18 +7678,18 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Publish firestore.rules again.</t>
+        </is>
+      </c>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr"/>
       <c r="K73" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7704,12 +7704,12 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Theoretical Framework (p.24)</t>
+          <t>Project Context (p.1)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
+          <t>Says the old POS couldn't print batch numbers, expiration dates or supplier details on receipts. The new receipts don't show them either; add batch/expiry to receipts and reports, or soften the sentence.</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>DONE 06574da: system now matches (BM-only finalize).</t>
+          <t>DONE Wholesale sales invoices, the Customer File report and Return/Exchange report carry batch + expiry per line; no paper change needed.</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Output) (p.27)</t>
+          <t>Theoretical Framework (p.24)</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
+          <t>'Only authorized branch managers can ... override automated inventory counts': needs the REQ061 fix (Branch Manager-only reconciliation finalize).</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>DONE footer links to legal.html on every page.</t>
+          <t>DONE 06574da: system now matches (BM-only finalize).</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -7801,17 +7801,17 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>System + paper</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Modules: Staff roles (p.45-46)</t>
+          <t>Conceptual Framework (Output) (p.27)</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
+          <t>'Terms and Conditions remain available throughout the session': footer Privacy/Terms links are dead. Link them to the existing legal text.</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
+          <t>DONE footer links to legal.html on every page.</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>Corrects / rewords</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr"/>
@@ -7852,22 +7852,22 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>System + paper</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>REQ001 registration, Scope and Limitations</t>
+          <t>Modules: Staff roles (p.45-46)</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Phone number verification by SMS code: on hold (every SMS costs money; Amson doesn't want to spend)</t>
+          <t>Lists 'void authorization' for Branch Manager and Technical Staff: needs the void feature. 'Sales Staff: product catalog viewing only': see REQ121 decision.</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Paper: state in Limitations (number format checked, not ownership) and in Recommendations (SMS OTP).</t>
+          <t>DONE 57f4d80: void built for BM/Technical; Sales Staff POS-only.</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -7893,7 +7893,7 @@
       <c r="J77" s="11" t="inlineStr"/>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7908,17 +7908,17 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Chapter 3 evaluation (Objective 4)</t>
+          <t>REQ001 registration, Scope and Limitations</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Evaluation survey questionnaires: Branch Manager, Technical Staff, Sales Staff and User forms, mapped to TAM + ISO/IEC 25010</t>
+          <t>Phone number verification by SMS code: on hold (every SMS costs money; Amson doesn't want to spend)</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Limitation</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>DONE Claude Docs, 2026-10-22. In Claude Docs ('Survey Questionnaires (Admin and User)'); maintainability covered by the developers' testing (no IT expert form).</t>
+          <t>Paper: state in Limitations (number format checked, not ownership) and in Recommendations (SMS OTP).</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -7944,7 +7944,7 @@
       <c r="J78" s="11" t="inlineStr"/>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7959,17 +7959,17 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>REQ007 / Technical Background p.35-36</t>
+          <t>Chapter 3 evaluation (Objective 4)</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
+          <t>Evaluation survey questionnaires: Branch Manager, Technical Staff, Sales Staff and User forms, mapped to TAM + ISO/IEC 25010</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Paper edit</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>See Contradictions / Paper Edits</t>
+          <t>DONE Claude Docs, 2026-10-22. In Claude Docs ('Survey Questionnaires (Admin and User)'); maintainability covered by the developers' testing (no IT expert form).</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -7995,7 +7995,7 @@
       <c r="J79" s="11" t="inlineStr"/>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>REQ008 p.47; Modules p.38</t>
+          <t>REQ007 / Technical Background p.35-36</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
+          <t>Password reset link is sent by Firebase Authentication, not EmailJS.</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -8038,9 +8038,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I80" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr"/>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>REQ031 p.50</t>
+          <t>REQ008 p.47; Modules p.38</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
+          <t>Drop 'promotions' unless you plan them; keep 'announcements' (banner to be built).</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>REQ073 p.55</t>
+          <t>REQ031 p.50</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
+          <t>Replace status list with: Pending Verification, Payment Confirmed, Dispatched / Ready for Pick-up, Delivered, Received / Picked Up, On Hold (with type), Closed (Unresolved).</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -8140,9 +8140,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I82" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr"/>
@@ -8163,12 +8163,12 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
+          <t>REQ073 p.55</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
+          <t>Add 'and the stated reason' (client requirement, Interview 2) - after the reason field is built.</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>REQ085, REQ087 p.57; Modules p.44</t>
+          <t>REQ083 p.56; Fig 2.6 text p.73; Fig 2.14 text p.89</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Default wholesale price per product, adjustable per order (C9).</t>
+          <t>Void applies to completed transactions, referencing the original receipt number (C4).</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -8242,9 +8242,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I84" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr"/>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
+          <t>REQ085, REQ087 p.57; Modules p.44</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
+          <t>Default wholesale price per product, adjustable per order (C9).</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
+          <t>REQ095, REQ098 p.58-59; Fig 2.6 text p.74; Fig 2.11 text p.83</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
+          <t>Overpayment is approved and the excess is added to the customer's store credit; three hold types plus overpayment-approval (C2).</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
@@ -8344,9 +8344,9 @@
           <t>See Contradictions / Paper Edits</t>
         </is>
       </c>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I86" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr"/>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>REQ121 p.61</t>
+          <t>REQ105 p.60; Fig 2.4 text p.71; Modules p.39-40</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
+          <t>Delivered is set by staff (or automatically after 3 days); the customer's confirmation marks it Received (C1).</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 text p.67</t>
+          <t>REQ121 p.61</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
+          <t>Only if you keep Sales Staff access to Walk-in Orders history: add it to REQ121.</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 diagram</t>
+          <t>Fig 2.2 text p.67</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
+          <t>Audit log is available to Technical Staff and Branch Manager (C6).</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.5 text p.72</t>
+          <t>Fig 2.2 diagram</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
+          <t>Connect 'Manage Live Chat' to Technical Staff; add missing bubbles or label as summary (C11); one name for the pre-order use case (C12).</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.2 / 2.7 diagrams</t>
+          <t>Fig 2.5 text p.72</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
+          <t>Technical Staff opens/counts; Branch Manager finalizes (C5).</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.8 diagram + text p.76-77</t>
+          <t>Fig 2.2 / 2.7 diagrams</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
+          <t>Overpayment, free-of-cost distribution: no bubble anywhere; add 'Record Free-of-Cost Distribution' under Manage Wholesale Accounts if REQ091 stays.</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.9 diagram + text p.78-79</t>
+          <t>Fig 2.8 diagram + text p.76-77</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
+          <t>Add reCAPTCHA, locked-account check, deactivated-account check, unverified-email redirect; make the wrong-OTP path match the text (C13).</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.10 diagram</t>
+          <t>Fig 2.9 diagram + text p.78-79</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
+          <t>Terms accepted before submit, duplicate email caught at account creation (C14); add Resend Code; end at the shop, signed in (C10).</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fig 2.11 diagram + text p.82-83</t>
+          <t>Fig 2.10 diagram</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
+          <t>Move the RX decision to the start of checkout; RX skips the address; add Upload Prescription Photo (C15); optionally add delivery schedule and store credit.</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
@@ -8826,17 +8826,17 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Title page / cover (i)</t>
+          <t>Fig 2.11 diagram + text p.82-83</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
+          <t>Prescription approval/rejection before confirmation (C3, after it is built); RX skips courier steps (C17); resolved holds return to admin review (C18); stock shortage -&gt; Out of Stock hold (C19); overpayment approved with credit (C2); expired holds closed by the System lane, credit kept.</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Manuscript pass</t>
+          <t>Paper edit</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -8849,7 +8849,11 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="H96" s="11" t="inlineStr"/>
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>See Contradictions / Paper Edits</t>
+        </is>
+      </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
           <t>Corrects / rewords</t>
@@ -8873,12 +8877,12 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Whole paper (-)</t>
+          <t>Title page / cover (i)</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
+          <t>Still labelled 'Capstone Project Proposal' dated May 16, 2026; update the label and date for the final manuscript.</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
@@ -8888,7 +8892,7 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -8920,12 +8924,12 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Comparative Analysis (p.18)</t>
+          <t>Whole paper (-)</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
+          <t>About 100 'will ...' sentences are written as a proposal. Ask the adviser whether the final manuscript should switch to past/present tense, then convert.</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -8935,7 +8939,7 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -8967,12 +8971,12 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Conceptual Framework (Input) (p.25)</t>
+          <t>Comparative Analysis (p.18)</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
+          <t>The three compared systems are named but not cited in that section: J1TEK = Binag et al. (2024), Online Transporter = Llorente et al. (2022), Bandung FEFO = Malasari &amp; Sudrajat (2023). Binag and Llorente are in the reference list but cited nowhere in the text.</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
@@ -8991,9 +8995,9 @@
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr"/>
-      <c r="I99" s="12" t="inlineStr">
-        <is>
-          <t>REMOVES / narrows - see Removals (Letter)</t>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Corrects / rewords</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr"/>
@@ -9014,12 +9018,12 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Methodology: sprint plan (p.30-35)</t>
+          <t>Conceptual Framework (Input) (p.25)</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
+          <t>Says wholesale buyers' info is captured during account registration and that wholesale purchase orders are submitted through the platform. Wholesale buyers don't register or order online; staff record them.</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -9038,9 +9042,9 @@
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr"/>
-      <c r="I100" s="11" t="inlineStr">
-        <is>
-          <t>Corrects / rewords</t>
+      <c r="I100" s="12" t="inlineStr">
+        <is>
+          <t>REMOVES / narrows - see Removals (Letter)</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr"/>
@@ -9061,12 +9065,12 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Calendar of Activities (p.96-98)</t>
+          <t>Methodology: sprint plan (p.30-35)</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
+          <t>Phases promise features that aren't built (device OTP, notifications by email, thermal printing, live chat, reports). Align with final decisions.</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
@@ -9113,7 +9117,7 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
+          <t>Lists a 'Fifth Interview', but the appendices only have four transcripts (J-M). Add the transcript and proof, or remove the row.</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -9150,22 +9154,22 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Price list</t>
+          <t>Calendar of Activities (p.96-98)</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Two price-list items have no price: Zardip Duo 40/5 (Telmisartan + Amlodipine) and Zincbos (Zinc Sulfate syrup)</t>
+          <t>Month header has no year. Update the bars to actual dates. The webapp branch history starts 2026-08-31 (earlier work isn't in this git history), so the team needs to fill earlier dates.</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Manuscript pass</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -9175,17 +9179,13 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H103" s="11" t="inlineStr">
-        <is>
-          <t>Left out of the upload files; add by hand once priced.</t>
-        </is>
-      </c>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr"/>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Corrects / rewords</t>
         </is>
       </c>